--- a/data/pbr_matchups_full.xlsx
+++ b/data/pbr_matchups_full.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cameronyoung/Desktop/rankratings:/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{273811C1-B0E2-B147-AC87-E500BDC0A9EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F18FEEAD-D115-564B-B80F-9BE393E2C4FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17640" xr2:uid="{63502F5A-9950-074D-B0A2-89EF4471630B}"/>
+    <workbookView xWindow="9280" yWindow="5620" windowWidth="30240" windowHeight="17640" xr2:uid="{63502F5A-9950-074D-B0A2-89EF4471630B}"/>
   </bookViews>
   <sheets>
     <sheet name="Billings Day 1" sheetId="1" r:id="rId1"/>
@@ -930,7 +930,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -983,6 +983,12 @@
       <name val="Verdana"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFD6D5D4"/>
+      <name val="Helvetica Neue"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1005,7 +1011,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
@@ -1017,6 +1023,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1463,15 +1470,15 @@
       <c r="O2" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="P2">
-        <v>0</v>
-      </c>
-      <c r="Q2">
-        <v>0</v>
+      <c r="P2" s="9">
+        <v>45.5</v>
+      </c>
+      <c r="Q2" s="9">
+        <v>45.25</v>
       </c>
       <c r="R2">
         <f>P2+Q2</f>
-        <v>0</v>
+        <v>90.75</v>
       </c>
       <c r="T2" t="s">
         <v>19</v>
@@ -1521,15 +1528,15 @@
       <c r="O3" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="P3">
-        <v>0</v>
-      </c>
-      <c r="Q3">
-        <v>0</v>
+      <c r="P3" s="9">
+        <v>43.75</v>
+      </c>
+      <c r="Q3" s="9">
+        <v>44</v>
       </c>
       <c r="R3">
         <f t="shared" ref="R3:R44" si="0">P3+Q3</f>
-        <v>0</v>
+        <v>87.75</v>
       </c>
       <c r="T3" t="s">
         <v>38</v>
@@ -1578,14 +1585,14 @@
         <v>44</v>
       </c>
       <c r="P4">
-        <v>0</v>
-      </c>
-      <c r="Q4">
+        <v>43</v>
+      </c>
+      <c r="Q4" s="9">
         <v>0</v>
       </c>
       <c r="R4">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="T4" t="s">
         <v>45</v>

--- a/data/pbr_matchups_full.xlsx
+++ b/data/pbr_matchups_full.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cameronyoung/Desktop/rankratings:/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F18FEEAD-D115-564B-B80F-9BE393E2C4FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F9EE457-5C12-B141-A738-D734706215C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9280" yWindow="5620" windowWidth="30240" windowHeight="17640" xr2:uid="{63502F5A-9950-074D-B0A2-89EF4471630B}"/>
+    <workbookView xWindow="13520" yWindow="740" windowWidth="16720" windowHeight="18900" xr2:uid="{63502F5A-9950-074D-B0A2-89EF4471630B}"/>
   </bookViews>
   <sheets>
     <sheet name="Billings Day 1" sheetId="1" r:id="rId1"/>
@@ -227,9 +227,6 @@
     <t>UNKNOWN</t>
   </si>
   <si>
-    <t>&lt;h2&gt;Rider&lt;/h2&gt;&lt;p&gt;&lt;strong&gt;Career:&amp;nbsp;&lt;/strong&gt;Career: 94 for 330 - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;28.48%&lt;/em&gt;&lt;/span&gt; - Rider Rating: .183&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Season:&amp;nbsp;&lt;/strong&gt;Rank&amp;nbsp;&lt;span style="color: #ff0000;"&gt;32&lt;/span&gt; (16 for 51 - &lt;em&gt;31.4%&lt;/em&gt;)&lt;em&gt;&lt;br /&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Points:&amp;nbsp;&lt;/strong&gt;137.00 pts &lt;span style="color: #ff0000;"&gt;&lt;em&gt;(-690.5)&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Earnings:&amp;nbsp;&lt;/strong&gt;&lt;span style="color: #008000;"&gt;&lt;em&gt;$49,517.31&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Potential&lt;/strong&gt;:&amp;nbsp;83.31 to 89.31 points&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;&lt;span style="text-decoration: underline;"&gt;&lt;strong&gt;Bull&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;em&gt;&lt;span style="color: #ff0000;"&gt;*No Previous Matchups&lt;/span&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;</t>
-  </si>
-  <si>
     <t>Fade</t>
   </si>
   <si>
@@ -248,9 +245,6 @@
     <t>Right</t>
   </si>
   <si>
-    <t>&lt;h2&gt;Rider&lt;/h2&gt;&lt;p&gt;&lt;strong&gt;Career:&amp;nbsp;&lt;/strong&gt;Career: 126 for 328 - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;38.41%&lt;/em&gt;&lt;/span&gt; - Rider Rating: *.269&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Season:&amp;nbsp;&lt;/strong&gt;Rank&amp;nbsp;&lt;span style="color: #ff0000;"&gt;10&lt;/span&gt; (26 for 67 - &lt;em&gt;38.8%&lt;/em&gt;)&lt;em&gt;&lt;br /&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Points:&amp;nbsp;&lt;/strong&gt;392.00 pts &lt;span style="color: #ff0000;"&gt;&lt;em&gt;(-435.5)&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Earnings:&amp;nbsp;&lt;/strong&gt;&lt;span style="color: #008000;"&gt;&lt;em&gt;$125,660.26&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Potential&lt;/strong&gt;:&amp;nbsp;85.96 to 91.96 points&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;&lt;span style="text-decoration: underline;"&gt;&lt;strong&gt;Bull&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;em&gt;&lt;span style="color: #ff0000;"&gt;*No Previous Matchups&lt;/span&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;</t>
-  </si>
-  <si>
     <t>Pass</t>
   </si>
   <si>
@@ -266,9 +260,6 @@
     <t>0.316 (6)</t>
   </si>
   <si>
-    <t>&lt;h2&gt;Rider&lt;/h2&gt;&lt;p&gt;&lt;strong&gt;Career:&amp;nbsp;&lt;/strong&gt;Career: 110 for 273 - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;40.29%&lt;/em&gt;&lt;/span&gt; - Rider Rating: *.295&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Season:&amp;nbsp;&lt;/strong&gt;Rank&amp;nbsp;&lt;span style="color: #ff0000;"&gt;16&lt;/span&gt; (21 for 56 - &lt;em&gt;37.5%&lt;/em&gt;)&lt;em&gt;&lt;br /&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Points:&amp;nbsp;&lt;/strong&gt;336.00 pts &lt;span style="color: #ff0000;"&gt;&lt;em&gt;(-491.5)&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Earnings:&amp;nbsp;&lt;/strong&gt;&lt;span style="color: #008000;"&gt;&lt;em&gt;$96,890.29&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Potential&lt;/strong&gt;:&amp;nbsp;83.9 to 89.9 points&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;&lt;span style="text-decoration: underline;"&gt;&lt;strong&gt;Bull&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;em&gt;&lt;span style="color: #ff0000;"&gt;*No Previous Matchups&lt;/span&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;</t>
-  </si>
-  <si>
     <t>--</t>
   </si>
   <si>
@@ -284,9 +275,6 @@
     <t>0.234 (5)</t>
   </si>
   <si>
-    <t>&lt;h2&gt;Rider&lt;/h2&gt;&lt;p&gt;&lt;strong&gt;Career:&amp;nbsp;&lt;/strong&gt;Career: 154 for 515 - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;29.9%&lt;/em&gt;&lt;/span&gt; - Rider Rating: *.250&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Season:&amp;nbsp;&lt;/strong&gt;Rank&amp;nbsp;&lt;span style="color: #ff0000;"&gt;38&lt;/span&gt; (21 for 70 - &lt;em&gt;30%&lt;/em&gt;)&lt;em&gt;&lt;br /&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Points:&amp;nbsp;&lt;/strong&gt;86.00 pts &lt;span style="color: #ff0000;"&gt;&lt;em&gt;(-741.5)&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Earnings:&amp;nbsp;&lt;/strong&gt;&lt;span style="color: #008000;"&gt;&lt;em&gt;$85,787.98&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Potential&lt;/strong&gt;:&amp;nbsp;-1 to 5 points&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;&lt;span style="text-decoration: underline;"&gt;&lt;strong&gt;Bull&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;em&gt;&lt;span style="color: #ff0000;"&gt;*No Previous Matchups&lt;/span&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;</t>
-  </si>
-  <si>
     <t>27-6 (2)</t>
   </si>
   <si>
@@ -305,9 +293,6 @@
     <t>Rider 3.00%</t>
   </si>
   <si>
-    <t>&lt;h2&gt;Rider&lt;/h2&gt;&lt;p&gt;&lt;strong&gt;Career:&amp;nbsp;&lt;/strong&gt;Career: 180 for 459 - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;39.22%&lt;/em&gt;&lt;/span&gt; - Rider Rating: *.278&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Season:&amp;nbsp;&lt;/strong&gt;Rank&amp;nbsp;&lt;span style="color: #ff0000;"&gt;17&lt;/span&gt; (31 for 59 - &lt;em&gt;52.5%&lt;/em&gt;)&lt;em&gt;&lt;br /&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Points:&amp;nbsp;&lt;/strong&gt;303.00 pts &lt;span style="color: #ff0000;"&gt;&lt;em&gt;(-524.5)&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Earnings:&amp;nbsp;&lt;/strong&gt;&lt;span style="color: #008000;"&gt;&lt;em&gt;$98,926.07&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Potential&lt;/strong&gt;:&amp;nbsp;81.92 to 87.92 points&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;&lt;span style="text-decoration: underline;"&gt;&lt;strong&gt;Bull&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;ALL:&lt;/strong&gt; 33 outs 6 rides - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;81.82%&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;UTB:&lt;/strong&gt; 11 outs 4 rides - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;63.64%&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;em&gt;&lt;span style="color: #ff0000;"&gt;*No Previous Matchups&lt;/span&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;</t>
-  </si>
-  <si>
     <t>7-0 (0)</t>
   </si>
   <si>
@@ -320,9 +305,6 @@
     <t>0.323 (7)</t>
   </si>
   <si>
-    <t>&lt;h2&gt;Rider&lt;/h2&gt;&lt;p&gt;&lt;strong&gt;Career:&amp;nbsp;&lt;/strong&gt;Career: 363 for 942 - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;38.54%&lt;/em&gt;&lt;/span&gt; - Rider Rating: *.294&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Season:&amp;nbsp;&lt;/strong&gt;Rank&amp;nbsp;&lt;span style="color: #ff0000;"&gt;9&lt;/span&gt; (34 for 69 - &lt;em&gt;49.3%&lt;/em&gt;)&lt;em&gt;&lt;br /&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Points:&amp;nbsp;&lt;/strong&gt;405.00 pts &lt;span style="color: #ff0000;"&gt;&lt;em&gt;(-422.5)&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Earnings:&amp;nbsp;&lt;/strong&gt;&lt;span style="color: #008000;"&gt;&lt;em&gt;$159,605.64&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Potential&lt;/strong&gt;:&amp;nbsp;82.8 to 88.8 points&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;&lt;span style="text-decoration: underline;"&gt;&lt;strong&gt;Bull&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;ALL:&lt;/strong&gt; 7 outs 0 rides - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;100%&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;em&gt;&lt;span style="color: #ff0000;"&gt;*No Previous Matchups&lt;/span&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;</t>
-  </si>
-  <si>
     <t>8-4 (1)</t>
   </si>
   <si>
@@ -359,9 +341,6 @@
     <t>Rider 40.00%</t>
   </si>
   <si>
-    <t>&lt;h2&gt;Rider&lt;/h2&gt;&lt;p&gt;&lt;strong&gt;Career:&amp;nbsp;&lt;/strong&gt;Career: 60 for 163 - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;36.81%&lt;/em&gt;&lt;/span&gt; - Rider Rating: *.221&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Season:&amp;nbsp;&lt;/strong&gt;Rank&amp;nbsp;&lt;span style="color: #ff0000;"&gt;3&lt;/span&gt; (24 for 38 - &lt;em&gt;63.2%&lt;/em&gt;)&lt;em&gt;&lt;br /&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Points:&amp;nbsp;&lt;/strong&gt;595.50 pts &lt;span style="color: #ff0000;"&gt;&lt;em&gt;(-232)&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Earnings:&amp;nbsp;&lt;/strong&gt;&lt;span style="color: #008000;"&gt;&lt;em&gt;$140,650.12&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Potential&lt;/strong&gt;:&amp;nbsp;83.9 to 89.9 points&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;&lt;span style="text-decoration: underline;"&gt;&lt;strong&gt;Bull&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;ALL:&lt;/strong&gt; 12 outs 2 rides - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;83.33%&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;UTB:&lt;/strong&gt; 10 outs 2 rides - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;80%&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;em&gt;&lt;span style="color: #ff0000;"&gt;*No Previous Matchups&lt;/span&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;</t>
-  </si>
-  <si>
     <t>2-2 (2)</t>
   </si>
   <si>
@@ -924,13 +903,662 @@
   </si>
   <si>
     <t>&lt;h2&gt;Rider&lt;/h2&gt;&lt;p&gt;&lt;strong&gt;Career:&amp;nbsp;&lt;/strong&gt;Career: 258 for 576 - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;44.79%&lt;/em&gt;&lt;/span&gt; - Rider Rating: *.372&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Season:&amp;nbsp;&lt;/strong&gt;Rank&amp;nbsp;&lt;span style="color: #ff0000;"&gt;6&lt;/span&gt; (36 for 66 - &lt;em&gt;54.5%&lt;/em&gt;)&lt;em&gt;&lt;br /&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Points:&amp;nbsp;&lt;/strong&gt;488.50 pts &lt;span style="color: #ff0000;"&gt;&lt;em&gt;(-339)&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Earnings:&amp;nbsp;&lt;/strong&gt;&lt;span style="color: #008000;"&gt;&lt;em&gt;$252,397.78&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Potential&lt;/strong&gt;:&amp;nbsp;83.74 to 89.74 points&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;&lt;span style="text-decoration: underline;"&gt;&lt;strong&gt;Bull&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;ALL:&lt;/strong&gt; 16 outs 7 rides - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;56.25%&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;UTB:&lt;/strong&gt; 13 outs 7 rides - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;46.15%&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;em&gt;&lt;span style="color: #ff0000;"&gt;*No Previous Matchups&lt;/span&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t>&lt;h2&gt;Rider&lt;/h2&gt;&lt;p&gt;&lt;strong&gt;Career:&amp;nbsp;&lt;/strong&gt;Career: 94 for 330 - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;28.48%&lt;/em&gt;&lt;/span&gt; - Rider Rating: .183&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Season:&amp;nbsp;&lt;/strong&gt;Rank&amp;nbsp;&lt;span style="color: #ff0000;"&gt;32&lt;/span&gt; (16 for 51 - &lt;em&gt;31.4%&lt;/em&gt;)&lt;em&gt;&lt;br /&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Points:&amp;nbsp;&lt;/strong&gt;137.00 pts &lt;span style="color: #ff0000;"&gt;&lt;em&gt;(-690.5)&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Earnings:&amp;nbsp;&lt;/strong&gt;&lt;span style="color: #008000;"&gt;&lt;em&gt;$49,517.31&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Potential&lt;/strong&gt;:&amp;nbsp;83.31 to 89.31 points&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;&lt;span style="text-decoration: underline;"&gt;&lt;strong&gt;Bull&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;em&gt;&lt;span style="color: #ff0000;"&gt;*No Previous Matchups&lt;/span&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;hr /&gt;
+&lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
+  Kase Hitt is a left-handed, up-and-coming PBR bull rider from Dickson, Oklahoma, known for being tall and athletic with a gritty, keep-coming-back mindset. 
+&lt;/p&gt;
+&lt;h2 id="basic-profile" class="font-editorial font-bold mb-2 mt-4 [.has-inline-images_&amp;amp;]:clear-end text-lg first:mt-0 md:text-lg [hr+&amp;amp;]:mt-4"&gt;
+  Basic profile
+&lt;/h2&gt;
+&lt;ul class="marker:text-quiet list-disc pl-8"&gt;
+  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
+    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
+      &lt;strong&gt;Name:&lt;/strong&gt;&amp;nbsp;Kase Hitt
+    &lt;/p&gt;
+  &lt;/li&gt;
+  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
+    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
+      &lt;strong&gt;Hometown:&lt;/strong&gt;&amp;nbsp;Dickson, Oklahoma, USA
+    &lt;/p&gt;
+  &lt;/li&gt;
+  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
+    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
+      &lt;strong&gt;Team:&lt;/strong&gt;&amp;nbsp;Oklahoma Wildcatters (PBR Teams)
+    &lt;/p&gt;
+  &lt;/li&gt;
+  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
+    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
+      &lt;strong&gt;Hand:&lt;/strong&gt;&amp;nbsp;Left
+    &lt;/p&gt;
+  &lt;/li&gt;
+  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
+    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
+      &lt;strong&gt;Age / Size:&lt;/strong&gt;&amp;nbsp;21 years old, 6'2", ~150 lbs
+    &lt;/p&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;
+&lt;h2 id="career-accomplishments" class="font-editorial font-bold mb-2 mt-4 [.has-inline-images_&amp;amp;]:clear-end text-lg first:mt-0 md:text-lg [hr+&amp;amp;]:mt-4"&gt;
+  Career accomplishments
+&lt;/h2&gt;
+&lt;ul class="marker:text-quiet list-disc pl-8"&gt;
+  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
+    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
+      Earned his first Pendleton Whisky Velocity Tour victory at PBR Bangor in early 2026 with a three-ride comeback after bucking off his opening bull. 
+    &lt;/p&gt;
+  &lt;/li&gt;
+  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
+    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
+      Logged a career-best UTB score with an 88.4‑point ride on Eyes On Me in the Championship Round at the 2026 PBR Pittsburgh Unleash The Beast event. 
+    &lt;/p&gt;
+  &lt;/li&gt;
+  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
+    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
+      Won the PBR Stockyards Showcase in Fort Worth in 2024 with a walk‑off ride on Free Ride at Cowtown Coliseum, one of his early statement wins in the Challenger ranks. 
+    &lt;/p&gt;
+  &lt;/li&gt;
+  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
+    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
+      Key closer for the Oklahoma Wildcatters in Teams competition, including clutch rides such as sealing wins at Thunder Days and other late‑game situations. 
+    &lt;/p&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;
+&lt;h2 id="style-background-and-persona" class="font-editorial font-bold mb-2 mt-4 [.has-inline-images_&amp;amp;]:clear-end text-lg first:mt-0 md:text-lg [hr+&amp;amp;]:mt-4"&gt;
+  Style, background, and persona
+&lt;/h2&gt;
+&lt;ul class="marker:text-quiet list-disc pl-8"&gt;
+  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
+    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
+      Tall, long‑levered left‑hander who uses his length and balance to stay over the front and finish strong, especially in rank short‑round matchups. 
+    &lt;/p&gt;
+  &lt;/li&gt;
+  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
+    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
+      Built his name through smaller PBR and open bull ridings before breaking through on the Velocity Tour and earning UTB opportunities. 
+    &lt;/p&gt;
+  &lt;/li&gt;
+  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
+    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
+      Recognized for mental toughness and the ability to bounce back after buckoffs, as seen in Bangor where he turned an early miss into a three‑ride surge for the win. 
+    &lt;/p&gt;
+  &lt;/li&gt;
+  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
+    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
+      Rides with a straightforward, blue‑collar attitude that fits Oklahoma’s rodeo culture and the Wildcatters’ identity. 
+    &lt;/p&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;
+&lt;h2 id="personality-notes" class="font-editorial font-bold mb-2 mt-4 [.has-inline-images_&amp;amp;]:clear-end text-lg first:mt-0 md:text-lg [hr+&amp;amp;]:mt-4"&gt;
+  Personality notes
+&lt;/h2&gt;
+&lt;ul class="marker:text-quiet list-disc pl-8"&gt;
+  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
+    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
+      Comes off as humble and soft‑spoken in interviews, but highly competitive in the chute, leaning on confidence in his feel and fundamentals more than flash. 
+    &lt;/p&gt;
+  &lt;/li&gt;
+  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
+    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
+      Has already ridden through bumps and soreness at big events, building a reputation as a guy who keeps nodding his head even when he’s banged up. 
+    &lt;/p&gt;
+  &lt;/li&gt;
+  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
+    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
+      Off the dirt, leans into the modern PBR lifestyle—social media, music, and team‑branding—while still coming across as a small‑town Oklahoma cowboy at heart. 
+    &lt;/p&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;</t>
+  </si>
+  <si>
+    <t>&lt;h2&gt;Rider&lt;/h2&gt;&lt;p&gt;&lt;strong&gt;Career:&amp;nbsp;&lt;/strong&gt;Career: 126 for 328 - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;38.41%&lt;/em&gt;&lt;/span&gt; - Rider Rating: *.269&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Season:&amp;nbsp;&lt;/strong&gt;Rank&amp;nbsp;&lt;span style="color: #ff0000;"&gt;10&lt;/span&gt; (26 for 67 - &lt;em&gt;38.8%&lt;/em&gt;)&lt;em&gt;&lt;br /&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Points:&amp;nbsp;&lt;/strong&gt;392.00 pts &lt;span style="color: #ff0000;"&gt;&lt;em&gt;(-435.5)&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Earnings:&amp;nbsp;&lt;/strong&gt;&lt;span style="color: #008000;"&gt;&lt;em&gt;$125,660.26&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Potential&lt;/strong&gt;:&amp;nbsp;85.96 to 91.96 points&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;&lt;span style="text-decoration: underline;"&gt;&lt;strong&gt;Bull&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;em&gt;&lt;span style="color: #ff0000;"&gt;*No Previous Matchups&lt;/span&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;hr /&gt;
+&lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
+  Julio Cesar Marques is a right-handed Brazilian bull rider from Tatuí, São Paulo, a new‑generation star who quickly climbed into the very top tier of the PBR standings. 
+&lt;/p&gt;
+&lt;h2 id="basic-profile" class="font-editorial font-bold mb-2 mt-4 [.has-inline-images_&amp;amp;]:clear-end text-lg first:mt-0 md:text-lg [hr+&amp;amp;]:mt-4"&gt;
+  Basic profile
+&lt;/h2&gt;
+&lt;ul class="marker:text-quiet list-disc pl-8"&gt;
+  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
+    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
+      &lt;strong&gt;Name:&lt;/strong&gt;&amp;nbsp;Julio Cesar Marques
+    &lt;/p&gt;
+  &lt;/li&gt;
+  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
+    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
+      &lt;strong&gt;Hometown:&lt;/strong&gt;&amp;nbsp;Tatuí, São Paulo, Brazil
+    &lt;/p&gt;
+  &lt;/li&gt;
+  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
+    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
+      &lt;strong&gt;Team:&lt;/strong&gt;&amp;nbsp;Kansas City Outlaws (PBR Teams)
+    &lt;/p&gt;
+  &lt;/li&gt;
+  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
+    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
+      &lt;strong&gt;Hand:&lt;/strong&gt;&amp;nbsp;Right
+    &lt;/p&gt;
+  &lt;/li&gt;
+  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
+    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
+      &lt;strong&gt;Age / Size:&lt;/strong&gt;&amp;nbsp;22 years old, 5'6", ~145 lbs
+    &lt;/p&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;
+&lt;h2 id="career-accomplishments" class="font-editorial font-bold mb-2 mt-4 [.has-inline-images_&amp;amp;]:clear-end text-lg first:mt-0 md:text-lg [hr+&amp;amp;]:mt-4"&gt;
+  Career accomplishments
+&lt;/h2&gt;
+&lt;ul class="marker:text-quiet list-disc pl-8"&gt;
+  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
+    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
+      Broke through with his first Unleash The Beast event win at PBR Albany in late 2024, going a perfect 3‑for‑3 to claim the title and surge up the world standings. 
+    &lt;/p&gt;
+  &lt;/li&gt;
+  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
+    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
+      Crowned “King of Deadwood” after dominating the historic Deadwood, South Dakota stop, stacking key rides in one of the tour’s most unique outdoor venues. 
+    &lt;/p&gt;
+  &lt;/li&gt;
+  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
+    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
+      Logged multiple high‑mark UTB rides, including big scores on bulls like Lights Out, Tacky Jack, and Bayou Boy that helped push him into the No. 1 ranking battle. 
+    &lt;/p&gt;
+  &lt;/li&gt;
+  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
+    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
+      Quickly became a consistent UTB contender, pushing into the top 5 and even No. 1 in the world race early in his career with strong finishes at major stops. 
+    &lt;/p&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;
+&lt;h2 id="style-background-and-persona" class="font-editorial font-bold mb-2 mt-4 [.has-inline-images_&amp;amp;]:clear-end text-lg first:mt-0 md:text-lg [hr+&amp;amp;]:mt-4"&gt;
+  Style, background, and persona
+&lt;/h2&gt;
+&lt;ul class="marker:text-quiet list-disc pl-8"&gt;
+  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
+    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
+      Classic young Brazilian technician with strong core position and timing, able to stay centered even when bulls are changing direction or speed. 
+    &lt;/p&gt;
+  &lt;/li&gt;
+  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
+    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
+      Built his résumé through Brazil and U.S. Challenger/Velocity events before quickly adapting to UTB bulls and arenas, with almost no drop‑off under brighter lights. 
+    &lt;/p&gt;
+  &lt;/li&gt;
+  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
+    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
+      Rides with a calm, composed look in the chute, then flips into an explosive, forward‑driving style once the gate opens. 
+    &lt;/p&gt;
+  &lt;/li&gt;
+  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
+    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
+      Already viewed as one of the leaders of the new Brazilian wave, regularly mentioned as a future world‑title threat. 
+    &lt;/p&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;
+&lt;h2 id="personality-notes" class="font-editorial font-bold mb-2 mt-4 [.has-inline-images_&amp;amp;]:clear-end text-lg first:mt-0 md:text-lg [hr+&amp;amp;]:mt-4"&gt;
+  Personality notes
+&lt;/h2&gt;
+&lt;ul class="marker:text-quiet list-disc pl-8"&gt;
+  &lt;li class="py-0 my-0 p</t>
+  </si>
+  <si>
+    <t>&lt;h2&gt;Rider&lt;/h2&gt;&lt;p&gt;&lt;strong&gt;Career:&amp;nbsp;&lt;/strong&gt;Career: 110 for 273 - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;40.29%&lt;/em&gt;&lt;/span&gt; - Rider Rating: *.295&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Season:&amp;nbsp;&lt;/strong&gt;Rank&amp;nbsp;&lt;span style="color: #ff0000;"&gt;16&lt;/span&gt; (21 for 56 - &lt;em&gt;37.5%&lt;/em&gt;)&lt;em&gt;&lt;br /&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Points:&amp;nbsp;&lt;/strong&gt;336.00 pts &lt;span style="color: #ff0000;"&gt;&lt;em&gt;(-491.5)&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Earnings:&amp;nbsp;&lt;/strong&gt;&lt;span style="color: #008000;"&gt;&lt;em&gt;$96,890.29&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Potential&lt;/strong&gt;:&amp;nbsp;83.9 to 89.9 points&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;&lt;span style="text-decoration: underline;"&gt;&lt;strong&gt;Bull&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;em&gt;&lt;span style="color: #ff0000;"&gt;*No Previous Matchups&lt;/span&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;hr /&gt;
+&lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
+  Kaiden “K‑Loud” Loud is a right-handed bull rider from Kaufman, Texas, a young UTB and Teams star known for big 90‑point moments and a loud, high‑energy presence in the arena. 
+&lt;/p&gt;
+&lt;h2 id="basic-profile" class="font-editorial font-bold mb-2 mt-4 [.has-inline-images_&amp;amp;]:clear-end text-lg first:mt-0 md:text-lg [hr+&amp;amp;]:mt-4"&gt;
+  Basic profile
+&lt;/h2&gt;
+&lt;ul class="marker:text-quiet list-disc pl-8"&gt;
+  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
+    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
+      &lt;strong&gt;Name:&lt;/strong&gt;&amp;nbsp;Kaiden Loud
+    &lt;/p&gt;
+  &lt;/li&gt;
+  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
+    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
+      &lt;strong&gt;Hometown:&lt;/strong&gt;&amp;nbsp;Kaufman, Texas, USA
+    &lt;/p&gt;
+  &lt;/li&gt;
+  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
+    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
+      &lt;strong&gt;Team:&lt;/strong&gt;&amp;nbsp;Nashville Stampede (PBR Teams)
+    &lt;/p&gt;
+  &lt;/li&gt;
+  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
+    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
+      &lt;strong&gt;Hand:&lt;/strong&gt;&amp;nbsp;Right
+    &lt;/p&gt;
+  &lt;/li&gt;
+  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
+    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
+      &lt;strong&gt;Age / Size:&lt;/strong&gt;&amp;nbsp;20 years old, athletic frame
+    &lt;/p&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;
+&lt;h2 id="career-accomplishments" class="font-editorial font-bold mb-2 mt-4 [.has-inline-images_&amp;amp;]:clear-end text-lg first:mt-0 md:text-lg [hr+&amp;amp;]:mt-4"&gt;
+  Career accomplishments
+&lt;/h2&gt;
+&lt;ul class="marker:text-quiet list-disc pl-8"&gt;
+  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
+    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
+      Dominated the high school ranks, including a Texas state title and youth bull riding championships, before jumping straight into the professional scene as a teenager. 
+    &lt;/p&gt;
+  &lt;/li&gt;
+  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
+    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
+      Grabbed early national attention by winning the 2023 Tuff Hedeman Bull Riding in New Mexico at just 18 years old. 
+    &lt;/p&gt;
+  &lt;/li&gt;
+  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
+    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
+      Selected by the Nashville Stampede in the second round of the 2023 PBR Teams Draft and quickly delivered clutch rides, including 90‑plus on bulls like Mike’s Motive and Ridin’ Salty. 
+    &lt;/p&gt;
+  &lt;/li&gt;
+  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
+    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
+      Broke out individually at the 2024 PBR World Finals Eliminations in Fort Worth, winning the stage by going 3‑for‑4 and posting a 91.75‑point career‑best ride on Doze You Down. 
+    &lt;/p&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;
+&lt;h2 id="style-background-and-persona" class="font-editorial font-bold mb-2 mt-4 [.has-inline-images_&amp;amp;]:clear-end text-lg first:mt-0 md:text-lg [hr+&amp;amp;]:mt-4"&gt;
+  Style, background, and persona
+&lt;/h2&gt;
+&lt;ul class="marker:text-quiet list-disc pl-8"&gt;
+  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
+    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
+      High‑energy, forward‑driving rider who uses quick reactions and strong hips to stay in the middle when bulls are firing hard and moving ahead. 
+    &lt;/p&gt;
+  &lt;/li&gt;
+  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
+    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
+      Comfortable under pressure in short‑round and World Finals‑type situations, with multiple rides over 88–90 points on big‑name bulls across UTB and Teams events. 
+    &lt;/p&gt;
+  &lt;/li&gt;
+  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
+    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
+      Brings a showman streak—feeding off the crowd, celebrating big rides—and fits perfectly with Nashville’s “Broadway” personality on the Teams side. 
+    &lt;/p&gt;
+  &lt;/li&gt;
+  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
+    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
+      Grew up in Texas rodeo culture and still trains and travels with other young guns like John Crimber, keeping a constant competitive environment around him. 
+    &lt;/p&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;
+&lt;h2 id="personality-notes" class="font-editorial font-bold mb-2 mt-4 [.has-inline-images_&amp;amp;]:clear-end text-lg first:mt-0 md:text-lg [hr+&amp;amp;]:mt-4"&gt;
+  Personality notes
+&lt;/h2&gt;
+&lt;ul class="marker:text-quiet list-disc pl-8"&gt;
+  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
+    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
+      Outgoing and media‑friendly, often featured in PBR content as “K‑Loud,” he leans into the spotlight without losing his workmanlike approach behind the scenes. 
+    &lt;/p&gt;
+  &lt;/li&gt;
+  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
+    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
+      Close friends with fellow young star John Crimber; the two often practice together and push each other in and out of the arena. 
+    &lt;/p&gt;
+  &lt;/li&gt;
+  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
+    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
+      Away from bull riding he stays active—shooting hoops, hanging around the barn, and keeping the same energetic, fun personality that shows up on TV. 
+    &lt;/p&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;</t>
+  </si>
+  <si>
+    <t>&lt;h2&gt;Rider&lt;/h2&gt;&lt;p&gt;&lt;strong&gt;Career:&amp;nbsp;&lt;/strong&gt;Career: 154 for 515 - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;29.9%&lt;/em&gt;&lt;/span&gt; - Rider Rating: *.250&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Season:&amp;nbsp;&lt;/strong&gt;Rank&amp;nbsp;&lt;span style="color: #ff0000;"&gt;38&lt;/span&gt; (21 for 70 - &lt;em&gt;30%&lt;/em&gt;)&lt;em&gt;&lt;br /&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Points:&amp;nbsp;&lt;/strong&gt;86.00 pts &lt;span style="color: #ff0000;"&gt;&lt;em&gt;(-741.5)&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Earnings:&amp;nbsp;&lt;/strong&gt;&lt;span style="color: #008000;"&gt;&lt;em&gt;$85,787.98&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Potential&lt;/strong&gt;:&amp;nbsp;-1 to 5 points&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;&lt;span style="text-decoration: underline;"&gt;&lt;strong&gt;Bull&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;em&gt;&lt;span style="color: #ff0000;"&gt;*No Previous Matchups&lt;/span&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;hr /&gt;
+&lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
+  Mauricio Gulla Moreira is a right-handed Brazilian bull rider from Gaviao Peixoto, São Paulo, a proven UTB and Teams veteran with a big-moment, high‑ceiling style. 
+&lt;/p&gt;
+&lt;h2 id="basic-profile" class="font-editorial font-bold mb-2 mt-4 [.has-inline-images_&amp;amp;]:clear-end text-lg first:mt-0 md:text-lg [hr+&amp;amp;]:mt-4"&gt;
+  Basic profile
+&lt;/h2&gt;
+&lt;ul class="marker:text-quiet list-disc pl-8"&gt;
+  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
+    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
+      &lt;strong&gt;Name:&lt;/strong&gt;&amp;nbsp;Mauricio Gulla Moreira
+    &lt;/p&gt;
+  &lt;/li&gt;
+  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
+    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
+      &lt;strong&gt;Hometown:&lt;/strong&gt;&amp;nbsp;Gaviao Peixoto, São Paulo, Brazil
+    &lt;/p&gt;
+  &lt;/li&gt;
+  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
+    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
+      &lt;strong&gt;Team:&lt;/strong&gt;&amp;nbsp;New York Mavericks (PBR Teams)
+    &lt;/p&gt;
+  &lt;/li&gt;
+  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
+    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
+      &lt;strong&gt;Hand:&lt;/strong&gt;&amp;nbsp;Right
+    &lt;/p&gt;
+  &lt;/li&gt;
+  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
+    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
+      &lt;strong&gt;Age / Size:&lt;/strong&gt;&amp;nbsp;Mid‑20s, compact and powerful build
+    &lt;/p&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;
+&lt;h2 id="career-accomplishments" class="font-editorial font-bold mb-2 mt-4 [.has-inline-images_&amp;amp;]:clear-end text-lg first:mt-0 md:text-lg [hr+&amp;amp;]:mt-4"&gt;
+  Career accomplishments
+&lt;/h2&gt;
+&lt;ul class="marker:text-quiet list-disc pl-8"&gt;
+  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
+    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
+      4‑time PBR World Finals qualifier and 3‑time Teams World Finals qualifier, established as a top‑tier rider on both the premier series and the team side. 
+    &lt;/p&gt;
+  &lt;/li&gt;
+  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
+    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
+      Multiple major wins and titles across PBR Brazil, Challenger, and Velocity‑type events, including an event championship at the historic PBR Stockyards Showcase in Fort Worth. 
+    &lt;/p&gt;
+  &lt;/li&gt;
+  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
+    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
+      Produced big‑time UTB rides such as 88.75 on Tijuana Two Step at Madison Square Garden, 87.75 on Hell Right in Albany, and a 90‑point monster on Doze You Down during PBR Teams Outlaw Days. 
+    &lt;/p&gt;
+  &lt;/li&gt;
+  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
+    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
+      Career headline stats: nearly 30% ride rate over more than 500 outs, a stack of mid‑to‑upper‑80s scores on rank bulls, and multiple 88‑90‑point rides that anchor both his individual and Teams résumé. 
+    &lt;/p&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;
+&lt;h2 id="style-background-and-persona" class="font-editorial font-bold mb-2 mt-4 [.has-inline-images_&amp;amp;]:clear-end text-lg first:mt-0 md:text-lg [hr+&amp;amp;]:mt-4"&gt;
+  Style, background, and persona
+&lt;/h2&gt;
+&lt;ul class="marker:text-quiet list-disc pl-8"&gt;
+  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
+    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
+      Classic Brazilian technician with strong posture, loose upper body and a lot of feel, letting bulls move around under him while he keeps his hips down and chest front. 
+    &lt;/p&gt;
+  &lt;/li&gt;
+  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
+    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
+      Comfortable in both big indoor arenas and smaller, rowdier outdoor setups; he has winning rides from New York City to Deadwood and Brazilian events back home. 
+    &lt;/p&gt;
+  &lt;/li&gt;
+  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
+    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
+      Known for being tough and durable across long seasons, riding through soreness and staying in the mix of the world‑title conversation for multiple years. 
+    &lt;/p&gt;
+  &lt;/li&gt;
+  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
+    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
+      Plays a veteran leader role on the New York Mavericks, often matched up with rank bulls in crucial Teams games. 
+    &lt;/p&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;
+&lt;h2 id="personality-notes" class="font-editorial font-bold mb-2 mt-4 [.has-inline-images_&amp;amp;]:clear-end text-lg first:mt-0 md:text-lg [hr+&amp;amp;]:mt-4"&gt;
+  Personality notes
+&lt;/h2&gt;
+&lt;ul class="marker:text-quiet list-disc pl-8"&gt;
+  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
+    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
+      Comes across as calm and humble, quick to credit his faith and family, and lets his riding do most of the talking in big moments. 
+    &lt;/p&gt;
+  &lt;/li&gt;
+  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
+    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
+      Has a strong fan following in both Brazil and the U.S., helped by his fun social‑media presence and highlight‑reel rides that regularly make PBR clips. 
+    &lt;/p&gt;
+  &lt;/li&gt;
+  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
+    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
+      Off the dirt he leans into music, family, and a laid‑back Brazilian cowboy lifestyle, but inside the arena he rides like a guy who expects to win every matchup. 
+    &lt;/p&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;</t>
+  </si>
+  <si>
+    <t>&lt;h2&gt;Rider&lt;/h2&gt;&lt;p&gt;&lt;strong&gt;Career:&amp;nbsp;&lt;/strong&gt;Career: 180&lt;h2&gt;Rider&lt;/h2&gt;&lt;p&gt;&lt;strong&gt;Career:&amp;nbsp;&lt;/strong&gt;Career: 180 for 459 - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;39.22%&lt;/em&gt;&lt;/span&gt; - Rider Rating: *.278&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Season:&amp;nbsp;&lt;/strong&gt;Rank&amp;nbsp;&lt;span style="color: #ff0000;"&gt;17&lt;/span&gt; (31 for 59 - &lt;em&gt;52.5%&lt;/em&gt;)&lt;em&gt;&lt;br /&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Points:&amp;nbsp;&lt;/strong&gt;303.00 pts &lt;span style="color: #ff0000;"&gt;&lt;em&gt;(-524.5)&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Earnings:&amp;nbsp;&lt;/strong&gt;&lt;span style="color: #008000;"&gt;&lt;em&gt;$98,926.07&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Potential&lt;/strong&gt;:&amp;nbsp;81.92 to 87.92 points&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;&lt;span style="text-decoration: underline;"&gt;&lt;strong&gt;Bull&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;ALL:&lt;/strong&gt; 33 outs 6 rides - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;81.82%&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;UTB:&lt;/strong&gt; 11 outs 4 rides - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;63.64%&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;em&gt;&lt;span style="color: #ff0000;"&gt;*No Previous Matchups&lt;/span&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;hr /&gt;
+&lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
+  Bob Mitchell is a right-handed bull rider from Steelville, Missouri, a gritty, blue‑collar competitor who has turned himself into a steady threat on Velocity, UTB, and Teams. 
+&lt;/p&gt;
+&lt;h2 id="basic-profile" class="font-editorial font-bold mb-2 mt-4 [.has-inline-images_&amp;amp;]:clear-end text-lg first:mt-0 md:text-lg [hr+&amp;amp;]:mt-4"&gt;
+  Basic profile
+&lt;/h2&gt;
+&lt;ul class="marker:text-quiet list-disc pl-8"&gt;
+  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
+    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
+      &lt;strong&gt;Name:&lt;/strong&gt;&amp;nbsp;Bob Mitchell
+    &lt;/p&gt;
+  &lt;/li&gt;
+  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
+    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
+      &lt;strong&gt;Hometown:&lt;/strong&gt;&amp;nbsp;Steelville, Missouri, USA
+    &lt;/p&gt;
+  &lt;/li&gt;
+  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
+    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
+      &lt;strong&gt;Team:&lt;/strong&gt;&amp;nbsp;New York Mavericks (PBR Teams)
+    &lt;/p&gt;
+  &lt;/li&gt;
+  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
+    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
+      &lt;strong&gt;Hand:&lt;/strong&gt;&amp;nbsp;Right
+    &lt;/p&gt;
+  &lt;/li&gt;
+  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
+    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
+      &lt;strong&gt;Age / Size:&lt;/strong&gt;&amp;nbsp;Early 20s, 5'10", 160–170 lbs
+    &lt;/p&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;
+&lt;h2 id="career-accomplishments" class="font-editorial font-bold mb-2 mt-4 [.has-inline-images_&amp;amp;]:clear-end text-lg first:mt-0 md:text-lg [hr+&amp;amp;]:mt-4"&gt;
+  Career accomplishments
+&lt;/h2&gt;
+&lt;ul class="marker:text-quiet list-disc pl-8"&gt;
+  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
+    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
+      Broke out as a teenager by cracking the premier series and climbing into the Top 20 in the world at just 19 years old. 
+    &lt;/p&gt;
+  &lt;/li&gt;
+  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
+    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
+      Logged key wins and rounds on the Pendleton Whisky Velocity Tour, including a Round 1 victory at PBR Grand Rapids and strong showings at Ride For Redemption in Fort Worth. 
+    &lt;/p&gt;
+  &lt;/li&gt;
+  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
+    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
+      Career headline stats: about a 39% ride rate over more than 450 outs, a career average score in the low‑to‑mid‑80s, and a growing stack of 88‑plus rides at Velocity and UTB stops. 
+    &lt;/p&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;
+&lt;h2 id="style-background-and-persona" class="font-editorial font-bold mb-2 mt-4 [.has-inline-images_&amp;amp;]:clear-end text-lg first:mt-0 md:text-lg [hr+&amp;amp;]:mt-4"&gt;
+  Style, background, and persona
+&lt;/h2&gt;
+&lt;ul class="marker:text-quiet list-disc pl-8"&gt;
+  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
+    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
+      Fundamentally sound, compact rider who stays forward and aggressive, relying on strength and timing more than wild spur motion. 
+    &lt;/p&gt;
+  &lt;/li&gt;
+  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
+    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
+      Comfortable battling back after rough stretches, using smaller events and Velocity stops to rebuild confidence and momentum. 
+    &lt;/p&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;
+&lt;h2 id="personality-notes" class="font-editorial font-bold mb-2 mt-4 [.has-inline-images_&amp;amp;]:clear-end text-lg first:mt-0 md:text-lg [hr+&amp;amp;]:mt-4"&gt;
+  Personality notes
+&lt;/h2&gt;
+&lt;ul class="marker:text-quiet list-disc pl-8"&gt;
+  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
+    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
+      Comes across as humble and straightforward, classic small‑town Missouri cowboy who doesn’t chase attention but rides with plenty of confidence. 
+    &lt;/p&gt;
+  &lt;/li&gt;
+&lt;/ul&gt; for 459 - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;39.22%&lt;/em&gt;&lt;/span&gt; - Rider Rating: *.278&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Season:&amp;nbsp;&lt;/strong&gt;Rank&amp;nbsp;&lt;span style="color: #ff0000;"&gt;17&lt;/span&gt; (31 for 59 - &lt;em&gt;52.5%&lt;/em&gt;)&lt;em&gt;&lt;br /&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Points:&amp;nbsp;&lt;/strong&gt;303.00 pts &lt;span style="color: #ff0000;"&gt;&lt;em&gt;(-524.5)&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Earnings:&amp;nbsp;&lt;/strong&gt;&lt;span style="color: #008000;"&gt;&lt;em&gt;$98,926.07&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Potential&lt;/strong&gt;:&amp;nbsp;81.92 to 87.92 points&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;&lt;span style="text-decoration: underline;"&gt;&lt;strong&gt;Bull&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;ALL:&lt;/strong&gt; 33 outs 6 rides - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;81.82%&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;UTB:&lt;/strong&gt; 11 outs 4 rides - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;63.64%&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;em&gt;&lt;span style="color: #ff0000;"&gt;*No Previous Matchups&lt;/span&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t>&lt;h2&gt;Rider&lt;/h2&gt;&lt;p&gt;&lt;strong&gt;Career:&amp;nbsp;&lt;/strong&gt;Career: 363 for 942 - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;38.54%&lt;/em&gt;&lt;/span&gt; - Rider Rating: *.294&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Season:&amp;nbsp;&lt;/strong&gt;Rank&amp;nbsp;&lt;span style="color: #ff0000;"&gt;9&lt;/span&gt; (34 for 69 - &lt;em&gt;49.3%&lt;/em&gt;)&lt;em&gt;&lt;br /&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Points:&amp;nbsp;&lt;/strong&gt;405.00 pts &lt;span style="color: #ff0000;"&gt;&lt;em&gt;(-422.5)&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Earnings:&amp;nbsp;&lt;/strong&gt;&lt;span style="color: #008000;"&gt;&lt;em&gt;$159,605.64&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Potential&lt;/strong&gt;:&amp;nbsp;82.8 to 88.8 points&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;&lt;span style="text-decoration: underline;"&gt;&lt;strong&gt;Bull&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;ALL:&lt;/strong&gt; 7 outs 0 rides - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;100%&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;em&gt;&lt;span style="color: #ff0000;"&gt;*No Previous Matchups&lt;/span&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;hr /&gt;
+&lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
+  Keyshawn Whitehorse is a right-handed bull rider from McCracken Spring, Utah, a seven‑time World Finals qualifier and cultural leader riding for the Navajo Nation. 
+&lt;/p&gt;
+&lt;h2 id="basic-profile" class="font-editorial font-bold mb-2 mt-4 [.has-inline-images_&amp;amp;]:clear-end text-lg first:mt-0 md:text-lg [hr+&amp;amp;]:mt-4"&gt;
+  Basic profile
+&lt;/h2&gt;
+&lt;ul class="marker:text-quiet list-disc pl-8"&gt;
+  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
+    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
+      &lt;strong&gt;Name:&lt;/strong&gt;&amp;nbsp;Keyshawn Whitehorse
+    &lt;/p&gt;
+  &lt;/li&gt;
+  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
+    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
+      &lt;strong&gt;Hometown:&lt;/strong&gt;&amp;nbsp;McCracken Spring, Utah, USA (Navajo Nation)
+    &lt;/p&gt;
+  &lt;/li&gt;
+  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
+    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
+      &lt;strong&gt;Team:&lt;/strong&gt;&amp;nbsp;Arizona Ridge Riders (PBR Teams)
+    &lt;/p&gt;
+  &lt;/li&gt;
+  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
+    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
+      &lt;strong&gt;Hand:&lt;/strong&gt;&amp;nbsp;Right
+    &lt;/p&gt;
+  &lt;/li&gt;
+  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
+    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
+      &lt;strong&gt;Age / Size:&lt;/strong&gt;&amp;nbsp;28 years old, 5'8", 155 lbs
+    &lt;/p&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;
+&lt;h2 id="career-accomplishments" class="font-editorial font-bold mb-2 mt-4 [.has-inline-images_&amp;amp;]:clear-end text-lg first:mt-0 md:text-lg [hr+&amp;amp;]:mt-4"&gt;
+  Career accomplishments
+&lt;/h2&gt;
+&lt;ul class="marker:text-quiet list-disc pl-8"&gt;
+  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
+    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
+      2018 PBR Rookie of the Year and multiple‑time PBR World Finals qualifier, established as one of the most consistent riders of his era. 
+    &lt;/p&gt;
+  &lt;/li&gt;
+  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
+    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
+      Has more than 20 career event wins across PBR levels, including multiple premier‑series titles and key Teams game‑winners. 
+    &lt;/p&gt;
+  &lt;/li&gt;
+  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
+    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
+      Career headline stats: high‑30s ride rate over nearly 1,000 outs, dozens of 90‑point and high‑80 rides, and an average scoring profile in the mid‑80s when he covers. 
+    &lt;/p&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;
+&lt;h2 id="style-background-and-persona" class="font-editorial font-bold mb-2 mt-4 [.has-inline-images_&amp;amp;]:clear-end text-lg first:mt-0 md:text-lg [hr+&amp;amp;]:mt-4"&gt;
+  Style, background, and persona
+&lt;/h2&gt;
+&lt;ul class="marker:text-quiet list-disc pl-8"&gt;
+  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
+    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
+      Compact, technically polished rider with excellent balance and timing, rarely out of position and extremely good at finishing strong through the whistle. 
+    &lt;/p&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;
+&lt;h2 id="personality-notes" class="font-editorial font-bold mb-2 mt-4 [.has-inline-images_&amp;amp;]:clear-end text-lg first:mt-0 md:text-lg [hr+&amp;amp;]:mt-4"&gt;
+  Personality notes
+&lt;/h2&gt;
+&lt;ul class="marker:text-quiet list-disc pl-8"&gt;
+  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
+    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
+      Proudly represents the Navajo Nation, often talking about riding with purpose to honor his family, his people, and his faith. 
+    &lt;/p&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;</t>
+  </si>
+  <si>
+    <t>&lt;h2&gt;Rider&lt;/h2&gt;&lt;p&gt;&lt;strong&gt;Career:&amp;nbsp;&lt;/strong&gt;Career: 60 for 163 - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;36.81%&lt;/em&gt;&lt;/span&gt; - Rider Rating: *.221&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Season:&amp;nbsp;&lt;/strong&gt;Rank&amp;nbsp;&lt;span style="color: #ff0000;"&gt;3&lt;/span&gt; (24 for 38 - &lt;em&gt;63.2%&lt;/em&gt;)&lt;em&gt;&lt;br /&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Points:&amp;nbsp;&lt;/strong&gt;595.50 pts &lt;span style="color: #ff0000;"&gt;&lt;em&gt;(-232)&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Earnings:&amp;nbsp;&lt;/strong&gt;&lt;span style="color: #008000;"&gt;&lt;em&gt;$140,650.12&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Potential&lt;/strong&gt;:&amp;nbsp;83.9 to 89.9 points&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;&lt;span style="text-decoration: underline;"&gt;&lt;strong&gt;Bull&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;ALL:&lt;/strong&gt; 12 outs 2 rides - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;83.33%&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;UTB:&lt;/strong&gt; 10 outs 2 rides - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;80%&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;em&gt;&lt;span style="color: #ff0000;"&gt;*No Previous Matchups&lt;/span&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;hr /&gt;
+&lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
+  Leandro Zampollo is a right-handed Brazilian bull rider from Pirassununga, São Paulo, one of the fastest‑rising young stars on the Unleash The Beast tour. 
+&lt;/p&gt;
+&lt;h2 id="basic-profile" class="font-editorial font-bold mb-2 mt-4 [.has-inline-images_&amp;amp;]:clear-end text-lg first:mt-0 md:text-lg [hr+&amp;amp;]:mt-4"&gt;
+  Basic profile
+&lt;/h2&gt;
+&lt;ul class="marker:text-quiet list-disc pl-8"&gt;
+  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
+    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
+      &lt;strong&gt;Name:&lt;/strong&gt;&amp;nbsp;Leandro Zampollo
+    &lt;/p&gt;
+  &lt;/li&gt;
+  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
+    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
+      &lt;strong&gt;Hometown:&lt;/strong&gt;&amp;nbsp;Pirassununga, São Paulo, Brazil
+    &lt;/p&gt;
+  &lt;/li&gt;
+  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
+    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
+      &lt;strong&gt;Team:&lt;/strong&gt;&amp;nbsp;Florida Freedom (PBR Teams)
+    &lt;/p&gt;
+  &lt;/li&gt;
+  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
+    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
+      &lt;strong&gt;Hand:&lt;/strong&gt;&amp;nbsp;Right
+    &lt;/p&gt;
+  &lt;/li&gt;
+  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
+    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
+      &lt;strong&gt;Age / Size:&lt;/strong&gt;&amp;nbsp;Mid‑20s, 5'9", ~154 lbs
+    &lt;/p&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;
+&lt;h2 id="career-accomplishments" class="font-editorial font-bold mb-2 mt-4 [.has-inline-images_&amp;amp;]:clear-end text-lg first:mt-0 md:text-lg [hr+&amp;amp;]:mt-4"&gt;
+  Career accomplishments
+&lt;/h2&gt;
+&lt;ul class="marker:text-quiet list-disc pl-8"&gt;
+  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
+    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
+      Won the 2024 Hondo (Bridgeport) event and other Challenger/Velocity stops to punch his ticket onto UTB, where he quickly moved into the Top 30 in the world. 
+    &lt;/p&gt;
+  &lt;/li&gt;
+  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
+    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
+      Claimed his first Unleash The Beast round win at Madison Square Garden in 2026, marked 88.4 points on UTZ BesTex Smokestack on Night 2 in New York. [web:243][web:246]
+    &lt;/p&gt;
+  &lt;/li&gt;
+  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
+    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
+      Career headline stats: nearly 37% ride rate early in his UTB career, with an average score in the mid‑80s when he covers and multiple 88‑90‑point rides already on the board. [web:249]
+    &lt;/p&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;
+&lt;h2 id="style-background-and-persona" class="font-editorial font-bold mb-2 mt-4 [.has-inline-images_&amp;amp;]:clear-end text-lg first:mt-0 md:text-lg [hr+&amp;amp;]:mt-4"&gt;
+  Style, background, and persona
+&lt;/h2&gt;
+&lt;ul class="marker:text-quiet list-disc pl-8"&gt;
+  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
+    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
+      Smooth, forward‑driving Brazilian style with great timing around the corner, allowing him to stay centered and build points as bulls get stronger. 
+    &lt;/p&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;
+&lt;h2 id="personality-notes" class="font-editorial font-bold mb-2 mt-4 [.has-inline-images_&amp;amp;]:clear-end text-lg first:mt-0 md:text-lg [hr+&amp;amp;]:mt-4"&gt;
+  Personality notes
+&lt;/h2&gt;
+&lt;ul class="marker:text-quiet list-disc pl-8"&gt;
+  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
+    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
+      Comes across as humble and appreciative of the opportunity, but rides with a chip‑on‑the‑shoulder intensity that fits his rapid rise from underdog to contender. 
+    &lt;/p&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -983,12 +1611,6 @@
       <name val="Verdana"/>
       <family val="2"/>
     </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FFD6D5D4"/>
-      <name val="Helvetica Neue"/>
-      <family val="2"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1011,7 +1633,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
@@ -1023,7 +1645,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1470,15 +2091,15 @@
       <c r="O2" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="P2" s="9">
-        <v>45.5</v>
-      </c>
-      <c r="Q2" s="9">
-        <v>45.25</v>
+      <c r="P2">
+        <v>0</v>
+      </c>
+      <c r="Q2">
+        <v>0</v>
       </c>
       <c r="R2">
         <f>P2+Q2</f>
-        <v>90.75</v>
+        <v>0</v>
       </c>
       <c r="T2" t="s">
         <v>19</v>
@@ -1525,21 +2146,21 @@
       <c r="N3" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="O3" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="P3" s="9">
-        <v>43.75</v>
-      </c>
-      <c r="Q3" s="9">
-        <v>44</v>
+      <c r="O3" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="P3">
+        <v>0</v>
+      </c>
+      <c r="Q3">
+        <v>0</v>
       </c>
       <c r="R3">
         <f t="shared" ref="R3:R44" si="0">P3+Q3</f>
-        <v>87.75</v>
+        <v>0</v>
       </c>
       <c r="T3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:20" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -1550,10 +2171,10 @@
         <v>31</v>
       </c>
       <c r="C4" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>39</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>40</v>
       </c>
       <c r="E4" s="1"/>
       <c r="F4" s="1" t="s">
@@ -1566,36 +2187,36 @@
         <v>1</v>
       </c>
       <c r="I4" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="J4" s="1" t="s">
         <v>41</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>42</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>26</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M4" s="6"/>
       <c r="N4" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="O4" s="3" t="s">
-        <v>44</v>
+      <c r="O4" s="4" t="s">
+        <v>264</v>
       </c>
       <c r="P4">
-        <v>43</v>
-      </c>
-      <c r="Q4" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q4">
         <v>0</v>
       </c>
       <c r="R4">
         <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="T4" t="s">
         <v>43</v>
-      </c>
-      <c r="T4" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="5" spans="1:20" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -1606,10 +2227,10 @@
         <v>31</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E5" s="1"/>
       <c r="F5" s="1" t="s">
@@ -1622,23 +2243,23 @@
         <v>1</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="K5" s="2" t="s">
         <v>26</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M5" s="6"/>
       <c r="N5" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="O5" s="3" t="s">
-        <v>50</v>
+      <c r="O5" s="4" t="s">
+        <v>265</v>
       </c>
       <c r="P5">
         <v>0</v>
@@ -1651,7 +2272,7 @@
         <v>0</v>
       </c>
       <c r="T5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="6" spans="1:20" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -1662,14 +2283,14 @@
         <v>31</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E6" s="1"/>
       <c r="F6" s="1" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>23</v>
@@ -1678,10 +2299,10 @@
         <v>1</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="K6" s="2" t="s">
         <v>26</v>
@@ -1693,8 +2314,8 @@
       <c r="N6" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="O6" s="3" t="s">
-        <v>56</v>
+      <c r="O6" s="4" t="s">
+        <v>266</v>
       </c>
       <c r="P6">
         <v>0</v>
@@ -1707,7 +2328,7 @@
         <v>0</v>
       </c>
       <c r="T6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:20" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -1718,14 +2339,14 @@
         <v>67.349999999999994</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="E7" s="1"/>
       <c r="F7" s="1" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>23</v>
@@ -1734,10 +2355,10 @@
         <v>1</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="K7" s="2" t="s">
         <v>26</v>
@@ -1746,13 +2367,13 @@
         <v>27</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="N7" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="O7" s="3" t="s">
-        <v>63</v>
+      <c r="O7" s="4" t="s">
+        <v>267</v>
       </c>
       <c r="P7">
         <v>0</v>
@@ -1776,14 +2397,14 @@
         <v>74.319999999999993</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="E8" s="1"/>
       <c r="F8" s="1" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>23</v>
@@ -1792,23 +2413,23 @@
         <v>2</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="K8" s="2" t="s">
         <v>26</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M8" s="3"/>
       <c r="N8" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="O8" s="3" t="s">
-        <v>68</v>
+      <c r="O8" s="4" t="s">
+        <v>268</v>
       </c>
       <c r="P8">
         <v>0</v>
@@ -1821,7 +2442,7 @@
         <v>0</v>
       </c>
       <c r="T8" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9" spans="1:20" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -1832,14 +2453,14 @@
         <v>67.02</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="E9" s="1"/>
       <c r="F9" s="1" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>23</v>
@@ -1848,10 +2469,10 @@
         <v>2</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>26</v>
@@ -1860,13 +2481,13 @@
         <v>27</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="N9" s="3" t="s">
         <v>29</v>
       </c>
       <c r="O9" s="3" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="P9">
         <v>0</v>
@@ -1879,7 +2500,7 @@
         <v>0</v>
       </c>
       <c r="T9" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10" spans="1:20" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -1890,14 +2511,14 @@
         <v>72.430000000000007</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="E10" s="1"/>
       <c r="F10" s="1" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>23</v>
@@ -1906,10 +2527,10 @@
         <v>2</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="K10" s="2" t="s">
         <v>26</v>
@@ -1918,13 +2539,13 @@
         <v>27</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="N10" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="O10" s="3" t="s">
-        <v>81</v>
+      <c r="O10" s="4" t="s">
+        <v>269</v>
       </c>
       <c r="P10">
         <v>0</v>
@@ -1948,14 +2569,14 @@
         <v>31</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="E11" s="1"/>
       <c r="F11" s="1" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="G11" s="1" t="s">
         <v>23</v>
@@ -1964,23 +2585,23 @@
         <v>2</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="K11" s="2" t="s">
         <v>26</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M11" s="6"/>
       <c r="N11" s="3" t="s">
         <v>36</v>
       </c>
       <c r="O11" s="3" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="P11">
         <v>0</v>
@@ -1993,7 +2614,7 @@
         <v>0</v>
       </c>
       <c r="T11" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="12" spans="1:20" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -2004,16 +2625,16 @@
         <v>41.22</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="E12" s="1">
         <v>10266759</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="G12" s="1" t="s">
         <v>23</v>
@@ -2022,10 +2643,10 @@
         <v>2</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="K12" s="2" t="s">
         <v>26</v>
@@ -2038,7 +2659,7 @@
         <v>36</v>
       </c>
       <c r="O12" s="3" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="P12">
         <v>0</v>
@@ -2062,16 +2683,16 @@
         <v>78.040000000000006</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="E13" s="1">
         <v>10231236</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="G13" s="1" t="s">
         <v>23</v>
@@ -2080,10 +2701,10 @@
         <v>2</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="K13" s="2" t="s">
         <v>26</v>
@@ -2092,13 +2713,13 @@
         <v>27</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="N13" s="3" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="O13" s="3" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="P13">
         <v>0</v>
@@ -2111,7 +2732,7 @@
         <v>0</v>
       </c>
       <c r="T13" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="14" spans="1:20" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -2125,13 +2746,13 @@
         <v>32</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="E14" s="1">
         <v>10259466</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="G14" s="1" t="s">
         <v>23</v>
@@ -2140,23 +2761,23 @@
         <v>3</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="K14" s="2" t="s">
         <v>26</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M14" s="6"/>
       <c r="N14" s="3" t="s">
         <v>36</v>
       </c>
       <c r="O14" s="3" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="P14">
         <v>0</v>
@@ -2169,7 +2790,7 @@
         <v>0</v>
       </c>
       <c r="T14" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="15" spans="1:20" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -2180,14 +2801,14 @@
         <v>59.91</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="E15" s="1"/>
       <c r="F15" s="1" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="G15" s="1" t="s">
         <v>23</v>
@@ -2196,10 +2817,10 @@
         <v>3</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="K15" s="2" t="s">
         <v>26</v>
@@ -2208,13 +2829,13 @@
         <v>27</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="N15" s="3" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="O15" s="3" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="P15">
         <v>0</v>
@@ -2227,7 +2848,7 @@
         <v>0</v>
       </c>
       <c r="T15" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="16" spans="1:20" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -2238,16 +2859,16 @@
         <v>71.7</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="E16" s="1">
         <v>10257887</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="G16" s="1" t="s">
         <v>23</v>
@@ -2256,23 +2877,23 @@
         <v>3</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="K16" s="2" t="s">
         <v>26</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M16" s="3"/>
       <c r="N16" s="3" t="s">
         <v>36</v>
       </c>
       <c r="O16" s="3" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="P16">
         <v>0</v>
@@ -2285,7 +2906,7 @@
         <v>0</v>
       </c>
       <c r="T16" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="17" spans="1:20" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -2296,14 +2917,14 @@
         <v>77.53</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="E17" s="1"/>
       <c r="F17" s="1" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="G17" s="1" t="s">
         <v>23</v>
@@ -2312,10 +2933,10 @@
         <v>3</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="K17" s="2" t="s">
         <v>26</v>
@@ -2328,7 +2949,7 @@
         <v>36</v>
       </c>
       <c r="O17" s="3" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="P17">
         <v>0</v>
@@ -2341,7 +2962,7 @@
         <v>0</v>
       </c>
       <c r="T17" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18" spans="1:20" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -2352,14 +2973,14 @@
         <v>69.67</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="E18" s="1"/>
       <c r="F18" s="1" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="G18" s="1" t="s">
         <v>23</v>
@@ -2368,25 +2989,25 @@
         <v>3</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="K18" s="2" t="s">
         <v>26</v>
       </c>
       <c r="L18" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="N18" s="3" t="s">
         <v>29</v>
       </c>
       <c r="O18" s="3" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="P18">
         <v>0</v>
@@ -2399,7 +3020,7 @@
         <v>0</v>
       </c>
       <c r="T18" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="19" spans="1:20" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -2410,14 +3031,14 @@
         <v>77.599999999999994</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="E19" s="1"/>
       <c r="F19" s="1" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="G19" s="1" t="s">
         <v>23</v>
@@ -2426,25 +3047,25 @@
         <v>3</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="K19" s="2" t="s">
         <v>26</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="N19" s="3" t="s">
         <v>29</v>
       </c>
       <c r="O19" s="3" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="P19">
         <v>0</v>
@@ -2457,7 +3078,7 @@
         <v>0</v>
       </c>
       <c r="T19" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20" spans="1:20" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -2468,14 +3089,14 @@
         <v>31</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="E20" s="1"/>
       <c r="F20" s="1" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>23</v>
@@ -2484,10 +3105,10 @@
         <v>4</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="K20" s="2" t="s">
         <v>26</v>
@@ -2500,7 +3121,7 @@
         <v>36</v>
       </c>
       <c r="O20" s="3" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="P20">
         <v>0</v>
@@ -2524,16 +3145,16 @@
         <v>31</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="E21" s="1">
         <v>10259151</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="G21" s="1" t="s">
         <v>23</v>
@@ -2542,23 +3163,23 @@
         <v>4</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="K21" s="2" t="s">
         <v>26</v>
       </c>
       <c r="L21" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M21" s="6"/>
       <c r="N21" s="3" t="s">
         <v>36</v>
       </c>
       <c r="O21" s="3" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="P21">
         <v>0</v>
@@ -2582,14 +3203,14 @@
         <v>31</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="E22" s="1"/>
       <c r="F22" s="1" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="G22" s="1" t="s">
         <v>23</v>
@@ -2598,23 +3219,23 @@
         <v>4</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="K22" s="2" t="s">
         <v>26</v>
       </c>
       <c r="L22" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M22" s="6"/>
       <c r="N22" s="3" t="s">
         <v>36</v>
       </c>
       <c r="O22" s="3" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="P22">
         <v>0</v>
@@ -2638,16 +3259,16 @@
         <v>64.7</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="E23" s="1">
         <v>10269156</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="G23" s="1" t="s">
         <v>23</v>
@@ -2656,23 +3277,23 @@
         <v>4</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="K23" s="2" t="s">
         <v>26</v>
       </c>
       <c r="L23" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M23" s="3"/>
       <c r="N23" s="3" t="s">
         <v>36</v>
       </c>
       <c r="O23" s="3" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="P23">
         <v>0</v>
@@ -2696,14 +3317,14 @@
         <v>64.67</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="E24" s="1"/>
       <c r="F24" s="1" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="G24" s="1" t="s">
         <v>23</v>
@@ -2712,25 +3333,25 @@
         <v>4</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="K24" s="2" t="s">
         <v>26</v>
       </c>
       <c r="L24" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M24" s="3" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="N24" s="3" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="O24" s="3" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="P24">
         <v>0</v>
@@ -2743,7 +3364,7 @@
         <v>0</v>
       </c>
       <c r="T24" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="25" spans="1:20" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -2754,14 +3375,14 @@
         <v>31</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="E25" s="1"/>
       <c r="F25" s="1" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="G25" s="1" t="s">
         <v>23</v>
@@ -2770,10 +3391,10 @@
         <v>4</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="K25" s="2" t="s">
         <v>26</v>
@@ -2786,7 +3407,7 @@
         <v>36</v>
       </c>
       <c r="O25" s="3" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="P25">
         <v>0</v>
@@ -2799,7 +3420,7 @@
         <v>0</v>
       </c>
       <c r="T25" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="26" spans="1:20" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -2810,16 +3431,16 @@
         <v>56.01</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="E26" s="1">
         <v>10239182</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="G26" s="1" t="s">
         <v>23</v>
@@ -2828,10 +3449,10 @@
         <v>5</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="K26" s="2" t="s">
         <v>26</v>
@@ -2840,13 +3461,13 @@
         <v>27</v>
       </c>
       <c r="M26" s="3" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="N26" s="3" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="O26" s="3" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="P26">
         <v>0</v>
@@ -2870,16 +3491,16 @@
         <v>31</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="E27" s="1">
         <v>10262517</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="G27" s="1" t="s">
         <v>23</v>
@@ -2888,23 +3509,23 @@
         <v>5</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="K27" s="2" t="s">
         <v>26</v>
       </c>
       <c r="L27" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M27" s="6"/>
       <c r="N27" s="3" t="s">
         <v>36</v>
       </c>
       <c r="O27" s="3" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="P27">
         <v>0</v>
@@ -2917,7 +3538,7 @@
         <v>0</v>
       </c>
       <c r="T27" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="28" spans="1:20" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -2928,14 +3549,14 @@
         <v>86.05</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="E28" s="1"/>
       <c r="F28" s="1" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="G28" s="1" t="s">
         <v>23</v>
@@ -2944,25 +3565,25 @@
         <v>5</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="K28" s="2" t="s">
         <v>26</v>
       </c>
       <c r="L28" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M28" s="3" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="N28" s="3" t="s">
         <v>29</v>
       </c>
       <c r="O28" s="3" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="P28">
         <v>0</v>
@@ -2975,7 +3596,7 @@
         <v>0</v>
       </c>
       <c r="T28" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="29" spans="1:20" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -2986,14 +3607,14 @@
         <v>70.64</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="E29" s="1"/>
       <c r="F29" s="1" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="G29" s="1" t="s">
         <v>23</v>
@@ -3002,10 +3623,10 @@
         <v>5</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="K29" s="2" t="s">
         <v>26</v>
@@ -3014,13 +3635,13 @@
         <v>27</v>
       </c>
       <c r="M29" s="3" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="N29" s="3" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="O29" s="3" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="P29">
         <v>0</v>
@@ -3033,7 +3654,7 @@
         <v>0</v>
       </c>
       <c r="T29" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="30" spans="1:20" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -3044,14 +3665,14 @@
         <v>31</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="E30" s="1"/>
       <c r="F30" s="1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="G30" s="1" t="s">
         <v>23</v>
@@ -3060,10 +3681,10 @@
         <v>5</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="K30" s="2" t="s">
         <v>26</v>
@@ -3076,7 +3697,7 @@
         <v>36</v>
       </c>
       <c r="O30" s="3" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="P30">
         <v>0</v>
@@ -3089,7 +3710,7 @@
         <v>0</v>
       </c>
       <c r="T30" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="31" spans="1:20" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -3100,14 +3721,14 @@
         <v>31</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="E31" s="1"/>
       <c r="F31" s="1" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="G31" s="1" t="s">
         <v>23</v>
@@ -3116,10 +3737,10 @@
         <v>6</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="K31" s="2" t="s">
         <v>26</v>
@@ -3132,7 +3753,7 @@
         <v>36</v>
       </c>
       <c r="O31" s="3" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="P31">
         <v>0</v>
@@ -3145,7 +3766,7 @@
         <v>0</v>
       </c>
       <c r="T31" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="32" spans="1:20" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -3156,16 +3777,16 @@
         <v>31</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="E32" s="1">
         <v>10266753</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="G32" s="1" t="s">
         <v>23</v>
@@ -3174,23 +3795,23 @@
         <v>6</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="K32" s="2" t="s">
         <v>26</v>
       </c>
       <c r="L32" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M32" s="6"/>
       <c r="N32" s="3" t="s">
         <v>36</v>
       </c>
       <c r="O32" s="3" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="P32">
         <v>0</v>
@@ -3214,16 +3835,16 @@
         <v>89.52</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="E33" s="1">
         <v>10203017</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="G33" s="1" t="s">
         <v>23</v>
@@ -3232,25 +3853,25 @@
         <v>6</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="K33" s="2" t="s">
         <v>26</v>
       </c>
       <c r="L33" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M33" s="3" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="N33" s="3" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="O33" s="3" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="P33">
         <v>0</v>
@@ -3263,7 +3884,7 @@
         <v>0</v>
       </c>
       <c r="T33" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="34" spans="1:20" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -3274,10 +3895,10 @@
         <v>74.709999999999994</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="E34" s="1"/>
       <c r="F34" s="1" t="s">
@@ -3290,25 +3911,25 @@
         <v>6</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="K34" s="2" t="s">
         <v>26</v>
       </c>
       <c r="L34" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M34" s="3" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="N34" s="3" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="O34" s="3" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="P34">
         <v>0</v>
@@ -3321,7 +3942,7 @@
         <v>0</v>
       </c>
       <c r="T34" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="35" spans="1:20" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -3332,14 +3953,14 @@
         <v>31</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="E35" s="1"/>
       <c r="F35" s="1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="G35" s="1" t="s">
         <v>23</v>
@@ -3348,25 +3969,25 @@
         <v>7</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="J35" s="1" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="K35" s="2" t="s">
         <v>26</v>
       </c>
       <c r="L35" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M35" s="3" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="N35" s="3" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="O35" s="3" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="P35">
         <v>0</v>
@@ -3379,7 +4000,7 @@
         <v>0</v>
       </c>
       <c r="T35" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="36" spans="1:20" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -3390,14 +4011,14 @@
         <v>31</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="E36" s="1"/>
       <c r="F36" s="1" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="G36" s="1" t="s">
         <v>23</v>
@@ -3406,23 +4027,23 @@
         <v>7</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="J36" s="1" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="K36" s="2" t="s">
         <v>26</v>
       </c>
       <c r="L36" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M36" s="6"/>
       <c r="N36" s="3" t="s">
         <v>36</v>
       </c>
       <c r="O36" s="3" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="P36">
         <v>0</v>
@@ -3435,7 +4056,7 @@
         <v>0</v>
       </c>
       <c r="T36" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="37" spans="1:20" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -3446,16 +4067,16 @@
         <v>81.430000000000007</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="E37" s="1">
         <v>10243244</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="G37" s="1" t="s">
         <v>23</v>
@@ -3464,25 +4085,25 @@
         <v>8</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="J37" s="1" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="K37" s="2" t="s">
         <v>26</v>
       </c>
       <c r="L37" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M37" s="3" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="N37" s="3" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="O37" s="3" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="P37">
         <v>0</v>
@@ -3495,7 +4116,7 @@
         <v>0</v>
       </c>
       <c r="T37" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="38" spans="1:20" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -3506,16 +4127,16 @@
         <v>31</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="E38" s="1">
         <v>10268368</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="G38" s="1" t="s">
         <v>23</v>
@@ -3524,23 +4145,23 @@
         <v>8</v>
       </c>
       <c r="I38" s="1" t="s">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="J38" s="1" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="K38" s="2" t="s">
         <v>26</v>
       </c>
       <c r="L38" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M38" s="6"/>
       <c r="N38" s="3" t="s">
         <v>36</v>
       </c>
       <c r="O38" s="3" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="P38">
         <v>0</v>
@@ -3553,7 +4174,7 @@
         <v>0</v>
       </c>
       <c r="T38" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="39" spans="1:20" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -3564,16 +4185,16 @@
         <v>57.96</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="E39" s="1">
         <v>10239944</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="G39" s="1" t="s">
         <v>23</v>
@@ -3582,10 +4203,10 @@
         <v>8</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="J39" s="1" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="K39" s="2" t="s">
         <v>26</v>
@@ -3594,13 +4215,13 @@
         <v>27</v>
       </c>
       <c r="M39" s="3" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="N39" s="3" t="s">
         <v>29</v>
       </c>
       <c r="O39" s="3" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="P39">
         <v>0</v>
@@ -3613,7 +4234,7 @@
         <v>0</v>
       </c>
       <c r="T39" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="40" spans="1:20" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -3624,14 +4245,14 @@
         <v>70.33</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="E40" s="1"/>
       <c r="F40" s="1" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="G40" s="1" t="s">
         <v>23</v>
@@ -3640,10 +4261,10 @@
         <v>8</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="J40" s="1" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="K40" s="2" t="s">
         <v>26</v>
@@ -3656,7 +4277,7 @@
         <v>36</v>
       </c>
       <c r="O40" s="3" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="P40">
         <v>0</v>
@@ -3680,16 +4301,16 @@
         <v>86.7</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="E41" s="1">
         <v>10222050</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="G41" s="1" t="s">
         <v>23</v>
@@ -3698,10 +4319,10 @@
         <v>9</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="J41" s="1" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="K41" s="2" t="s">
         <v>26</v>
@@ -3710,13 +4331,13 @@
         <v>27</v>
       </c>
       <c r="M41" s="3" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="N41" s="3" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="O41" s="3" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="P41">
         <v>0</v>
@@ -3729,7 +4350,7 @@
         <v>0</v>
       </c>
       <c r="T41" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="42" spans="1:20" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -3743,13 +4364,13 @@
         <v>32</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="E42" s="1">
         <v>10274756</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="G42" s="1" t="s">
         <v>23</v>
@@ -3758,10 +4379,10 @@
         <v>9</v>
       </c>
       <c r="I42" s="1" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="J42" s="1" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="K42" s="2" t="s">
         <v>26</v>
@@ -3774,7 +4395,7 @@
         <v>36</v>
       </c>
       <c r="O42" s="3" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="P42">
         <v>0</v>
@@ -3787,7 +4408,7 @@
         <v>0</v>
       </c>
       <c r="T42" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="43" spans="1:20" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -3798,14 +4419,14 @@
         <v>52.8</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="E43" s="1"/>
       <c r="F43" s="1" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="G43" s="1" t="s">
         <v>23</v>
@@ -3814,25 +4435,25 @@
         <v>9</v>
       </c>
       <c r="I43" s="1" t="s">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="J43" s="1" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="K43" s="2" t="s">
         <v>26</v>
       </c>
       <c r="L43" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M43" s="3" t="s">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="N43" s="3" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="O43" s="3" t="s">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="P43">
         <v>0</v>
@@ -3856,16 +4477,16 @@
         <v>65.78</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="E44" s="1">
         <v>10258756</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="G44" s="1" t="s">
         <v>23</v>
@@ -3874,10 +4495,10 @@
         <v>9</v>
       </c>
       <c r="I44" s="1" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="J44" s="1" t="s">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="K44" s="2" t="s">
         <v>26</v>
@@ -3886,13 +4507,13 @@
         <v>27</v>
       </c>
       <c r="M44" s="3" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="N44" s="3" t="s">
         <v>29</v>
       </c>
       <c r="O44" s="3" t="s">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="P44">
         <v>0</v>

--- a/data/pbr_matchups_full.xlsx
+++ b/data/pbr_matchups_full.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cameronyoung/Desktop/rankratings:/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F9EE457-5C12-B141-A738-D734706215C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{984531D3-2181-B341-9799-2E07C7255540}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="13520" yWindow="740" windowWidth="16720" windowHeight="18900" xr2:uid="{63502F5A-9950-074D-B0A2-89EF4471630B}"/>
   </bookViews>
@@ -227,6 +227,9 @@
     <t>UNKNOWN</t>
   </si>
   <si>
+    <t>&lt;h2&gt;Rider&lt;/h2&gt;&lt;p&gt;&lt;strong&gt;Career:&amp;nbsp;&lt;/strong&gt;Career: 94 for 330 - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;28.48%&lt;/em&gt;&lt;/span&gt; - Rider Rating: .183&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Season:&amp;nbsp;&lt;/strong&gt;Rank&amp;nbsp;&lt;span style="color: #ff0000;"&gt;32&lt;/span&gt; (16 for 51 - &lt;em&gt;31.4%&lt;/em&gt;)&lt;em&gt;&lt;br /&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Points:&amp;nbsp;&lt;/strong&gt;137.00 pts &lt;span style="color: #ff0000;"&gt;&lt;em&gt;(-690.5)&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Earnings:&amp;nbsp;&lt;/strong&gt;&lt;span style="color: #008000;"&gt;&lt;em&gt;$49,517.31&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Potential&lt;/strong&gt;:&amp;nbsp;83.31 to 89.31 points&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;&lt;span style="text-decoration: underline;"&gt;&lt;strong&gt;Bull&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;em&gt;&lt;span style="color: #ff0000;"&gt;*No Previous Matchups&lt;/span&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;</t>
+  </si>
+  <si>
     <t>Fade</t>
   </si>
   <si>
@@ -245,6 +248,9 @@
     <t>Right</t>
   </si>
   <si>
+    <t>&lt;h2&gt;Rider&lt;/h2&gt;&lt;p&gt;&lt;strong&gt;Career:&amp;nbsp;&lt;/strong&gt;Career: 126 for 328 - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;38.41%&lt;/em&gt;&lt;/span&gt; - Rider Rating: *.269&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Season:&amp;nbsp;&lt;/strong&gt;Rank&amp;nbsp;&lt;span style="color: #ff0000;"&gt;10&lt;/span&gt; (26 for 67 - &lt;em&gt;38.8%&lt;/em&gt;)&lt;em&gt;&lt;br /&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Points:&amp;nbsp;&lt;/strong&gt;392.00 pts &lt;span style="color: #ff0000;"&gt;&lt;em&gt;(-435.5)&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Earnings:&amp;nbsp;&lt;/strong&gt;&lt;span style="color: #008000;"&gt;&lt;em&gt;$125,660.26&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Potential&lt;/strong&gt;:&amp;nbsp;85.96 to 91.96 points&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;&lt;span style="text-decoration: underline;"&gt;&lt;strong&gt;Bull&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;em&gt;&lt;span style="color: #ff0000;"&gt;*No Previous Matchups&lt;/span&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;</t>
+  </si>
+  <si>
     <t>Pass</t>
   </si>
   <si>
@@ -260,6 +266,9 @@
     <t>0.316 (6)</t>
   </si>
   <si>
+    <t>&lt;h2&gt;Rider&lt;/h2&gt;&lt;p&gt;&lt;strong&gt;Career:&amp;nbsp;&lt;/strong&gt;Career: 110 for 273 - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;40.29%&lt;/em&gt;&lt;/span&gt; - Rider Rating: *.295&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Season:&amp;nbsp;&lt;/strong&gt;Rank&amp;nbsp;&lt;span style="color: #ff0000;"&gt;16&lt;/span&gt; (21 for 56 - &lt;em&gt;37.5%&lt;/em&gt;)&lt;em&gt;&lt;br /&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Points:&amp;nbsp;&lt;/strong&gt;336.00 pts &lt;span style="color: #ff0000;"&gt;&lt;em&gt;(-491.5)&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Earnings:&amp;nbsp;&lt;/strong&gt;&lt;span style="color: #008000;"&gt;&lt;em&gt;$96,890.29&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Potential&lt;/strong&gt;:&amp;nbsp;83.9 to 89.9 points&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;&lt;span style="text-decoration: underline;"&gt;&lt;strong&gt;Bull&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;em&gt;&lt;span style="color: #ff0000;"&gt;*No Previous Matchups&lt;/span&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;</t>
+  </si>
+  <si>
     <t>--</t>
   </si>
   <si>
@@ -275,6 +284,9 @@
     <t>0.234 (5)</t>
   </si>
   <si>
+    <t>&lt;h2&gt;Rider&lt;/h2&gt;&lt;p&gt;&lt;strong&gt;Career:&amp;nbsp;&lt;/strong&gt;Career: 154 for 515 - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;29.9%&lt;/em&gt;&lt;/span&gt; - Rider Rating: *.250&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Season:&amp;nbsp;&lt;/strong&gt;Rank&amp;nbsp;&lt;span style="color: #ff0000;"&gt;38&lt;/span&gt; (21 for 70 - &lt;em&gt;30%&lt;/em&gt;)&lt;em&gt;&lt;br /&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Points:&amp;nbsp;&lt;/strong&gt;86.00 pts &lt;span style="color: #ff0000;"&gt;&lt;em&gt;(-741.5)&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Earnings:&amp;nbsp;&lt;/strong&gt;&lt;span style="color: #008000;"&gt;&lt;em&gt;$85,787.98&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Potential&lt;/strong&gt;:&amp;nbsp;-1 to 5 points&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;&lt;span style="text-decoration: underline;"&gt;&lt;strong&gt;Bull&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;em&gt;&lt;span style="color: #ff0000;"&gt;*No Previous Matchups&lt;/span&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;</t>
+  </si>
+  <si>
     <t>27-6 (2)</t>
   </si>
   <si>
@@ -293,6 +305,9 @@
     <t>Rider 3.00%</t>
   </si>
   <si>
+    <t>&lt;h2&gt;Rider&lt;/h2&gt;&lt;p&gt;&lt;strong&gt;Career:&amp;nbsp;&lt;/strong&gt;Career: 180 for 459 - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;39.22%&lt;/em&gt;&lt;/span&gt; - Rider Rating: *.278&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Season:&amp;nbsp;&lt;/strong&gt;Rank&amp;nbsp;&lt;span style="color: #ff0000;"&gt;17&lt;/span&gt; (31 for 59 - &lt;em&gt;52.5%&lt;/em&gt;)&lt;em&gt;&lt;br /&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Points:&amp;nbsp;&lt;/strong&gt;303.00 pts &lt;span style="color: #ff0000;"&gt;&lt;em&gt;(-524.5)&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Earnings:&amp;nbsp;&lt;/strong&gt;&lt;span style="color: #008000;"&gt;&lt;em&gt;$98,926.07&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Potential&lt;/strong&gt;:&amp;nbsp;81.92 to 87.92 points&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;&lt;span style="text-decoration: underline;"&gt;&lt;strong&gt;Bull&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;ALL:&lt;/strong&gt; 33 outs 6 rides - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;81.82%&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;UTB:&lt;/strong&gt; 11 outs 4 rides - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;63.64%&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;em&gt;&lt;span style="color: #ff0000;"&gt;*No Previous Matchups&lt;/span&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;</t>
+  </si>
+  <si>
     <t>7-0 (0)</t>
   </si>
   <si>
@@ -305,6 +320,9 @@
     <t>0.323 (7)</t>
   </si>
   <si>
+    <t>&lt;h2&gt;Rider&lt;/h2&gt;&lt;p&gt;&lt;strong&gt;Career:&amp;nbsp;&lt;/strong&gt;Career: 363 for 942 - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;38.54%&lt;/em&gt;&lt;/span&gt; - Rider Rating: *.294&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Season:&amp;nbsp;&lt;/strong&gt;Rank&amp;nbsp;&lt;span style="color: #ff0000;"&gt;9&lt;/span&gt; (34 for 69 - &lt;em&gt;49.3%&lt;/em&gt;)&lt;em&gt;&lt;br /&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Points:&amp;nbsp;&lt;/strong&gt;405.00 pts &lt;span style="color: #ff0000;"&gt;&lt;em&gt;(-422.5)&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Earnings:&amp;nbsp;&lt;/strong&gt;&lt;span style="color: #008000;"&gt;&lt;em&gt;$159,605.64&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Potential&lt;/strong&gt;:&amp;nbsp;82.8 to 88.8 points&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;&lt;span style="text-decoration: underline;"&gt;&lt;strong&gt;Bull&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;ALL:&lt;/strong&gt; 7 outs 0 rides - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;100%&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;em&gt;&lt;span style="color: #ff0000;"&gt;*No Previous Matchups&lt;/span&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;</t>
+  </si>
+  <si>
     <t>8-4 (1)</t>
   </si>
   <si>
@@ -341,6 +359,9 @@
     <t>Rider 40.00%</t>
   </si>
   <si>
+    <t>&lt;h2&gt;Rider&lt;/h2&gt;&lt;p&gt;&lt;strong&gt;Career:&amp;nbsp;&lt;/strong&gt;Career: 60 for 163 - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;36.81%&lt;/em&gt;&lt;/span&gt; - Rider Rating: *.221&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Season:&amp;nbsp;&lt;/strong&gt;Rank&amp;nbsp;&lt;span style="color: #ff0000;"&gt;3&lt;/span&gt; (24 for 38 - &lt;em&gt;63.2%&lt;/em&gt;)&lt;em&gt;&lt;br /&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Points:&amp;nbsp;&lt;/strong&gt;595.50 pts &lt;span style="color: #ff0000;"&gt;&lt;em&gt;(-232)&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Earnings:&amp;nbsp;&lt;/strong&gt;&lt;span style="color: #008000;"&gt;&lt;em&gt;$140,650.12&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Potential&lt;/strong&gt;:&amp;nbsp;83.9 to 89.9 points&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;&lt;span style="text-decoration: underline;"&gt;&lt;strong&gt;Bull&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;ALL:&lt;/strong&gt; 12 outs 2 rides - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;83.33%&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;UTB:&lt;/strong&gt; 10 outs 2 rides - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;80%&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;em&gt;&lt;span style="color: #ff0000;"&gt;*No Previous Matchups&lt;/span&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;</t>
+  </si>
+  <si>
     <t>2-2 (2)</t>
   </si>
   <si>
@@ -903,662 +924,13 @@
   </si>
   <si>
     <t>&lt;h2&gt;Rider&lt;/h2&gt;&lt;p&gt;&lt;strong&gt;Career:&amp;nbsp;&lt;/strong&gt;Career: 258 for 576 - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;44.79%&lt;/em&gt;&lt;/span&gt; - Rider Rating: *.372&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Season:&amp;nbsp;&lt;/strong&gt;Rank&amp;nbsp;&lt;span style="color: #ff0000;"&gt;6&lt;/span&gt; (36 for 66 - &lt;em&gt;54.5%&lt;/em&gt;)&lt;em&gt;&lt;br /&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Points:&amp;nbsp;&lt;/strong&gt;488.50 pts &lt;span style="color: #ff0000;"&gt;&lt;em&gt;(-339)&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Earnings:&amp;nbsp;&lt;/strong&gt;&lt;span style="color: #008000;"&gt;&lt;em&gt;$252,397.78&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Potential&lt;/strong&gt;:&amp;nbsp;83.74 to 89.74 points&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;&lt;span style="text-decoration: underline;"&gt;&lt;strong&gt;Bull&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;ALL:&lt;/strong&gt; 16 outs 7 rides - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;56.25%&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;UTB:&lt;/strong&gt; 13 outs 7 rides - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;46.15%&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;em&gt;&lt;span style="color: #ff0000;"&gt;*No Previous Matchups&lt;/span&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t>&lt;h2&gt;Rider&lt;/h2&gt;&lt;p&gt;&lt;strong&gt;Career:&amp;nbsp;&lt;/strong&gt;Career: 94 for 330 - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;28.48%&lt;/em&gt;&lt;/span&gt; - Rider Rating: .183&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Season:&amp;nbsp;&lt;/strong&gt;Rank&amp;nbsp;&lt;span style="color: #ff0000;"&gt;32&lt;/span&gt; (16 for 51 - &lt;em&gt;31.4%&lt;/em&gt;)&lt;em&gt;&lt;br /&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Points:&amp;nbsp;&lt;/strong&gt;137.00 pts &lt;span style="color: #ff0000;"&gt;&lt;em&gt;(-690.5)&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Earnings:&amp;nbsp;&lt;/strong&gt;&lt;span style="color: #008000;"&gt;&lt;em&gt;$49,517.31&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Potential&lt;/strong&gt;:&amp;nbsp;83.31 to 89.31 points&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;&lt;span style="text-decoration: underline;"&gt;&lt;strong&gt;Bull&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;em&gt;&lt;span style="color: #ff0000;"&gt;*No Previous Matchups&lt;/span&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;
-&lt;hr /&gt;
-&lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-  Kase Hitt is a left-handed, up-and-coming PBR bull rider from Dickson, Oklahoma, known for being tall and athletic with a gritty, keep-coming-back mindset. 
-&lt;/p&gt;
-&lt;h2 id="basic-profile" class="font-editorial font-bold mb-2 mt-4 [.has-inline-images_&amp;amp;]:clear-end text-lg first:mt-0 md:text-lg [hr+&amp;amp;]:mt-4"&gt;
-  Basic profile
-&lt;/h2&gt;
-&lt;ul class="marker:text-quiet list-disc pl-8"&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      &lt;strong&gt;Name:&lt;/strong&gt;&amp;nbsp;Kase Hitt
-    &lt;/p&gt;
-  &lt;/li&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      &lt;strong&gt;Hometown:&lt;/strong&gt;&amp;nbsp;Dickson, Oklahoma, USA
-    &lt;/p&gt;
-  &lt;/li&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      &lt;strong&gt;Team:&lt;/strong&gt;&amp;nbsp;Oklahoma Wildcatters (PBR Teams)
-    &lt;/p&gt;
-  &lt;/li&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      &lt;strong&gt;Hand:&lt;/strong&gt;&amp;nbsp;Left
-    &lt;/p&gt;
-  &lt;/li&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      &lt;strong&gt;Age / Size:&lt;/strong&gt;&amp;nbsp;21 years old, 6'2", ~150 lbs
-    &lt;/p&gt;
-  &lt;/li&gt;
-&lt;/ul&gt;
-&lt;h2 id="career-accomplishments" class="font-editorial font-bold mb-2 mt-4 [.has-inline-images_&amp;amp;]:clear-end text-lg first:mt-0 md:text-lg [hr+&amp;amp;]:mt-4"&gt;
-  Career accomplishments
-&lt;/h2&gt;
-&lt;ul class="marker:text-quiet list-disc pl-8"&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      Earned his first Pendleton Whisky Velocity Tour victory at PBR Bangor in early 2026 with a three-ride comeback after bucking off his opening bull. 
-    &lt;/p&gt;
-  &lt;/li&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      Logged a career-best UTB score with an 88.4‑point ride on Eyes On Me in the Championship Round at the 2026 PBR Pittsburgh Unleash The Beast event. 
-    &lt;/p&gt;
-  &lt;/li&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      Won the PBR Stockyards Showcase in Fort Worth in 2024 with a walk‑off ride on Free Ride at Cowtown Coliseum, one of his early statement wins in the Challenger ranks. 
-    &lt;/p&gt;
-  &lt;/li&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      Key closer for the Oklahoma Wildcatters in Teams competition, including clutch rides such as sealing wins at Thunder Days and other late‑game situations. 
-    &lt;/p&gt;
-  &lt;/li&gt;
-&lt;/ul&gt;
-&lt;h2 id="style-background-and-persona" class="font-editorial font-bold mb-2 mt-4 [.has-inline-images_&amp;amp;]:clear-end text-lg first:mt-0 md:text-lg [hr+&amp;amp;]:mt-4"&gt;
-  Style, background, and persona
-&lt;/h2&gt;
-&lt;ul class="marker:text-quiet list-disc pl-8"&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      Tall, long‑levered left‑hander who uses his length and balance to stay over the front and finish strong, especially in rank short‑round matchups. 
-    &lt;/p&gt;
-  &lt;/li&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      Built his name through smaller PBR and open bull ridings before breaking through on the Velocity Tour and earning UTB opportunities. 
-    &lt;/p&gt;
-  &lt;/li&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      Recognized for mental toughness and the ability to bounce back after buckoffs, as seen in Bangor where he turned an early miss into a three‑ride surge for the win. 
-    &lt;/p&gt;
-  &lt;/li&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      Rides with a straightforward, blue‑collar attitude that fits Oklahoma’s rodeo culture and the Wildcatters’ identity. 
-    &lt;/p&gt;
-  &lt;/li&gt;
-&lt;/ul&gt;
-&lt;h2 id="personality-notes" class="font-editorial font-bold mb-2 mt-4 [.has-inline-images_&amp;amp;]:clear-end text-lg first:mt-0 md:text-lg [hr+&amp;amp;]:mt-4"&gt;
-  Personality notes
-&lt;/h2&gt;
-&lt;ul class="marker:text-quiet list-disc pl-8"&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      Comes off as humble and soft‑spoken in interviews, but highly competitive in the chute, leaning on confidence in his feel and fundamentals more than flash. 
-    &lt;/p&gt;
-  &lt;/li&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      Has already ridden through bumps and soreness at big events, building a reputation as a guy who keeps nodding his head even when he’s banged up. 
-    &lt;/p&gt;
-  &lt;/li&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      Off the dirt, leans into the modern PBR lifestyle—social media, music, and team‑branding—while still coming across as a small‑town Oklahoma cowboy at heart. 
-    &lt;/p&gt;
-  &lt;/li&gt;
-&lt;/ul&gt;</t>
-  </si>
-  <si>
-    <t>&lt;h2&gt;Rider&lt;/h2&gt;&lt;p&gt;&lt;strong&gt;Career:&amp;nbsp;&lt;/strong&gt;Career: 126 for 328 - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;38.41%&lt;/em&gt;&lt;/span&gt; - Rider Rating: *.269&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Season:&amp;nbsp;&lt;/strong&gt;Rank&amp;nbsp;&lt;span style="color: #ff0000;"&gt;10&lt;/span&gt; (26 for 67 - &lt;em&gt;38.8%&lt;/em&gt;)&lt;em&gt;&lt;br /&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Points:&amp;nbsp;&lt;/strong&gt;392.00 pts &lt;span style="color: #ff0000;"&gt;&lt;em&gt;(-435.5)&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Earnings:&amp;nbsp;&lt;/strong&gt;&lt;span style="color: #008000;"&gt;&lt;em&gt;$125,660.26&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Potential&lt;/strong&gt;:&amp;nbsp;85.96 to 91.96 points&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;&lt;span style="text-decoration: underline;"&gt;&lt;strong&gt;Bull&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;em&gt;&lt;span style="color: #ff0000;"&gt;*No Previous Matchups&lt;/span&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;
-&lt;hr /&gt;
-&lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-  Julio Cesar Marques is a right-handed Brazilian bull rider from Tatuí, São Paulo, a new‑generation star who quickly climbed into the very top tier of the PBR standings. 
-&lt;/p&gt;
-&lt;h2 id="basic-profile" class="font-editorial font-bold mb-2 mt-4 [.has-inline-images_&amp;amp;]:clear-end text-lg first:mt-0 md:text-lg [hr+&amp;amp;]:mt-4"&gt;
-  Basic profile
-&lt;/h2&gt;
-&lt;ul class="marker:text-quiet list-disc pl-8"&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      &lt;strong&gt;Name:&lt;/strong&gt;&amp;nbsp;Julio Cesar Marques
-    &lt;/p&gt;
-  &lt;/li&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      &lt;strong&gt;Hometown:&lt;/strong&gt;&amp;nbsp;Tatuí, São Paulo, Brazil
-    &lt;/p&gt;
-  &lt;/li&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      &lt;strong&gt;Team:&lt;/strong&gt;&amp;nbsp;Kansas City Outlaws (PBR Teams)
-    &lt;/p&gt;
-  &lt;/li&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      &lt;strong&gt;Hand:&lt;/strong&gt;&amp;nbsp;Right
-    &lt;/p&gt;
-  &lt;/li&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      &lt;strong&gt;Age / Size:&lt;/strong&gt;&amp;nbsp;22 years old, 5'6", ~145 lbs
-    &lt;/p&gt;
-  &lt;/li&gt;
-&lt;/ul&gt;
-&lt;h2 id="career-accomplishments" class="font-editorial font-bold mb-2 mt-4 [.has-inline-images_&amp;amp;]:clear-end text-lg first:mt-0 md:text-lg [hr+&amp;amp;]:mt-4"&gt;
-  Career accomplishments
-&lt;/h2&gt;
-&lt;ul class="marker:text-quiet list-disc pl-8"&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      Broke through with his first Unleash The Beast event win at PBR Albany in late 2024, going a perfect 3‑for‑3 to claim the title and surge up the world standings. 
-    &lt;/p&gt;
-  &lt;/li&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      Crowned “King of Deadwood” after dominating the historic Deadwood, South Dakota stop, stacking key rides in one of the tour’s most unique outdoor venues. 
-    &lt;/p&gt;
-  &lt;/li&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      Logged multiple high‑mark UTB rides, including big scores on bulls like Lights Out, Tacky Jack, and Bayou Boy that helped push him into the No. 1 ranking battle. 
-    &lt;/p&gt;
-  &lt;/li&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      Quickly became a consistent UTB contender, pushing into the top 5 and even No. 1 in the world race early in his career with strong finishes at major stops. 
-    &lt;/p&gt;
-  &lt;/li&gt;
-&lt;/ul&gt;
-&lt;h2 id="style-background-and-persona" class="font-editorial font-bold mb-2 mt-4 [.has-inline-images_&amp;amp;]:clear-end text-lg first:mt-0 md:text-lg [hr+&amp;amp;]:mt-4"&gt;
-  Style, background, and persona
-&lt;/h2&gt;
-&lt;ul class="marker:text-quiet list-disc pl-8"&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      Classic young Brazilian technician with strong core position and timing, able to stay centered even when bulls are changing direction or speed. 
-    &lt;/p&gt;
-  &lt;/li&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      Built his résumé through Brazil and U.S. Challenger/Velocity events before quickly adapting to UTB bulls and arenas, with almost no drop‑off under brighter lights. 
-    &lt;/p&gt;
-  &lt;/li&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      Rides with a calm, composed look in the chute, then flips into an explosive, forward‑driving style once the gate opens. 
-    &lt;/p&gt;
-  &lt;/li&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      Already viewed as one of the leaders of the new Brazilian wave, regularly mentioned as a future world‑title threat. 
-    &lt;/p&gt;
-  &lt;/li&gt;
-&lt;/ul&gt;
-&lt;h2 id="personality-notes" class="font-editorial font-bold mb-2 mt-4 [.has-inline-images_&amp;amp;]:clear-end text-lg first:mt-0 md:text-lg [hr+&amp;amp;]:mt-4"&gt;
-  Personality notes
-&lt;/h2&gt;
-&lt;ul class="marker:text-quiet list-disc pl-8"&gt;
-  &lt;li class="py-0 my-0 p</t>
-  </si>
-  <si>
-    <t>&lt;h2&gt;Rider&lt;/h2&gt;&lt;p&gt;&lt;strong&gt;Career:&amp;nbsp;&lt;/strong&gt;Career: 110 for 273 - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;40.29%&lt;/em&gt;&lt;/span&gt; - Rider Rating: *.295&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Season:&amp;nbsp;&lt;/strong&gt;Rank&amp;nbsp;&lt;span style="color: #ff0000;"&gt;16&lt;/span&gt; (21 for 56 - &lt;em&gt;37.5%&lt;/em&gt;)&lt;em&gt;&lt;br /&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Points:&amp;nbsp;&lt;/strong&gt;336.00 pts &lt;span style="color: #ff0000;"&gt;&lt;em&gt;(-491.5)&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Earnings:&amp;nbsp;&lt;/strong&gt;&lt;span style="color: #008000;"&gt;&lt;em&gt;$96,890.29&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Potential&lt;/strong&gt;:&amp;nbsp;83.9 to 89.9 points&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;&lt;span style="text-decoration: underline;"&gt;&lt;strong&gt;Bull&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;em&gt;&lt;span style="color: #ff0000;"&gt;*No Previous Matchups&lt;/span&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;
-&lt;hr /&gt;
-&lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-  Kaiden “K‑Loud” Loud is a right-handed bull rider from Kaufman, Texas, a young UTB and Teams star known for big 90‑point moments and a loud, high‑energy presence in the arena. 
-&lt;/p&gt;
-&lt;h2 id="basic-profile" class="font-editorial font-bold mb-2 mt-4 [.has-inline-images_&amp;amp;]:clear-end text-lg first:mt-0 md:text-lg [hr+&amp;amp;]:mt-4"&gt;
-  Basic profile
-&lt;/h2&gt;
-&lt;ul class="marker:text-quiet list-disc pl-8"&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      &lt;strong&gt;Name:&lt;/strong&gt;&amp;nbsp;Kaiden Loud
-    &lt;/p&gt;
-  &lt;/li&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      &lt;strong&gt;Hometown:&lt;/strong&gt;&amp;nbsp;Kaufman, Texas, USA
-    &lt;/p&gt;
-  &lt;/li&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      &lt;strong&gt;Team:&lt;/strong&gt;&amp;nbsp;Nashville Stampede (PBR Teams)
-    &lt;/p&gt;
-  &lt;/li&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      &lt;strong&gt;Hand:&lt;/strong&gt;&amp;nbsp;Right
-    &lt;/p&gt;
-  &lt;/li&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      &lt;strong&gt;Age / Size:&lt;/strong&gt;&amp;nbsp;20 years old, athletic frame
-    &lt;/p&gt;
-  &lt;/li&gt;
-&lt;/ul&gt;
-&lt;h2 id="career-accomplishments" class="font-editorial font-bold mb-2 mt-4 [.has-inline-images_&amp;amp;]:clear-end text-lg first:mt-0 md:text-lg [hr+&amp;amp;]:mt-4"&gt;
-  Career accomplishments
-&lt;/h2&gt;
-&lt;ul class="marker:text-quiet list-disc pl-8"&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      Dominated the high school ranks, including a Texas state title and youth bull riding championships, before jumping straight into the professional scene as a teenager. 
-    &lt;/p&gt;
-  &lt;/li&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      Grabbed early national attention by winning the 2023 Tuff Hedeman Bull Riding in New Mexico at just 18 years old. 
-    &lt;/p&gt;
-  &lt;/li&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      Selected by the Nashville Stampede in the second round of the 2023 PBR Teams Draft and quickly delivered clutch rides, including 90‑plus on bulls like Mike’s Motive and Ridin’ Salty. 
-    &lt;/p&gt;
-  &lt;/li&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      Broke out individually at the 2024 PBR World Finals Eliminations in Fort Worth, winning the stage by going 3‑for‑4 and posting a 91.75‑point career‑best ride on Doze You Down. 
-    &lt;/p&gt;
-  &lt;/li&gt;
-&lt;/ul&gt;
-&lt;h2 id="style-background-and-persona" class="font-editorial font-bold mb-2 mt-4 [.has-inline-images_&amp;amp;]:clear-end text-lg first:mt-0 md:text-lg [hr+&amp;amp;]:mt-4"&gt;
-  Style, background, and persona
-&lt;/h2&gt;
-&lt;ul class="marker:text-quiet list-disc pl-8"&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      High‑energy, forward‑driving rider who uses quick reactions and strong hips to stay in the middle when bulls are firing hard and moving ahead. 
-    &lt;/p&gt;
-  &lt;/li&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      Comfortable under pressure in short‑round and World Finals‑type situations, with multiple rides over 88–90 points on big‑name bulls across UTB and Teams events. 
-    &lt;/p&gt;
-  &lt;/li&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      Brings a showman streak—feeding off the crowd, celebrating big rides—and fits perfectly with Nashville’s “Broadway” personality on the Teams side. 
-    &lt;/p&gt;
-  &lt;/li&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      Grew up in Texas rodeo culture and still trains and travels with other young guns like John Crimber, keeping a constant competitive environment around him. 
-    &lt;/p&gt;
-  &lt;/li&gt;
-&lt;/ul&gt;
-&lt;h2 id="personality-notes" class="font-editorial font-bold mb-2 mt-4 [.has-inline-images_&amp;amp;]:clear-end text-lg first:mt-0 md:text-lg [hr+&amp;amp;]:mt-4"&gt;
-  Personality notes
-&lt;/h2&gt;
-&lt;ul class="marker:text-quiet list-disc pl-8"&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      Outgoing and media‑friendly, often featured in PBR content as “K‑Loud,” he leans into the spotlight without losing his workmanlike approach behind the scenes. 
-    &lt;/p&gt;
-  &lt;/li&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      Close friends with fellow young star John Crimber; the two often practice together and push each other in and out of the arena. 
-    &lt;/p&gt;
-  &lt;/li&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      Away from bull riding he stays active—shooting hoops, hanging around the barn, and keeping the same energetic, fun personality that shows up on TV. 
-    &lt;/p&gt;
-  &lt;/li&gt;
-&lt;/ul&gt;</t>
-  </si>
-  <si>
-    <t>&lt;h2&gt;Rider&lt;/h2&gt;&lt;p&gt;&lt;strong&gt;Career:&amp;nbsp;&lt;/strong&gt;Career: 154 for 515 - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;29.9%&lt;/em&gt;&lt;/span&gt; - Rider Rating: *.250&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Season:&amp;nbsp;&lt;/strong&gt;Rank&amp;nbsp;&lt;span style="color: #ff0000;"&gt;38&lt;/span&gt; (21 for 70 - &lt;em&gt;30%&lt;/em&gt;)&lt;em&gt;&lt;br /&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Points:&amp;nbsp;&lt;/strong&gt;86.00 pts &lt;span style="color: #ff0000;"&gt;&lt;em&gt;(-741.5)&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Earnings:&amp;nbsp;&lt;/strong&gt;&lt;span style="color: #008000;"&gt;&lt;em&gt;$85,787.98&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Potential&lt;/strong&gt;:&amp;nbsp;-1 to 5 points&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;&lt;span style="text-decoration: underline;"&gt;&lt;strong&gt;Bull&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;em&gt;&lt;span style="color: #ff0000;"&gt;*No Previous Matchups&lt;/span&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;
-&lt;hr /&gt;
-&lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-  Mauricio Gulla Moreira is a right-handed Brazilian bull rider from Gaviao Peixoto, São Paulo, a proven UTB and Teams veteran with a big-moment, high‑ceiling style. 
-&lt;/p&gt;
-&lt;h2 id="basic-profile" class="font-editorial font-bold mb-2 mt-4 [.has-inline-images_&amp;amp;]:clear-end text-lg first:mt-0 md:text-lg [hr+&amp;amp;]:mt-4"&gt;
-  Basic profile
-&lt;/h2&gt;
-&lt;ul class="marker:text-quiet list-disc pl-8"&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      &lt;strong&gt;Name:&lt;/strong&gt;&amp;nbsp;Mauricio Gulla Moreira
-    &lt;/p&gt;
-  &lt;/li&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      &lt;strong&gt;Hometown:&lt;/strong&gt;&amp;nbsp;Gaviao Peixoto, São Paulo, Brazil
-    &lt;/p&gt;
-  &lt;/li&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      &lt;strong&gt;Team:&lt;/strong&gt;&amp;nbsp;New York Mavericks (PBR Teams)
-    &lt;/p&gt;
-  &lt;/li&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      &lt;strong&gt;Hand:&lt;/strong&gt;&amp;nbsp;Right
-    &lt;/p&gt;
-  &lt;/li&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      &lt;strong&gt;Age / Size:&lt;/strong&gt;&amp;nbsp;Mid‑20s, compact and powerful build
-    &lt;/p&gt;
-  &lt;/li&gt;
-&lt;/ul&gt;
-&lt;h2 id="career-accomplishments" class="font-editorial font-bold mb-2 mt-4 [.has-inline-images_&amp;amp;]:clear-end text-lg first:mt-0 md:text-lg [hr+&amp;amp;]:mt-4"&gt;
-  Career accomplishments
-&lt;/h2&gt;
-&lt;ul class="marker:text-quiet list-disc pl-8"&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      4‑time PBR World Finals qualifier and 3‑time Teams World Finals qualifier, established as a top‑tier rider on both the premier series and the team side. 
-    &lt;/p&gt;
-  &lt;/li&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      Multiple major wins and titles across PBR Brazil, Challenger, and Velocity‑type events, including an event championship at the historic PBR Stockyards Showcase in Fort Worth. 
-    &lt;/p&gt;
-  &lt;/li&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      Produced big‑time UTB rides such as 88.75 on Tijuana Two Step at Madison Square Garden, 87.75 on Hell Right in Albany, and a 90‑point monster on Doze You Down during PBR Teams Outlaw Days. 
-    &lt;/p&gt;
-  &lt;/li&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      Career headline stats: nearly 30% ride rate over more than 500 outs, a stack of mid‑to‑upper‑80s scores on rank bulls, and multiple 88‑90‑point rides that anchor both his individual and Teams résumé. 
-    &lt;/p&gt;
-  &lt;/li&gt;
-&lt;/ul&gt;
-&lt;h2 id="style-background-and-persona" class="font-editorial font-bold mb-2 mt-4 [.has-inline-images_&amp;amp;]:clear-end text-lg first:mt-0 md:text-lg [hr+&amp;amp;]:mt-4"&gt;
-  Style, background, and persona
-&lt;/h2&gt;
-&lt;ul class="marker:text-quiet list-disc pl-8"&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      Classic Brazilian technician with strong posture, loose upper body and a lot of feel, letting bulls move around under him while he keeps his hips down and chest front. 
-    &lt;/p&gt;
-  &lt;/li&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      Comfortable in both big indoor arenas and smaller, rowdier outdoor setups; he has winning rides from New York City to Deadwood and Brazilian events back home. 
-    &lt;/p&gt;
-  &lt;/li&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      Known for being tough and durable across long seasons, riding through soreness and staying in the mix of the world‑title conversation for multiple years. 
-    &lt;/p&gt;
-  &lt;/li&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      Plays a veteran leader role on the New York Mavericks, often matched up with rank bulls in crucial Teams games. 
-    &lt;/p&gt;
-  &lt;/li&gt;
-&lt;/ul&gt;
-&lt;h2 id="personality-notes" class="font-editorial font-bold mb-2 mt-4 [.has-inline-images_&amp;amp;]:clear-end text-lg first:mt-0 md:text-lg [hr+&amp;amp;]:mt-4"&gt;
-  Personality notes
-&lt;/h2&gt;
-&lt;ul class="marker:text-quiet list-disc pl-8"&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      Comes across as calm and humble, quick to credit his faith and family, and lets his riding do most of the talking in big moments. 
-    &lt;/p&gt;
-  &lt;/li&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      Has a strong fan following in both Brazil and the U.S., helped by his fun social‑media presence and highlight‑reel rides that regularly make PBR clips. 
-    &lt;/p&gt;
-  &lt;/li&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      Off the dirt he leans into music, family, and a laid‑back Brazilian cowboy lifestyle, but inside the arena he rides like a guy who expects to win every matchup. 
-    &lt;/p&gt;
-  &lt;/li&gt;
-&lt;/ul&gt;</t>
-  </si>
-  <si>
-    <t>&lt;h2&gt;Rider&lt;/h2&gt;&lt;p&gt;&lt;strong&gt;Career:&amp;nbsp;&lt;/strong&gt;Career: 180&lt;h2&gt;Rider&lt;/h2&gt;&lt;p&gt;&lt;strong&gt;Career:&amp;nbsp;&lt;/strong&gt;Career: 180 for 459 - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;39.22%&lt;/em&gt;&lt;/span&gt; - Rider Rating: *.278&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Season:&amp;nbsp;&lt;/strong&gt;Rank&amp;nbsp;&lt;span style="color: #ff0000;"&gt;17&lt;/span&gt; (31 for 59 - &lt;em&gt;52.5%&lt;/em&gt;)&lt;em&gt;&lt;br /&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Points:&amp;nbsp;&lt;/strong&gt;303.00 pts &lt;span style="color: #ff0000;"&gt;&lt;em&gt;(-524.5)&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Earnings:&amp;nbsp;&lt;/strong&gt;&lt;span style="color: #008000;"&gt;&lt;em&gt;$98,926.07&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Potential&lt;/strong&gt;:&amp;nbsp;81.92 to 87.92 points&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;&lt;span style="text-decoration: underline;"&gt;&lt;strong&gt;Bull&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;ALL:&lt;/strong&gt; 33 outs 6 rides - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;81.82%&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;UTB:&lt;/strong&gt; 11 outs 4 rides - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;63.64%&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;em&gt;&lt;span style="color: #ff0000;"&gt;*No Previous Matchups&lt;/span&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;
-&lt;hr /&gt;
-&lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-  Bob Mitchell is a right-handed bull rider from Steelville, Missouri, a gritty, blue‑collar competitor who has turned himself into a steady threat on Velocity, UTB, and Teams. 
-&lt;/p&gt;
-&lt;h2 id="basic-profile" class="font-editorial font-bold mb-2 mt-4 [.has-inline-images_&amp;amp;]:clear-end text-lg first:mt-0 md:text-lg [hr+&amp;amp;]:mt-4"&gt;
-  Basic profile
-&lt;/h2&gt;
-&lt;ul class="marker:text-quiet list-disc pl-8"&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      &lt;strong&gt;Name:&lt;/strong&gt;&amp;nbsp;Bob Mitchell
-    &lt;/p&gt;
-  &lt;/li&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      &lt;strong&gt;Hometown:&lt;/strong&gt;&amp;nbsp;Steelville, Missouri, USA
-    &lt;/p&gt;
-  &lt;/li&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      &lt;strong&gt;Team:&lt;/strong&gt;&amp;nbsp;New York Mavericks (PBR Teams)
-    &lt;/p&gt;
-  &lt;/li&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      &lt;strong&gt;Hand:&lt;/strong&gt;&amp;nbsp;Right
-    &lt;/p&gt;
-  &lt;/li&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      &lt;strong&gt;Age / Size:&lt;/strong&gt;&amp;nbsp;Early 20s, 5'10", 160–170 lbs
-    &lt;/p&gt;
-  &lt;/li&gt;
-&lt;/ul&gt;
-&lt;h2 id="career-accomplishments" class="font-editorial font-bold mb-2 mt-4 [.has-inline-images_&amp;amp;]:clear-end text-lg first:mt-0 md:text-lg [hr+&amp;amp;]:mt-4"&gt;
-  Career accomplishments
-&lt;/h2&gt;
-&lt;ul class="marker:text-quiet list-disc pl-8"&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      Broke out as a teenager by cracking the premier series and climbing into the Top 20 in the world at just 19 years old. 
-    &lt;/p&gt;
-  &lt;/li&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      Logged key wins and rounds on the Pendleton Whisky Velocity Tour, including a Round 1 victory at PBR Grand Rapids and strong showings at Ride For Redemption in Fort Worth. 
-    &lt;/p&gt;
-  &lt;/li&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      Career headline stats: about a 39% ride rate over more than 450 outs, a career average score in the low‑to‑mid‑80s, and a growing stack of 88‑plus rides at Velocity and UTB stops. 
-    &lt;/p&gt;
-  &lt;/li&gt;
-&lt;/ul&gt;
-&lt;h2 id="style-background-and-persona" class="font-editorial font-bold mb-2 mt-4 [.has-inline-images_&amp;amp;]:clear-end text-lg first:mt-0 md:text-lg [hr+&amp;amp;]:mt-4"&gt;
-  Style, background, and persona
-&lt;/h2&gt;
-&lt;ul class="marker:text-quiet list-disc pl-8"&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      Fundamentally sound, compact rider who stays forward and aggressive, relying on strength and timing more than wild spur motion. 
-    &lt;/p&gt;
-  &lt;/li&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      Comfortable battling back after rough stretches, using smaller events and Velocity stops to rebuild confidence and momentum. 
-    &lt;/p&gt;
-  &lt;/li&gt;
-&lt;/ul&gt;
-&lt;h2 id="personality-notes" class="font-editorial font-bold mb-2 mt-4 [.has-inline-images_&amp;amp;]:clear-end text-lg first:mt-0 md:text-lg [hr+&amp;amp;]:mt-4"&gt;
-  Personality notes
-&lt;/h2&gt;
-&lt;ul class="marker:text-quiet list-disc pl-8"&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      Comes across as humble and straightforward, classic small‑town Missouri cowboy who doesn’t chase attention but rides with plenty of confidence. 
-    &lt;/p&gt;
-  &lt;/li&gt;
-&lt;/ul&gt; for 459 - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;39.22%&lt;/em&gt;&lt;/span&gt; - Rider Rating: *.278&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Season:&amp;nbsp;&lt;/strong&gt;Rank&amp;nbsp;&lt;span style="color: #ff0000;"&gt;17&lt;/span&gt; (31 for 59 - &lt;em&gt;52.5%&lt;/em&gt;)&lt;em&gt;&lt;br /&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Points:&amp;nbsp;&lt;/strong&gt;303.00 pts &lt;span style="color: #ff0000;"&gt;&lt;em&gt;(-524.5)&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Earnings:&amp;nbsp;&lt;/strong&gt;&lt;span style="color: #008000;"&gt;&lt;em&gt;$98,926.07&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Potential&lt;/strong&gt;:&amp;nbsp;81.92 to 87.92 points&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;&lt;span style="text-decoration: underline;"&gt;&lt;strong&gt;Bull&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;ALL:&lt;/strong&gt; 33 outs 6 rides - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;81.82%&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;UTB:&lt;/strong&gt; 11 outs 4 rides - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;63.64%&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;em&gt;&lt;span style="color: #ff0000;"&gt;*No Previous Matchups&lt;/span&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t>&lt;h2&gt;Rider&lt;/h2&gt;&lt;p&gt;&lt;strong&gt;Career:&amp;nbsp;&lt;/strong&gt;Career: 363 for 942 - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;38.54%&lt;/em&gt;&lt;/span&gt; - Rider Rating: *.294&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Season:&amp;nbsp;&lt;/strong&gt;Rank&amp;nbsp;&lt;span style="color: #ff0000;"&gt;9&lt;/span&gt; (34 for 69 - &lt;em&gt;49.3%&lt;/em&gt;)&lt;em&gt;&lt;br /&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Points:&amp;nbsp;&lt;/strong&gt;405.00 pts &lt;span style="color: #ff0000;"&gt;&lt;em&gt;(-422.5)&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Earnings:&amp;nbsp;&lt;/strong&gt;&lt;span style="color: #008000;"&gt;&lt;em&gt;$159,605.64&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Potential&lt;/strong&gt;:&amp;nbsp;82.8 to 88.8 points&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;&lt;span style="text-decoration: underline;"&gt;&lt;strong&gt;Bull&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;ALL:&lt;/strong&gt; 7 outs 0 rides - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;100%&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;em&gt;&lt;span style="color: #ff0000;"&gt;*No Previous Matchups&lt;/span&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;
-&lt;hr /&gt;
-&lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-  Keyshawn Whitehorse is a right-handed bull rider from McCracken Spring, Utah, a seven‑time World Finals qualifier and cultural leader riding for the Navajo Nation. 
-&lt;/p&gt;
-&lt;h2 id="basic-profile" class="font-editorial font-bold mb-2 mt-4 [.has-inline-images_&amp;amp;]:clear-end text-lg first:mt-0 md:text-lg [hr+&amp;amp;]:mt-4"&gt;
-  Basic profile
-&lt;/h2&gt;
-&lt;ul class="marker:text-quiet list-disc pl-8"&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      &lt;strong&gt;Name:&lt;/strong&gt;&amp;nbsp;Keyshawn Whitehorse
-    &lt;/p&gt;
-  &lt;/li&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      &lt;strong&gt;Hometown:&lt;/strong&gt;&amp;nbsp;McCracken Spring, Utah, USA (Navajo Nation)
-    &lt;/p&gt;
-  &lt;/li&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      &lt;strong&gt;Team:&lt;/strong&gt;&amp;nbsp;Arizona Ridge Riders (PBR Teams)
-    &lt;/p&gt;
-  &lt;/li&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      &lt;strong&gt;Hand:&lt;/strong&gt;&amp;nbsp;Right
-    &lt;/p&gt;
-  &lt;/li&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      &lt;strong&gt;Age / Size:&lt;/strong&gt;&amp;nbsp;28 years old, 5'8", 155 lbs
-    &lt;/p&gt;
-  &lt;/li&gt;
-&lt;/ul&gt;
-&lt;h2 id="career-accomplishments" class="font-editorial font-bold mb-2 mt-4 [.has-inline-images_&amp;amp;]:clear-end text-lg first:mt-0 md:text-lg [hr+&amp;amp;]:mt-4"&gt;
-  Career accomplishments
-&lt;/h2&gt;
-&lt;ul class="marker:text-quiet list-disc pl-8"&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      2018 PBR Rookie of the Year and multiple‑time PBR World Finals qualifier, established as one of the most consistent riders of his era. 
-    &lt;/p&gt;
-  &lt;/li&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      Has more than 20 career event wins across PBR levels, including multiple premier‑series titles and key Teams game‑winners. 
-    &lt;/p&gt;
-  &lt;/li&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      Career headline stats: high‑30s ride rate over nearly 1,000 outs, dozens of 90‑point and high‑80 rides, and an average scoring profile in the mid‑80s when he covers. 
-    &lt;/p&gt;
-  &lt;/li&gt;
-&lt;/ul&gt;
-&lt;h2 id="style-background-and-persona" class="font-editorial font-bold mb-2 mt-4 [.has-inline-images_&amp;amp;]:clear-end text-lg first:mt-0 md:text-lg [hr+&amp;amp;]:mt-4"&gt;
-  Style, background, and persona
-&lt;/h2&gt;
-&lt;ul class="marker:text-quiet list-disc pl-8"&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      Compact, technically polished rider with excellent balance and timing, rarely out of position and extremely good at finishing strong through the whistle. 
-    &lt;/p&gt;
-  &lt;/li&gt;
-&lt;/ul&gt;
-&lt;h2 id="personality-notes" class="font-editorial font-bold mb-2 mt-4 [.has-inline-images_&amp;amp;]:clear-end text-lg first:mt-0 md:text-lg [hr+&amp;amp;]:mt-4"&gt;
-  Personality notes
-&lt;/h2&gt;
-&lt;ul class="marker:text-quiet list-disc pl-8"&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      Proudly represents the Navajo Nation, often talking about riding with purpose to honor his family, his people, and his faith. 
-    &lt;/p&gt;
-  &lt;/li&gt;
-&lt;/ul&gt;</t>
-  </si>
-  <si>
-    <t>&lt;h2&gt;Rider&lt;/h2&gt;&lt;p&gt;&lt;strong&gt;Career:&amp;nbsp;&lt;/strong&gt;Career: 60 for 163 - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;36.81%&lt;/em&gt;&lt;/span&gt; - Rider Rating: *.221&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Season:&amp;nbsp;&lt;/strong&gt;Rank&amp;nbsp;&lt;span style="color: #ff0000;"&gt;3&lt;/span&gt; (24 for 38 - &lt;em&gt;63.2%&lt;/em&gt;)&lt;em&gt;&lt;br /&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Points:&amp;nbsp;&lt;/strong&gt;595.50 pts &lt;span style="color: #ff0000;"&gt;&lt;em&gt;(-232)&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Earnings:&amp;nbsp;&lt;/strong&gt;&lt;span style="color: #008000;"&gt;&lt;em&gt;$140,650.12&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Potential&lt;/strong&gt;:&amp;nbsp;83.9 to 89.9 points&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;&lt;span style="text-decoration: underline;"&gt;&lt;strong&gt;Bull&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;ALL:&lt;/strong&gt; 12 outs 2 rides - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;83.33%&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;UTB:&lt;/strong&gt; 10 outs 2 rides - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;80%&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;em&gt;&lt;span style="color: #ff0000;"&gt;*No Previous Matchups&lt;/span&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;
-&lt;hr /&gt;
-&lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-  Leandro Zampollo is a right-handed Brazilian bull rider from Pirassununga, São Paulo, one of the fastest‑rising young stars on the Unleash The Beast tour. 
-&lt;/p&gt;
-&lt;h2 id="basic-profile" class="font-editorial font-bold mb-2 mt-4 [.has-inline-images_&amp;amp;]:clear-end text-lg first:mt-0 md:text-lg [hr+&amp;amp;]:mt-4"&gt;
-  Basic profile
-&lt;/h2&gt;
-&lt;ul class="marker:text-quiet list-disc pl-8"&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      &lt;strong&gt;Name:&lt;/strong&gt;&amp;nbsp;Leandro Zampollo
-    &lt;/p&gt;
-  &lt;/li&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      &lt;strong&gt;Hometown:&lt;/strong&gt;&amp;nbsp;Pirassununga, São Paulo, Brazil
-    &lt;/p&gt;
-  &lt;/li&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      &lt;strong&gt;Team:&lt;/strong&gt;&amp;nbsp;Florida Freedom (PBR Teams)
-    &lt;/p&gt;
-  &lt;/li&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      &lt;strong&gt;Hand:&lt;/strong&gt;&amp;nbsp;Right
-    &lt;/p&gt;
-  &lt;/li&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      &lt;strong&gt;Age / Size:&lt;/strong&gt;&amp;nbsp;Mid‑20s, 5'9", ~154 lbs
-    &lt;/p&gt;
-  &lt;/li&gt;
-&lt;/ul&gt;
-&lt;h2 id="career-accomplishments" class="font-editorial font-bold mb-2 mt-4 [.has-inline-images_&amp;amp;]:clear-end text-lg first:mt-0 md:text-lg [hr+&amp;amp;]:mt-4"&gt;
-  Career accomplishments
-&lt;/h2&gt;
-&lt;ul class="marker:text-quiet list-disc pl-8"&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      Won the 2024 Hondo (Bridgeport) event and other Challenger/Velocity stops to punch his ticket onto UTB, where he quickly moved into the Top 30 in the world. 
-    &lt;/p&gt;
-  &lt;/li&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      Claimed his first Unleash The Beast round win at Madison Square Garden in 2026, marked 88.4 points on UTZ BesTex Smokestack on Night 2 in New York. [web:243][web:246]
-    &lt;/p&gt;
-  &lt;/li&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      Career headline stats: nearly 37% ride rate early in his UTB career, with an average score in the mid‑80s when he covers and multiple 88‑90‑point rides already on the board. [web:249]
-    &lt;/p&gt;
-  &lt;/li&gt;
-&lt;/ul&gt;
-&lt;h2 id="style-background-and-persona" class="font-editorial font-bold mb-2 mt-4 [.has-inline-images_&amp;amp;]:clear-end text-lg first:mt-0 md:text-lg [hr+&amp;amp;]:mt-4"&gt;
-  Style, background, and persona
-&lt;/h2&gt;
-&lt;ul class="marker:text-quiet list-disc pl-8"&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      Smooth, forward‑driving Brazilian style with great timing around the corner, allowing him to stay centered and build points as bulls get stronger. 
-    &lt;/p&gt;
-  &lt;/li&gt;
-&lt;/ul&gt;
-&lt;h2 id="personality-notes" class="font-editorial font-bold mb-2 mt-4 [.has-inline-images_&amp;amp;]:clear-end text-lg first:mt-0 md:text-lg [hr+&amp;amp;]:mt-4"&gt;
-  Personality notes
-&lt;/h2&gt;
-&lt;ul class="marker:text-quiet list-disc pl-8"&gt;
-  &lt;li class="py-0 my-0 prose-p:pt-0 prose-p:mb-2 prose-p:my-0 [&amp;amp;&amp;gt;p]:pt-0 [&amp;amp;&amp;gt;p]:mb-2 [&amp;amp;&amp;gt;p]:my-0"&gt;
-    &lt;p class="my-2 [&amp;amp;+p]:mt-4 [&amp;amp;_strong:has(+br)]:inline-block [&amp;amp;_strong:has(+br)]:pb-2"&gt;
-      Comes across as humble and appreciative of the opportunity, but rides with a chip‑on‑the‑shoulder intensity that fits his rapid rise from underdog to contender. 
-    &lt;/p&gt;
-  &lt;/li&gt;
-&lt;/ul&gt;</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1611,6 +983,12 @@
       <name val="Verdana"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFD6D5D4"/>
+      <name val="Helvetica Neue"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1633,7 +1011,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
@@ -1645,6 +1023,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2094,12 +1473,12 @@
       <c r="P2">
         <v>0</v>
       </c>
-      <c r="Q2">
-        <v>0</v>
+      <c r="Q2" s="9">
+        <v>45.25</v>
       </c>
       <c r="R2">
         <f>P2+Q2</f>
-        <v>0</v>
+        <v>45.25</v>
       </c>
       <c r="T2" t="s">
         <v>19</v>
@@ -2146,21 +1525,21 @@
       <c r="N3" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="O3" s="4" t="s">
-        <v>263</v>
+      <c r="O3" s="3" t="s">
+        <v>37</v>
       </c>
       <c r="P3">
         <v>0</v>
       </c>
-      <c r="Q3">
-        <v>0</v>
+      <c r="Q3" s="9">
+        <v>44</v>
       </c>
       <c r="R3">
         <f t="shared" ref="R3:R44" si="0">P3+Q3</f>
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="T3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4" spans="1:20" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -2171,10 +1550,10 @@
         <v>31</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E4" s="1"/>
       <c r="F4" s="1" t="s">
@@ -2187,28 +1566,28 @@
         <v>1</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>26</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M4" s="6"/>
       <c r="N4" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="O4" s="4" t="s">
-        <v>264</v>
+      <c r="O4" s="3" t="s">
+        <v>44</v>
       </c>
       <c r="P4">
         <v>0</v>
       </c>
-      <c r="Q4">
+      <c r="Q4" s="9">
         <v>0</v>
       </c>
       <c r="R4">
@@ -2216,7 +1595,7 @@
         <v>0</v>
       </c>
       <c r="T4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="5" spans="1:20" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -2227,10 +1606,10 @@
         <v>31</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E5" s="1"/>
       <c r="F5" s="1" t="s">
@@ -2243,23 +1622,23 @@
         <v>1</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K5" s="2" t="s">
         <v>26</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M5" s="6"/>
       <c r="N5" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="O5" s="4" t="s">
-        <v>265</v>
+      <c r="O5" s="3" t="s">
+        <v>50</v>
       </c>
       <c r="P5">
         <v>0</v>
@@ -2272,7 +1651,7 @@
         <v>0</v>
       </c>
       <c r="T5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="6" spans="1:20" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -2283,14 +1662,14 @@
         <v>31</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="E6" s="1"/>
       <c r="F6" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>23</v>
@@ -2299,10 +1678,10 @@
         <v>1</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="K6" s="2" t="s">
         <v>26</v>
@@ -2314,8 +1693,8 @@
       <c r="N6" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="O6" s="4" t="s">
-        <v>266</v>
+      <c r="O6" s="3" t="s">
+        <v>56</v>
       </c>
       <c r="P6">
         <v>0</v>
@@ -2328,7 +1707,7 @@
         <v>0</v>
       </c>
       <c r="T6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7" spans="1:20" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -2339,14 +1718,14 @@
         <v>67.349999999999994</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="E7" s="1"/>
       <c r="F7" s="1" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>23</v>
@@ -2355,10 +1734,10 @@
         <v>1</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="K7" s="2" t="s">
         <v>26</v>
@@ -2367,13 +1746,13 @@
         <v>27</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="N7" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="O7" s="4" t="s">
-        <v>267</v>
+      <c r="O7" s="3" t="s">
+        <v>63</v>
       </c>
       <c r="P7">
         <v>0</v>
@@ -2397,14 +1776,14 @@
         <v>74.319999999999993</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="E8" s="1"/>
       <c r="F8" s="1" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>23</v>
@@ -2413,23 +1792,23 @@
         <v>2</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="K8" s="2" t="s">
         <v>26</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M8" s="3"/>
       <c r="N8" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="O8" s="4" t="s">
-        <v>268</v>
+      <c r="O8" s="3" t="s">
+        <v>68</v>
       </c>
       <c r="P8">
         <v>0</v>
@@ -2442,7 +1821,7 @@
         <v>0</v>
       </c>
       <c r="T8" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9" spans="1:20" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -2453,14 +1832,14 @@
         <v>67.02</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="E9" s="1"/>
       <c r="F9" s="1" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>23</v>
@@ -2469,10 +1848,10 @@
         <v>2</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>26</v>
@@ -2481,13 +1860,13 @@
         <v>27</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="N9" s="3" t="s">
         <v>29</v>
       </c>
       <c r="O9" s="3" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="P9">
         <v>0</v>
@@ -2500,7 +1879,7 @@
         <v>0</v>
       </c>
       <c r="T9" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="10" spans="1:20" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -2511,14 +1890,14 @@
         <v>72.430000000000007</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="E10" s="1"/>
       <c r="F10" s="1" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>23</v>
@@ -2527,10 +1906,10 @@
         <v>2</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="K10" s="2" t="s">
         <v>26</v>
@@ -2539,13 +1918,13 @@
         <v>27</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="N10" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="O10" s="4" t="s">
-        <v>269</v>
+      <c r="O10" s="3" t="s">
+        <v>81</v>
       </c>
       <c r="P10">
         <v>0</v>
@@ -2569,14 +1948,14 @@
         <v>31</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="E11" s="1"/>
       <c r="F11" s="1" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="G11" s="1" t="s">
         <v>23</v>
@@ -2585,23 +1964,23 @@
         <v>2</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="K11" s="2" t="s">
         <v>26</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M11" s="6"/>
       <c r="N11" s="3" t="s">
         <v>36</v>
       </c>
       <c r="O11" s="3" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="P11">
         <v>0</v>
@@ -2614,7 +1993,7 @@
         <v>0</v>
       </c>
       <c r="T11" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="12" spans="1:20" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -2625,16 +2004,16 @@
         <v>41.22</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="E12" s="1">
         <v>10266759</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="G12" s="1" t="s">
         <v>23</v>
@@ -2643,10 +2022,10 @@
         <v>2</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="K12" s="2" t="s">
         <v>26</v>
@@ -2659,7 +2038,7 @@
         <v>36</v>
       </c>
       <c r="O12" s="3" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="P12">
         <v>0</v>
@@ -2683,16 +2062,16 @@
         <v>78.040000000000006</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="E13" s="1">
         <v>10231236</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="G13" s="1" t="s">
         <v>23</v>
@@ -2701,10 +2080,10 @@
         <v>2</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="K13" s="2" t="s">
         <v>26</v>
@@ -2713,13 +2092,13 @@
         <v>27</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="N13" s="3" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="O13" s="3" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="P13">
         <v>0</v>
@@ -2732,7 +2111,7 @@
         <v>0</v>
       </c>
       <c r="T13" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="14" spans="1:20" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -2746,13 +2125,13 @@
         <v>32</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="E14" s="1">
         <v>10259466</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G14" s="1" t="s">
         <v>23</v>
@@ -2761,23 +2140,23 @@
         <v>3</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="K14" s="2" t="s">
         <v>26</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M14" s="6"/>
       <c r="N14" s="3" t="s">
         <v>36</v>
       </c>
       <c r="O14" s="3" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="P14">
         <v>0</v>
@@ -2790,7 +2169,7 @@
         <v>0</v>
       </c>
       <c r="T14" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="15" spans="1:20" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -2801,14 +2180,14 @@
         <v>59.91</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="E15" s="1"/>
       <c r="F15" s="1" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="G15" s="1" t="s">
         <v>23</v>
@@ -2817,10 +2196,10 @@
         <v>3</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="K15" s="2" t="s">
         <v>26</v>
@@ -2829,13 +2208,13 @@
         <v>27</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="N15" s="3" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="O15" s="3" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="P15">
         <v>0</v>
@@ -2848,7 +2227,7 @@
         <v>0</v>
       </c>
       <c r="T15" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="16" spans="1:20" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -2859,16 +2238,16 @@
         <v>71.7</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="E16" s="1">
         <v>10257887</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="G16" s="1" t="s">
         <v>23</v>
@@ -2877,23 +2256,23 @@
         <v>3</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="K16" s="2" t="s">
         <v>26</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M16" s="3"/>
       <c r="N16" s="3" t="s">
         <v>36</v>
       </c>
       <c r="O16" s="3" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="P16">
         <v>0</v>
@@ -2906,7 +2285,7 @@
         <v>0</v>
       </c>
       <c r="T16" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="17" spans="1:20" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -2917,14 +2296,14 @@
         <v>77.53</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="E17" s="1"/>
       <c r="F17" s="1" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="G17" s="1" t="s">
         <v>23</v>
@@ -2933,10 +2312,10 @@
         <v>3</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="K17" s="2" t="s">
         <v>26</v>
@@ -2949,7 +2328,7 @@
         <v>36</v>
       </c>
       <c r="O17" s="3" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="P17">
         <v>0</v>
@@ -2962,7 +2341,7 @@
         <v>0</v>
       </c>
       <c r="T17" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18" spans="1:20" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -2973,14 +2352,14 @@
         <v>69.67</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="E18" s="1"/>
       <c r="F18" s="1" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="G18" s="1" t="s">
         <v>23</v>
@@ -2989,25 +2368,25 @@
         <v>3</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="K18" s="2" t="s">
         <v>26</v>
       </c>
       <c r="L18" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="N18" s="3" t="s">
         <v>29</v>
       </c>
       <c r="O18" s="3" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="P18">
         <v>0</v>
@@ -3020,7 +2399,7 @@
         <v>0</v>
       </c>
       <c r="T18" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="19" spans="1:20" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -3031,14 +2410,14 @@
         <v>77.599999999999994</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="E19" s="1"/>
       <c r="F19" s="1" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="G19" s="1" t="s">
         <v>23</v>
@@ -3047,25 +2426,25 @@
         <v>3</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="K19" s="2" t="s">
         <v>26</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="N19" s="3" t="s">
         <v>29</v>
       </c>
       <c r="O19" s="3" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="P19">
         <v>0</v>
@@ -3078,7 +2457,7 @@
         <v>0</v>
       </c>
       <c r="T19" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20" spans="1:20" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -3089,14 +2468,14 @@
         <v>31</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="E20" s="1"/>
       <c r="F20" s="1" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>23</v>
@@ -3105,10 +2484,10 @@
         <v>4</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="K20" s="2" t="s">
         <v>26</v>
@@ -3121,7 +2500,7 @@
         <v>36</v>
       </c>
       <c r="O20" s="3" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="P20">
         <v>0</v>
@@ -3145,16 +2524,16 @@
         <v>31</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="E21" s="1">
         <v>10259151</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="G21" s="1" t="s">
         <v>23</v>
@@ -3163,23 +2542,23 @@
         <v>4</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="K21" s="2" t="s">
         <v>26</v>
       </c>
       <c r="L21" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M21" s="6"/>
       <c r="N21" s="3" t="s">
         <v>36</v>
       </c>
       <c r="O21" s="3" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="P21">
         <v>0</v>
@@ -3203,14 +2582,14 @@
         <v>31</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="E22" s="1"/>
       <c r="F22" s="1" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="G22" s="1" t="s">
         <v>23</v>
@@ -3219,23 +2598,23 @@
         <v>4</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="K22" s="2" t="s">
         <v>26</v>
       </c>
       <c r="L22" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M22" s="6"/>
       <c r="N22" s="3" t="s">
         <v>36</v>
       </c>
       <c r="O22" s="3" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="P22">
         <v>0</v>
@@ -3259,16 +2638,16 @@
         <v>64.7</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="E23" s="1">
         <v>10269156</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="G23" s="1" t="s">
         <v>23</v>
@@ -3277,23 +2656,23 @@
         <v>4</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="K23" s="2" t="s">
         <v>26</v>
       </c>
       <c r="L23" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M23" s="3"/>
       <c r="N23" s="3" t="s">
         <v>36</v>
       </c>
       <c r="O23" s="3" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="P23">
         <v>0</v>
@@ -3317,14 +2696,14 @@
         <v>64.67</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="E24" s="1"/>
       <c r="F24" s="1" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="G24" s="1" t="s">
         <v>23</v>
@@ -3333,25 +2712,25 @@
         <v>4</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="K24" s="2" t="s">
         <v>26</v>
       </c>
       <c r="L24" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M24" s="3" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="N24" s="3" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="O24" s="3" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="P24">
         <v>0</v>
@@ -3364,7 +2743,7 @@
         <v>0</v>
       </c>
       <c r="T24" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="25" spans="1:20" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -3375,14 +2754,14 @@
         <v>31</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="E25" s="1"/>
       <c r="F25" s="1" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="G25" s="1" t="s">
         <v>23</v>
@@ -3391,10 +2770,10 @@
         <v>4</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="K25" s="2" t="s">
         <v>26</v>
@@ -3407,7 +2786,7 @@
         <v>36</v>
       </c>
       <c r="O25" s="3" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="P25">
         <v>0</v>
@@ -3420,7 +2799,7 @@
         <v>0</v>
       </c>
       <c r="T25" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="26" spans="1:20" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -3431,16 +2810,16 @@
         <v>56.01</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="E26" s="1">
         <v>10239182</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="G26" s="1" t="s">
         <v>23</v>
@@ -3449,10 +2828,10 @@
         <v>5</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="K26" s="2" t="s">
         <v>26</v>
@@ -3461,13 +2840,13 @@
         <v>27</v>
       </c>
       <c r="M26" s="3" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="N26" s="3" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="O26" s="3" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="P26">
         <v>0</v>
@@ -3491,16 +2870,16 @@
         <v>31</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="E27" s="1">
         <v>10262517</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="G27" s="1" t="s">
         <v>23</v>
@@ -3509,23 +2888,23 @@
         <v>5</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="K27" s="2" t="s">
         <v>26</v>
       </c>
       <c r="L27" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M27" s="6"/>
       <c r="N27" s="3" t="s">
         <v>36</v>
       </c>
       <c r="O27" s="3" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="P27">
         <v>0</v>
@@ -3538,7 +2917,7 @@
         <v>0</v>
       </c>
       <c r="T27" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="28" spans="1:20" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -3549,14 +2928,14 @@
         <v>86.05</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="E28" s="1"/>
       <c r="F28" s="1" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="G28" s="1" t="s">
         <v>23</v>
@@ -3565,25 +2944,25 @@
         <v>5</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="K28" s="2" t="s">
         <v>26</v>
       </c>
       <c r="L28" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M28" s="3" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="N28" s="3" t="s">
         <v>29</v>
       </c>
       <c r="O28" s="3" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="P28">
         <v>0</v>
@@ -3596,7 +2975,7 @@
         <v>0</v>
       </c>
       <c r="T28" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="29" spans="1:20" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -3607,14 +2986,14 @@
         <v>70.64</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="E29" s="1"/>
       <c r="F29" s="1" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="G29" s="1" t="s">
         <v>23</v>
@@ -3623,10 +3002,10 @@
         <v>5</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="K29" s="2" t="s">
         <v>26</v>
@@ -3635,13 +3014,13 @@
         <v>27</v>
       </c>
       <c r="M29" s="3" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="N29" s="3" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="O29" s="3" t="s">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="P29">
         <v>0</v>
@@ -3654,7 +3033,7 @@
         <v>0</v>
       </c>
       <c r="T29" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="30" spans="1:20" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -3665,14 +3044,14 @@
         <v>31</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="E30" s="1"/>
       <c r="F30" s="1" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="G30" s="1" t="s">
         <v>23</v>
@@ -3681,10 +3060,10 @@
         <v>5</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="K30" s="2" t="s">
         <v>26</v>
@@ -3697,7 +3076,7 @@
         <v>36</v>
       </c>
       <c r="O30" s="3" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="P30">
         <v>0</v>
@@ -3710,7 +3089,7 @@
         <v>0</v>
       </c>
       <c r="T30" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="31" spans="1:20" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -3721,14 +3100,14 @@
         <v>31</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="E31" s="1"/>
       <c r="F31" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G31" s="1" t="s">
         <v>23</v>
@@ -3737,10 +3116,10 @@
         <v>6</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="K31" s="2" t="s">
         <v>26</v>
@@ -3753,7 +3132,7 @@
         <v>36</v>
       </c>
       <c r="O31" s="3" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="P31">
         <v>0</v>
@@ -3766,7 +3145,7 @@
         <v>0</v>
       </c>
       <c r="T31" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="32" spans="1:20" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -3777,16 +3156,16 @@
         <v>31</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="E32" s="1">
         <v>10266753</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="G32" s="1" t="s">
         <v>23</v>
@@ -3795,23 +3174,23 @@
         <v>6</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="K32" s="2" t="s">
         <v>26</v>
       </c>
       <c r="L32" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M32" s="6"/>
       <c r="N32" s="3" t="s">
         <v>36</v>
       </c>
       <c r="O32" s="3" t="s">
-        <v>197</v>
+        <v>204</v>
       </c>
       <c r="P32">
         <v>0</v>
@@ -3835,16 +3214,16 @@
         <v>89.52</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="E33" s="1">
         <v>10203017</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="G33" s="1" t="s">
         <v>23</v>
@@ -3853,25 +3232,25 @@
         <v>6</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="K33" s="2" t="s">
         <v>26</v>
       </c>
       <c r="L33" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M33" s="3" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="N33" s="3" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="O33" s="3" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="P33">
         <v>0</v>
@@ -3884,7 +3263,7 @@
         <v>0</v>
       </c>
       <c r="T33" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="34" spans="1:20" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -3895,10 +3274,10 @@
         <v>74.709999999999994</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="E34" s="1"/>
       <c r="F34" s="1" t="s">
@@ -3911,25 +3290,25 @@
         <v>6</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="K34" s="2" t="s">
         <v>26</v>
       </c>
       <c r="L34" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M34" s="3" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="N34" s="3" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="O34" s="3" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="P34">
         <v>0</v>
@@ -3942,7 +3321,7 @@
         <v>0</v>
       </c>
       <c r="T34" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="35" spans="1:20" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -3953,14 +3332,14 @@
         <v>31</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="E35" s="1"/>
       <c r="F35" s="1" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="G35" s="1" t="s">
         <v>23</v>
@@ -3969,25 +3348,25 @@
         <v>7</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="J35" s="1" t="s">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="K35" s="2" t="s">
         <v>26</v>
       </c>
       <c r="L35" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M35" s="3" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="N35" s="3" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="O35" s="3" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="P35">
         <v>0</v>
@@ -4000,7 +3379,7 @@
         <v>0</v>
       </c>
       <c r="T35" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="36" spans="1:20" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -4011,14 +3390,14 @@
         <v>31</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="E36" s="1"/>
       <c r="F36" s="1" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="G36" s="1" t="s">
         <v>23</v>
@@ -4027,23 +3406,23 @@
         <v>7</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="J36" s="1" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="K36" s="2" t="s">
         <v>26</v>
       </c>
       <c r="L36" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M36" s="6"/>
       <c r="N36" s="3" t="s">
         <v>36</v>
       </c>
       <c r="O36" s="3" t="s">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="P36">
         <v>0</v>
@@ -4056,7 +3435,7 @@
         <v>0</v>
       </c>
       <c r="T36" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="37" spans="1:20" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -4067,16 +3446,16 @@
         <v>81.430000000000007</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="E37" s="1">
         <v>10243244</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="G37" s="1" t="s">
         <v>23</v>
@@ -4085,25 +3464,25 @@
         <v>8</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="J37" s="1" t="s">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="K37" s="2" t="s">
         <v>26</v>
       </c>
       <c r="L37" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M37" s="3" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="N37" s="3" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="O37" s="3" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="P37">
         <v>0</v>
@@ -4116,7 +3495,7 @@
         <v>0</v>
       </c>
       <c r="T37" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="38" spans="1:20" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -4127,16 +3506,16 @@
         <v>31</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="E38" s="1">
         <v>10268368</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="G38" s="1" t="s">
         <v>23</v>
@@ -4145,23 +3524,23 @@
         <v>8</v>
       </c>
       <c r="I38" s="1" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="J38" s="1" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="K38" s="2" t="s">
         <v>26</v>
       </c>
       <c r="L38" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M38" s="6"/>
       <c r="N38" s="3" t="s">
         <v>36</v>
       </c>
       <c r="O38" s="3" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="P38">
         <v>0</v>
@@ -4174,7 +3553,7 @@
         <v>0</v>
       </c>
       <c r="T38" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="39" spans="1:20" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -4185,16 +3564,16 @@
         <v>57.96</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="E39" s="1">
         <v>10239944</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="G39" s="1" t="s">
         <v>23</v>
@@ -4203,10 +3582,10 @@
         <v>8</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="J39" s="1" t="s">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="K39" s="2" t="s">
         <v>26</v>
@@ -4215,13 +3594,13 @@
         <v>27</v>
       </c>
       <c r="M39" s="3" t="s">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="N39" s="3" t="s">
         <v>29</v>
       </c>
       <c r="O39" s="3" t="s">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="P39">
         <v>0</v>
@@ -4234,7 +3613,7 @@
         <v>0</v>
       </c>
       <c r="T39" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="40" spans="1:20" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -4245,14 +3624,14 @@
         <v>70.33</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="E40" s="1"/>
       <c r="F40" s="1" t="s">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="G40" s="1" t="s">
         <v>23</v>
@@ -4261,10 +3640,10 @@
         <v>8</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="J40" s="1" t="s">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="K40" s="2" t="s">
         <v>26</v>
@@ -4277,7 +3656,7 @@
         <v>36</v>
       </c>
       <c r="O40" s="3" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="P40">
         <v>0</v>
@@ -4301,16 +3680,16 @@
         <v>86.7</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="E41" s="1">
         <v>10222050</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="G41" s="1" t="s">
         <v>23</v>
@@ -4319,10 +3698,10 @@
         <v>9</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="J41" s="1" t="s">
-        <v>244</v>
+        <v>251</v>
       </c>
       <c r="K41" s="2" t="s">
         <v>26</v>
@@ -4331,13 +3710,13 @@
         <v>27</v>
       </c>
       <c r="M41" s="3" t="s">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="N41" s="3" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="O41" s="3" t="s">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="P41">
         <v>0</v>
@@ -4350,7 +3729,7 @@
         <v>0</v>
       </c>
       <c r="T41" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="42" spans="1:20" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -4364,13 +3743,13 @@
         <v>32</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>247</v>
+        <v>254</v>
       </c>
       <c r="E42" s="1">
         <v>10274756</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G42" s="1" t="s">
         <v>23</v>
@@ -4379,10 +3758,10 @@
         <v>9</v>
       </c>
       <c r="I42" s="1" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="J42" s="1" t="s">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="K42" s="2" t="s">
         <v>26</v>
@@ -4395,7 +3774,7 @@
         <v>36</v>
       </c>
       <c r="O42" s="3" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="P42">
         <v>0</v>
@@ -4408,7 +3787,7 @@
         <v>0</v>
       </c>
       <c r="T42" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="43" spans="1:20" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -4419,14 +3798,14 @@
         <v>52.8</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="E43" s="1"/>
       <c r="F43" s="1" t="s">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="G43" s="1" t="s">
         <v>23</v>
@@ -4435,25 +3814,25 @@
         <v>9</v>
       </c>
       <c r="I43" s="1" t="s">
-        <v>253</v>
+        <v>260</v>
       </c>
       <c r="J43" s="1" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="K43" s="2" t="s">
         <v>26</v>
       </c>
       <c r="L43" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M43" s="3" t="s">
-        <v>255</v>
+        <v>262</v>
       </c>
       <c r="N43" s="3" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="O43" s="3" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="P43">
         <v>0</v>
@@ -4477,16 +3856,16 @@
         <v>65.78</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>258</v>
+        <v>265</v>
       </c>
       <c r="E44" s="1">
         <v>10258756</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="G44" s="1" t="s">
         <v>23</v>
@@ -4495,10 +3874,10 @@
         <v>9</v>
       </c>
       <c r="I44" s="1" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="J44" s="1" t="s">
-        <v>260</v>
+        <v>267</v>
       </c>
       <c r="K44" s="2" t="s">
         <v>26</v>
@@ -4507,13 +3886,13 @@
         <v>27</v>
       </c>
       <c r="M44" s="3" t="s">
-        <v>261</v>
+        <v>268</v>
       </c>
       <c r="N44" s="3" t="s">
         <v>29</v>
       </c>
       <c r="O44" s="3" t="s">
-        <v>262</v>
+        <v>269</v>
       </c>
       <c r="P44">
         <v>0</v>

--- a/data/pbr_matchups_full.xlsx
+++ b/data/pbr_matchups_full.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cameronyoung/Desktop/rankratings:/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{984531D3-2181-B341-9799-2E07C7255540}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1289698-5506-7F42-9EE9-B423F85A4FC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="13520" yWindow="740" windowWidth="16720" windowHeight="18900" xr2:uid="{63502F5A-9950-074D-B0A2-89EF4471630B}"/>
   </bookViews>
@@ -1474,11 +1474,11 @@
         <v>0</v>
       </c>
       <c r="Q2" s="9">
-        <v>45.25</v>
+        <v>0</v>
       </c>
       <c r="R2">
         <f>P2+Q2</f>
-        <v>45.25</v>
+        <v>0</v>
       </c>
       <c r="T2" t="s">
         <v>19</v>
@@ -1532,11 +1532,11 @@
         <v>0</v>
       </c>
       <c r="Q3" s="9">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="R3">
         <f t="shared" ref="R3:R44" si="0">P3+Q3</f>
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="T3" t="s">
         <v>38</v>

--- a/data/pbr_matchups_full.xlsx
+++ b/data/pbr_matchups_full.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cameronyoung/Desktop/rankratings:/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1289698-5506-7F42-9EE9-B423F85A4FC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98087A87-7FB5-5349-BADE-DB3E307B18F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13520" yWindow="740" windowWidth="16720" windowHeight="18900" xr2:uid="{63502F5A-9950-074D-B0A2-89EF4471630B}"/>
+    <workbookView xWindow="20240" yWindow="740" windowWidth="10000" windowHeight="18900" xr2:uid="{63502F5A-9950-074D-B0A2-89EF4471630B}"/>
   </bookViews>
   <sheets>
     <sheet name="Billings Day 1" sheetId="1" r:id="rId1"/>
@@ -984,9 +984,9 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color rgb="FFD6D5D4"/>
-      <name val="Helvetica Neue"/>
+      <sz val="16"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -1471,14 +1471,13 @@
         <v>30</v>
       </c>
       <c r="P2">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="9">
-        <v>0</v>
+        <v>43.1</v>
+      </c>
+      <c r="Q2">
+        <v>45.4</v>
       </c>
       <c r="R2">
-        <f>P2+Q2</f>
-        <v>0</v>
+        <v>88.5</v>
       </c>
       <c r="T2" t="s">
         <v>19</v>
@@ -1529,14 +1528,14 @@
         <v>37</v>
       </c>
       <c r="P3">
-        <v>0</v>
-      </c>
-      <c r="Q3" s="9">
-        <v>0</v>
+        <v>42.7</v>
+      </c>
+      <c r="Q3">
+        <v>-3.69</v>
       </c>
       <c r="R3">
-        <f t="shared" ref="R3:R44" si="0">P3+Q3</f>
-        <v>0</v>
+        <f>P3+Q3</f>
+        <v>39.010000000000005</v>
       </c>
       <c r="T3" t="s">
         <v>38</v>
@@ -1585,14 +1584,14 @@
         <v>44</v>
       </c>
       <c r="P4">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="9">
-        <v>0</v>
+        <v>41.7</v>
+      </c>
+      <c r="Q4">
+        <v>41.45</v>
       </c>
       <c r="R4">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f>P4+Q4</f>
+        <v>83.15</v>
       </c>
       <c r="T4" t="s">
         <v>45</v>
@@ -1641,14 +1640,14 @@
         <v>50</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>44.2</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>-3.07</v>
       </c>
       <c r="R5">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f>P5+Q5</f>
+        <v>41.13</v>
       </c>
       <c r="T5" t="s">
         <v>45</v>
@@ -1697,15 +1696,12 @@
         <v>56</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>44.2</v>
       </c>
       <c r="Q6">
-        <v>0</v>
-      </c>
-      <c r="R6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+        <v>-1.36</v>
+      </c>
+      <c r="R6" s="9"/>
       <c r="T6" t="s">
         <v>38</v>
       </c>
@@ -1761,7 +1757,7 @@
         <v>0</v>
       </c>
       <c r="R7">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="R6:R44" si="0">P7+Q7</f>
         <v>0</v>
       </c>
       <c r="T7" t="s">

--- a/data/pbr_matchups_full.xlsx
+++ b/data/pbr_matchups_full.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cameronyoung/Desktop/rankratings:/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98087A87-7FB5-5349-BADE-DB3E307B18F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABE56B78-3C48-EB48-AE88-568ED71A0D13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20240" yWindow="740" windowWidth="10000" windowHeight="18900" xr2:uid="{63502F5A-9950-074D-B0A2-89EF4471630B}"/>
   </bookViews>
@@ -930,7 +930,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -983,12 +983,6 @@
       <name val="Verdana"/>
       <family val="2"/>
     </font>
-    <font>
-      <sz val="16"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1011,7 +1005,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
@@ -1023,7 +1017,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1388,25 +1381,25 @@
         <v>9</v>
       </c>
       <c r="I1" t="s">
+        <v>11</v>
+      </c>
+      <c r="J1" t="s">
+        <v>12</v>
+      </c>
+      <c r="K1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1" t="s">
+        <v>1</v>
+      </c>
+      <c r="M1" t="s">
+        <v>14</v>
+      </c>
+      <c r="N1" t="s">
+        <v>15</v>
+      </c>
+      <c r="O1" t="s">
         <v>10</v>
-      </c>
-      <c r="J1" t="s">
-        <v>11</v>
-      </c>
-      <c r="K1" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1" t="s">
-        <v>13</v>
-      </c>
-      <c r="M1" t="s">
-        <v>1</v>
-      </c>
-      <c r="N1" t="s">
-        <v>14</v>
-      </c>
-      <c r="O1" t="s">
-        <v>15</v>
       </c>
       <c r="P1" t="s">
         <v>16</v>
@@ -1450,25 +1443,25 @@
         <v>1</v>
       </c>
       <c r="I2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="N2" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="O2" s="1" t="s">
         <v>24</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="L2" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="N2" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="O2" s="4" t="s">
-        <v>30</v>
       </c>
       <c r="P2">
         <v>43.1</v>
@@ -1509,23 +1502,23 @@
         <v>1</v>
       </c>
       <c r="I3" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="L3" s="6"/>
+      <c r="M3" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="O3" s="1" t="s">
         <v>34</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="L3" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="M3" s="6"/>
-      <c r="N3" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="O3" s="3" t="s">
-        <v>37</v>
       </c>
       <c r="P3">
         <v>42.7</v>
@@ -1565,23 +1558,23 @@
         <v>1</v>
       </c>
       <c r="I4" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="L4" s="6"/>
+      <c r="M4" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="N4" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="O4" s="1" t="s">
         <v>41</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="L4" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="M4" s="6"/>
-      <c r="N4" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="O4" s="3" t="s">
-        <v>44</v>
       </c>
       <c r="P4">
         <v>41.7</v>
@@ -1621,23 +1614,23 @@
         <v>1</v>
       </c>
       <c r="I5" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="L5" s="6"/>
+      <c r="M5" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="N5" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="O5" s="1" t="s">
         <v>48</v>
-      </c>
-      <c r="J5" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="L5" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="M5" s="6"/>
-      <c r="N5" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="O5" s="3" t="s">
-        <v>50</v>
       </c>
       <c r="P5">
         <v>44.2</v>
@@ -1677,23 +1670,23 @@
         <v>1</v>
       </c>
       <c r="I6" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="L6" s="6"/>
+      <c r="M6" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="N6" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="O6" s="1" t="s">
         <v>54</v>
-      </c>
-      <c r="J6" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="L6" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="M6" s="6"/>
-      <c r="N6" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="O6" s="3" t="s">
-        <v>56</v>
       </c>
       <c r="P6">
         <v>44.2</v>
@@ -1701,7 +1694,9 @@
       <c r="Q6">
         <v>-1.36</v>
       </c>
-      <c r="R6" s="9"/>
+      <c r="R6">
+        <v>44.2</v>
+      </c>
       <c r="T6" t="s">
         <v>38</v>
       </c>
@@ -1730,26 +1725,26 @@
         <v>1</v>
       </c>
       <c r="I7" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="L7" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="M7" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="N7" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="O7" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="J7" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="L7" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="M7" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="N7" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="O7" s="3" t="s">
-        <v>63</v>
-      </c>
       <c r="P7">
         <v>0</v>
       </c>
@@ -1757,7 +1752,7 @@
         <v>0</v>
       </c>
       <c r="R7">
-        <f t="shared" ref="R6:R44" si="0">P7+Q7</f>
+        <f t="shared" ref="R7:R44" si="0">P7+Q7</f>
         <v>0</v>
       </c>
       <c r="T7" t="s">
@@ -1788,23 +1783,23 @@
         <v>2</v>
       </c>
       <c r="I8" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="L8" s="3"/>
+      <c r="M8" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="N8" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="O8" s="1" t="s">
         <v>66</v>
-      </c>
-      <c r="J8" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="L8" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="M8" s="3"/>
-      <c r="N8" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="O8" s="3" t="s">
-        <v>68</v>
       </c>
       <c r="P8">
         <v>0</v>
@@ -1844,25 +1839,25 @@
         <v>2</v>
       </c>
       <c r="I9" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="L9" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="N9" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="O9" s="1" t="s">
         <v>72</v>
-      </c>
-      <c r="J9" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="L9" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="M9" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="N9" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="O9" s="3" t="s">
-        <v>75</v>
       </c>
       <c r="P9">
         <v>0</v>
@@ -1902,25 +1897,25 @@
         <v>2</v>
       </c>
       <c r="I10" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="L10" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="M10" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="N10" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="O10" s="1" t="s">
         <v>78</v>
-      </c>
-      <c r="J10" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="K10" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="L10" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="M10" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="N10" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="O10" s="3" t="s">
-        <v>81</v>
       </c>
       <c r="P10">
         <v>0</v>
@@ -1960,23 +1955,23 @@
         <v>2</v>
       </c>
       <c r="I11" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K11" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="L11" s="6"/>
+      <c r="M11" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="N11" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="O11" s="1" t="s">
         <v>85</v>
-      </c>
-      <c r="J11" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="K11" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="L11" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="M11" s="6"/>
-      <c r="N11" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="O11" s="3" t="s">
-        <v>87</v>
       </c>
       <c r="P11">
         <v>0</v>
@@ -2018,23 +2013,23 @@
         <v>2</v>
       </c>
       <c r="I12" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="L12" s="3"/>
+      <c r="M12" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="N12" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="O12" s="1" t="s">
         <v>90</v>
-      </c>
-      <c r="J12" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="K12" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="L12" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="M12" s="3"/>
-      <c r="N12" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="O12" s="3" t="s">
-        <v>92</v>
       </c>
       <c r="P12">
         <v>0</v>
@@ -2076,25 +2071,25 @@
         <v>2</v>
       </c>
       <c r="I13" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K13" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="L13" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="M13" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="N13" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="O13" s="1" t="s">
         <v>96</v>
-      </c>
-      <c r="J13" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="K13" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="L13" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="M13" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="N13" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="O13" s="3" t="s">
-        <v>100</v>
       </c>
       <c r="P13">
         <v>0</v>
@@ -2136,23 +2131,23 @@
         <v>3</v>
       </c>
       <c r="I14" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="L14" s="6"/>
+      <c r="M14" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="N14" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="O14" s="1" t="s">
         <v>102</v>
-      </c>
-      <c r="J14" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="K14" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="M14" s="6"/>
-      <c r="N14" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="O14" s="3" t="s">
-        <v>104</v>
       </c>
       <c r="P14">
         <v>0</v>
@@ -2192,25 +2187,25 @@
         <v>3</v>
       </c>
       <c r="I15" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="L15" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="M15" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="N15" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="O15" s="1" t="s">
         <v>108</v>
-      </c>
-      <c r="J15" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="K15" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="L15" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="M15" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="N15" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="O15" s="3" t="s">
-        <v>111</v>
       </c>
       <c r="P15">
         <v>0</v>
@@ -2252,23 +2247,23 @@
         <v>3</v>
       </c>
       <c r="I16" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K16" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="L16" s="3"/>
+      <c r="M16" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="N16" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="O16" s="1" t="s">
         <v>114</v>
-      </c>
-      <c r="J16" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="K16" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="L16" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="M16" s="3"/>
-      <c r="N16" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="O16" s="3" t="s">
-        <v>116</v>
       </c>
       <c r="P16">
         <v>0</v>
@@ -2308,23 +2303,23 @@
         <v>3</v>
       </c>
       <c r="I17" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="L17" s="3"/>
+      <c r="M17" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="N17" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="O17" s="1" t="s">
         <v>120</v>
-      </c>
-      <c r="J17" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="K17" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="L17" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="M17" s="3"/>
-      <c r="N17" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="O17" s="3" t="s">
-        <v>122</v>
       </c>
       <c r="P17">
         <v>0</v>
@@ -2364,25 +2359,25 @@
         <v>3</v>
       </c>
       <c r="I18" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="L18" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="M18" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="N18" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="O18" s="1" t="s">
         <v>125</v>
-      </c>
-      <c r="J18" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="K18" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="L18" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="M18" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="N18" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="O18" s="3" t="s">
-        <v>128</v>
       </c>
       <c r="P18">
         <v>0</v>
@@ -2422,25 +2417,25 @@
         <v>3</v>
       </c>
       <c r="I19" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K19" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="L19" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="M19" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="N19" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="O19" s="1" t="s">
         <v>131</v>
-      </c>
-      <c r="J19" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="K19" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="L19" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="M19" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="N19" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="O19" s="3" t="s">
-        <v>134</v>
       </c>
       <c r="P19">
         <v>0</v>
@@ -2480,23 +2475,23 @@
         <v>4</v>
       </c>
       <c r="I20" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="L20" s="6"/>
+      <c r="M20" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="N20" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="O20" s="1" t="s">
         <v>136</v>
-      </c>
-      <c r="J20" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="K20" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="L20" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="M20" s="6"/>
-      <c r="N20" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="O20" s="3" t="s">
-        <v>138</v>
       </c>
       <c r="P20">
         <v>0</v>
@@ -2538,23 +2533,23 @@
         <v>4</v>
       </c>
       <c r="I21" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K21" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="L21" s="6"/>
+      <c r="M21" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="N21" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="O21" s="1" t="s">
         <v>141</v>
-      </c>
-      <c r="J21" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="K21" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="L21" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="M21" s="6"/>
-      <c r="N21" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="O21" s="3" t="s">
-        <v>143</v>
       </c>
       <c r="P21">
         <v>0</v>
@@ -2594,23 +2589,23 @@
         <v>4</v>
       </c>
       <c r="I22" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="L22" s="6"/>
+      <c r="M22" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="N22" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="O22" s="1" t="s">
         <v>146</v>
-      </c>
-      <c r="J22" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="K22" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="L22" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="M22" s="6"/>
-      <c r="N22" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="O22" s="3" t="s">
-        <v>148</v>
       </c>
       <c r="P22">
         <v>0</v>
@@ -2652,23 +2647,23 @@
         <v>4</v>
       </c>
       <c r="I23" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K23" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="L23" s="3"/>
+      <c r="M23" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="N23" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="O23" s="1" t="s">
         <v>151</v>
-      </c>
-      <c r="J23" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="K23" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="L23" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="M23" s="3"/>
-      <c r="N23" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="O23" s="3" t="s">
-        <v>153</v>
       </c>
       <c r="P23">
         <v>0</v>
@@ -2708,25 +2703,25 @@
         <v>4</v>
       </c>
       <c r="I24" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K24" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="L24" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="M24" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="N24" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="O24" s="1" t="s">
         <v>157</v>
-      </c>
-      <c r="J24" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="K24" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="L24" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="M24" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="N24" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="O24" s="3" t="s">
-        <v>160</v>
       </c>
       <c r="P24">
         <v>0</v>
@@ -2766,23 +2761,23 @@
         <v>4</v>
       </c>
       <c r="I25" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K25" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="L25" s="6"/>
+      <c r="M25" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="N25" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="O25" s="1" t="s">
         <v>163</v>
-      </c>
-      <c r="J25" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="K25" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="L25" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="M25" s="6"/>
-      <c r="N25" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="O25" s="3" t="s">
-        <v>165</v>
       </c>
       <c r="P25">
         <v>0</v>
@@ -2824,25 +2819,25 @@
         <v>5</v>
       </c>
       <c r="I26" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K26" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="L26" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="M26" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="N26" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="O26" s="1" t="s">
         <v>169</v>
-      </c>
-      <c r="J26" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="K26" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="L26" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="M26" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="N26" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="O26" s="3" t="s">
-        <v>172</v>
       </c>
       <c r="P26">
         <v>0</v>
@@ -2884,23 +2879,23 @@
         <v>5</v>
       </c>
       <c r="I27" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K27" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="L27" s="6"/>
+      <c r="M27" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="N27" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="O27" s="1" t="s">
         <v>174</v>
-      </c>
-      <c r="J27" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="K27" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="L27" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="M27" s="6"/>
-      <c r="N27" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="O27" s="3" t="s">
-        <v>176</v>
       </c>
       <c r="P27">
         <v>0</v>
@@ -2940,25 +2935,25 @@
         <v>5</v>
       </c>
       <c r="I28" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K28" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="L28" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="M28" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="N28" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="O28" s="1" t="s">
         <v>180</v>
-      </c>
-      <c r="J28" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="K28" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="L28" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="M28" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="N28" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="O28" s="3" t="s">
-        <v>183</v>
       </c>
       <c r="P28">
         <v>0</v>
@@ -2998,25 +2993,25 @@
         <v>5</v>
       </c>
       <c r="I29" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="J29" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K29" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="L29" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="M29" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="N29" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="O29" s="1" t="s">
         <v>187</v>
-      </c>
-      <c r="J29" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="K29" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="L29" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="M29" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="N29" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="O29" s="3" t="s">
-        <v>190</v>
       </c>
       <c r="P29">
         <v>0</v>
@@ -3056,23 +3051,23 @@
         <v>5</v>
       </c>
       <c r="I30" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="J30" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K30" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="L30" s="6"/>
+      <c r="M30" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="N30" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="O30" s="1" t="s">
         <v>193</v>
-      </c>
-      <c r="J30" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="K30" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="L30" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="M30" s="6"/>
-      <c r="N30" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="O30" s="3" t="s">
-        <v>195</v>
       </c>
       <c r="P30">
         <v>0</v>
@@ -3112,23 +3107,23 @@
         <v>6</v>
       </c>
       <c r="I31" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="J31" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K31" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="L31" s="6"/>
+      <c r="M31" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="N31" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="O31" s="1" t="s">
         <v>197</v>
-      </c>
-      <c r="J31" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="K31" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="L31" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="M31" s="6"/>
-      <c r="N31" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="O31" s="3" t="s">
-        <v>199</v>
       </c>
       <c r="P31">
         <v>0</v>
@@ -3170,23 +3165,23 @@
         <v>6</v>
       </c>
       <c r="I32" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="J32" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K32" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="L32" s="6"/>
+      <c r="M32" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="N32" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="O32" s="1" t="s">
         <v>202</v>
-      </c>
-      <c r="J32" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="K32" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="L32" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="M32" s="6"/>
-      <c r="N32" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="O32" s="3" t="s">
-        <v>204</v>
       </c>
       <c r="P32">
         <v>0</v>
@@ -3228,25 +3223,25 @@
         <v>6</v>
       </c>
       <c r="I33" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="J33" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K33" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="L33" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="M33" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="N33" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="O33" s="1" t="s">
         <v>207</v>
-      </c>
-      <c r="J33" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="K33" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="L33" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="M33" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="N33" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="O33" s="3" t="s">
-        <v>210</v>
       </c>
       <c r="P33">
         <v>0</v>
@@ -3286,25 +3281,25 @@
         <v>6</v>
       </c>
       <c r="I34" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="J34" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K34" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="L34" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="M34" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="N34" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="O34" s="1" t="s">
         <v>213</v>
-      </c>
-      <c r="J34" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="K34" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="L34" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="M34" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="N34" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="O34" s="3" t="s">
-        <v>216</v>
       </c>
       <c r="P34">
         <v>0</v>
@@ -3344,25 +3339,25 @@
         <v>7</v>
       </c>
       <c r="I35" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="J35" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K35" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="L35" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="M35" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="N35" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="O35" s="1" t="s">
         <v>219</v>
-      </c>
-      <c r="J35" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="K35" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="L35" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="M35" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="N35" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="O35" s="3" t="s">
-        <v>216</v>
       </c>
       <c r="P35">
         <v>0</v>
@@ -3402,23 +3397,23 @@
         <v>7</v>
       </c>
       <c r="I36" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="J36" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K36" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="L36" s="6"/>
+      <c r="M36" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="N36" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="O36" s="1" t="s">
         <v>222</v>
-      </c>
-      <c r="J36" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="K36" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="L36" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="M36" s="6"/>
-      <c r="N36" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="O36" s="3" t="s">
-        <v>224</v>
       </c>
       <c r="P36">
         <v>0</v>
@@ -3460,25 +3455,25 @@
         <v>8</v>
       </c>
       <c r="I37" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="J37" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K37" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="L37" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="M37" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="N37" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="O37" s="1" t="s">
         <v>227</v>
-      </c>
-      <c r="J37" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="K37" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="L37" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="M37" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="N37" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="O37" s="3" t="s">
-        <v>230</v>
       </c>
       <c r="P37">
         <v>0</v>
@@ -3520,23 +3515,23 @@
         <v>8</v>
       </c>
       <c r="I38" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="J38" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K38" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="L38" s="6"/>
+      <c r="M38" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="N38" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="O38" s="1" t="s">
         <v>232</v>
-      </c>
-      <c r="J38" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="K38" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="L38" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="M38" s="6"/>
-      <c r="N38" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="O38" s="3" t="s">
-        <v>234</v>
       </c>
       <c r="P38">
         <v>0</v>
@@ -3578,25 +3573,25 @@
         <v>8</v>
       </c>
       <c r="I39" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="J39" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K39" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="L39" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="M39" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="N39" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="O39" s="1" t="s">
         <v>238</v>
-      </c>
-      <c r="J39" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="K39" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="L39" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="M39" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="N39" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="O39" s="3" t="s">
-        <v>241</v>
       </c>
       <c r="P39">
         <v>0</v>
@@ -3636,23 +3631,23 @@
         <v>8</v>
       </c>
       <c r="I40" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="J40" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K40" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="L40" s="3"/>
+      <c r="M40" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="N40" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="O40" s="1" t="s">
         <v>244</v>
-      </c>
-      <c r="J40" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="K40" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="L40" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="M40" s="3"/>
-      <c r="N40" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="O40" s="3" t="s">
-        <v>246</v>
       </c>
       <c r="P40">
         <v>0</v>
@@ -3694,25 +3689,25 @@
         <v>9</v>
       </c>
       <c r="I41" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="J41" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K41" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="L41" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="M41" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="N41" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="O41" s="1" t="s">
         <v>250</v>
-      </c>
-      <c r="J41" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="K41" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="L41" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="M41" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="N41" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="O41" s="3" t="s">
-        <v>253</v>
       </c>
       <c r="P41">
         <v>0</v>
@@ -3754,23 +3749,23 @@
         <v>9</v>
       </c>
       <c r="I42" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="J42" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K42" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="L42" s="6"/>
+      <c r="M42" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="N42" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="O42" s="1" t="s">
         <v>255</v>
-      </c>
-      <c r="J42" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="K42" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="L42" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="M42" s="6"/>
-      <c r="N42" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="O42" s="3" t="s">
-        <v>257</v>
       </c>
       <c r="P42">
         <v>0</v>
@@ -3810,25 +3805,25 @@
         <v>9</v>
       </c>
       <c r="I43" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="J43" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K43" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="L43" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="M43" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="N43" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="O43" s="1" t="s">
         <v>260</v>
-      </c>
-      <c r="J43" s="1" t="s">
-        <v>261</v>
-      </c>
-      <c r="K43" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="L43" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="M43" s="3" t="s">
-        <v>262</v>
-      </c>
-      <c r="N43" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="O43" s="3" t="s">
-        <v>263</v>
       </c>
       <c r="P43">
         <v>0</v>
@@ -3870,25 +3865,25 @@
         <v>9</v>
       </c>
       <c r="I44" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="J44" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K44" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="L44" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="M44" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="N44" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="O44" s="1" t="s">
         <v>266</v>
-      </c>
-      <c r="J44" s="1" t="s">
-        <v>267</v>
-      </c>
-      <c r="K44" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="L44" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="M44" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="N44" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="O44" s="3" t="s">
-        <v>269</v>
       </c>
       <c r="P44">
         <v>0</v>
@@ -3906,49 +3901,49 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="K2" r:id="rId1" display="https://probullstats.com/loggers/matchup.php?bull=52839&amp;guy=Jess+Lockwood" xr:uid="{F970B9C6-9BCD-5E46-AA4F-71F0EACB3924}"/>
-    <hyperlink ref="K3" r:id="rId2" display="https://probullstats.com/loggers/matchup.php?bull=56214&amp;guy=Kase+Hitt" xr:uid="{F506C8E8-40E1-964F-B9DA-D7FE929F019A}"/>
-    <hyperlink ref="K4" r:id="rId3" display="https://probullstats.com/loggers/matchup.php?bull=56035&amp;guy=Julio+Cesar+Marques" xr:uid="{053518A0-6349-4744-95DE-41EFA4861A41}"/>
-    <hyperlink ref="K5" r:id="rId4" display="https://probullstats.com/loggers/matchup.php?bull=55806&amp;guy=Kaiden+Loud" xr:uid="{8C7DDD88-3D1A-C94E-923A-DA0DBC8146AD}"/>
-    <hyperlink ref="K6" r:id="rId5" display="https://probullstats.com/loggers/matchup.php?bull=56540&amp;guy=Mauricio+Gulla+Moreira" xr:uid="{FD7D6547-2C8C-2840-A167-738CAB9A832C}"/>
-    <hyperlink ref="K7" r:id="rId6" display="https://probullstats.com/loggers/matchup.php?bull=48948&amp;guy=Bob+Mitchell" xr:uid="{F0059777-5DFE-F946-AC6B-1EDDB6C3D6AF}"/>
-    <hyperlink ref="K8" r:id="rId7" display="https://probullstats.com/loggers/matchup.php?bull=54839&amp;guy=Keyshawn+Whitehorse" xr:uid="{B26D7B4B-123C-0149-ADFC-45AB02B58CFD}"/>
-    <hyperlink ref="K9" r:id="rId8" display="https://probullstats.com/loggers/matchup.php?bull=53968&amp;guy=Manoelito+de+Souza+Junior" xr:uid="{569F14A1-459F-2244-90DC-CB697A4D3339}"/>
-    <hyperlink ref="K10" r:id="rId9" display="https://probullstats.com/loggers/matchup.php?bull=53970&amp;guy=Leandro+Zampollo" xr:uid="{1F2BFB5A-99B7-9846-A2AC-C3775B994DBD}"/>
-    <hyperlink ref="K11" r:id="rId10" display="https://probullstats.com/loggers/matchup.php?bull=56046&amp;guy=Paulo+Eduardo+Rossetto" xr:uid="{6DB243E9-BFED-B842-B9FC-F6B37C950BA1}"/>
-    <hyperlink ref="K12" r:id="rId11" display="https://probullstats.com/loggers/matchup.php?bull=54711&amp;guy=Alex+Cerqueira" xr:uid="{6008F3BA-B37C-924B-8487-8673B80C5062}"/>
-    <hyperlink ref="K13" r:id="rId12" display="https://probullstats.com/loggers/matchup.php?bull=47944&amp;guy=Luciano+De+Castro" xr:uid="{9267FA7D-248E-B34C-8C38-7BE0A78E8AEA}"/>
-    <hyperlink ref="K14" r:id="rId13" display="https://probullstats.com/loggers/matchup.php?bull=54869&amp;guy=Maverick+Smith" xr:uid="{D678A161-F7D7-2F41-B2E8-5D745A686CC6}"/>
-    <hyperlink ref="K15" r:id="rId14" display="https://probullstats.com/loggers/matchup.php?bull=52181&amp;guy=Hudson+Bolton" xr:uid="{AD073728-5785-1A4F-A08B-4B96F315C8A4}"/>
-    <hyperlink ref="K16" r:id="rId15" display="https://probullstats.com/loggers/matchup.php?bull=52572&amp;guy=Alex+Junior+da+Silva" xr:uid="{7E120FEA-998C-D94A-9898-25668BC671E8}"/>
-    <hyperlink ref="K17" r:id="rId16" display="https://probullstats.com/loggers/matchup.php?bull=55061&amp;guy=Bruno+Carvalho" xr:uid="{0556D485-6D01-CC4C-87EB-623E88F2E932}"/>
-    <hyperlink ref="K18" r:id="rId17" display="https://probullstats.com/loggers/matchup.php?bull=54896&amp;guy=Mason+Taylor" xr:uid="{4D30E132-8232-7C42-9CD6-B9669F98DF66}"/>
-    <hyperlink ref="K19" r:id="rId18" display="https://probullstats.com/loggers/matchup.php?bull=52731&amp;guy=Marco+Rizzo" xr:uid="{1266D028-E5E7-0146-B7F2-D84A3EB2D983}"/>
-    <hyperlink ref="K20" r:id="rId19" display="https://probullstats.com/loggers/matchup.php?bull=56541&amp;guy=John+Crimber" xr:uid="{B409839B-8FC2-804B-92CB-C6EB4D712DA3}"/>
-    <hyperlink ref="K21" r:id="rId20" display="https://probullstats.com/loggers/matchup.php?bull=55423&amp;guy=Eduardo+Aparecido" xr:uid="{581E78AC-8306-9D44-B916-342AC1D9626F}"/>
-    <hyperlink ref="K22" r:id="rId21" display="https://probullstats.com/loggers/matchup.php?bull=55889&amp;guy=Brady+Fielder" xr:uid="{325C0132-97EC-AB4C-9652-5EB81533072B}"/>
-    <hyperlink ref="K23" r:id="rId22" display="https://probullstats.com/loggers/matchup.php?bull=55691&amp;guy=Claudio+Montanha+Jr." xr:uid="{7CD20EF3-9BDD-5748-87FB-A8B4A3E49BDB}"/>
-    <hyperlink ref="K24" r:id="rId23" display="https://probullstats.com/loggers/matchup.php?bull=50890&amp;guy=Trace+Redd" xr:uid="{2C05EFFD-59C7-DC42-AE87-3CEB6B55C7DD}"/>
-    <hyperlink ref="K25" r:id="rId24" display="https://probullstats.com/loggers/matchup.php?bull=56045&amp;guy=Daniel+Keeping" xr:uid="{469A118B-00C6-4B49-B5C6-A3C6C9B15ACC}"/>
-    <hyperlink ref="K26" r:id="rId25" display="https://probullstats.com/loggers/matchup.php?bull=52122&amp;guy=Jose+Vitor+Leme" xr:uid="{3C3E0CC1-BD10-3B44-ADAF-07E4338402BA}"/>
-    <hyperlink ref="K27" r:id="rId26" display="https://probullstats.com/loggers/matchup.php?bull=56542&amp;guy=Cort+McFadden" xr:uid="{129071F9-1177-4340-9B59-0E2D000E9C69}"/>
-    <hyperlink ref="K28" r:id="rId27" display="https://probullstats.com/loggers/matchup.php?bull=45407&amp;guy=Jadon+Hayes" xr:uid="{963E5A5A-6D28-2349-935F-133EDC8262EA}"/>
-    <hyperlink ref="K29" r:id="rId28" display="https://probullstats.com/loggers/matchup.php?bull=48463&amp;guy=Joao+Ricardo+Vieira" xr:uid="{9ACEEFE7-F7D3-7E4A-9BF5-24143405AFA1}"/>
-    <hyperlink ref="K30" r:id="rId29" display="https://probullstats.com/loggers/matchup.php?bull=53635&amp;guy=Macaulie+Leather" xr:uid="{B697B491-58DB-4B4B-8562-9AB358049F51}"/>
-    <hyperlink ref="K31" r:id="rId30" display="https://probullstats.com/loggers/matchup.php?bull=56345&amp;guy=Natanael+Serra+Aires" xr:uid="{0BCBF768-93D3-8F43-8AD5-206A7FB3B833}"/>
-    <hyperlink ref="K32" r:id="rId31" display="https://probullstats.com/loggers/matchup.php?bull=55084&amp;guy=Sage+Kimzey" xr:uid="{D66640D7-CE04-A640-86B0-643111985C5C}"/>
-    <hyperlink ref="K33" r:id="rId32" display="https://probullstats.com/loggers/matchup.php?bull=43263&amp;guy=Eric+Henrique+Domingos" xr:uid="{716167A1-FB1B-D243-A41C-5B4ADE29A6E6}"/>
-    <hyperlink ref="K34" r:id="rId33" display="https://probullstats.com/loggers/matchup.php?bull=50683&amp;guy=Kaique+Pacheco" xr:uid="{180B9CC1-DC3C-A947-96FF-6EB1A3EB77CB}"/>
-    <hyperlink ref="K35" r:id="rId34" display="https://probullstats.com/loggers/matchup.php?bull=53634&amp;guy=Marcelo+De+Souza+Dias+Junior" xr:uid="{0BB40081-B139-2F4C-B0A3-9745E426BEAF}"/>
-    <hyperlink ref="K36" r:id="rId35" display="https://probullstats.com/loggers/matchup.php?bull=55693&amp;guy=Callum+Miller" xr:uid="{2A7095C3-9A96-904C-8825-FDD5D393F760}"/>
-    <hyperlink ref="K37" r:id="rId36" display="https://probullstats.com/loggers/matchup.php?bull=52004&amp;guy=Bruno+Roberto" xr:uid="{2A512A64-74CA-7246-911B-43D2ADA4C788}"/>
-    <hyperlink ref="K38" r:id="rId37" display="https://probullstats.com/loggers/matchup.php?bull=56543&amp;guy=Lucas+Divino" xr:uid="{74303718-CC19-714D-B767-E9BF6F270DFC}"/>
-    <hyperlink ref="K39" r:id="rId38" display="https://probullstats.com/loggers/matchup.php?bull=47812&amp;guy=Andy+Guzman" xr:uid="{BCB8E763-7EFC-C64A-A714-03EAC79C3956}"/>
-    <hyperlink ref="K40" r:id="rId39" display="https://probullstats.com/loggers/matchup.php?bull=52618&amp;guy=Dener+Barbosa" xr:uid="{094DB341-E704-864E-ABEE-F20088B176D7}"/>
-    <hyperlink ref="K41" r:id="rId40" display="https://probullstats.com/loggers/matchup.php?bull=47325&amp;guy=Koltin+Hevalow" xr:uid="{0A517EBE-BEF9-0B49-A775-5E7D09C557BE}"/>
-    <hyperlink ref="K42" r:id="rId41" display="https://probullstats.com/loggers/matchup.php?bull=56319&amp;guy=Vinicius+Pinheiro+Correa" xr:uid="{7DAB5BE5-3791-D249-A50F-F3D91CAD6DA7}"/>
-    <hyperlink ref="K43" r:id="rId42" display="https://probullstats.com/loggers/matchup.php?bull=52178&amp;guy=Cassio+Dias" xr:uid="{3D7C6384-160B-8A48-A29D-CB20A28B4E76}"/>
-    <hyperlink ref="K44" r:id="rId43" display="https://probullstats.com/loggers/matchup.php?bull=54035&amp;guy=Dalton+Kasel" xr:uid="{0EDD66C9-F792-EC45-A24C-1F3BD6F40636}"/>
+    <hyperlink ref="J2" r:id="rId1" display="https://probullstats.com/loggers/matchup.php?bull=52839&amp;guy=Jess+Lockwood" xr:uid="{F970B9C6-9BCD-5E46-AA4F-71F0EACB3924}"/>
+    <hyperlink ref="J3" r:id="rId2" display="https://probullstats.com/loggers/matchup.php?bull=56214&amp;guy=Kase+Hitt" xr:uid="{F506C8E8-40E1-964F-B9DA-D7FE929F019A}"/>
+    <hyperlink ref="J4" r:id="rId3" display="https://probullstats.com/loggers/matchup.php?bull=56035&amp;guy=Julio+Cesar+Marques" xr:uid="{053518A0-6349-4744-95DE-41EFA4861A41}"/>
+    <hyperlink ref="J5" r:id="rId4" display="https://probullstats.com/loggers/matchup.php?bull=55806&amp;guy=Kaiden+Loud" xr:uid="{8C7DDD88-3D1A-C94E-923A-DA0DBC8146AD}"/>
+    <hyperlink ref="J6" r:id="rId5" display="https://probullstats.com/loggers/matchup.php?bull=56540&amp;guy=Mauricio+Gulla+Moreira" xr:uid="{FD7D6547-2C8C-2840-A167-738CAB9A832C}"/>
+    <hyperlink ref="J7" r:id="rId6" display="https://probullstats.com/loggers/matchup.php?bull=48948&amp;guy=Bob+Mitchell" xr:uid="{F0059777-5DFE-F946-AC6B-1EDDB6C3D6AF}"/>
+    <hyperlink ref="J8" r:id="rId7" display="https://probullstats.com/loggers/matchup.php?bull=54839&amp;guy=Keyshawn+Whitehorse" xr:uid="{B26D7B4B-123C-0149-ADFC-45AB02B58CFD}"/>
+    <hyperlink ref="J9" r:id="rId8" display="https://probullstats.com/loggers/matchup.php?bull=53968&amp;guy=Manoelito+de+Souza+Junior" xr:uid="{569F14A1-459F-2244-90DC-CB697A4D3339}"/>
+    <hyperlink ref="J10" r:id="rId9" display="https://probullstats.com/loggers/matchup.php?bull=53970&amp;guy=Leandro+Zampollo" xr:uid="{1F2BFB5A-99B7-9846-A2AC-C3775B994DBD}"/>
+    <hyperlink ref="J11" r:id="rId10" display="https://probullstats.com/loggers/matchup.php?bull=56046&amp;guy=Paulo+Eduardo+Rossetto" xr:uid="{6DB243E9-BFED-B842-B9FC-F6B37C950BA1}"/>
+    <hyperlink ref="J12" r:id="rId11" display="https://probullstats.com/loggers/matchup.php?bull=54711&amp;guy=Alex+Cerqueira" xr:uid="{6008F3BA-B37C-924B-8487-8673B80C5062}"/>
+    <hyperlink ref="J13" r:id="rId12" display="https://probullstats.com/loggers/matchup.php?bull=47944&amp;guy=Luciano+De+Castro" xr:uid="{9267FA7D-248E-B34C-8C38-7BE0A78E8AEA}"/>
+    <hyperlink ref="J14" r:id="rId13" display="https://probullstats.com/loggers/matchup.php?bull=54869&amp;guy=Maverick+Smith" xr:uid="{D678A161-F7D7-2F41-B2E8-5D745A686CC6}"/>
+    <hyperlink ref="J15" r:id="rId14" display="https://probullstats.com/loggers/matchup.php?bull=52181&amp;guy=Hudson+Bolton" xr:uid="{AD073728-5785-1A4F-A08B-4B96F315C8A4}"/>
+    <hyperlink ref="J16" r:id="rId15" display="https://probullstats.com/loggers/matchup.php?bull=52572&amp;guy=Alex+Junior+da+Silva" xr:uid="{7E120FEA-998C-D94A-9898-25668BC671E8}"/>
+    <hyperlink ref="J17" r:id="rId16" display="https://probullstats.com/loggers/matchup.php?bull=55061&amp;guy=Bruno+Carvalho" xr:uid="{0556D485-6D01-CC4C-87EB-623E88F2E932}"/>
+    <hyperlink ref="J18" r:id="rId17" display="https://probullstats.com/loggers/matchup.php?bull=54896&amp;guy=Mason+Taylor" xr:uid="{4D30E132-8232-7C42-9CD6-B9669F98DF66}"/>
+    <hyperlink ref="J19" r:id="rId18" display="https://probullstats.com/loggers/matchup.php?bull=52731&amp;guy=Marco+Rizzo" xr:uid="{1266D028-E5E7-0146-B7F2-D84A3EB2D983}"/>
+    <hyperlink ref="J20" r:id="rId19" display="https://probullstats.com/loggers/matchup.php?bull=56541&amp;guy=John+Crimber" xr:uid="{B409839B-8FC2-804B-92CB-C6EB4D712DA3}"/>
+    <hyperlink ref="J21" r:id="rId20" display="https://probullstats.com/loggers/matchup.php?bull=55423&amp;guy=Eduardo+Aparecido" xr:uid="{581E78AC-8306-9D44-B916-342AC1D9626F}"/>
+    <hyperlink ref="J22" r:id="rId21" display="https://probullstats.com/loggers/matchup.php?bull=55889&amp;guy=Brady+Fielder" xr:uid="{325C0132-97EC-AB4C-9652-5EB81533072B}"/>
+    <hyperlink ref="J23" r:id="rId22" display="https://probullstats.com/loggers/matchup.php?bull=55691&amp;guy=Claudio+Montanha+Jr." xr:uid="{7CD20EF3-9BDD-5748-87FB-A8B4A3E49BDB}"/>
+    <hyperlink ref="J24" r:id="rId23" display="https://probullstats.com/loggers/matchup.php?bull=50890&amp;guy=Trace+Redd" xr:uid="{2C05EFFD-59C7-DC42-AE87-3CEB6B55C7DD}"/>
+    <hyperlink ref="J25" r:id="rId24" display="https://probullstats.com/loggers/matchup.php?bull=56045&amp;guy=Daniel+Keeping" xr:uid="{469A118B-00C6-4B49-B5C6-A3C6C9B15ACC}"/>
+    <hyperlink ref="J26" r:id="rId25" display="https://probullstats.com/loggers/matchup.php?bull=52122&amp;guy=Jose+Vitor+Leme" xr:uid="{3C3E0CC1-BD10-3B44-ADAF-07E4338402BA}"/>
+    <hyperlink ref="J27" r:id="rId26" display="https://probullstats.com/loggers/matchup.php?bull=56542&amp;guy=Cort+McFadden" xr:uid="{129071F9-1177-4340-9B59-0E2D000E9C69}"/>
+    <hyperlink ref="J28" r:id="rId27" display="https://probullstats.com/loggers/matchup.php?bull=45407&amp;guy=Jadon+Hayes" xr:uid="{963E5A5A-6D28-2349-935F-133EDC8262EA}"/>
+    <hyperlink ref="J29" r:id="rId28" display="https://probullstats.com/loggers/matchup.php?bull=48463&amp;guy=Joao+Ricardo+Vieira" xr:uid="{9ACEEFE7-F7D3-7E4A-9BF5-24143405AFA1}"/>
+    <hyperlink ref="J30" r:id="rId29" display="https://probullstats.com/loggers/matchup.php?bull=53635&amp;guy=Macaulie+Leather" xr:uid="{B697B491-58DB-4B4B-8562-9AB358049F51}"/>
+    <hyperlink ref="J31" r:id="rId30" display="https://probullstats.com/loggers/matchup.php?bull=56345&amp;guy=Natanael+Serra+Aires" xr:uid="{0BCBF768-93D3-8F43-8AD5-206A7FB3B833}"/>
+    <hyperlink ref="J32" r:id="rId31" display="https://probullstats.com/loggers/matchup.php?bull=55084&amp;guy=Sage+Kimzey" xr:uid="{D66640D7-CE04-A640-86B0-643111985C5C}"/>
+    <hyperlink ref="J33" r:id="rId32" display="https://probullstats.com/loggers/matchup.php?bull=43263&amp;guy=Eric+Henrique+Domingos" xr:uid="{716167A1-FB1B-D243-A41C-5B4ADE29A6E6}"/>
+    <hyperlink ref="J34" r:id="rId33" display="https://probullstats.com/loggers/matchup.php?bull=50683&amp;guy=Kaique+Pacheco" xr:uid="{180B9CC1-DC3C-A947-96FF-6EB1A3EB77CB}"/>
+    <hyperlink ref="J35" r:id="rId34" display="https://probullstats.com/loggers/matchup.php?bull=53634&amp;guy=Marcelo+De+Souza+Dias+Junior" xr:uid="{0BB40081-B139-2F4C-B0A3-9745E426BEAF}"/>
+    <hyperlink ref="J36" r:id="rId35" display="https://probullstats.com/loggers/matchup.php?bull=55693&amp;guy=Callum+Miller" xr:uid="{2A7095C3-9A96-904C-8825-FDD5D393F760}"/>
+    <hyperlink ref="J37" r:id="rId36" display="https://probullstats.com/loggers/matchup.php?bull=52004&amp;guy=Bruno+Roberto" xr:uid="{2A512A64-74CA-7246-911B-43D2ADA4C788}"/>
+    <hyperlink ref="J38" r:id="rId37" display="https://probullstats.com/loggers/matchup.php?bull=56543&amp;guy=Lucas+Divino" xr:uid="{74303718-CC19-714D-B767-E9BF6F270DFC}"/>
+    <hyperlink ref="J39" r:id="rId38" display="https://probullstats.com/loggers/matchup.php?bull=47812&amp;guy=Andy+Guzman" xr:uid="{BCB8E763-7EFC-C64A-A714-03EAC79C3956}"/>
+    <hyperlink ref="J40" r:id="rId39" display="https://probullstats.com/loggers/matchup.php?bull=52618&amp;guy=Dener+Barbosa" xr:uid="{094DB341-E704-864E-ABEE-F20088B176D7}"/>
+    <hyperlink ref="J41" r:id="rId40" display="https://probullstats.com/loggers/matchup.php?bull=47325&amp;guy=Koltin+Hevalow" xr:uid="{0A517EBE-BEF9-0B49-A775-5E7D09C557BE}"/>
+    <hyperlink ref="J42" r:id="rId41" display="https://probullstats.com/loggers/matchup.php?bull=56319&amp;guy=Vinicius+Pinheiro+Correa" xr:uid="{7DAB5BE5-3791-D249-A50F-F3D91CAD6DA7}"/>
+    <hyperlink ref="J43" r:id="rId42" display="https://probullstats.com/loggers/matchup.php?bull=52178&amp;guy=Cassio+Dias" xr:uid="{3D7C6384-160B-8A48-A29D-CB20A28B4E76}"/>
+    <hyperlink ref="J44" r:id="rId43" display="https://probullstats.com/loggers/matchup.php?bull=54035&amp;guy=Dalton+Kasel" xr:uid="{0EDD66C9-F792-EC45-A24C-1F3BD6F40636}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/pbr_matchups_full.xlsx
+++ b/data/pbr_matchups_full.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cameronyoung/Desktop/rankratings:/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABE56B78-3C48-EB48-AE88-568ED71A0D13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D41F8F47-A246-0F40-9184-3181A997C7A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20240" yWindow="740" windowWidth="10000" windowHeight="18900" xr2:uid="{63502F5A-9950-074D-B0A2-89EF4471630B}"/>
+    <workbookView xWindow="10240" yWindow="740" windowWidth="20000" windowHeight="18900" xr2:uid="{63502F5A-9950-074D-B0A2-89EF4471630B}"/>
   </bookViews>
   <sheets>
     <sheet name="Billings Day 1" sheetId="1" r:id="rId1"/>
@@ -1354,6 +1354,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B688787-F410-204A-8FD8-EC4B8315D133}">
   <dimension ref="A1:T44"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="15" max="15" width="17.1640625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
@@ -1467,10 +1470,11 @@
         <v>43.1</v>
       </c>
       <c r="Q2">
-        <v>45.4</v>
+        <f>IF(OR(P2="",R2=""),0,R2-P2)</f>
+        <v>45.35</v>
       </c>
       <c r="R2">
-        <v>88.5</v>
+        <v>88.45</v>
       </c>
       <c r="T2" t="s">
         <v>19</v>
@@ -1524,11 +1528,11 @@
         <v>42.7</v>
       </c>
       <c r="Q3">
-        <v>-3.69</v>
+        <f t="shared" ref="Q3:Q44" si="0">IF(OR(P3="",R3=""),0,R3-P3)</f>
+        <v>-42.7</v>
       </c>
       <c r="R3">
-        <f>P3+Q3</f>
-        <v>39.010000000000005</v>
+        <v>0</v>
       </c>
       <c r="T3" t="s">
         <v>38</v>
@@ -1580,10 +1584,11 @@
         <v>41.7</v>
       </c>
       <c r="Q4">
-        <v>41.45</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>45.4</v>
       </c>
       <c r="R4">
-        <f>P4+Q4</f>
+        <f ca="1">P4+Q4</f>
         <v>83.15</v>
       </c>
       <c r="T4" t="s">
@@ -1636,11 +1641,11 @@
         <v>44.2</v>
       </c>
       <c r="Q5">
-        <v>-3.07</v>
+        <f t="shared" si="0"/>
+        <v>-44.2</v>
       </c>
       <c r="R5">
-        <f>P5+Q5</f>
-        <v>41.13</v>
+        <v>0</v>
       </c>
       <c r="T5" t="s">
         <v>45</v>
@@ -1692,10 +1697,11 @@
         <v>44.2</v>
       </c>
       <c r="Q6">
-        <v>-1.36</v>
+        <f t="shared" si="0"/>
+        <v>-44.2</v>
       </c>
       <c r="R6">
-        <v>44.2</v>
+        <v>0</v>
       </c>
       <c r="T6" t="s">
         <v>38</v>
@@ -1746,14 +1752,14 @@
         <v>60</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>41.1</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>42.749999999999993</v>
       </c>
       <c r="R7">
-        <f t="shared" ref="R7:R44" si="0">P7+Q7</f>
-        <v>0</v>
+        <v>83.85</v>
       </c>
       <c r="T7" t="s">
         <v>19</v>
@@ -1802,13 +1808,14 @@
         <v>66</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>44.15</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>45.4</v>
       </c>
       <c r="R8">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="R8:R44" ca="1" si="1">P8+Q8</f>
         <v>0</v>
       </c>
       <c r="T8" t="s">
@@ -1860,13 +1867,14 @@
         <v>72</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>42.9</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>45.4</v>
       </c>
       <c r="R9">
-        <f t="shared" si="0"/>
+        <f t="shared" ca="1" si="1"/>
         <v>0</v>
       </c>
       <c r="T9" t="s">
@@ -1921,10 +1929,11 @@
         <v>0</v>
       </c>
       <c r="Q10">
-        <v>0</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>45.4</v>
       </c>
       <c r="R10">
-        <f t="shared" si="0"/>
+        <f t="shared" ca="1" si="1"/>
         <v>0</v>
       </c>
       <c r="T10" t="s">
@@ -1974,14 +1983,14 @@
         <v>85</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>43.55</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>45.960000000000008</v>
       </c>
       <c r="R11">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <v>89.51</v>
       </c>
       <c r="T11" t="s">
         <v>45</v>
@@ -2035,10 +2044,10 @@
         <v>0</v>
       </c>
       <c r="Q12">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R12">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="T12" t="s">
@@ -2095,10 +2104,10 @@
         <v>0</v>
       </c>
       <c r="Q13">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R13">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="T13" t="s">
@@ -2153,10 +2162,10 @@
         <v>0</v>
       </c>
       <c r="Q14">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R14">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="T14" t="s">
@@ -2211,10 +2220,10 @@
         <v>0</v>
       </c>
       <c r="Q15">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R15">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="T15" t="s">
@@ -2269,10 +2278,10 @@
         <v>0</v>
       </c>
       <c r="Q16">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R16">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="T16" t="s">
@@ -2325,10 +2334,10 @@
         <v>0</v>
       </c>
       <c r="Q17">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R17">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="T17" t="s">
@@ -2383,10 +2392,10 @@
         <v>0</v>
       </c>
       <c r="Q18">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R18">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="T18" t="s">
@@ -2441,10 +2450,10 @@
         <v>0</v>
       </c>
       <c r="Q19">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R19">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="T19" t="s">
@@ -2497,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="Q20">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R20">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="T20" t="s">
@@ -2555,10 +2564,10 @@
         <v>0</v>
       </c>
       <c r="Q21">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R21">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="T21" t="s">
@@ -2611,10 +2620,10 @@
         <v>0</v>
       </c>
       <c r="Q22">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R22">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="T22" t="s">
@@ -2669,10 +2678,10 @@
         <v>0</v>
       </c>
       <c r="Q23">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R23">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="T23" t="s">
@@ -2727,10 +2736,10 @@
         <v>0</v>
       </c>
       <c r="Q24">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R24">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="T24" t="s">
@@ -2783,10 +2792,10 @@
         <v>0</v>
       </c>
       <c r="Q25">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R25">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="T25" t="s">
@@ -2843,10 +2852,10 @@
         <v>0</v>
       </c>
       <c r="Q26">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R26">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="T26" t="s">
@@ -2901,10 +2910,10 @@
         <v>0</v>
       </c>
       <c r="Q27">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R27">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="T27" t="s">
@@ -2959,10 +2968,10 @@
         <v>0</v>
       </c>
       <c r="Q28">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R28">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="T28" t="s">
@@ -3017,10 +3026,10 @@
         <v>0</v>
       </c>
       <c r="Q29">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R29">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="T29" t="s">
@@ -3073,10 +3082,10 @@
         <v>0</v>
       </c>
       <c r="Q30">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R30">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="T30" t="s">
@@ -3129,10 +3138,10 @@
         <v>0</v>
       </c>
       <c r="Q31">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R31">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="T31" t="s">
@@ -3187,10 +3196,10 @@
         <v>0</v>
       </c>
       <c r="Q32">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R32">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="T32" t="s">
@@ -3247,10 +3256,10 @@
         <v>0</v>
       </c>
       <c r="Q33">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R33">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="T33" t="s">
@@ -3305,10 +3314,10 @@
         <v>0</v>
       </c>
       <c r="Q34">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R34">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="T34" t="s">
@@ -3363,10 +3372,10 @@
         <v>0</v>
       </c>
       <c r="Q35">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R35">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="T35" t="s">
@@ -3419,10 +3428,10 @@
         <v>0</v>
       </c>
       <c r="Q36">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R36">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="T36" t="s">
@@ -3479,10 +3488,10 @@
         <v>0</v>
       </c>
       <c r="Q37">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R37">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="T37" t="s">
@@ -3537,10 +3546,10 @@
         <v>0</v>
       </c>
       <c r="Q38">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R38">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="T38" t="s">
@@ -3597,10 +3606,10 @@
         <v>0</v>
       </c>
       <c r="Q39">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R39">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="T39" t="s">
@@ -3653,10 +3662,10 @@
         <v>0</v>
       </c>
       <c r="Q40">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R40">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="T40" t="s">
@@ -3713,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="Q41">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R41">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="T41" t="s">
@@ -3771,10 +3780,10 @@
         <v>0</v>
       </c>
       <c r="Q42">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R42">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="T42" t="s">
@@ -3829,10 +3838,10 @@
         <v>0</v>
       </c>
       <c r="Q43">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R43">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="T43" t="s">
@@ -3889,10 +3898,10 @@
         <v>0</v>
       </c>
       <c r="Q44">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R44">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="T44" t="s">

--- a/data/pbr_matchups_full.xlsx
+++ b/data/pbr_matchups_full.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cameronyoung/Desktop/rankratings:/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D41F8F47-A246-0F40-9184-3181A997C7A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53E020B8-F5C8-5947-9BF6-37F532740415}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10240" yWindow="740" windowWidth="20000" windowHeight="18900" xr2:uid="{63502F5A-9950-074D-B0A2-89EF4471630B}"/>
+    <workbookView xWindow="19600" yWindow="740" windowWidth="10640" windowHeight="18900" xr2:uid="{63502F5A-9950-074D-B0A2-89EF4471630B}"/>
   </bookViews>
   <sheets>
     <sheet name="Billings Day 1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="531" uniqueCount="270">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="534" uniqueCount="271">
   <si>
     <t>Bull Power</t>
   </si>
@@ -924,6 +924,9 @@
   </si>
   <si>
     <t>&lt;h2&gt;Rider&lt;/h2&gt;&lt;p&gt;&lt;strong&gt;Career:&amp;nbsp;&lt;/strong&gt;Career: 258 for 576 - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;44.79%&lt;/em&gt;&lt;/span&gt; - Rider Rating: *.372&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Season:&amp;nbsp;&lt;/strong&gt;Rank&amp;nbsp;&lt;span style="color: #ff0000;"&gt;6&lt;/span&gt; (36 for 66 - &lt;em&gt;54.5%&lt;/em&gt;)&lt;em&gt;&lt;br /&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Points:&amp;nbsp;&lt;/strong&gt;488.50 pts &lt;span style="color: #ff0000;"&gt;&lt;em&gt;(-339)&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Earnings:&amp;nbsp;&lt;/strong&gt;&lt;span style="color: #008000;"&gt;&lt;em&gt;$252,397.78&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Potential&lt;/strong&gt;:&amp;nbsp;83.74 to 89.74 points&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;&lt;span style="text-decoration: underline;"&gt;&lt;strong&gt;Bull&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;ALL:&lt;/strong&gt; 16 outs 7 rides - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;56.25%&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;UTB:&lt;/strong&gt; 13 outs 7 rides - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;46.15%&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;em&gt;&lt;span style="color: #ff0000;"&gt;*No Previous Matchups&lt;/span&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t>rr</t>
   </si>
 </sst>
 </file>
@@ -1528,8 +1531,7 @@
         <v>42.7</v>
       </c>
       <c r="Q3">
-        <f t="shared" ref="Q3:Q44" si="0">IF(OR(P3="",R3=""),0,R3-P3)</f>
-        <v>-42.7</v>
+        <v>0</v>
       </c>
       <c r="R3">
         <v>0</v>
@@ -1584,7 +1586,7 @@
         <v>41.7</v>
       </c>
       <c r="Q4">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" ref="Q3:Q44" ca="1" si="0">IF(OR(P4="",R4=""),0,R4-P4)</f>
         <v>45.4</v>
       </c>
       <c r="R4">
@@ -1641,8 +1643,7 @@
         <v>44.2</v>
       </c>
       <c r="Q5">
-        <f t="shared" si="0"/>
-        <v>-44.2</v>
+        <v>0</v>
       </c>
       <c r="R5">
         <v>0</v>
@@ -1697,8 +1698,7 @@
         <v>44.2</v>
       </c>
       <c r="Q6">
-        <f t="shared" si="0"/>
-        <v>-44.2</v>
+        <v>0</v>
       </c>
       <c r="R6">
         <v>0</v>
@@ -1755,8 +1755,7 @@
         <v>41.1</v>
       </c>
       <c r="Q7">
-        <f t="shared" si="0"/>
-        <v>42.749999999999993</v>
+        <v>0</v>
       </c>
       <c r="R7">
         <v>83.85</v>
@@ -1811,12 +1810,11 @@
         <v>44.15</v>
       </c>
       <c r="Q8">
-        <f t="shared" ca="1" si="0"/>
-        <v>45.4</v>
+        <v>0</v>
       </c>
       <c r="R8">
-        <f t="shared" ref="R8:R44" ca="1" si="1">P8+Q8</f>
-        <v>0</v>
+        <f t="shared" ref="R8:R44" si="1">P8+Q8</f>
+        <v>44.15</v>
       </c>
       <c r="T8" t="s">
         <v>45</v>
@@ -1870,12 +1868,11 @@
         <v>42.9</v>
       </c>
       <c r="Q9">
-        <f t="shared" ca="1" si="0"/>
-        <v>45.4</v>
+        <v>0</v>
       </c>
       <c r="R9">
-        <f t="shared" ca="1" si="1"/>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>42.9</v>
       </c>
       <c r="T9" t="s">
         <v>45</v>
@@ -1929,11 +1926,9 @@
         <v>0</v>
       </c>
       <c r="Q10">
-        <f t="shared" ca="1" si="0"/>
-        <v>45.4</v>
+        <v>0</v>
       </c>
       <c r="R10">
-        <f t="shared" ca="1" si="1"/>
         <v>0</v>
       </c>
       <c r="T10" t="s">
@@ -2040,15 +2035,14 @@
       <c r="O12" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="P12">
-        <v>0</v>
-      </c>
-      <c r="Q12">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="R12">
-        <v>0</v>
+      <c r="P12" t="s">
+        <v>270</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>270</v>
+      </c>
+      <c r="R12" t="s">
+        <v>270</v>
       </c>
       <c r="T12" t="s">
         <v>19</v>
@@ -2101,14 +2095,14 @@
         <v>96</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>43.15</v>
       </c>
       <c r="Q13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>43.000000000000007</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>86.15</v>
       </c>
       <c r="T13" t="s">
         <v>45</v>
@@ -2159,11 +2153,11 @@
         <v>102</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="Q14">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-43</v>
       </c>
       <c r="R14">
         <v>0</v>

--- a/data/pbr_matchups_full.xlsx
+++ b/data/pbr_matchups_full.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cameronyoung/Desktop/rankratings:/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53E020B8-F5C8-5947-9BF6-37F532740415}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A8D8790-AFF0-2841-85E1-2622544CCF09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19600" yWindow="740" windowWidth="10640" windowHeight="18900" xr2:uid="{63502F5A-9950-074D-B0A2-89EF4471630B}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="534" uniqueCount="271">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="542" uniqueCount="274">
   <si>
     <t>Bull Power</t>
   </si>
@@ -928,12 +928,21 @@
   <si>
     <t>rr</t>
   </si>
+  <si>
+    <t>Chute Clock Foul</t>
+  </si>
+  <si>
+    <t>Chute  contact challenge; shawn ramirez; Successful challeange</t>
+  </si>
+  <si>
+    <t>cy</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -986,6 +995,28 @@
       <name val="Verdana"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1008,7 +1039,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
@@ -1020,6 +1051,9 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1359,6 +1393,9 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="15" max="15" width="17.1640625" customWidth="1"/>
+    <col min="16" max="16" width="10.83203125" style="9"/>
+    <col min="17" max="17" width="10.83203125" style="10"/>
+    <col min="18" max="18" width="10.83203125" style="11"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.2">
@@ -1407,13 +1444,13 @@
       <c r="O1" t="s">
         <v>10</v>
       </c>
-      <c r="P1" t="s">
+      <c r="P1" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="Q1" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="R1" t="s">
+      <c r="R1" s="11" t="s">
         <v>2</v>
       </c>
       <c r="S1" t="s">
@@ -1469,14 +1506,14 @@
       <c r="O2" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="P2">
+      <c r="P2" s="9">
         <v>43.1</v>
       </c>
-      <c r="Q2">
+      <c r="Q2" s="10">
         <f>IF(OR(P2="",R2=""),0,R2-P2)</f>
         <v>45.35</v>
       </c>
-      <c r="R2">
+      <c r="R2" s="11">
         <v>88.45</v>
       </c>
       <c r="T2" t="s">
@@ -1527,13 +1564,13 @@
       <c r="O3" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="P3">
+      <c r="P3" s="9">
         <v>42.7</v>
       </c>
-      <c r="Q3">
-        <v>0</v>
-      </c>
-      <c r="R3">
+      <c r="Q3" s="10">
+        <v>0</v>
+      </c>
+      <c r="R3" s="11">
         <v>0</v>
       </c>
       <c r="T3" t="s">
@@ -1582,14 +1619,14 @@
       <c r="O4" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="P4">
+      <c r="P4" s="9">
         <v>41.7</v>
       </c>
-      <c r="Q4">
+      <c r="Q4" s="10">
         <f t="shared" ref="Q3:Q44" ca="1" si="0">IF(OR(P4="",R4=""),0,R4-P4)</f>
         <v>45.4</v>
       </c>
-      <c r="R4">
+      <c r="R4" s="11">
         <f ca="1">P4+Q4</f>
         <v>83.15</v>
       </c>
@@ -1639,13 +1676,13 @@
       <c r="O5" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="P5">
+      <c r="P5" s="9">
         <v>44.2</v>
       </c>
-      <c r="Q5">
-        <v>0</v>
-      </c>
-      <c r="R5">
+      <c r="Q5" s="10">
+        <v>0</v>
+      </c>
+      <c r="R5" s="11">
         <v>0</v>
       </c>
       <c r="T5" t="s">
@@ -1694,13 +1731,13 @@
       <c r="O6" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="P6">
+      <c r="P6" s="9">
         <v>44.2</v>
       </c>
-      <c r="Q6">
-        <v>0</v>
-      </c>
-      <c r="R6">
+      <c r="Q6" s="10">
+        <v>0</v>
+      </c>
+      <c r="R6" s="11">
         <v>0</v>
       </c>
       <c r="T6" t="s">
@@ -1751,13 +1788,13 @@
       <c r="O7" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="P7">
+      <c r="P7" s="9">
         <v>41.1</v>
       </c>
-      <c r="Q7">
-        <v>0</v>
-      </c>
-      <c r="R7">
+      <c r="Q7" s="10">
+        <v>0</v>
+      </c>
+      <c r="R7" s="11">
         <v>83.85</v>
       </c>
       <c r="T7" t="s">
@@ -1806,13 +1843,13 @@
       <c r="O8" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="P8">
+      <c r="P8" s="9">
         <v>44.15</v>
       </c>
-      <c r="Q8">
-        <v>0</v>
-      </c>
-      <c r="R8">
+      <c r="Q8" s="10">
+        <v>0</v>
+      </c>
+      <c r="R8" s="11">
         <f t="shared" ref="R8:R44" si="1">P8+Q8</f>
         <v>44.15</v>
       </c>
@@ -1864,13 +1901,13 @@
       <c r="O9" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="P9">
+      <c r="P9" s="9">
         <v>42.9</v>
       </c>
-      <c r="Q9">
-        <v>0</v>
-      </c>
-      <c r="R9">
+      <c r="Q9" s="10">
+        <v>0</v>
+      </c>
+      <c r="R9" s="11">
         <f t="shared" si="1"/>
         <v>42.9</v>
       </c>
@@ -1922,13 +1959,13 @@
       <c r="O10" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="P10">
-        <v>0</v>
-      </c>
-      <c r="Q10">
-        <v>0</v>
-      </c>
-      <c r="R10">
+      <c r="P10" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="10">
+        <v>0</v>
+      </c>
+      <c r="R10" s="11">
         <v>0</v>
       </c>
       <c r="T10" t="s">
@@ -1977,14 +2014,14 @@
       <c r="O11" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="P11">
+      <c r="P11" s="9">
         <v>43.55</v>
       </c>
-      <c r="Q11">
+      <c r="Q11" s="10">
         <f t="shared" si="0"/>
         <v>45.960000000000008</v>
       </c>
-      <c r="R11">
+      <c r="R11" s="11">
         <v>89.51</v>
       </c>
       <c r="T11" t="s">
@@ -2035,13 +2072,13 @@
       <c r="O12" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="P12" t="s">
+      <c r="P12" s="9" t="s">
         <v>270</v>
       </c>
-      <c r="Q12" t="s">
+      <c r="Q12" s="10" t="s">
         <v>270</v>
       </c>
-      <c r="R12" t="s">
+      <c r="R12" s="11" t="s">
         <v>270</v>
       </c>
       <c r="T12" t="s">
@@ -2094,14 +2131,14 @@
       <c r="O13" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="P13">
+      <c r="P13" s="9">
         <v>43.15</v>
       </c>
-      <c r="Q13">
+      <c r="Q13" s="10">
         <f t="shared" si="0"/>
         <v>43.000000000000007</v>
       </c>
-      <c r="R13">
+      <c r="R13" s="11">
         <v>86.15</v>
       </c>
       <c r="T13" t="s">
@@ -2152,14 +2189,13 @@
       <c r="O14" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="P14">
-        <v>43</v>
-      </c>
-      <c r="Q14">
-        <f t="shared" si="0"/>
-        <v>-43</v>
-      </c>
-      <c r="R14">
+      <c r="P14" s="9">
+        <v>43.05</v>
+      </c>
+      <c r="Q14" s="10">
+        <v>0</v>
+      </c>
+      <c r="R14" s="11">
         <v>0</v>
       </c>
       <c r="T14" t="s">
@@ -2210,15 +2246,15 @@
       <c r="O15" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="P15">
-        <v>0</v>
-      </c>
-      <c r="Q15">
+      <c r="P15" s="9">
+        <v>42.5</v>
+      </c>
+      <c r="Q15" s="10">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="R15">
-        <v>0</v>
+        <v>45.5</v>
+      </c>
+      <c r="R15" s="11">
+        <v>88</v>
       </c>
       <c r="T15" t="s">
         <v>45</v>
@@ -2268,15 +2304,17 @@
       <c r="O16" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="P16">
-        <v>0</v>
-      </c>
-      <c r="Q16">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="R16">
-        <v>0</v>
+      <c r="P16" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="Q16" s="10" t="s">
+        <v>270</v>
+      </c>
+      <c r="R16" s="11" t="s">
+        <v>270</v>
+      </c>
+      <c r="S16" t="s">
+        <v>271</v>
       </c>
       <c r="T16" t="s">
         <v>45</v>
@@ -2324,14 +2362,14 @@
       <c r="O17" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="P17">
-        <v>0</v>
-      </c>
-      <c r="Q17">
+      <c r="P17" s="9">
+        <v>34.4</v>
+      </c>
+      <c r="Q17" s="10">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="R17">
+        <v>-34.4</v>
+      </c>
+      <c r="R17" s="11">
         <v>0</v>
       </c>
       <c r="T17" t="s">
@@ -2382,14 +2420,14 @@
       <c r="O18" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="P18">
-        <v>0</v>
-      </c>
-      <c r="Q18">
+      <c r="P18" s="9">
+        <v>43.85</v>
+      </c>
+      <c r="Q18" s="10">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="R18">
+        <v>-43.85</v>
+      </c>
+      <c r="R18" s="11">
         <v>0</v>
       </c>
       <c r="T18" t="s">
@@ -2440,15 +2478,17 @@
       <c r="O19" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="P19">
-        <v>0</v>
-      </c>
-      <c r="Q19">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="R19">
-        <v>0</v>
+      <c r="P19" s="9" t="s">
+        <v>273</v>
+      </c>
+      <c r="Q19" s="10" t="s">
+        <v>273</v>
+      </c>
+      <c r="R19" s="11" t="s">
+        <v>273</v>
+      </c>
+      <c r="S19" t="s">
+        <v>272</v>
       </c>
       <c r="T19" t="s">
         <v>38</v>
@@ -2496,14 +2536,14 @@
       <c r="O20" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="P20">
-        <v>0</v>
-      </c>
-      <c r="Q20">
+      <c r="P20" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="10">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="R20">
+      <c r="R20" s="11">
         <v>0</v>
       </c>
       <c r="T20" t="s">
@@ -2554,14 +2594,14 @@
       <c r="O21" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="P21">
-        <v>0</v>
-      </c>
-      <c r="Q21">
+      <c r="P21" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="10">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="R21">
+      <c r="R21" s="11">
         <v>0</v>
       </c>
       <c r="T21" t="s">
@@ -2610,14 +2650,14 @@
       <c r="O22" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="P22">
-        <v>0</v>
-      </c>
-      <c r="Q22">
+      <c r="P22" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="10">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="R22">
+      <c r="R22" s="11">
         <v>0</v>
       </c>
       <c r="T22" t="s">
@@ -2668,14 +2708,14 @@
       <c r="O23" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="P23">
-        <v>0</v>
-      </c>
-      <c r="Q23">
+      <c r="P23" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="10">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="R23">
+      <c r="R23" s="11">
         <v>0</v>
       </c>
       <c r="T23" t="s">
@@ -2726,14 +2766,14 @@
       <c r="O24" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="P24">
-        <v>0</v>
-      </c>
-      <c r="Q24">
+      <c r="P24" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="10">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="R24">
+      <c r="R24" s="11">
         <v>0</v>
       </c>
       <c r="T24" t="s">
@@ -2782,14 +2822,14 @@
       <c r="O25" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="P25">
-        <v>0</v>
-      </c>
-      <c r="Q25">
+      <c r="P25" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="10">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="R25">
+      <c r="R25" s="11">
         <v>0</v>
       </c>
       <c r="T25" t="s">
@@ -2842,14 +2882,14 @@
       <c r="O26" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="P26">
-        <v>0</v>
-      </c>
-      <c r="Q26">
+      <c r="P26" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="10">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="R26">
+      <c r="R26" s="11">
         <v>0</v>
       </c>
       <c r="T26" t="s">
@@ -2900,14 +2940,14 @@
       <c r="O27" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="P27">
-        <v>0</v>
-      </c>
-      <c r="Q27">
+      <c r="P27" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="10">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="R27">
+      <c r="R27" s="11">
         <v>0</v>
       </c>
       <c r="T27" t="s">
@@ -2958,14 +2998,14 @@
       <c r="O28" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="P28">
-        <v>0</v>
-      </c>
-      <c r="Q28">
+      <c r="P28" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="10">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="R28">
+      <c r="R28" s="11">
         <v>0</v>
       </c>
       <c r="T28" t="s">
@@ -3016,14 +3056,14 @@
       <c r="O29" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="P29">
-        <v>0</v>
-      </c>
-      <c r="Q29">
+      <c r="P29" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="10">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="R29">
+      <c r="R29" s="11">
         <v>0</v>
       </c>
       <c r="T29" t="s">
@@ -3072,14 +3112,14 @@
       <c r="O30" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="P30">
-        <v>0</v>
-      </c>
-      <c r="Q30">
+      <c r="P30" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="10">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="R30">
+      <c r="R30" s="11">
         <v>0</v>
       </c>
       <c r="T30" t="s">
@@ -3128,14 +3168,14 @@
       <c r="O31" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="P31">
-        <v>0</v>
-      </c>
-      <c r="Q31">
+      <c r="P31" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="10">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="R31">
+      <c r="R31" s="11">
         <v>0</v>
       </c>
       <c r="T31" t="s">
@@ -3186,14 +3226,14 @@
       <c r="O32" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="P32">
-        <v>0</v>
-      </c>
-      <c r="Q32">
+      <c r="P32" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="10">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="R32">
+      <c r="R32" s="11">
         <v>0</v>
       </c>
       <c r="T32" t="s">
@@ -3246,14 +3286,14 @@
       <c r="O33" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="P33">
-        <v>0</v>
-      </c>
-      <c r="Q33">
+      <c r="P33" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q33" s="10">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="R33">
+      <c r="R33" s="11">
         <v>0</v>
       </c>
       <c r="T33" t="s">
@@ -3304,14 +3344,14 @@
       <c r="O34" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="P34">
-        <v>0</v>
-      </c>
-      <c r="Q34">
+      <c r="P34" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="10">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="R34">
+      <c r="R34" s="11">
         <v>0</v>
       </c>
       <c r="T34" t="s">
@@ -3362,14 +3402,14 @@
       <c r="O35" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="P35">
-        <v>0</v>
-      </c>
-      <c r="Q35">
+      <c r="P35" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q35" s="10">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="R35">
+      <c r="R35" s="11">
         <v>0</v>
       </c>
       <c r="T35" t="s">
@@ -3418,14 +3458,14 @@
       <c r="O36" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="P36">
-        <v>0</v>
-      </c>
-      <c r="Q36">
+      <c r="P36" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q36" s="10">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="R36">
+      <c r="R36" s="11">
         <v>0</v>
       </c>
       <c r="T36" t="s">
@@ -3478,14 +3518,14 @@
       <c r="O37" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="P37">
-        <v>0</v>
-      </c>
-      <c r="Q37">
+      <c r="P37" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q37" s="10">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="R37">
+      <c r="R37" s="11">
         <v>0</v>
       </c>
       <c r="T37" t="s">
@@ -3536,14 +3576,14 @@
       <c r="O38" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="P38">
-        <v>0</v>
-      </c>
-      <c r="Q38">
+      <c r="P38" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q38" s="10">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="R38">
+      <c r="R38" s="11">
         <v>0</v>
       </c>
       <c r="T38" t="s">
@@ -3596,14 +3636,14 @@
       <c r="O39" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="P39">
-        <v>0</v>
-      </c>
-      <c r="Q39">
+      <c r="P39" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q39" s="10">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="R39">
+      <c r="R39" s="11">
         <v>0</v>
       </c>
       <c r="T39" t="s">
@@ -3652,14 +3692,14 @@
       <c r="O40" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="P40">
-        <v>0</v>
-      </c>
-      <c r="Q40">
+      <c r="P40" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q40" s="10">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="R40">
+      <c r="R40" s="11">
         <v>0</v>
       </c>
       <c r="T40" t="s">
@@ -3712,14 +3752,14 @@
       <c r="O41" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="P41">
-        <v>0</v>
-      </c>
-      <c r="Q41">
+      <c r="P41" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q41" s="10">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="R41">
+      <c r="R41" s="11">
         <v>0</v>
       </c>
       <c r="T41" t="s">
@@ -3770,14 +3810,14 @@
       <c r="O42" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="P42">
-        <v>0</v>
-      </c>
-      <c r="Q42">
+      <c r="P42" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="10">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="R42">
+      <c r="R42" s="11">
         <v>0</v>
       </c>
       <c r="T42" t="s">
@@ -3828,14 +3868,14 @@
       <c r="O43" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="P43">
-        <v>0</v>
-      </c>
-      <c r="Q43">
+      <c r="P43" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q43" s="10">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="R43">
+      <c r="R43" s="11">
         <v>0</v>
       </c>
       <c r="T43" t="s">
@@ -3888,14 +3928,14 @@
       <c r="O44" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="P44">
-        <v>0</v>
-      </c>
-      <c r="Q44">
+      <c r="P44" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="10">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="R44">
+      <c r="R44" s="11">
         <v>0</v>
       </c>
       <c r="T44" t="s">

--- a/data/pbr_matchups_full.xlsx
+++ b/data/pbr_matchups_full.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cameronyoung/Desktop/rankratings:/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A8D8790-AFF0-2841-85E1-2622544CCF09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E103E2DF-2A17-5F4A-AFE4-8DAB8FFECB87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19600" yWindow="740" windowWidth="10640" windowHeight="18900" xr2:uid="{63502F5A-9950-074D-B0A2-89EF4471630B}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="542" uniqueCount="274">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="543" uniqueCount="275">
   <si>
     <t>Bull Power</t>
   </si>
@@ -935,7 +935,10 @@
     <t>Chute  contact challenge; shawn ramirez; Successful challeange</t>
   </si>
   <si>
-    <t>cy</t>
+    <t>CA</t>
+  </si>
+  <si>
+    <t>.02 off 8 (granted auto challenge)</t>
   </si>
 </sst>
 </file>
@@ -1792,7 +1795,7 @@
         <v>41.1</v>
       </c>
       <c r="Q7" s="10">
-        <v>0</v>
+        <v>83.85</v>
       </c>
       <c r="R7" s="11">
         <v>83.85</v>
@@ -2537,11 +2540,11 @@
         <v>136</v>
       </c>
       <c r="P20" s="9">
-        <v>0</v>
+        <v>43.1</v>
       </c>
       <c r="Q20" s="10">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-43.1</v>
       </c>
       <c r="R20" s="11">
         <v>0</v>
@@ -2595,14 +2598,17 @@
         <v>141</v>
       </c>
       <c r="P21" s="9">
-        <v>0</v>
+        <v>42.85</v>
       </c>
       <c r="Q21" s="10">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>42.15</v>
       </c>
       <c r="R21" s="11">
-        <v>0</v>
+        <v>85</v>
+      </c>
+      <c r="S21" t="s">
+        <v>274</v>
       </c>
       <c r="T21" t="s">
         <v>19</v>

--- a/data/pbr_matchups_full.xlsx
+++ b/data/pbr_matchups_full.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cameronyoung/Desktop/rankratings:/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E103E2DF-2A17-5F4A-AFE4-8DAB8FFECB87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5F83755-90E0-E744-86FF-2EE6A58A4DCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19600" yWindow="740" windowWidth="10640" windowHeight="18900" xr2:uid="{63502F5A-9950-074D-B0A2-89EF4471630B}"/>
   </bookViews>
@@ -2657,14 +2657,14 @@
         <v>146</v>
       </c>
       <c r="P22" s="9">
-        <v>0</v>
+        <v>42.8</v>
       </c>
       <c r="Q22" s="10">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>45.5</v>
       </c>
       <c r="R22" s="11">
-        <v>0</v>
+        <v>88.3</v>
       </c>
       <c r="T22" t="s">
         <v>19</v>

--- a/data/pbr_matchups_full.xlsx
+++ b/data/pbr_matchups_full.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cameronyoung/Desktop/rankratings:/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5F83755-90E0-E744-86FF-2EE6A58A4DCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3F875B4-2ACA-C540-8E61-93D8F4758E57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19600" yWindow="740" windowWidth="10640" windowHeight="18900" xr2:uid="{63502F5A-9950-074D-B0A2-89EF4471630B}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="543" uniqueCount="275">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="544" uniqueCount="276">
   <si>
     <t>Bull Power</t>
   </si>
@@ -926,9 +926,6 @@
     <t>&lt;h2&gt;Rider&lt;/h2&gt;&lt;p&gt;&lt;strong&gt;Career:&amp;nbsp;&lt;/strong&gt;Career: 258 for 576 - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;44.79%&lt;/em&gt;&lt;/span&gt; - Rider Rating: *.372&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Season:&amp;nbsp;&lt;/strong&gt;Rank&amp;nbsp;&lt;span style="color: #ff0000;"&gt;6&lt;/span&gt; (36 for 66 - &lt;em&gt;54.5%&lt;/em&gt;)&lt;em&gt;&lt;br /&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Points:&amp;nbsp;&lt;/strong&gt;488.50 pts &lt;span style="color: #ff0000;"&gt;&lt;em&gt;(-339)&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Earnings:&amp;nbsp;&lt;/strong&gt;&lt;span style="color: #008000;"&gt;&lt;em&gt;$252,397.78&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Potential&lt;/strong&gt;:&amp;nbsp;83.74 to 89.74 points&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;&lt;span style="text-decoration: underline;"&gt;&lt;strong&gt;Bull&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;ALL:&lt;/strong&gt; 16 outs 7 rides - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;56.25%&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;UTB:&lt;/strong&gt; 13 outs 7 rides - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;46.15%&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;em&gt;&lt;span style="color: #ff0000;"&gt;*No Previous Matchups&lt;/span&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;</t>
   </si>
   <si>
-    <t>rr</t>
-  </si>
-  <si>
     <t>Chute Clock Foul</t>
   </si>
   <si>
@@ -939,6 +936,12 @@
   </si>
   <si>
     <t>.02 off 8 (granted auto challenge)</t>
+  </si>
+  <si>
+    <t>RR</t>
+  </si>
+  <si>
+    <t>wow lots of rides in a row,shits on lucas theodoro the bull fighter who is hurt</t>
   </si>
 </sst>
 </file>
@@ -2076,13 +2079,13 @@
         <v>90</v>
       </c>
       <c r="P12" s="9" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="Q12" s="10" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="R12" s="11" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="T12" t="s">
         <v>19</v>
@@ -2308,16 +2311,16 @@
         <v>114</v>
       </c>
       <c r="P16" s="9" t="s">
+        <v>274</v>
+      </c>
+      <c r="Q16" s="10" t="s">
+        <v>274</v>
+      </c>
+      <c r="R16" s="11" t="s">
+        <v>274</v>
+      </c>
+      <c r="S16" t="s">
         <v>270</v>
-      </c>
-      <c r="Q16" s="10" t="s">
-        <v>270</v>
-      </c>
-      <c r="R16" s="11" t="s">
-        <v>270</v>
-      </c>
-      <c r="S16" t="s">
-        <v>271</v>
       </c>
       <c r="T16" t="s">
         <v>45</v>
@@ -2482,16 +2485,16 @@
         <v>131</v>
       </c>
       <c r="P19" s="9" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="Q19" s="10" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="R19" s="11" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="S19" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="T19" t="s">
         <v>38</v>
@@ -2608,7 +2611,7 @@
         <v>85</v>
       </c>
       <c r="S21" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="T21" t="s">
         <v>19</v>
@@ -2715,14 +2718,14 @@
         <v>151</v>
       </c>
       <c r="P23" s="9">
-        <v>0</v>
+        <v>43.95</v>
       </c>
       <c r="Q23" s="10">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>44.599999999999994</v>
       </c>
       <c r="R23" s="11">
-        <v>0</v>
+        <v>88.55</v>
       </c>
       <c r="T23" t="s">
         <v>19</v>
@@ -2773,14 +2776,17 @@
         <v>157</v>
       </c>
       <c r="P24" s="9">
-        <v>0</v>
+        <v>41.25</v>
       </c>
       <c r="Q24" s="10">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>43.25</v>
       </c>
       <c r="R24" s="11">
-        <v>0</v>
+        <v>84.5</v>
+      </c>
+      <c r="S24" t="s">
+        <v>275</v>
       </c>
       <c r="T24" t="s">
         <v>38</v>

--- a/data/pbr_matchups_full.xlsx
+++ b/data/pbr_matchups_full.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cameronyoung/Desktop/rankratings:/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3F875B4-2ACA-C540-8E61-93D8F4758E57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50D2FA8B-5119-FE4A-AACF-CB09959EC24D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19600" yWindow="740" windowWidth="10640" windowHeight="18900" xr2:uid="{63502F5A-9950-074D-B0A2-89EF4471630B}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="544" uniqueCount="276">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="545" uniqueCount="277">
   <si>
     <t>Bull Power</t>
   </si>
@@ -942,6 +942,9 @@
   </si>
   <si>
     <t>wow lots of rides in a row,shits on lucas theodoro the bull fighter who is hurt</t>
+  </si>
+  <si>
+    <t>Danny keep gets his 100th ride after 19 hour ride</t>
   </si>
 </sst>
 </file>
@@ -2835,14 +2838,17 @@
         <v>163</v>
       </c>
       <c r="P25" s="9">
-        <v>0</v>
+        <v>41.5</v>
       </c>
       <c r="Q25" s="10">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>43.95</v>
       </c>
       <c r="R25" s="11">
-        <v>0</v>
+        <v>85.45</v>
+      </c>
+      <c r="S25" t="s">
+        <v>276</v>
       </c>
       <c r="T25" t="s">
         <v>45</v>

--- a/data/pbr_matchups_full.xlsx
+++ b/data/pbr_matchups_full.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10412"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10419"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cameronyoung/Desktop/rankratings:/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50D2FA8B-5119-FE4A-AACF-CB09959EC24D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DDC9C8D-609E-CF47-B306-812F3E6188B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19600" yWindow="740" windowWidth="10640" windowHeight="18900" xr2:uid="{63502F5A-9950-074D-B0A2-89EF4471630B}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="30240" windowHeight="18900" xr2:uid="{63502F5A-9950-074D-B0A2-89EF4471630B}"/>
   </bookViews>
   <sheets>
-    <sheet name="Billings Day 1" sheetId="1" r:id="rId1"/>
+    <sheet name="Tacoma Day 1" sheetId="2" r:id="rId1"/>
+    <sheet name="Billings Day 1" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="545" uniqueCount="277">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1041" uniqueCount="505">
   <si>
     <t>Bull Power</t>
   </si>
@@ -946,12 +947,2076 @@
   <si>
     <t>Danny keep gets his 100th ride after 19 hour ride</t>
   </si>
+  <si>
+    <t>hand up in the chute goes down quick id challenge, hed challenge and it makes sense, should be a reride, lets see what ramirez says; awarded a reride from obvious contact</t>
+  </si>
+  <si>
+    <t>New bull 4 years old; Big SHOTT spins in the chute and it looks like it will be an auto ride as it .03 away. Auto review; spins hard in chute keeps intensity; ramirez calls it clearly a ride</t>
+  </si>
+  <si>
+    <t>X</t>
+  </si>
+  <si>
+    <t>9-0 (0)</t>
+  </si>
+  <si>
+    <t>UTB-TAC</t>
+  </si>
+  <si>
+    <t>0.247 (7)</t>
+  </si>
+  <si>
+    <t>0-1 (0)</t>
+  </si>
+  <si>
+    <t>0.371 (6)</t>
+  </si>
+  <si>
+    <t>3-2 (1)</t>
+  </si>
+  <si>
+    <t>065J Uncle Doc(54130)</t>
+  </si>
+  <si>
+    <t>HWKN</t>
+  </si>
+  <si>
+    <t>0.343 (7)</t>
+  </si>
+  <si>
+    <t>15-16 (6)</t>
+  </si>
+  <si>
+    <t>048 Rank Hank(51428)</t>
+  </si>
+  <si>
+    <t>Grayson Cole</t>
+  </si>
+  <si>
+    <t>0.266 (10)</t>
+  </si>
+  <si>
+    <t>53 Keystone(56381)</t>
+  </si>
+  <si>
+    <t>CLPB</t>
+  </si>
+  <si>
+    <t>Vinicius Rodrigues Pereira</t>
+  </si>
+  <si>
+    <t>Ednelio Rodrigues</t>
+  </si>
+  <si>
+    <t>0.177 (7)</t>
+  </si>
+  <si>
+    <t>7-5 (1)</t>
+  </si>
+  <si>
+    <t>22J Average Joe(53419)</t>
+  </si>
+  <si>
+    <t>0.320 (8)</t>
+  </si>
+  <si>
+    <t>C1 Me More Cowboy(56047)</t>
+  </si>
+  <si>
+    <t>0.514 (6)</t>
+  </si>
+  <si>
+    <t>230 Dance Monkey(55809)</t>
+  </si>
+  <si>
+    <t>DMDC</t>
+  </si>
+  <si>
+    <t>Ramon Fiorini</t>
+  </si>
+  <si>
+    <t>0.247 (6)</t>
+  </si>
+  <si>
+    <t>1710 Taco Truck(56578)</t>
+  </si>
+  <si>
+    <t>0.357 (5)</t>
+  </si>
+  <si>
+    <t>102 Wreck It Ralph(56236)</t>
+  </si>
+  <si>
+    <t>THCC</t>
+  </si>
+  <si>
+    <t>0.242 (6)</t>
+  </si>
+  <si>
+    <t>22-14 (6)</t>
+  </si>
+  <si>
+    <t>95J Alakazoo(51896)</t>
+  </si>
+  <si>
+    <t>FFRF</t>
+  </si>
+  <si>
+    <t>Eric Novoa</t>
+  </si>
+  <si>
+    <t>0.343 (10)</t>
+  </si>
+  <si>
+    <t>5-9 (2)</t>
+  </si>
+  <si>
+    <t>X26 Real Deal(52820)</t>
+  </si>
+  <si>
+    <t>0.645 (8)</t>
+  </si>
+  <si>
+    <t>9-4 (1)</t>
+  </si>
+  <si>
+    <t>61G Big Timber(50989)</t>
+  </si>
+  <si>
+    <t>0.299 (8)</t>
+  </si>
+  <si>
+    <t>7-10 (4)</t>
+  </si>
+  <si>
+    <t>120 Smooth Violation(54227)</t>
+  </si>
+  <si>
+    <t>0.483 (9)</t>
+  </si>
+  <si>
+    <t>7-3 (2)</t>
+  </si>
+  <si>
+    <t>-1K Johnny Dang(54171)</t>
+  </si>
+  <si>
+    <t>0.431 (8)</t>
+  </si>
+  <si>
+    <t>26-4 (1)</t>
+  </si>
+  <si>
+    <t>67 Benjamin Ranklin(51690)</t>
+  </si>
+  <si>
+    <t>0.369 (10)</t>
+  </si>
+  <si>
+    <t>15-12 (4)</t>
+  </si>
+  <si>
+    <t>816 Bad Bob(53018)</t>
+  </si>
+  <si>
+    <t>D4CC</t>
+  </si>
+  <si>
+    <t>0.521 (10)</t>
+  </si>
+  <si>
+    <t>956G Sucker Punch(47941)</t>
+  </si>
+  <si>
+    <t>0.408 (8)</t>
+  </si>
+  <si>
+    <t>0160 Level Up(53535)</t>
+  </si>
+  <si>
+    <t>0.457 (8)</t>
+  </si>
+  <si>
+    <t>26-1 (0)</t>
+  </si>
+  <si>
+    <t>2719 Unhinged(49727)</t>
+  </si>
+  <si>
+    <t>WI</t>
+  </si>
+  <si>
+    <t>0.163 (10)</t>
+  </si>
+  <si>
+    <t>1-0 (0)</t>
+  </si>
+  <si>
+    <t>0.334 (6)</t>
+  </si>
+  <si>
+    <t>25-8 (6)</t>
+  </si>
+  <si>
+    <t>68E Oreo(44656)</t>
+  </si>
+  <si>
+    <t>0.213 (10)</t>
+  </si>
+  <si>
+    <t>19-4 (3)</t>
+  </si>
+  <si>
+    <t>0498 Long Gone(50380)</t>
+  </si>
+  <si>
+    <t>0.223 (9)</t>
+  </si>
+  <si>
+    <t>9-1 (1)</t>
+  </si>
+  <si>
+    <t>891F Testified(53892)</t>
+  </si>
+  <si>
+    <t>PGAO</t>
+  </si>
+  <si>
+    <t>0.270 (8)</t>
+  </si>
+  <si>
+    <t>10-5 (0)</t>
+  </si>
+  <si>
+    <t>102 Cracky Chan(53319)</t>
+  </si>
+  <si>
+    <t>Thiago Salgado</t>
+  </si>
+  <si>
+    <t>0.390 (9)</t>
+  </si>
+  <si>
+    <t>52-22 (12)</t>
+  </si>
+  <si>
+    <t>829 Ugly This(48315)</t>
+  </si>
+  <si>
+    <t>CMCY</t>
+  </si>
+  <si>
+    <t>Daylon Swearingen</t>
+  </si>
+  <si>
+    <t>0.480 (10)</t>
+  </si>
+  <si>
+    <t>8-0 (0)</t>
+  </si>
+  <si>
+    <t>02K Smoke Screen(54209)</t>
+  </si>
+  <si>
+    <t>Andrew Alvidrez</t>
+  </si>
+  <si>
+    <t>0.209 (7)</t>
+  </si>
+  <si>
+    <t>26-3 (1)</t>
+  </si>
+  <si>
+    <t>071H Apple Juicing(51949)</t>
+  </si>
+  <si>
+    <t>0.364 (10)</t>
+  </si>
+  <si>
+    <t>38K Masterpiece(56577)</t>
+  </si>
+  <si>
+    <t>0.337 (5)</t>
+  </si>
+  <si>
+    <t>10-7 (4)</t>
+  </si>
+  <si>
+    <t>012H Sunrise(53617)</t>
+  </si>
+  <si>
+    <t>0.542 (9)</t>
+  </si>
+  <si>
+    <t>4-6 (2)</t>
+  </si>
+  <si>
+    <t>106 MF Darkside(55454)</t>
+  </si>
+  <si>
+    <t>Romario Leite</t>
+  </si>
+  <si>
+    <t>0.389 (8)</t>
+  </si>
+  <si>
+    <t>0.297 (6)</t>
+  </si>
+  <si>
+    <t>20-7 (4)</t>
+  </si>
+  <si>
+    <t>Alan de Souza</t>
+  </si>
+  <si>
+    <t>0.368 (10)</t>
+  </si>
+  <si>
+    <t>1-2 (1)</t>
+  </si>
+  <si>
+    <t>0.368 (6)</t>
+  </si>
+  <si>
+    <t>17-7 (1)</t>
+  </si>
+  <si>
+    <t>54E Carlos Danger(45633)</t>
+  </si>
+  <si>
+    <t>0.385 (9)</t>
+  </si>
+  <si>
+    <t>8-9 (3)</t>
+  </si>
+  <si>
+    <t>128J Love County(53773)</t>
+  </si>
+  <si>
+    <t>0.467 (9)</t>
+  </si>
+  <si>
+    <t>6-1 (1)</t>
+  </si>
+  <si>
+    <t>937 Whacky Wizard(52929)</t>
+  </si>
+  <si>
+    <t>PPHT</t>
+  </si>
+  <si>
+    <t>0.249 (7)</t>
+  </si>
+  <si>
+    <t>6-1 (0)</t>
+  </si>
+  <si>
+    <t>7030 After Hours(47126)</t>
+  </si>
+  <si>
+    <t>XVJB</t>
+  </si>
+  <si>
+    <t>0.156 (7)</t>
+  </si>
+  <si>
+    <t>18-13 (8)</t>
+  </si>
+  <si>
+    <t>567 Body Roc(51996)</t>
+  </si>
+  <si>
+    <t>0.423 (10)</t>
+  </si>
+  <si>
+    <t>Bull 22.00%</t>
+  </si>
+  <si>
+    <t>Eduardo Aparecido on 567 Body Roc (PGAO)
+Qualified Ride Probability: 42.3% (confidence 10 of 10)
+Ride Score Potential: 83.15 to 89.15 points
+Eduardo Aparecido Riding Hand: Right
+Career: 496 for 1134 - 43.74% - Rider Rating: *.360
+Short Rounds: 53 for 156 - 33.97%
+Current Streak: 5 / 15 - 33.33%
+PBR Current Season: Rank: 30 (31 for 72 - 43.1%) 189.00 pts (-703.5) - $133,872.04
+PBR Points Per Out: 3 - Points Per QR: 6
+vs. Left: 121-231 (34.38%) -- vs. Right: 238-178 (57.21%) -- vs. ?: 18-50 (26.47%) -- +22.83%/13.47% RIGHT
+567 Body Roc - PBS -
+Power Rating: 66.79
+ALL: 31 outs 13 rides - 58.06%
+UTB: 17 outs 10 rides - 41.18%
+vs. Left:  8-10 - 44.44%
+vs. Right: 6-3 - 66.67%
+vs. Top:   8-10 - 44.44%
+Riding Hand Advantage: LEFT (22.00%)
+Previous Outs for 567 Body Roc
+Event	Level	Matchup	Score	Marks	Time	Notes
+Fort Worth Mar '26	PBR	Blake Geibel	-	21.40 - 21.40	2.62	*
+Bucktown Feb '26	OPEN	Riggs Caldwell	-	21.75 - 21.75	3.03	*
+Milwaukee Jan '26	PBR	* Keyshawn Whitehorse	-	20.90 - 21.15	3.68	*
+Nashville Aug '25	PBR	* Daylon Swearingen	-	19.75 - 18.75	7.46	*
+Fort Worth Jul '25	PBR	Damiao Soares	82.50	20.50 - 20.00	8.00	*
+Oklahoma City Jul '25	PBR	Miguel de Jesus	87.00	21.25 - 21.25	8.00	*
+Rocksprings Jun '25	PBR	Chance Lopez	-	21.50 - 21.50	3.19	*
+Rocksprings Jun '25	PBR	Douglas Lino de Souza	-	21.00 - 21.50	1.97	*
+Palm Springs Mar '25	PBR	* Derek Kolbaba	88.25	21.50 - 21.50	8.00	*
+Salt Lake City Feb '25	PBR	* Koltin Hevalow	87.75	21.25 - 21.50	8.00	*
+Fort Worth Jan '25	PBR	* Ezekiel Mitchell	86.25	21.00 - 21.00	8.00	*
+Denver Jan '25	PBR	Alex Junior da Silva	78.50	20.00 - 19.50	8.00	*
+Denver Jan '25	PBR	* Cole Melancon	-	21.00 - 20.00	6.09	*
+Wichita Dec '24	PBR	* Luciano De Castro	87.00	21.00 - 21.50	8.00	*
+St. Louis Dec '24	PBR	* Cort McFadden	86.25	21.00 - 20.75	8.00	*
+Previous Matchups at probability 0.423
+Rider Count	88
+Avg Rider Rating	.267
+Total Outs	127
+Qualified Rides	65
+Riding %	51.18%
+87+ points	18.11%</t>
+  </si>
+  <si>
+    <t>Manoelito de Souza Junior on 7030 After Hours (XVJB)
+Qualified Ride Probability: 15.6% (confidence 7 of 10)
+Ride Score Potential: 81.86 to 87.86 points
+Manoelito de Souza Junior Riding Hand: Left
+Career: 112 for 417 - 26.86% - Rider Rating: *.202
+Short Rounds: 12 for 60 - 20%
+Current Streak: 1 / 15 - 6.67%
+PBR Current Season: Rank: 35 (6 for 28 - 21.4%) 112.00 pts (-780.5) - $18,250.00
+PBR Points Per Out: 4 - Points Per QR: 19
+vs. Left: 63-83 (43.15%) -- vs. Right: 9-90 (9.09%) -- vs. ?: 13-53 (19.7%) -- +34.06%/16.29% LEFT
+7030 After Hours - PBS -
+Power Rating: 41.71
+ALL: 7 outs 1 rides - 85.71%
+vs. Left:  4-0 - 100.00%
+vs. Right: 2-1 - 66.67%
+vs. Top:   0-0 - 0.00%
+Riding Hand Advantage: UNKNOWN (0.00%)
+Previous Outs for 7030 After Hours
+Event	Level	Matchup	Score	Marks	Time	Notes
+Paris Jul '23	PBR	Laramie Craigen	-	-	-	RR foul
+Fort Worth Aug '22	PBR	Davi Henrique de Lima	-	17.00 - 19.50	6.22	*
+Paris Jul '22	PBR	Levi Hershberger	-	21.50 - 21.00	4.92	*
+Casper Apr '22	PBR	Cole Skender	82.50	20.00 - 20.00	8.00	*
+Knoxville Feb '22	PBR	Colt Robinson	-	21.50 - 21.00	7.10	*
+Memphis Feb '22	PBR	Thor Hoefer II	-	22.00 - 21.50	2.37	*
+North Charleston Feb '22	PBR	Casey Roberts	-	21.50 - 21.00	4.50	*
+Jacksonville Jan '22	PBR	Quentin Vaught	-	21.00 - 21.50	4.75	*
+Previous Matchups at probability 0.156
+Rider Count	257
+Avg Rider Rating	.111
+Total Outs	346
+Qualified Rides	45
+Riding %	13.01%
+87+ points	4.34%</t>
+  </si>
+  <si>
+    <t>Kase Hitt on 937 Whacky Wizard (PPHT)
+Qualified Ride Probability: 24.9% (confidence 7 of 10)
+Ride Score Potential: 83.07 to 89.07 points
+Kase Hitt Riding Hand: Left
+Career: 94 for 332 - 28.31% - Rider Rating: .179
+Short Rounds: 6 for 23 - 26.09%
+Current Streak: 4 / 15 - 26.67%
+PBR Current Season: Rank: 33 (16 for 53 - 30.2%) 137.00 pts (-755.5) - $49,767.31
+PBR Points Per Out: 3 - Points Per QR: 9
+vs. Left: 40-59 (40.4%) -- vs. Right: 15-81 (15.63%) -- vs. ?: 17-28 (37.78%) -- +24.77%/12.09% LEFT
+937 Whacky Wizard - PBS - 10230319
+Power Rating: 58.27
+ALL: 7 outs 1 rides - 85.71%
+vs. Left:  2-0 - 100.00%
+vs. Right: 3-1 - 75.00%
+vs. Top:   1-1 - 50.00%
+Riding Hand Advantage: UNKNOWN (0.00%)
+Previous Outs for 937 Whacky Wizard
+Event	Level	Matchup	Score	Marks	Time	Notes
+Fort Worth Mar '26	PBR	Eikson Pereira	-	21.20 - 20.80	7.58	*
+Fort Worth Jul '25	PBR	Tuff Morgan	-	20.50 - 20.00	2.81	*
+Fort Worth Feb '25	PBR	Rogerio Venancio	-	19.00 - 19.50	6.69	*
+Fort Worth Sep '24	PBR	Callum Miller	-	21.50 - 21.00	4.00	*
+Anaheim Sep '24	PBR	* Dawson Branton	-	22.00 - 21.75	5.20	*
+Anaheim Sep '24	PBR	Grayson Cole	-	22.00 - 21.75	3.13	*
+Fort Lauderdale Aug '24	PBR	* Keyshawn Whitehorse	89.00	21.25 - 22.00	8.00	*
+Previous Matchups at probability 0.249
+Rider Count	264
+Avg Rider Rating	.174
+Total Outs	411
+Qualified Rides	91
+Riding %	22.14%
+87+ points	3.41%</t>
+  </si>
+  <si>
+    <t>Bruno Carvalho on 128J Love County (PGAO)
+Qualified Ride Probability: 46.7% (confidence 9 of 10)
+Ride Score Potential: 83.5 to 89.5 points
+Bruno Carvalho Riding Hand: Left
+Career: 70 for 219 - 31.96% - Rider Rating: *.208
+Short Rounds: 6 for 22 - 27.27%
+Current Streak: 4 / 15 - 26.67%
+PBR Current Season: Rank: 42 (9 for 34 - 26.5%) 71.50 pts (-821) - $30,778.26
+PBR Points Per Out: 2 - Points Per QR: 8
+vs. Left: 33-33 (50%) -- vs. Right: 3-41 (6.82%) -- vs. ?: 10-24 (29.41%) -- +43.18%/18.04% LEFT
+128J Love County - PBS - 10256903
+Power Rating: 48.73
+ALL: 17 outs 9 rides - 47.06%
+UTB: 7 outs 5 rides - 28.57%
+vs. Left:  2-6 - 25.00%
+vs. Right: 6-3 - 66.67%
+vs. Top:   1-8 - 11.11%
+Riding Hand Advantage: LEFT (42.00%)
+Previous Outs for 128J Love County
+Event	Level	Matchup	Score	Marks	Time	Notes
+Cleburne Mar '26	OPEN	* Qynn Andersen	86.60	21.05 - 21.05	8.00	*
+Fort Worth Mar '26	PBR	Tyler Villarreal	-	21.30 - 21.10	2.59	*
+Bucktown Feb '26	OPEN	* Wacey Schalla	85.00	20.50 - 20.50	8.00	*
+Milwaukee Jan '26	PBR	Alison dos Santos	85.45	20.90 - 20.85	8.00	*
+Houma Jan '26	OPEN	* Vinicius Pinheiro Correa	-	20.60 - 20.60	4.09	*
+Granbury Nov '25	OPEN	* Alex Cerqueira	87.50	21.28 - 21.28	8.00	*
+Kansas City Oct '25	PBR	Miguel de Jesus	-	21.25 - 21.00	7.76	*
+Fort Worth Sep '25	PBR	* John Crimber	86.50	20.75 - 20.75	8.00	*
+Anaheim Sep '25	PBR	* Jess Lockwood	89.00	21.50 - 21.50	8.00	*
+Anaheim Sep '25	PBR	* John Crimber	88.25	21.00 - 21.00	8.00	*
+Fort Worth Jun '25	PBR	* Guilherme Valleiras	86.50	21.00 - 21.50	8.00	*
+Decatur May '25	PBR	Leonardo Lima	-	21.00 - 21.50	1.25	*
+Grand Forks Apr '25	PBR	Zane Cook	-	21.00 - 21.00	2.22	*
+Little Rock Mar '25	PBR	* Koltin Hevalow	84.75	20.75 - 21.00	8.00	*
+Little Rock Mar '25	PBR	Trace Redd	-	21.75 - 22.00	3.72	*
+Previous Matchups at probability 0.467
+Rider Count	63
+Avg Rider Rating	.279
+Total Outs	85
+Qualified Rides	42
+Riding %	49.41%
+87+ points	20%</t>
+  </si>
+  <si>
+    <t>Marco Rizzo on 54E Carlos Danger (TFRS)
+Qualified Ride Probability: 38.5% (confidence 9 of 10)
+Ride Score Potential: 82.79 to 88.79 points
+Marco Rizzo Riding Hand: Right
+Career: 62 for 178 - 34.83% - Rider Rating: *.215
+Short Rounds: 4 for 23 - 17.39%
+Current Streak: 6 / 15 - 40.00%
+PBR Current Season: Rank: 9 (27 for 72 - 37.5%) 405.00 pts (-487.5) - $143,765.82
+PBR Points Per Out: 6 - Points Per QR: 15
+vs. Left: 9-37 (19.57%) -- vs. Right: 30-39 (43.48%) -- vs. ?: 8-15 (34.78%) -- +23.91%/8.65% RIGHT
+54E Carlos Danger - PBS - 10215145
+Power Rating: 68.94
+ALL: 24 outs 7 rides - 70.83%
+UTB: 12 outs 4 rides - 66.67%
+vs. Left:  6-2 - 75.00%
+vs. Right: 8-5 - 61.54%
+vs. Top:   8-6 - 57.14%
+Riding Hand Advantage: RIGHT (13.00%)
+Previous Outs for 54E Carlos Danger
+Event	Level	Matchup	Score	Marks	Time	Notes
+Sacramento Jan '26	PBR	Elijah Jennings	84.40	20.40 - 20.70	8.00	*
+Waco Oct '25	PRCA	Gavan Hauck	-	22.50 - 20.50	2.58	*
+Eagle Jul '25	PRCA	Colton Clymer	-	23.00 - 23.00	2.45	*
+Fort Collins Jul '25	PBR	* Sandro Batista	83.50	20.00 - 20.50	8.00	*
+Evergreen Jun '25	PRCA	Adam Cook	-	22.00 - 19.00	4.00	(nt)
+Evergreen Jun '25	PRCA	Cody Wooldridge	-	-	4.00	(nm)(nt)
+Nampa Apr '25	PBR	* Ezekiel Mitchell	-	-	-	RR foul (head rope)
+Fort Worth Mar '25	PBR	Wallace Vieira de Oliveira	-	-	-	RR foul
+Billings Apr '24	PBR	* Silvano Alves	-	19.25 - 20.00	0.09	*
+Fort Worth Mar '24	PBR	* Paulo Eduardo Rossetto	-	21.00 - 20.50	4.31	*
+Fort Worth Mar '24	PBR	* Leandro Machado	83.00	21.00 - 20.00	8.00	*
+Fort Worth Feb '24	PBR	* Cassio Dias	-	-	-	RR foul
+Fort Worth Feb '24	PBR	Bruno Jose Barros	-	-	-	DQ chute
+Fort Worth Jan '24	PBR	Leonardo Lima	-	21.00 - 20.00	2.24	*
+Fort Worth Dec '23	PBR	Cody McCandless	-	20.50 - 21.00	5.86	*
+Previous Matchups at probability 0.385
+Rider Count	133
+Avg Rider Rating	.236
+Total Outs	193
+Qualified Rides	75
+Riding %	38.86%
+87+ points	12.95%</t>
+  </si>
+  <si>
+    <t>Cassio Dias on 012 Crockett (BMJM)
+Qualified Ride Probability: 37.1% (confidence 6 of 10)
+Ride Score Potential: 84.77 to 90.77 points
+Cassio Dias Riding Hand: Right
+Career: 125 for 249 - 50.2% - Rider Rating: *.410
+Short Rounds: 18 for 32 - 56.25%
+Current Streak: 3 / 15 - 20.00%
+PBR Current Season: Rank: 19 (13 for 45 - 28.9%) 295.50 pts (-597) - $98,807.28
+PBR Points Per Out: 7 - Points Per QR: 23
+vs. Left: 23-40 (36.51%) -- vs. Right: 79-44 (64.23%) -- vs. ?: 12-16 (42.86%) -- +27.72%/14.03% RIGHT
+012 Crockett PBS
+no compiled stats
+Previous Outs for 012 Crockett
+Event	Level	Matchup	Score	Marks	Time	Notes
+Billings Apr '26	PBR	* Julio Cesar Marques	83.15	20.80 - 20.90	8.00	*
+Belton Feb '26	OPEN	Jeferson Silva	-	20.98 - 20.98	5.97	*
+Perry Feb '26	PRCA	Cooper Caldwell	91.00	23.00 - 22.00	8.00	*
+Previous Matchups at probability 0.371
+Rider Count	140
+Avg Rider Rating	.235
+Total Outs	204
+Qualified Rides	86
+Riding %	42.16%
+87+ points	8.82%</t>
+  </si>
+  <si>
+    <t>Alan de Souza on 933G Gene's Best (BMJM)
+Qualified Ride Probability: 36.8% (confidence 10 of 10)
+Ride Score Potential: 82.98 to 88.98 points
+Alan de Souza Riding Hand: Right
+Career: 211 for 397 - 53.15% - Rider Rating: *.339
+Short Rounds: 24 for 48 - 50%
+Current Streak: 4 / 15 - 26.67%
+PBR Current Season: Rank: 31 (35 for 70 - 50%) 178.00 pts (-714.5) - $102,574.30
+PBR Points Per Out: 3 - Points Per QR: 5
+vs. Left: 38-62 (38%) -- vs. Right: 109-70 (60.89%) -- vs. ?: 22-15 (59.46%) -- +22.89%/7.74% RIGHT
+933G Gene's Best - PBS - 10229185
+Power Rating: 71.00
+ALL: 27 outs 7 rides - 74.07%
+UTB: 13 outs 7 rides - 46.15%
+vs. Left:  4-6 - 40.00%
+vs. Right: 14-1 - 93.33%
+vs. Top:   9-6 - 60.00%
+Riding Hand Advantage: LEFT (53.00%)
+Previous Outs for 933G Gene's Best
+Event	Level	Matchup	Score	Marks	Time	Notes
+Billings Apr '26	PBR	* Jess Lockwood	88.45	21.90 - 21.20	8.00	*
+Perry Feb '26	PRCA	* Hayes Weight	-	12.00 - 12.00	4.00	(nmb)(nt)
+Tulsa Jan '26	PBR	Damien Krushall	-	21.00 - 20.90	1.60	*
+Bangor Jan '26	PBR	Claudio Rogerio Alves Junior	-	21.60 - 21.80	6.41	*
+Bangor Jan '26	PBR	Grayson Cole	-	21.80 - 22.00	4.21	*
+Green Bay Sep '25	PBR	* Kyler Oliver	-	21.00 - 21.00	6.12	*
+Kansas City Apr '25	PBR	Thomas Hudson	-	19.50 - 16.50	-	RR inf
+Ardmore Mar '25	PRCAX	Jacob Carige	-	21.50 - 21.00	4.40	*
+Austin Mar '25	PRCA	Maverick Potter	-	-	-	RR foul
+Little Rock Mar '25	PBR	* Austin Richardson	-	21.25 - 21.50	6.31	*
+Jacksonville Feb '25	PBR	* John Crimber	86.00	21.00 - 20.50	8.00	*
+Salt Lake City Feb '25	PBR	* Dalton Kasel	-	22.00 - 22.50	6.36	*
+Sacramento Jan '25	PBR	* Luciano De Castro	90.75	22.00 - 22.25	8.00	*
+Sacramento Jan '25	PBR	* Keyshawn Whitehorse	-	21.50 - 21.00	4.00	*
+Sacramento Jan '25	PBR	* Claudio Montanha Jr.	-	-	-	RR chute
+Previous Matchups at probability 0.368
+Rider Count	135
+Avg Rider Rating	.235
+Total Outs	204
+Qualified Rides	90
+Riding %	44.12%
+87+ points	11.76%</t>
+  </si>
+  <si>
+    <t>Alex Cerqueira on 127 Bulldog (BMJM)
+Qualified Ride Probability: 30.1% (confidence 6 of 10)
+Ride Score Potential: 83.67 to 89.67 points
+Alex Cerqueira Riding Hand: Left
+Career: 197 for 513 - 38.4% - Rider Rating: *.270
+Short Rounds: 22 for 60 - 36.67%
+Current Streak: 6 / 15 - 40.00%
+PBR Current Season: Rank: 6 (33 for 65 - 50.8%) 502.50 pts (-390) - $162,721.28
+PBR Points Per Out: 8 - Points Per QR: 15
+vs. Left: 110-93 (54.19%) -- vs. Right: 32-108 (22.86%) -- vs. ?: 14-24 (36.84%) -- +31.33%/15.79% LEFT
+127 Bulldog PBS 10250898
+no compiled stats
+Previous Outs for 127 Bulldog
+Event	Level	Matchup	Score	Marks	Time	Notes
+Billings Apr '26	PBR	Kase Hitt	-	21.50 - 21.20	3.69	*
+Little Rock Mar '26	PBR	* Sage Kimzey	-	20.80 - 20.45	5.67	*
+Belton Feb '26	OPEN	Braydan Kilcrease	-	21.53 - 21.53	3.97	*
+Previous Matchups at probability 0.301
+Rider Count	235
+Avg Rider Rating	.194
+Total Outs	340
+Qualified Rides	92
+Riding %	27.06%
+87+ points	9.12%</t>
+  </si>
+  <si>
+    <t>Romario Leite on 106 MF Darkside (BSBL)
+Qualified Ride Probability: 38.9% (confidence 8 of 10)
+Ride Score Potential: 83.32 to 89.32 points
+Romario Leite Riding Hand: Left
+Career: 25 for 78 - 32.05% - Rider Rating: .156
+Short Rounds: 1 for 8 - 12.5%
+Current Streak: 3 / 15 - 20.00%
+PBR Current Season: Rank: 60 (1 for 11 - 9.1%) 8.00 pts (-884.5) - $9,446.45
+PBR Points Per Out: 1 - Points Per QR: 8
+vs. Left: 11-8 (57.89%) -- vs. Right: 3-12 (20%) -- vs. ?: 4-14 (22.22%) -- +37.89%/25.84% LEFT
+106 MF Darkside - PBS -
+Power Rating: 52.32
+ALL: 10 outs 6 rides - 40%
+UTB: 9 outs 6 rides - 33.33%
+vs. Left:  2-6 - 25.00%
+vs. Right: 2-0 - 100.00%
+vs. Top:   2-4 - 33.33%
+Riding Hand Advantage: LEFT (75.00%)
+Previous Outs for 106 MF Darkside
+Event	Level	Matchup	Score	Marks	Time	Notes
+Bridgeport Feb '26	PBR	* Bruno Carvalho	81.70	19.90 - 20.40	8.00	*
+Jacksonville Feb '26	PBR	* Andrew Alvidrez	-	20.70 - 21.20	6.04	*
+Pittsburgh Feb '26	PBR	* Thiago Salgado	85.15	21.15 - 21.20	8.00	*
+Milwaukee Jan '26	PBR	* John Crimber	87.60	21.35 - 21.15	8.00	*
+New York Jan '26	PBR	* Afonso Quintino	85.80	20.95 - 21.10	8.00	*
+Manchester Dec '25	PBR	* Bob Mitchell	86.85	21.30 - 20.95	8.00	*
+Las Vegas Oct '25	PBR	Winy dos Santos	-	21.25 - 21.00	7.76	*
+Las Vegas Oct '25	PBR	Lauro Nunes Vieira	-	20.75 - 20.75	4.29	*
+Glendale Oct '25	PBR	* Everton Natan da Silva	87.75	21.50 - 21.50	8.00	*
+Glendale Oct '25	PBR	* Boudreaux Campbell	-	21.50 - 22.00	3.50	*
+Previous Matchups at probability 0.389
+Rider Count	119
+Avg Rider Rating	.243
+Total Outs	167
+Qualified Rides	73
+Riding %	43.71%
+87+ points	14.37%</t>
+  </si>
+  <si>
+    <t>Bob Mitchell on 012H Sunrise (BSBL)
+Qualified Ride Probability: 54.2% (confidence 9 of 10)
+Ride Score Potential: 83.96 to 89.96 points
+Bob Mitchell Riding Hand: Left
+Career: 183 for 462 - 39.61% - Rider Rating: *.283
+Short Rounds: 18 for 73 - 24.66%
+Current Streak: 10 / 15 - 66.67%
+PBR Current Season: Rank: 13 (34 for 62 - 54.8%) 396.00 pts (-496.5) - $123,666.07
+PBR Points Per Out: 6 - Points Per QR: 12
+vs. Left: 98-90 (52.13%) -- vs. Right: 32-89 (26.45%) -- vs. ?: 18-24 (42.86%) -- +25.68%/12.52% LEFT
+012H Sunrise - PBS -
+Power Rating: 59.59
+ALL: 17 outs 7 rides - 58.82%
+UTB: 11 outs 7 rides - 36.36%
+vs. Left:  2-2 - 50.00%
+vs. Right: 7-5 - 58.33%
+vs. Top:   4-6 - 40.00%
+Riding Hand Advantage: LEFT (8.00%)
+Previous Outs for 012H Sunrise
+Event	Level	Matchup	Score	Marks	Time	Notes
+Billings Apr '26	PBR	* Jose Vitor Leme	87.20	21.30 - 21.20	8.00	*
+Bridgeport Feb '26	PBR	Elijah Jennings	-	21.05 - 21.70	6.32	*
+Jacksonville Feb '26	PBR	* Joao Ricardo Vieira	82.65	19.90 - 20.30	8.00	*
+Pittsburgh Feb '26	PBR	* Cort McFadden	87.40	21.05 - 21.30	8.00	*
+Tampa Jan '26	PBR	* Sage Kimzey	88.10	21.40 - 21.50	8.00	*
+Milwaukee Jan '26	PBR	* Leandro Zampollo	-	21.85 - 21.80	4.27	*
+Milwaukee Jan '26	PBR	JaCauy Hale	-	21.35 - 21.80	1.92	*
+Manchester Dec '25	PBR	Callum Miller	86.65	21.10 - 21.05	8.00	*
+Las Vegas Oct '25	PBR	* Cooper Davis	87.25	21.25 - 21.50	8.00	*
+Las Vegas Oct '25	PBR	Alex Junior da Silva	-	21.25 - 21.25	2.73	*
+Glendale Oct '25	PBR	* Alan de Souza	84.75	21.25 - 21.00	8.00	*
+Glendale Oct '25	PBR	* Andrew Alvidrez	-	21.50 - 21.50	6.17	*
+Topeka Jul '25	PBR	Boston Leather	-	21.50 - 21.50	1.99	*
+Tallahassee Mar '25	PBR	Weslei Ferreira de Jesus	-	22.00 - 21.00	1.17	*
+Lexington Mar '25	PBR	Brody Robinson	-	21.00 - 21.00	2.54	*
+Previous Matchups at probability 0.542
+Rider Count	28
+Avg Rider Rating	.303
+Total Outs	31
+Qualified Rides	17
+Riding %	54.84%
+87+ points	16.13%</t>
+  </si>
+  <si>
+    <t>Daniel Keeping on 38K Masterpiece (BSBL)
+Qualified Ride Probability: 34.5% (confidence 5 of 10)
+Ride Score Potential: -1 to 5 points
+Daniel Keeping Riding Hand: Left
+Career: 162 for 417 - 38.85% - Rider Rating: *.273
+Short Rounds: 10 for 45 - 22.22%
+Current Streak: 6 / 15 - 40.00%
+PBR Current Season: Rank: 21 (33 for 71 - 46.5%) 255.00 pts (-637.5) - $146,643.44
+PBR Points Per Out: 4 - Points Per QR: 8
+vs. Left: 99-76 (56.57%) -- vs. Right: 18-85 (17.48%) -- vs. ?: 13-26 (33.33%) -- +39.09%/17.72% LEFT
+38K Masterpiece PBS 10268379
+no compiled stats
+no recorded outs
+Previous Matchups at probability 0.345
+Rider Count	158
+Avg Rider Rating	.230
+Total Outs	235
+Qualified Rides	89
+Riding %	37.87%
+87+ points	10.64%</t>
+  </si>
+  <si>
+    <t>Jess Lockwood on 071H Apple Juicing (WI)
+Qualified Ride Probability: 36.4% (confidence 10 of 10)
+Ride Score Potential: 83.71 to 89.71 points
+Jess Lockwood Riding Hand: Left
+Career: 268 for 553 - 48.46% - Rider Rating: *.408
+Short Rounds: 42 for 100 - 42%
+Current Streak: 8 / 15 - 53.33%
+PBR Current Season: Rank: 20 (20 for 42 - 47.6%) 292.00 pts (-600.5) - $230,842.06
+PBR Points Per Out: 7 - Points Per QR: 15
+vs. Left: 142-99 (58.92%) -- vs. Right: 44-86 (33.85%) -- vs. ?: 23-26 (46.94%) -- +25.07%/10.46% LEFT
+071H Apple Juicing - PBS -
+Power Rating: 67.21
+ALL: 29 outs 3 rides - 89.66%
+vs. Left:  9-0 - 100.00%
+vs. Right: 12-3 - 80.00%
+vs. Top:   4-2 - 66.67%
+Riding Hand Advantage: RIGHT (20.00%)
+Previous Outs for 071H Apple Juicing
+Event	Level	Matchup	Score	Marks	Time	Notes
+Oakland Apr '26	PBR	Edgardo Figueroa	-	21.60 - 21.00	1.87	*
+Fresno Mar '26	PBR	Jairo Castellanos	-	21.10 - 21.80	2.25	*
+Bakersfield Mar '26	PBR	* Braidy Randolph	-	21.50 - 21.60	6.72	*
+Sacramento Jan '26	PBR	* Clay Guiton	87.00	21.10 - 20.95	8.00	*
+Ontario Jan '26	PBR	Landen Jones	-	20.70 - 21.30	1.52	*
+Ontario Jan '26	PBR	* Vinicius Pinheiro Correa	-	22.10 - 21.60	3.21	*
+Red Bluff Dec '25	PRCA	Ray Mayo	-	21.00 - 20.50	3.22	*
+Glendale Oct '25	PBR	* Eduardo Aparecido	-	21.00 - 21.00	3.71	*
+Bremerton Aug '25	PRCAX	Gavin Mitchell	-	21.50 - 21.00	3.28	*
+Bremerton Aug '25	PRCA	Rawley Johnson	-	-	-	RR foul
+Salinas Jul '25	PRCAX	Andy Valdez	-	22.00 - 21.00	1.61	*
+Reno Jun '25	PRCA	Kase Hitt	-	20.50 - 22.50	1.68	*
+Reno Jun '25	PRCAX	Ernie Courson	84.00	22.00 - 22.00	8.00	*
+Lakeside Apr '25	PRCA	Jate Frost	-	20.00 - 20.50	4.00	(nt)
+Oakland Apr '25	PBR	Jacob David	-	21.00 - 21.50	2.53	*
+Previous Matchups at probability 0.364
+Rider Count	140
+Avg Rider Rating	.231
+Total Outs	210
+Qualified Rides	94
+Riding %	44.76%
+87+ points	11.43%</t>
+  </si>
+  <si>
+    <t>Andrew Alvidrez on 02K Smoke Screen (HWKN)
+Qualified Ride Probability: 20.9% (confidence 7 of 10)
+Ride Score Potential: 86.19 to 92.19 points
+Andrew Alvidrez Riding Hand: Right
+Career: 233 for 735 - 31.7% - Rider Rating: *.245
+Short Rounds: 29 for 99 - 29.29%
+Current Streak: 4 / 15 - 26.67%
+PBR Current Season: Rank: 25 (19 for 64 - 29.7%) 219.00 pts (-673.5) - $154,923.02
+PBR Points Per Out: 3 - Points Per QR: 12
+vs. Left: 58-175 (24.89%) -- vs. Right: 104-146 (41.6%) -- vs. ?: 24-52 (31.58%) -- +16.71%/9.9% RIGHT
+02K Smoke Screen - PBS - 10272036
+Power Rating: 75.92
+ALL: 8 outs 0 rides - 100%
+vs. Left:  2-0 - 100.00%
+vs. Right: 3-0 - 100.00%
+vs. Top:   2-0 - 100.00%
+Riding Hand Advantage: UNKNOWN (0.00%)
+Previous Outs for 02K Smoke Screen
+Event	Level	Matchup	Score	Marks	Time	Notes
+Oakland Apr '26	PBR	* Vitor Losnake	-	22.70 - 22.60	1.87	*
+Palm Desert Mar '26	PBR	Dakota Johnson	-	22.10 - 21.10	2.80	*
+Bakersfield Mar '26	PBR	* Dener Barbosa	-	22.00 - 21.80	4.94	*
+Reno Feb '26	PBR	Dakota Johnson	-	21.50 - 20.95	4.26	*
+Ontario Jan '26	PBR	Dione de Souza Ribeiro	-	21.20 - 21.40	4.57	*
+Portland Jan '26	PBR	Dakota Johnson	-	21.40 - 21.80	4.02	*
+Portland Jan '26	PBR	Levi Quillan	-	22.00 - 21.20	3.09	*
+Ardmore Mar '25	PRCAX	Ernie Courson	-	22.00 - 23.00	4.78	*
+Previous Matchups at probability 0.209
+Rider Count	250
+Avg Rider Rating	.155
+Total Outs	366
+Qualified Rides	74
+Riding %	20.22%
+87+ points	4.37%</t>
+  </si>
+  <si>
+    <t>Daylon Swearingen on 829 Ugly This (CMCY)
+Qualified Ride Probability: 48% (confidence 10 of 10)
+Ride Score Potential: 85.25 to 91.25 points
+Daylon Swearingen Riding Hand: Left
+Career: 352 for 823 - 42.77% - Rider Rating: *.341
+Short Rounds: 47 for 123 - 38.21%
+Current Streak: 7 / 15 - 46.67%
+PBR Current Season: Rank: 16 (19 for 46 - 41.3%) 362.50 pts (-530) - $150,772.22
+PBR Points Per Out: 8 - Points Per QR: 19
+vs. Left: 204-165 (55.28%) -- vs. Right: 55-143 (27.78%) -- vs. ?: 23-48 (32.39%) -- +27.5%/12.51% LEFT
+829 Ugly This - PBS -
+Power Rating: 78.86
+ALL: 74 outs 22 rides - 70.27%
+UTB: 32 outs 15 rides - 53.13%
+vs. Left:  23-16 - 58.97%
+vs. Right: 22-6 - 78.57%
+vs. Top:   27-19 - 58.70%
+Riding Hand Advantage: LEFT (20.00%)
+Previous Matchups
+Event	Level	Matchup	Score	Marks	Time	Notes
+Las Vegas Oct '24	PBR	Daylon Swearingen on 48315	89.75	21.75 - 21.25	8.00	*
+Previous Outs for 829 Ugly This
+Event	Level	Matchup	Score	Marks	Time	Notes
+New Orleans Apr '26	HONDO	* Boudreaux Campbell	-	21.80 - 21.90	4.09	*
+New Orleans Apr '26	HONDO	* Hayden Welsh	88.90	21.60 - 21.90	8.00	*
+Albuquerque Mar '26	PBR	* Bob Mitchell	86.90	21.20 - 21.15	8.00	*
+Mercedes Mar '26	PRCAX	Cody Fraser	-	20.50 - 19.50	3.96	*
+Mercedes Mar '26	PRCAX	* Wacey Schalla	-	-	-	TO
+Mercedes Mar '26	PRCAX	Hayden Ferguson	-	21.00 - 22.50	3.66	*
+Tallahassee Mar '26	PBR	* Bruno Carvalho	85.75	21.10 - 21.00	8.00	*
+Little Rock Mar '26	PBR	* Koltin Hevalow	87.55	21.30 - 21.40	8.00	*
+Jacksonville Feb '26	PBR	Andy Guzman	-	20.95 - 21.60	2.71	*
+Guthrie Feb '26	PRCAX	Wyatt Bowman	-	20.00 - 21.00	4.00	(nt)
+Guthrie Feb '26	PRCAX	Tucker Root	-	20.00 - 21.50	4.00	(nt)
+Pawhuska Jan '26	PRCA	Patterson Starcher	-	20.00 - 21.00	4.00	(nt)
+New York Jan '26	PBR	* Qynn Andersen	-	21.30 - 21.40	6.53	*
+Las Vegas (NFR) Dec '25	PRCA	* Hayes Weight	-	21.75 - 21.50	4.02	*
+Las Vegas (NFR) Dec '25	PRCA	* Luke Mackey	82.50	21.00 - 19.75	8.00	*
+Previous Matchups at probability 0.48
+Rider Count	60
+Avg Rider Rating	.279
+Total Outs	78
+Qualified Rides	44
+Riding %	56.41%
+87+ points	15.38%</t>
+  </si>
+  <si>
+    <t>Thiago Salgado on 102 Cracky Chan (CLPB)
+Qualified Ride Probability: 39% (confidence 9 of 10)
+Ride Score Potential: 83.56 to 89.56 points
+Thiago Salgado Riding Hand: Left
+Career: 176 for 430 - 40.93% - Rider Rating: *.281
+Short Rounds: 16 for 50 - 32%
+Current Streak: 4 / 15 - 26.67%
+PBR Current Season: Rank: 24 (38 for 74 - 51.4%) 224.00 pts (-668.5) - $173,189.21
+PBR Points Per Out: 3 - Points Per QR: 6
+vs. Left: 103-89 (53.65%) -- vs. Right: 20-82 (19.61%) -- vs. ?: 15-18 (45.45%) -- +34.04%/12.72% LEFT
+102 Cracky Chan - PBS -
+Power Rating: 57.72
+ALL: 15 outs 5 rides - 66.67%
+UTB: 6 outs 4 rides - 33.33%
+vs. Left:  6-1 - 85.71%
+vs. Right: 3-4 - 42.86%
+vs. Top:   3-5 - 37.50%
+Riding Hand Advantage: RIGHT (43.00%)
+Previous Outs for 102 Cracky Chan
+Event	Level	Matchup	Score	Marks	Time	Notes
+Oakland Apr '26	PBR	Justice Forsythe	-	19.60 - 20.50	1.19	*
+Salt Lake City Feb '26	PBR	* Cort McFadden	-	21.25 - 21.60	6.93	*
+Sacramento Jan '26	PBR	* Luciano De Castro	-	20.95 - 21.25	3.23	*
+Sacramento Jan '26	PBR	* Maverick Smith	85.70	21.35 - 20.80	8.00	*
+Ontario Jan '26	PBR	Kingston Herrero	-	22.30 - 22.10	2.03	*
+Anaheim Sep '25	PBR	* Claudio Montanha Jr.	86.00	21.00 - 21.00	8.00	*
+Anaheim Sep '25	PBR	* Keyshawn Whitehorse	-	-	-	RR foul
+Anaheim Sep '25	PBR	* Paulo Eduardo Rossetto	86.25	21.00 - 21.00	8.00	*
+Oakland Apr '25	PBR	* Bob Mitchell	86.00	21.00 - 21.00	8.00	*
+Palm Springs Mar '25	PBR	* Andrew Alvidrez	85.00	20.50 - 20.50	8.00	*
+Fort Worth Jan '25	PBR	* Koltin Hevalow	-	21.00 - 21.25	6.61	*
+Fort Worth Jan '25	PBR	* Austin Richardson	-	21.75 - 21.25	-	RR no nod
+Denver Jan '25	PBR	* Ednelio Rodrigues	-	21.50 - 21.00	3.58	*
+Denver Jan '25	PBR	Eric Henrique Domingos	-	21.50 - 21.00	5.36	*
+Queen Creek Nov '24	PRCAX	Rawley Johnson	-	21.50 - 21.00	4.00	(nt)
+Previous Matchups at probability 0.39
+Rider Count	117
+Avg Rider Rating	.248
+Total Outs	168
+Qualified Rides	77
+Riding %	45.83%
+87+ points	12.5%</t>
+  </si>
+  <si>
+    <t>Joao Ricardo Vieira on 891F Testified (PGAO)
+Qualified Ride Probability: 27% (confidence 8 of 10)
+Ride Score Potential: 84.24 to 90.24 points
+Joao Ricardo Vieira Riding Hand: Left
+Career: 599 for 1325 - 45.21% - Rider Rating: *.356
+Short Rounds: 86 for 200 - 43%
+Current Streak: 2 / 15 - 13.33%
+PBR Current Season: Rank: 37 (18 for 52 - 34.6%) 92.50 pts (-800) - $83,389.62
+PBR Points Per Out: 2 - Points Per QR: 5
+vs. Left: 359-237 (60.23%) -- vs. Right: 81-232 (25.88%) -- vs. ?: 46-52 (46.94%) -- +34.35%/15.02% LEFT
+891F Testified - PBS - 10276006
+Power Rating: 65.19
+ALL: 10 outs 1 rides - 90%
+vs. Left:  1-0 - 100.00%
+vs. Right: 6-1 - 85.71%
+vs. Top:   2-1 - 66.67%
+Riding Hand Advantage: RIGHT (14.00%)
+Previous Outs for 891F Testified
+Event	Level	Matchup	Score	Marks	Time	Notes
+Bucktown Feb '26	OPEN	* Wacey Schalla	89.00	21.50 - 21.50	8.00	*
+Fort Worth Jan '26	PBR	Tennessee Owens	-	20.90 - 21.30	2.23	*
+Sioux Falls Sep '25	PRCA	Rawley Johnson	-	22.25 - 22.00	6.78	*
+Albuquerque Sep '25	PRCAX	Tyce Willis	-	21.50 - 20.00	6.35	*
+Albuquerque Sep '25	PRCAX	Hudson Williams	-	20.00 - 23.00	2.06	*
+Ogden Jul '25	PRCA	Jestyn Jax Woodward	-	22.50 - 22.00	5.11	*
+Ogden Jul '25	PRCA	Tristan Mize	-	22.00 - 22.00	2.69	*
+Oklahoma City Jul '25	PBR	* Braidy Randolph	-	19.50 - 19.25	6.87	*
+Oklahoma City Jul '25	PBR	* Guilherme Valleiras	-	21.00 - 20.75	3.09	*
+Belton Feb '25	OPEN	Jack Mitchell	-	21.63 - 21.63	2.56	*
+Previous Matchups at probability 0.27
+Rider Count	235
+Avg Rider Rating	.187
+Total Outs	358
+Qualified Rides	93
+Riding %	25.98%
+87+ points	5.31%</t>
+  </si>
+  <si>
+    <t>Andy Guzman on 0498 Long Gone (THCC)
+Qualified Ride Probability: 22.3% (confidence 9 of 10)
+Ride Score Potential: 84.22 to 90.22 points
+Andy Guzman Riding Hand: Left
+Career: 51 for 222 - 22.97% - Rider Rating: .119
+Short Rounds: 5 for 22 - 22.73%
+Current Streak: 1 / 15 - 6.67%
+PBR Current Season: Rank: 40 (4 for 30 - 13.3%) 78.00 pts (-814.5) - $11,800.00
+PBR Points Per Out: 3 - Points Per QR: 20
+vs. Left: 18-49 (26.87%) -- vs. Right: 4-52 (7.14%) -- vs. ?: 13-25 (34.21%) -- +19.73%/3.9% LEFT
+0498 Long Gone - PBS - 10243159
+Power Rating: 66.97
+ALL: 23 outs 4 rides - 82.61%
+UTB: 7 outs 2 rides - 71.43%
+vs. Left:  7-3 - 70.00%
+vs. Right: 10-1 - 90.91%
+vs. Top:   5-3 - 62.50%
+Riding Hand Advantage: LEFT (21.00%)
+Previous Outs for 0498 Long Gone
+Event	Level	Matchup	Score	Marks	Time	Notes
+Reno Feb '26	PBR	Chase Hamlin	-	21.80 - 21.70	1.80	*
+Reno Feb '26	PBR	Zane Cook	-	21.35 - 21.50	2.10	*
+Lexington Feb '26	PBR	Vinicius Rodrigues Pereira	-	20.45 - 20.30	6.30	*
+Tulsa Jan '26	PBR	Zane Cook	-	22.10 - 22.30	2.00	*
+Tucson Dec '25	PBR	Ayslan Jeferson	-	21.25 - 21.05	2.51	*
+Las Vegas Oct '25	PBR	Alvaro Ariel	-	22.00 - 21.25	1.55	*
+Las Vegas Oct '25	PBR	Wyatt Rogers	-	-	-	RR chute
+Springfield Aug '25	PBR	* Cody Jesus	-	21.75 - 21.50	6.69	*
+Springfield Aug '25	PBR	* Everton Natan da Silva	87.75	21.50 - 21.25	8.00	*
+Austin Aug '25	PBR	* Koltin Hevalow	-	20.25 - 20.25	7.75	*
+Oklahoma City Jul '25	PBR	* Daylon Swearingen	87.00	21.00 - 21.00	8.00	*
+Oklahoma City Jul '25	PBR	* Dalton Kasel	-	21.75 - 21.75	6.37	*
+Tallahassee Mar '25	PBR	Wyatt Rogers	-	21.50 - 21.00	2.46	*
+Laredo Jan '25	PBR	Guthrie Long	-	22.00 - 21.50	3.98	*
+Birmingham Jan '25	PBR	Carlos Garcia	-	20.00 - 22.00	3.37	*
+Previous Matchups at probability 0.223
+Rider Count	267
+Avg Rider Rating	.160
+Total Outs	371
+Qualified Rides	83
+Riding %	22.37%
+87+ points	4.85%</t>
+  </si>
+  <si>
+    <t>Mauricio Gulla Moreira on 68E Oreo (THCC)
+Qualified Ride Probability: 21.3% (confidence 10 of 10)
+Ride Score Potential: 85.28 to 91.28 points
+Mauricio Gulla Moreira Riding Hand: Left
+Career: 154 for 517 - 29.79% - Rider Rating: *.248
+Short Rounds: 10 for 57 - 17.54%
+Current Streak: 1 / 15 - 6.67%
+PBR Current Season: Rank: 38 (21 for 72 - 29.2%) 86.00 pts (-806.5) - $86,037.98
+PBR Points Per Out: 1 - Points Per QR: 4
+vs. Left: 81-124 (39.51%) -- vs. Right: 24-126 (16%) -- vs. ?: 14-27 (34.15%) -- +23.51%/9.72% LEFT
+68E Oreo - PBS - 10205390
+Power Rating: 75.71
+ALL: 33 outs 8 rides - 75.76%
+UTB: 11 outs 4 rides - 63.64%
+vs. Left:  10-0 - 100.00%
+vs. Right: 12-8 - 60.00%
+vs. Top:   12-8 - 60.00%
+Riding Hand Advantage: RIGHT (40.00%)
+Previous Outs for 68E Oreo
+Event	Level	Matchup	Score	Marks	Time	Notes
+Ennis Oct '25	OPEN	* Lane Vaughan	87.30	21.45 - 21.45	8.00	*
+Fort Worth Jul '25	PBR	Natanael Serra Aires	-	21.50 - 21.00	5.31	*
+Fort Worth Jan '25	PBR	Mossy Waite	-	20.00 - 21.00	6.44	*
+Anaheim Sep '24	PBR	* Julio Cesar Marques	88.50	21.50 - 21.75	8.00	*
+New York Aug '24	PBR	* Leandro Machado	-	19.75 - 20.50	1.61	*
+Fort Lauderdale Aug '24	PBR	* Silvano Alves	-	21.25 - 21.25	7.16	*
+Fort Lauderdale Aug '24	PBR	* Kaique Pacheco	85.00	20.25 - 22.00	8.00	*
+Fort Worth Jun '24	PBR	Dione de Souza Ribeiro	-	23.00 - 22.50	1.51	*
+Liberty May '24	OPEN	* Lane Vaughan	-	22.05 - 22.05	4.45	*
+Corpus Christi May '24	PBR	* Paulo Eduardo Rossetto	89.00	21.50 - 21.75	8.00	*
+Wichita Apr '24	PBR	* Elizmar Jeremias	-	21.00 - 21.50	1.49	*
+Mobile Mar '24	PBR	Alvaro Ariel	-	21.00 - 21.50	1.44	*
+Youngstown Feb '24	PBR	João Paulo Fernandes	-	21.00 - 21.50	3.26	*
+Reno Jan '24	PBR	* Leonardo Castro	90.50	22.50 - 21.50	8.00	*
+Grandview Aug '23	OPEN	Fernando Da Conceicao	-	21.93 - 21.93	2.65	*
+Previous Matchups at probability 0.213
+Rider Count	271
+Avg Rider Rating	.153
+Total Outs	387
+Qualified Rides	75
+Riding %	19.38%
+87+ points	2.58%</t>
+  </si>
+  <si>
+    <t>Luciano De Castro on 497 MF Cupcake (BSBL)
+Qualified Ride Probability: 35.1% (confidence 6 of 10)
+Ride Score Potential: 87.4 to 93.4 points
+Luciano De Castro Riding Hand: Left
+Career: 353 for 770 - 45.84% - Rider Rating: *.341
+Short Rounds: 47 for 108 - 43.52%
+Current Streak: 9 / 15 - 60.00%
+PBR Current Season: Rank: 18 (36 for 74 - 48.6%) 304.00 pts (-588.5) - $151,952.86
+PBR Points Per Out: 4 - Points Per QR: 8
+vs. Left: 207-121 (63.11%) -- vs. Right: 42-136 (23.6%) -- vs. ?: 22-36 (37.93%) -- +39.51%/17.27% LEFT
+497 MF Cupcake PBS
+no compiled stats
+Previous Outs for 497 MF Cupcake
+Event	Level	Matchup	Score	Marks	Time	Notes
+Billings Apr '26	PBR	* Mauricio Gulla Moreira	-	22.05 - 22.15	1.36	*
+Previous Matchups at probability 0.351
+Rider Count	148
+Avg Rider Rating	.238
+Total Outs	245
+Qualified Rides	84
+Riding %	34.29%
+87+ points	10.2%</t>
+  </si>
+  <si>
+    <t>Alex Junior da Silva on 2719 Unhinged (WI)
+Qualified Ride Probability: 16.3% (confidence 10 of 10)
+Ride Score Potential: 83.27 to 89.27 points
+Alex Junior da Silva Riding Hand: Right
+Career: 45 for 158 - 28.48% - Rider Rating: .160
+Short Rounds: 2 for 17 - 11.76%
+Current Streak: 5 / 15 - 33.33%
+PBR Current Season: Rank: 43 (4 for 12 - 33.3%) 49.50 pts (-843) - $4,025.00
+PBR Points Per Out: 4 - Points Per QR: 12
+vs. Left: 8-47 (14.55%) -- vs. Right: 16-12 (57.14%) -- vs. ?: 8-14 (36.36%) -- +42.59%/28.66% RIGHT
+2719 Unhinged - PBS - 10231548
+Power Rating: 77.82
+ALL: 27 outs 1 rides - 96.3%
+vs. Left:  7-1 - 87.50%
+vs. Right: 16-0 - 100.00%
+vs. Top:   6-0 - 100.00%
+Riding Hand Advantage: LEFT (13.00%)
+Previous Matchups
+Event	Level	Matchup	Score	Marks	Time	Notes
+Fort Worth Feb '25	PBR	Alex Junior da Silva on 49727	-	21.00 - 21.50	1.71	*
+Previous Outs for 2719 Unhinged
+Event	Level	Matchup	Score	Marks	Time	Notes
+Fresno Mar '26	PBR	Jace Catlin	-	20.50 - 21.30	1.60	*
+Palm Desert Mar '26	PBR	Zane Cook	-	21.50 - 21.60	2.71	*
+Vernal Mar '26	PRCAX	* Dawson Branton	-	21.50 - 19.00	2.55	*
+Vernal Mar '26	PRCAX	Connor Trevathan	-	22.00 - 22.50	3.12	*
+Sacramento Jan '26	PBR	* Cort McFadden	-	20.85 - 20.95	4.06	*
+Sacramento Jan '26	PBR	* Manoelito de Souza Junior	86.50	21.40 - 20.85	8.00	*
+Portland Jan '26	PBR	* Lane Vaughan	-	20.50 - 20.70	3.61	*
+Tucson Dec '25	PBR	Weslei Ferreira de Jesus	-	21.00 - 20.25	0.91	*
+Albuquerque Sep '25	PRCA	Cade Griego	-	-	-	RR foul
+Lovington Aug '25	PRCA	* Creek Young	-	-	-	DR
+Lovington Aug '25	PRCAX	* Wacey Schalla	-	22.00 - 22.00	7.96	*
+Manhattan Jul '25	PRCA	Lane Clark	-	21.50 - 19.50	4.00	(nt)
+Manhattan Jul '25	PRCA	Kale Visnieski	-	21.00 - 20.00	4.00	(nt)
+Colorado Springs Jul '25	PRCA	* Hudson Bolton	-	22.50 - 21.50	5.04	*
+Weatherford Jun '25	PRCA	Harley Rowland	-	-	-	RR fell decl
+Previous Matchups at probability 0.163
+Rider Count	245
+Avg Rider Rating	.125
+Total Outs	311
+Qualified Rides	44
+Riding %	14.15%
+87+ points	1.29%</t>
+  </si>
+  <si>
+    <t>John Crimber on 0160 Level Up (D4CC)
+Qualified Ride Probability: 45.7% (confidence 8 of 10)
+Ride Score Potential: 86.08 to 92.08 points
+John Crimber Riding Hand: Left
+Career: 228 for 379 - 60.16% - Rider Rating: *.428
+Short Rounds: 25 for 51 - 49.02%
+Current Streak: 11 / 15 - 73.33%
+PBR Current Season: Rank: 1 (54 for 82 - 65.9%) 892.50 pts (-0) - $452,429.21
+PBR Points Per Out: 11 - Points Per QR: 17
+vs. Left: 129-53 (70.88%) -- vs. Right: 35-47 (42.68%) -- vs. ?: 22-16 (57.89%) -- +28.2%/10.72% LEFT
+0160 Level Up - PBS - 10268851
+Power Rating: 73.45
+ALL: 12 outs 1 rides - 91.67%
+vs. Left:  4-1 - 80.00%
+vs. Right: 7-0 - 100.00%
+vs. Top:   5-1 - 83.33%
+Riding Hand Advantage: LEFT (20.00%)
+Previous Outs for 0160 Level Up
+Event	Level	Matchup	Score	Marks	Time	Notes
+Billings Apr '26	PBR	* Bob Mitchell	89.50	21.90 - 22.00	8.00	*
+Little Rock Mar '26	PBR	* Joao Ricardo Vieira	-	21.50 - 22.05	2.16	*
+Grand Forks Feb '26	PBR	Tyler Villarreal	-	22.05 - 21.35	1.69	*
+Tulsa Jan '26	PBR	Hayden Harris	-	21.90 - 21.95	3.33	*
+Tucson Dec '25	PBR	Brady Turgeon	-	21.55 - 21.95	2.53	*
+Las Vegas Dec '25	PBR	Wyatt Nez	-	21.10 - 20.80	1.99	*
+Las Vegas Oct '25	PBR	* Eduardo Aparecido	-	-	-	RR foul
+Las Vegas Oct '25	PBR	* Mason Taylor	-	22.00 - 22.00	3.60	*
+Kansas City Oct '25	PBR	Eric Henrique Domingos	-	21.50 - 21.75	6.83	*
+Kansas City Oct '25	PBR	* Leonardo Castro	-	22.25 - 22.25	3.05	*
+Greensboro Sep '25	PBR	* Ezekiel Mitchell	-	-	-	RR foul
+Fort Worth Aug '25	PBR	Jhon Carlos Moreira	-	21.50 - 22.00	1.45	*
+Las Vegas Dec '24	OPEN	* Ethan Winckler	-	21.50 - 21.88	5.06	*
+Las Vegas Dec '24	OPEN	* Cole Melancon	-	21.88 - 21.88	2.85	*
+Previous Matchups at probability 0.457
+Rider Count	64
+Avg Rider Rating	.270
+Total Outs	83
+Qualified Rides	49
+Riding %	59.04%
+87+ points	26.51%</t>
+  </si>
+  <si>
+    <t>Brady Fielder on 956G Sucker Punch (D4CC)
+Qualified Ride Probability: 40.8% (confidence 8 of 10)
+Ride Score Potential: 82.25 to 88.25 points
+Brady Fielder Riding Hand: Right
+Career: 242 for 475 - 50.95% - Rider Rating: *.369
+Short Rounds: 26 for 66 - 39.39%
+Current Streak: 10 / 15 - 66.67%
+PBR Current Season: Rank: 2 (52 for 85 - 61.2%) 717.00 pts (-175.5) - $412,126.95
+PBR Points Per Out: 8 - Points Per QR: 14
+vs. Left: 51-86 (37.23%) -- vs. Right: 116-68 (63.04%) -- vs. ?: 19-15 (55.88%) -- +25.81%/12.09% RIGHT
+956G Sucker Punch - PBS - 10229189
+Power Rating: 74.90
+ALL: 13 outs 0 rides - 100%
+vs. Left:  2-0 - 100.00%
+vs. Right: 9-0 - 100.00%
+vs. Top:   2-0 - 100.00%
+Riding Hand Advantage: UNKNOWN (0.00%)
+Previous Outs for 956G Sucker Punch
+Event	Level	Matchup	Score	Marks	Time	Notes
+Billings Apr '26	PBR	Callum Miller	-	22.50 - 22.00	4.96	*
+Tulsa Jan '26	PBR	Dalton Rudman	-	21.60 - 22.00	2.89	*
+Tucson Dec '25	PBR	Grayson Cole	-	11.85 - 13.55	4.24	*
+Las Vegas Dec '25	PBR	JaCauy Hale	-	22.30 - 22.10	5.59	*
+Las Vegas Oct '25	PBR	Leandro da Silva	-	-	-	DQ chute
+Oklahoma City Sep '25	OPEN	Lucas Martins Costa	-	-	-	DQ chute
+Fort Worth Sep '25	PBR	Natanael Serra Aires	-	21.50 - 21.50	3.16	*
+Dayton Mar '24	PBR	Grayson Cole	-	-	-	RR foul
+Las Vegas Oct '23	PBR	* Bob Mitchell	-	-	-	RR chute
+Lawton Aug '23	PRCA	Dustin Pinson	-	-	-	RR foul
+Woodstown Aug '23	PBR	Jarred Walker	-	-	-	RR foul
+Little Rock Mar '23	PBR	* Kaique Pacheco	-	-	-	RR chute
+Memphis Feb '23	PBR	Justin Bates	-	22.00 - 22.00	3.62	*
+Tulsa Feb '23	PBR	Casey Coulter	-	22.50 - 22.50	2.93	*
+Indianapolis Jan '23	PBR	* Vitor Losnake	-	22.50 - 22.75	6.74	*
+Previous Matchups at probability 0.408
+Rider Count	98
+Avg Rider Rating	.266
+Total Outs	148
+Qualified Rides	67
+Riding %	45.27%
+87+ points	16.89%</t>
+  </si>
+  <si>
+    <t>Keyshawn Whitehorse on 816 Bad Bob (D4CC)
+Qualified Ride Probability: 52.1% (confidence 10 of 10)
+Ride Score Potential: 83.68 to 89.68 points
+Keyshawn Whitehorse Riding Hand: Right
+Career: 363 for 944 - 38.45% - Rider Rating: *.293
+Short Rounds: 44 for 145 - 30.34%
+Current Streak: 9 / 15 - 60.00%
+PBR Current Season: Rank: 9 (34 for 71 - 47.9%) 405.00 pts (-487.5) - $159,855.64
+PBR Points Per Out: 6 - Points Per QR: 12
+vs. Left: 84-221 (27.54%) -- vs. Right: 138-152 (47.59%) -- vs. ?: 37-56 (39.78%) -- +20.05%/9.14% RIGHT
+816 Bad Bob - PBS - 10262490
+Power Rating: 61.01
+ALL: 27 outs 12 rides - 55.56%
+UTB: 13 outs 7 rides - 46.15%
+vs. Left:  12-8 - 60.00%
+vs. Right: 3-4 - 42.86%
+vs. Top:   5-9 - 35.71%
+Riding Hand Advantage: RIGHT (17.00%)
+Previous Outs for 816 Bad Bob
+Event	Level	Matchup	Score	Marks	Time	Notes
+Billings Apr '26	PBR	Andy Guzman	-	20.80 - 21.10	4.86	*
+Tulsa Jan '26	PBR	Dione de Souza Ribeiro	-	21.15 - 21.70	3.26	*
+Tucson Dec '25	PBR	Colt Robinson	-	21.65 - 21.60	7.70	*
+Las Vegas Dec '25	PBR	Dalton Allred	-	22.00 - 21.40	6.75	*
+Las Vegas Oct '25	PBR	Alvaro Ariel	86.00	21.25 - 20.75	8.00	*
+Ennis Oct '25	OPEN	* Aaron Pass	-	21.78 - 21.78	4.85	*
+Oklahoma City Sep '25	OPEN	Natanael Serra Aires	-	21.25 - 21.50	4.20	*
+Greensboro Sep '25	PBR	* Luciano De Castro	-	18.25 - 17.75	-	RR inf
+Greensboro Sep '25	PBR	* Thiago Salgado	-	21.75 - 22.00	5.58	*
+Austin Aug '25	PBR	Natanael Serra Aires	-	21.00 - 21.00	6.41	*
+Duluth Jul '25	PBR	* Jose Vitor Leme	86.50	21.00 - 21.00	8.00	*
+Duluth Jul '25	PBR	* Ramon de Lima	-	21.00 - 21.00	7.22	*
+Oklahoma City Jul '25	PBR	* Luciano De Castro	86.75	21.00 - 21.25	8.00	*
+Oklahoma City Jul '25	PBR	Caden Bunch	-	21.50 - 21.50	6.11	*
+Grandview Jun '25	OPEN	* Thiago Salgado	87.40	21.37 - 21.37	8.00	*
+Previous Matchups at probability 0.521
+Rider Count	40
+Avg Rider Rating	.316
+Total Outs	57
+Qualified Rides	37
+Riding %	64.91%
+87+ points	21.05%</t>
+  </si>
+  <si>
+    <t>Hudson Bolton on 67 Benjamin Ranklin (TFRS)
+Qualified Ride Probability: 36.9% (confidence 10 of 10)
+Ride Score Potential: 83.47 to 89.47 points
+Hudson Bolton Riding Hand: Left
+Career: 140 for 260 - 53.85% - Rider Rating: *.368
+Short Rounds: 10 for 21 - 47.62%
+Current Streak: 8 / 15 - 53.33%
+PBR Current Season: Rank: 22 (15 for 31 - 48.4%) 247.00 pts (-645.5) - $73,908.24
+PBR Points Per Out: 8 - Points Per QR: 16
+vs. Left: 65-43 (60.19%) -- vs. Right: 28-35 (44.44%) -- vs. ?: 15-14 (51.72%) -- +15.75%/6.34% LEFT
+67 Benjamin Ranklin - PBS -
+Power Rating: 84.69
+ALL: 30 outs 4 rides - 86.67%
+UTB: 21 outs 3 rides - 85.71%
+vs. Left:  6-1 - 85.71%
+vs. Right: 19-3 - 86.36%
+vs. Top:   18-3 - 85.71%
+Riding Hand Advantage: LEFT (1.00%)
+Previous Outs for 67 Benjamin Ranklin
+Event	Level	Matchup	Score	Marks	Time	Notes
+Albuquerque Mar '26	PBR	* Sage Kimzey	-	21.85 - 21.85	7.34	*
+Salt Lake City Feb '26	PBR	* Julio Cesar Marques	-	21.35 - 21.10	7.15	*
+Sacramento Jan '26	PBR	Alison dos Santos	-	21.40 - 21.30	4.25	*
+Las Vegas Oct '25	PBR	* Eduardo Aparecido	-	21.25 - 21.25	3.72	*
+Las Vegas Oct '25	PBR	* Ethan Winckler	-	21.50 - 21.25	3.18	*
+Glendale Oct '25	PBR	Jean Carlos Teodoro	-	20.50 - 21.00	4.61	*
+Glendale Oct '25	PBR	Kase Hitt	-	21.50 - 21.50	4.75	*
+Fort Worth Sep '25	PBR	Tate Pollmeier	-	21.25 - 21.50	4.64	*
+Fort Collins Jul '25	PBR	Andy Guzman	-	20.75 - 20.75	2.83	*
+Fort Collins Jul '25	PBR	* Leonardo Castro	-	21.00 - 20.75	6.83	*
+Evergreen Jun '25	PRCA	Mason Reine	-	21.00 - 20.00	4.00	(nt)
+Fort Worth (PBRF) May '25	PBR	* Julio Cesar Marques	-	20.00 - 20.50	6.85	*
+Fort Worth (PBRF) May '25	PBR	* Kaique Pacheco	-	21.25 - 21.50	2.75	*
+Nampa Apr '25	PBR	* Julio Cesar Marques	-	21.25 - 21.25	3.70	*
+Billings Apr '25	PBR	* Austin Richardson	-	20.75 - 20.50	6.35	*
+Previous Matchups at probability 0.369
+Rider Count	133
+Avg Rider Rating	.239
+Total Outs	192
+Qualified Rides	72
+Riding %	37.5%
+87+ points	10.94%</t>
+  </si>
+  <si>
+    <t>Koltin Hevalow on -1K Johnny Dang (HWKN)
+Qualified Ride Probability: 43.1% (confidence 8 of 10)
+Ride Score Potential: 85.69 to 91.69 points
+Koltin Hevalow Riding Hand: Left
+Career: 154 for 416 - 37.02% - Rider Rating: *.266
+Short Rounds: 9 for 40 - 22.5%
+Current Streak: 2 / 15 - 13.33%
+PBR Current Season: Rank: 23 (35 for 80 - 43.8%) 246.50 pts (-646) - $123,896.04
+PBR Points Per Out: 3 - Points Per QR: 7
+vs. Left: 108-98 (52.43%) -- vs. Right: 24-81 (22.86%) -- vs. ?: 10-22 (31.25%) -- +29.57%/15.41% LEFT
+-1K Johnny Dang - PBS - 10270857
+Power Rating: 42.09
+ALL: 10 outs 3 rides - 70%
+vs. Left:  1-0 - 100.00%
+vs. Right: 2-3 - 40.00%
+vs. Top:   0-1 - 0.00%
+Riding Hand Advantage: RIGHT (60.00%)
+Previous Outs for -1K Johnny Dang
+Event	Level	Matchup	Score	Marks	Time	Notes
+Oakland Apr '26	PBR	Keola Nishimoto	-	21.70 - 20.70	1.09	*
+Palm Desert Mar '26	PBR	Grayson Cole	-	22.20 - 21.40	1.95	*
+Bakersfield Mar '26	PBR	Eric Novoa	88.80	22.00 - 21.80	8.00	*
+Reno Feb '26	PBR	Jose Natanael Marcodes da Silva	-	21.65 - 21.55	1.98	*
+Salt Lake City Feb '26	PBR	Callum Miller	-	22.15 - 21.75	2.67	*
+Salt Lake City Feb '26	PBR	Cleber Henrique Marques	-	21.70 - 21.90	1.91	*
+Sacramento Jan '26	PBR	* Lucas Divino	84.30	21.15 - 21.60	8.00	*
+Ontario Jan '26	PBR	Wyatt Vineyard	-	21.40 - 21.70	2.73	*
+Portland Jan '26	PBR	* Lane Vaughan	-	-	-	RR chute
+Las Vegas Dec '25	PBR	Dalton Allred	90.20	22.50 - 21.60	8.00	*
+Ardmore Mar '25	PRCAX	James Cole	-	21.00 - 22.00	2.82	*
+Previous Matchups at probability 0.431
+Rider Count	99
+Avg Rider Rating	.258
+Total Outs	124
+Qualified Rides	52
+Riding %	41.94%
+87+ points	13.71%</t>
+  </si>
+  <si>
+    <t>Claudio Montanha Jr. on 120 Smooth Violation (TFRS)
+Qualified Ride Probability: 48.3% (confidence 9 of 10)
+Ride Score Potential: 83.75 to 89.75 points
+Claudio Montanha Jr. Riding Hand: Right
+Career: 335 for 867 - 38.64% - Rider Rating: *.274
+Short Rounds: 39 for 128 - 30.47%
+Current Streak: 9 / 15 - 60.00%
+PBR Current Season: Rank: 9 (35 for 69 - 50.7%) 405.00 pts (-487.5) - $166,975.45
+PBR Points Per Out: 6 - Points Per QR: 12
+vs. Left: 75-192 (28.09%) -- vs. Right: 139-123 (53.05%) -- vs. ?: 31-54 (36.47%) -- +24.96%/14.41% RIGHT
+120 Smooth Violation - PBS -
+Power Rating: 55.03
+ALL: 17 outs 10 rides - 41.18%
+UTB: 11 outs 8 rides - 27.27%
+vs. Left:  1-9 - 10.00%
+vs. Right: 5-1 - 83.33%
+vs. Top:   3-6 - 33.33%
+Riding Hand Advantage: LEFT (73.00%)
+Previous Outs for 120 Smooth Violation
+Event	Level	Matchup	Score	Marks	Time	Notes
+Albuquerque Mar '26	PBR	Kase Hitt	86.45	21.40 - 21.40	8.00	*
+Sacramento Jan '26	PBR	Andy Guzman	85.50	21.30 - 21.30	8.00	*
+Las Vegas Oct '25	PBR	Ramon Fiorini	-	20.50 - 20.75	4.47	*
+Glendale Oct '25	PBR	* John Crimber	86.25	21.00 - 20.75	8.00	*
+Glendale Oct '25	PBR	* Bob Mitchell	-	-	-	RR foul
+Waco Oct '25	PRCA	Kristopher Baker	-	21.50 - 21.00	3.61	*
+Fort Worth Sep '25	PBR	Natanael Serra Aires	86.50	21.25 - 21.00	8.00	*
+Fort Worth Sep '25	PBR	* Paulo Eduardo Rossetto	87.75	21.50 - 21.50	8.00	*
+Eagle Jul '25	PRCA	Mason Spain	-	20.00 - 21.50	3.16	*
+Fort Collins Jul '25	PBR	* Sandro Batista	85.50	20.50 - 21.00	8.00	*
+Fort Collins Jul '25	PBR	* Daylon Swearingen	87.50	21.25 - 21.25	8.00	*
+Evergreen Jun '25	PRCA	Cooper McClain	-	22.00 - 19.00	4.00	(nt)
+Fort Worth (PBRF) May '25	PBR	* Vinicius Pinheiro Correa	-	21.50 - 21.50	4.20	*
+Fort Worth (PBRF) May '25	PBR	Murilo Henrique de Oliveira	87.75	21.25 - 21.25	8.00	*
+Fort Worth (PBRF) May '25	PBR	* Dener Barbosa	86.75	21.00 - 21.25	8.00	*
+Previous Matchups at probability 0.483
+Rider Count	48
+Avg Rider Rating	.296
+Total Outs	67
+Qualified Rides	44
+Riding %	65.67%
+87+ points	17.91%</t>
+  </si>
+  <si>
+    <t>Lucas Divino on 61G Big Timber (BSBL)
+Qualified Ride Probability: 29.9% (confidence 8 of 10)
+Ride Score Potential: 83.6 to 89.6 points
+Lucas Divino Riding Hand: Right
+Career: 232 for 601 - 38.6% - Rider Rating: *.304
+Short Rounds: 29 for 74 - 39.19%
+Current Streak: 4 / 15 - 26.67%
+PBR Current Season: Rank: 32 (19 for 51 - 37.3%) 150.00 pts (-742.5) - $77,559.34
+PBR Points Per Out: 3 - Points Per QR: 8
+vs. Left: 42-122 (25.61%) -- vs. Right: 130-122 (51.59%) -- vs. ?: 12-30 (28.57%) -- +25.98%/12.99% RIGHT
+61G Big Timber - PBS - 10229166
+Power Rating: 68.46
+ALL: 13 outs 4 rides - 69.23%
+UTB: 9 outs 3 rides - 66.67%
+vs. Left:  2-2 - 50.00%
+vs. Right: 6-1 - 85.71%
+vs. Top:   4-1 - 80.00%
+Riding Hand Advantage: LEFT (36.00%)
+Previous Outs for 61G Big Timber
+Event	Level	Matchup	Score	Marks	Time	Notes
+Jacksonville Feb '26	PBR	* Manoelito de Souza Junior	79.25	19.65 - 20.65	8.00	*
+Pittsburgh Feb '26	PBR	* Brady Fielder	-	21.20 - 21.05	3.21	*
+Tampa Jan '26	PBR	Callum Miller	-	21.45 - 21.40	7.08	*
+New York Jan '26	PBR	* Cort McFadden	87.00	21.00 - 21.35	8.00	*
+New York Jan '26	PBR	Alvaro Ariel	-	21.35 - 21.75	2.36	*
+Manchester Dec '25	PBR	* Kaique Pacheco	-	21.40 - 20.20	2.16	*
+Glendale Oct '25	PBR	Kase Hitt	82.50	21.00 - 21.25	8.00	*
+Greensboro Sep '25	PBR	* Maverick Smith	-	21.75 - 22.00	3.17	*
+Greensboro Sep '25	PBR	* Dawson Branton	-	21.75 - 21.50	2.51	*
+Archdale Jun '25	PBR	Carlos Garcia	-	21.50 - 21.00	2.27	*
+Archdale Jun '25	PBR	Gabriel Thiago Da Silva	-	21.50 - 21.00	-	RR no nod
+Archdale Jun '24	PBR	Caleb Cantrell	85.00	20.50 - 21.00	8.00	*
+Archdale Jun '24	PBR	Alex Cantoral	-	21.50 - 21.50	3.24	*
+Lewisville Sep '23	PBR	Ben Bode	-	21.00 - 20.00	2.57	*
+Previous Matchups at probability 0.299
+Rider Count	207
+Avg Rider Rating	.201
+Total Outs	317
+Qualified Rides	94
+Riding %	29.65%
+87+ points	8.83%</t>
+  </si>
+  <si>
+    <t>Paulo Eduardo Rossetto on X26 Real Deal (BSBL)
+Qualified Ride Probability: 64.5% (confidence 8 of 10)
+Ride Score Potential: 82.61 to 88.61 points
+Paulo Eduardo Rossetto Riding Hand: Right
+Career: 142 for 334 - 42.51% - Rider Rating: *.316
+Short Rounds: 16 for 39 - 41.03%
+Current Streak: 3 / 15 - 20.00%
+PBR Current Season: Rank: 7 (42 for 84 - 50%) 497.00 pts (-395.5) - $235,394.68
+PBR Points Per Out: 6 - Points Per QR: 12
+vs. Left: 36-67 (34.95%) -- vs. Right: 70-62 (53.03%) -- vs. ?: 11-13 (45.83%) -- +18.08%/10.52% RIGHT
+X26 Real Deal - PBS -
+Power Rating: 51.27
+ALL: 14 outs 9 rides - 35.71%
+UTB: 11 outs 9 rides - 18.18%
+vs. Left:  2-2 - 50.00%
+vs. Right: 1-7 - 12.50%
+vs. Top:   2-9 - 18.18%
+Riding Hand Advantage: RIGHT (38.00%)
+Previous Matchups
+Event	Level	Matchup	Score	Marks	Time	Notes
+Glendale Oct '25	PBR	Paulo Eduardo Rossetto on 52820	86.25	21.00 - 21.00	8.00	*
+Previous Outs for X26 Real Deal
+Event	Level	Matchup	Score	Marks	Time	Notes
+Tallahassee Mar '26	PBR	* Lucas Divino	84.95	20.80 - 20.60	8.00	*
+Bridgeport Feb '26	PBR	* Andrew Alvidrez	86.40	21.00 - 20.95	8.00	*
+Jacksonville Feb '26	PBR	* Kaiden Loud	83.30	20.00 - 20.50	8.00	*
+Pittsburgh Feb '26	PBR	* Hudson Bolton	-	21.00 - 21.25	4.78	*
+Milwaukee Jan '26	PBR	* Daylon Swearingen	87.20	21.00 - 21.15	8.00	*
+New York Jan '26	PBR	* Cassio Dias	86.35	20.65 - 21.30	8.00	*
+Manchester Dec '25	PBR	* Kaiden Loud	84.70	20.35 - 20.95	8.00	*
+Las Vegas Oct '25	PBR	* Wingson Henrique da Silva	-	21.50 - 21.50	6.37	*
+Glendale Oct '25	PBR	* Paulo Eduardo Rossetto	86.25	21.00 - 21.00	8.00	*
+Glendale Oct '25	PBR	* Daniel Keeping	88.25	21.50 - 21.50	8.00	*
+Charlottesville Sep '25	PBR	Lucas Ferreira	-	21.00 - 21.00	1.25	*
+Tacoma Apr '25	PBR	* Claudio Montanha Jr.	83.50	20.00 - 20.75	8.00	*
+Memphis Feb '25	PBR	Max Castro	-	20.50 - 20.50	2.14	*
+Fort Worth Jul '24	PBR	Joao Mauro Kugel	-	21.00 - 21.00	5.24	*
+Previous Matchups at probability 0.645
+Rider Count	11
+Avg Rider Rating	.323
+Total Outs	11
+Qualified Rides	6
+Riding %	54.55%
+87+ points	18.18%</t>
+  </si>
+  <si>
+    <t>Eric Novoa on 95J Alakazoo (FFRF)
+Qualified Ride Probability: 34.3% (confidence 10 of 10)
+Ride Score Potential: 84.44 to 90.44 points
+Eric Novoa Riding Hand: Right
+Career: 29 for 72 - 40.28% - Rider Rating: .167
+Short Rounds: 3 for 13 - 23.08%
+Current Streak: 7 / 15 - 46.67%
+PBR Current Season: Rank: 67 (0 for 2 - 0%) 0.00 pts (-892.5) - $9,000.00
+PBR Points Per Out: 0 - Points Per QR: 0
+vs. Left: 6-12 (33.33%) -- vs. Right: 11-11 (50%) -- vs. ?: 7-9 (43.75%) -- +16.67%/9.72% RIGHT
+95J Alakazoo - PBS - 10257997
+Power Rating: 72.58
+ALL: 36 outs 14 rides - 61.11%
+UTB: 23 outs 7 rides - 69.57%
+vs. Left:  11-11 - 50.00%
+vs. Right: 9-3 - 75.00%
+vs. Top:   11-10 - 52.38%
+Riding Hand Advantage: LEFT (25.00%)
+Previous Outs for 95J Alakazoo
+Event	Level	Matchup	Score	Marks	Time	Notes
+Billings Apr '26	PBR	* Lucas Divino	87.75	21.35 - 21.45	8.00	*
+Grand Forks Feb '26	PBR	Tucker Mertens	-	21.10 - 21.05	2.02	*
+Tulsa Jan '26	PBR	* Dener Barbosa	-	20.95 - 21.05	5.06	*
+Granbury Nov '25	OPEN	* Thiago Salgado	86.00	20.97 - 20.97	8.00	*
+Las Vegas Oct '25	PBR	Miguel de Jesus	-	20.50 - 21.00	2.63	*
+Fort Worth Sep '25	PBR	Riquelmi Silva	86.00	21.00 - 21.00	8.00	*
+Fort Worth Sep '25	PBR	* Bob Mitchell	-	21.25 - 21.00	2.89	*
+Greensboro Sep '25	PBR	* Braidy Randolph	-	21.25 - 21.50	2.88	*
+Greensboro Sep '25	PBR	Macaulie Leather	-	20.75 - 21.00	3.98	*
+Austin Aug '25	PBR	Jeferson Silva	-	21.25 - 21.75	2.01	*
+Austin Aug '25	PBR	Dalton Krantz	-	21.50 - 21.75	3.92	*
+Duluth Jul '25	PBR	* Luciano De Castro	87.25	21.25 - 21.00	8.00	*
+Duluth Jul '25	PBR	Brody Robinson	-	21.50 - 22.00	2.99	*
+Oklahoma City Jul '25	PBR	Eric Henrique Domingos	-	22.00 - 22.25	2.45	*
+Oklahoma City Jul '25	PBR	* Sandro Batista	88.00	21.75 - 21.50	8.00	*
+Previous Matchups at probability 0.343
+Rider Count	184
+Avg Rider Rating	.223
+Total Outs	265
+Qualified Rides	104
+Riding %	39.25%
+87+ points	11.32%</t>
+  </si>
+  <si>
+    <t>Macaulie Leather on 102 Wreck It Ralph (THCC)
+Qualified Ride Probability: 23.2% (confidence 6 of 10)
+Ride Score Potential: 81.2 to 87.2 points
+Macaulie Leather Riding Hand: Left
+Career: 33 for 82 - 40.24% - Rider Rating: .193
+Short Rounds: 5 for 9 - 55.56%
+Current Streak: 4 / 15 - 26.67%
+PBR Current Season: Rank: 67 (4 for 27 - 14.8%) 0.00 pts (-892.5) - $68,882.98
+PBR Points Per Out: 0 - Points Per QR: 0
+vs. Left: 18-15 (54.55%) -- vs. Right: 4-13 (23.53%) -- vs. ?: 3-8 (27.27%) -- +31.02%/14.31% LEFT
+102 Wreck It Ralph PBS 10262368
+no compiled stats
+Previous Outs for 102 Wreck It Ralph
+Event	Level	Matchup	Score	Marks	Time	Notes
+Indianapolis Mar '26	PBR	* Bob Mitchell	-	20.70 - 20.70	5.50	*
+Reno Feb '26	PBR	Saul Zambrano	-	20.85 - 19.55	2.20	*
+Fort Worth Sep '25	PBR	Romario Leite	-	21.50 - 20.00	3.08	*
+Previous Matchups at probability 0.232
+Rider Count	262
+Avg Rider Rating	.166
+Total Outs	403
+Qualified Rides	95
+Riding %	23.57%
+87+ points	3.23%</t>
+  </si>
+  <si>
+    <t>Vinicius Pinheiro Correa on 1710 Taco Truck (TFRS)
+Qualified Ride Probability: 37.6% (confidence 5 of 10)
+Ride Score Potential: -1 to 5 points
+Vinicius Pinheiro Correa Riding Hand: Left
+Career: 44 for 122 - 36.07% - Rider Rating: *.215
+Short Rounds: 4 for 16 - 25%
+Current Streak: 8 / 15 - 53.33%
+PBR Current Season: Rank: 67 (1 for 4 - 25%) 0.00 pts (-892.5) - $15,572.53
+PBR Points Per Out: 0 - Points Per QR: 0
+vs. Left: 25-23 (52.08%) -- vs. Right: 3-29 (9.38%) -- vs. ?: 6-8 (42.86%) -- +42.7%/16.01% LEFT
+1710 Taco Truck PBS
+no compiled stats
+no recorded outs
+Previous Matchups at probability 0.376
+Rider Count	128
+Avg Rider Rating	.238
+Total Outs	176
+Qualified Rides	73
+Riding %	41.48%
+87+ points	10.8%</t>
+  </si>
+  <si>
+    <t>Dener Barbosa on C1 Me More Cowboy (TFRS)
+Qualified Ride Probability: 50.2% (confidence 6 of 10)
+Ride Score Potential: 81.2 to 87.2 points
+Dener Barbosa Riding Hand: Left
+Career: 380 for 760 - 50% - Rider Rating: *.369
+Short Rounds: 50 for 140 - 35.71%
+Current Streak: 6 / 15 - 40.00%
+PBR Current Season: Rank: 41 (16 for 37 - 43.2%) 74.00 pts (-818.5) - $93,253.57
+PBR Points Per Out: 2 - Points Per QR: 5
+vs. Left: 198-120 (62.26%) -- vs. Right: 48-133 (26.52%) -- vs. ?: 36-28 (56.25%) -- +35.74%/12.26% LEFT
+C1 Me More Cowboy PBS
+no compiled stats
+Previous Outs for C1 Me More Cowboy
+Event	Level	Matchup	Score	Marks	Time	Notes
+Salt Lake City Feb '26	PBR	* Alan de Souza	82.35	20.50 - 20.60	8.00	*
+Sacramento Jan '26	PBR	* Marco Rizzo	-	-	-	RR fell
+Previous Matchups at probability 0.502
+Rider Count	45
+Avg Rider Rating	.293
+Total Outs	54
+Qualified Rides	27
+Riding %	50%
+87+ points	9.26%</t>
+  </si>
+  <si>
+    <t>Ramon Fiorini on 230 Dance Monkey (DMDC)
+Qualified Ride Probability: 24.9% (confidence 6 of 10)
+Ride Score Potential: 82.53 to 88.53 points
+Ramon Fiorini Riding Hand: Right
+Career: 34 for 99 - 34.34% - Rider Rating: .160
+Short Rounds: 2 for 5 - 40%
+Current Streak: 7 / 15 - 46.67%
+PBR Current Season: Rank: 66 (1 for 5 - 20%) 7.00 pts (-885.5) - $39,101.98
+PBR Points Per Out: 1 - Points Per QR: 7
+vs. Left: 8-12 (40%) -- vs. Right: 14-21 (40%) -- vs. ?: 4-16 (20%) -- +0%/5.66% PUSH
+230 Dance Monkey PBS
+no compiled stats
+Previous Outs for 230 Dance Monkey
+Event	Level	Matchup	Score	Marks	Time	Notes
+Everett Feb '26	PBR	Tahj Wells	-	21.60 - 21.10	3.02	*
+Nampa Jan '26	PBR	Jace Catlin	-	18.90 - 21.20	5.08	*
+Portland Jan '26	PBR	Colt Schneiderman	-	21.60 - 20.90	1.95	*
+Previous Matchups at probability 0.249
+Rider Count	264
+Avg Rider Rating	.174
+Total Outs	411
+Qualified Rides	91
+Riding %	22.14%
+87+ points	3.41%</t>
+  </si>
+  <si>
+    <t>Mason Taylor on 22J Average Joe (TFRS)
+Qualified Ride Probability: 32% (confidence 8 of 10)
+Ride Score Potential: 81.78 to 87.78 points
+Mason Taylor Riding Hand: Right
+Career: 235 for 693 - 33.91% - Rider Rating: *.250
+Short Rounds: 22 for 99 - 22.22%
+Current Streak: 2 / 15 - 13.33%
+PBR Current Season: Rank: 51 (3 for 28 - 10.7%) 16.00 pts (-876.5) - $28,189.34
+PBR Points Per Out: 1 - Points Per QR: 5
+vs. Left: 63-164 (27.75%) -- vs. Right: 88-128 (40.74%) -- vs. ?: 16-34 (32%) -- +12.99%/6.83% RIGHT
+22J Average Joe - PBS -
+Power Rating: 61.69
+ALL: 12 outs 5 rides - 58.33%
+UTB: 5 outs 2 rides - 60%
+vs. Left:  3-4 - 42.86%
+vs. Right: 4-1 - 80.00%
+vs. Top:   4-3 - 57.14%
+Riding Hand Advantage: LEFT (37.00%)
+Previous Outs for 22J Average Joe
+Event	Level	Matchup	Score	Marks	Time	Notes
+Billings Apr '26	PBR	* Julio Cesar Marques	-	21.40 - 21.30	4.85	*
+Bucktown Feb '26	OPEN	* Daniel Keeping	84.00	20.25 - 20.25	8.00	*
+Salt Lake City Feb '26	PBR	* Hudson Bolton	-	17.80 - 16.75	-	RR inf
+Sacramento Jan '26	PBR	Wyatt Vineyard	-	-	-	RR foul
+Sacramento Jan '26	PBR	* Kade Madsen	-	21.55 - 21.60	4.75	*
+Fort Worth Nov '25	PBR	Gavin Mitchell	-	-	-	*
+Glendale Oct '25	PBR	* Hudson Bolton	87.25	21.00 - 21.25	8.00	*
+Glendale Oct '25	PBR	Riquelmi Silva	-	21.50 - 22.00	7.21	*
+Eagle Jul '25	PRCA	Dillon Tyner	84.00	22.00 - 20.00	8.00	*
+Fort Collins Jul '25	PBR	* Eduardo Aparecido	-	19.25 - 18.25	6.80	*
+Fort Collins Jul '25	PBR	* Ezekiel Mitchell	-	21.50 - 21.50	2.60	*
+Evergreen Jun '25	PRCA	Brody Nelson	-	22.00 - 21.00	4.00	(nt)
+Fort Worth Mar '25	PBR	Anthony Lyons	-	21.00 - 21.50	5.36	*
+Fort Worth Nov '24	PBR	Rogerio Venancio	84.50	21.00 - 21.00	8.00	*
+Previous Matchups at probability 0.32
+Rider Count	185
+Avg Rider Rating	.207
+Total Outs	277
+Qualified Rides	96
+Riding %	34.66%
+87+ points	7.22%</t>
+  </si>
+  <si>
+    <t>Ednelio Rodrigues on 22-9 Kay Dog (BMJM)
+Qualified Ride Probability: 17.7% (confidence 7 of 10)
+Ride Score Potential: 83.72 to 89.72 points
+Ednelio Rodrigues Riding Hand: Left
+Career: 75 for 287 - 26.13% - Rider Rating: *.206
+Short Rounds: 5 for 27 - 18.52%
+Current Streak: 0 / 15 - 0.00%
+PBR Current Season: Rank: 67 (1 for 6 - 16.7%) 0.00 pts (-892.5) - $22,645.05
+PBR Points Per Out: 0 - Points Per QR: 0
+vs. Left: 38-58 (39.58%) -- vs. Right: 11-63 (14.86%) -- vs. ?: 5-20 (20%) -- +24.72%/13.45% LEFT
+22-9 Kay Dog - PBS -
+Power Rating: 73.28
+ALL: 5 outs 1 rides - 80%
+vs. Left:  1-0 - 100.00%
+vs. Right: 2-1 - 66.67%
+vs. Top:   2-0 - 100.00%
+Riding Hand Advantage: UNKNOWN (0.00%)
+Previous Outs for 22-9 Kay Dog
+Event	Level	Matchup	Score	Marks	Time	Notes
+Billings Apr '26	PBR	* Kaiden Loud	-	21.10 - 20.90	3.07	*
+Reading Mar '26	PBR	* Dener Barbosa	-	21.60 - 21.80	1.97	*
+Reading Mar '26	PBR	Gustavo Santos Borges	-	19.70 - 21.20	3.82	*
+Perry Feb '26	PRCA	Taylor Allen	88.50	22.00 - 21.50	8.00	*
+Perry Feb '26	PRCA	Dustin Boquet	-	21.00 - 21.00	4.00	(nt)
+Previous Matchups at probability 0.177
+Rider Count	234
+Avg Rider Rating	.128
+Total Outs	320
+Qualified Rides	48
+Riding %	15%
+87+ points	1.88%</t>
+  </si>
+  <si>
+    <t>Vinicius Rodrigues Pereira on 53 Keystone (CLPB)
+Qualified Ride Probability: 24.7% (confidence 6 of 10)
+Ride Score Potential: 84.4 to 90.4 points
+Vinicius Rodrigues Pereira Riding Hand: Right
+Career: 23 for 82 - 28.05% - Rider Rating: .166
+Short Rounds: 2 for 11 - 18.18%
+Current Streak: 1 / 15 - 6.67%
+PBR Current Season: Rank: 67 (0 for 3 - 0%) 0.00 pts (-892.5) - $17,646.45
+PBR Points Per Out: 0 - Points Per QR: 0
+vs. Left: 5-17 (22.73%) -- vs. Right: 9-11 (45%) -- vs. ?: 5-13 (27.78%) -- +22.27%/16.95% RIGHT
+53 Keystone PBS
+no compiled stats
+Previous Outs for 53 Keystone
+Event	Level	Matchup	Score	Marks	Time	Notes
+Palm Desert Mar '26	PBR	Eric Novoa	-	21.20 - 21.40	3.76	*
+Palm Desert Mar '26	PBR	Grayson Cole	87.60	21.30 - 21.50	8.00	*
+Previous Matchups at probability 0.247
+Rider Count	260
+Avg Rider Rating	.175
+Total Outs	378
+Qualified Rides	106
+Riding %	28.04%
+87+ points	7.14%</t>
+  </si>
+  <si>
+    <t>Grayson Cole on 048 Rank Hank (BSBL)
+Qualified Ride Probability: 26.6% (confidence 10 of 10)
+Ride Score Potential: 83.01 to 89.01 points
+Grayson Cole Riding Hand: Right
+Career: 184 for 747 - 24.63% - Rider Rating: .167
+Short Rounds: 13 for 72 - 18.06%
+Current Streak: 3 / 15 - 20.00%
+PBR Current Season: Rank: 60 (2 for 17 - 11.8%) 8.00 pts (-884.5) - $55,628.97
+PBR Points Per Out: 0 - Points Per QR: 4
+vs. Left: 31-192 (13.9%) -- vs. Right: 80-133 (37.56%) -- vs. ?: 27-81 (25%) -- +23.66%/12.93% RIGHT
+048 Rank Hank - PBS - 10243021
+Power Rating: 69.68
+ALL: 31 outs 16 rides - 48.39%
+UTB: 27 outs 14 rides - 48.15%
+vs. Left:  5-13 - 27.78%
+vs. Right: 10-3 - 76.92%
+vs. Top:   10-13 - 43.48%
+Riding Hand Advantage: LEFT (49.00%)
+Previous Outs for 048 Rank Hank
+Event	Level	Matchup	Score	Marks	Time	Notes
+Bridgeport Feb '26	PBR	Andy Guzman	-	21.10 - 21.10	3.37	*
+Jacksonville Feb '26	PBR	* Maverick Smith	-	19.30 - 19.80	-	RR inf
+Pittsburgh Feb '26	PBR	* Bruno Carvalho	83.45	20.95 - 21.10	8.00	*
+Tampa Jan '26	PBR	* Kade Madsen	-	21.30 - 21.05	3.19	*
+Milwaukee Jan '26	PBR	* Kaiden Loud	-	21.30 - 21.10	5.66	*
+Boston Jan '26	PBR	* Everton Natan da Silva	-	21.30 - 21.20	3.77	*
+Manchester Dec '25	PBR	Cleber Henrique Marques	-	21.05 - 21.05	3.77	*
+St. Louis Dec '25	PBR	Miguel de Jesus	84.70	20.55 - 20.60	8.00	*
+St. Louis Dec '25	PBR	Dustin Herman	-	21.00 - 21.10	2.25	*
+Granbury Nov '25	OPEN	* Alex Cerqueira	88.20	21.62 - 21.62	8.00	*
+Las Vegas Oct '25	PBR	Wyatt Rogers	-	20.50 - 21.00	2.10	*
+Glendale Oct '25	PBR	* Brady Fielder	88.25	21.50 - 21.50	8.00	*
+Glendale Oct '25	PBR	* Brady Fielder	-	21.00 - 21.00	4.22	*
+Fort Worth Sep '25	PBR	Murilo Henrique de Oliveira	85.25	20.75 - 20.75	8.00	*
+Belmont Park Sep '25	PBR	* Josh Frost	86.00	21.00 - 21.00	8.00	*
+Previous Matchups at probability 0.266
+Rider Count	239
+Avg Rider Rating	.181
+Total Outs	360
+Qualified Rides	100
+Riding %	27.78%
+87+ points	6.67%</t>
+  </si>
+  <si>
+    <t>Trace Redd on 065J Uncle Doc (HWKN)
+Qualified Ride Probability: 34.3% (confidence 7 of 10)
+Ride Score Potential: 84.34 to 90.34 points
+Trace Redd Riding Hand: Right
+Career: 64 for 237 - 27% - Rider Rating: .168
+Short Rounds: 4 for 26 - 15.38%
+Current Streak: 4 / 15 - 26.67%
+PBR Current Season: Rank: 36 (6 for 24 - 25%) 95.00 pts (-797.5) - $46,556.47
+PBR Points Per Out: 4 - Points Per QR: 16
+vs. Left: 9-55 (14.06%) -- vs. Right: 29-48 (37.66%) -- vs. ?: 11-19 (36.67%) -- +23.6%/10.66% RIGHT
+065J Uncle Doc - PBS - 10276169
+Power Rating: 52.22
+ALL: 5 outs 2 rides - 60%
+vs. Left:  1-1 - 50.00%
+vs. Right: 1-1 - 50.00%
+vs. Top:   1-2 - 33.33%
+Riding Hand Advantage: UNKNOWN (0.00%)
+Previous Outs for 065J Uncle Doc
+Event	Level	Matchup	Score	Marks	Time	Notes
+Oakland Apr '26	PBR	Jairo Castellanos	-	21.40 - 22.10	3.98	*
+Salt Lake City Feb '26	PBR	* Clay Guiton	87.60	21.25 - 21.55	8.00	*
+Sacramento Jan '26	PBR	* Mauricio Gulla Moreira	86.75	21.25 - 21.05	8.00	*
+Anaheim Sep '25	PBR	* Guilherme Valleiras	-	-	-	RR foul
+Anaheim Sep '25	PBR	* Guilherme Valleiras	-	21.75 - 21.50	6.06	*
+Eugene Apr '25	PBR	Dustin Herman	-	-	-	RR chute
+Fresno Mar '25	PBR	Andy Valdez	-	21.00 - 20.50	2.03	*
+Previous Matchups at probability 0.343
+Rider Count	184
+Avg Rider Rating	.223
+Total Outs	265
+Qualified Rides	104
+Riding %	39.25%
+87+ points	11.32%</t>
+  </si>
+  <si>
+    <t>Callum Miller on 238 Frankenstomp (TFRS)
+Qualified Ride Probability: 36.1% (confidence 6 of 10)
+Ride Score Potential: 85.5 to 91.5 points
+Callum Miller Riding Hand: Right
+Career: 128 for 442 - 28.96% - Rider Rating: .190
+Short Rounds: 19 for 68 - 27.94%
+Current Streak: 2 / 15 - 13.33%
+PBR Current Season: Rank: 27 (21 for 58 - 36.2%) 209.00 pts (-683.5) - $103,513.47
+PBR Points Per Out: 4 - Points Per QR: 10
+vs. Left: 24-111 (17.78%) -- vs. Right: 65-81 (44.52%) -- vs. ?: 10-31 (24.39%) -- +26.74%/15.56% RIGHT
+238 Frankenstomp PBS 10262517
+no compiled stats
+Previous Outs for 238 Frankenstomp
+Event	Level	Matchup	Score	Marks	Time	Notes
+Billings Apr '26	PBR	* Cort McFadden	86.90	21.55 - 21.70	8.00	*
+Previous Matchups at probability 0.361
+Rider Count	142
+Avg Rider Rating	.226
+Total Outs	211
+Qualified Rides	79
+Riding %	37.44%
+87+ points	9.48%</t>
+  </si>
+  <si>
+    <t>Julio Cesar Marques on W251 Kinky Brahmer (CWTZ)
+Qualified Ride Probability: 24.7% (confidence 7 of 10)
+Ride Score Potential: 82.77 to 88.77 points
+Julio Cesar Marques Riding Hand: Right
+Career: 127 for 330 - 38.48% - Rider Rating: *.269
+Short Rounds: 13 for 35 - 37.14%
+Current Streak: 5 / 15 - 33.33%
+PBR Current Season: Rank: 12 (27 for 69 - 39.1%) 400.00 pts (-492.5) - $126,110.26
+PBR Points Per Out: 6 - Points Per QR: 15
+vs. Left: 29-65 (30.85%) -- vs. Right: 56-50 (52.83%) -- vs. ?: 14-23 (37.84%) -- +21.98%/14.35% RIGHT
+W251 Kinky Brahmer - PBS -
+Power Rating: 75.91
+ALL: 9 outs 0 rides - 100%
+vs. Left:  3-0 - 100.00%
+vs. Right: 2-0 - 100.00%
+vs. Top:   3-0 - 100.00%
+Riding Hand Advantage: UNKNOWN (0.00%)
+Previous Outs for W251 Kinky Brahmer
+Event	Level	Matchup	Score	Marks	Time	Notes
+Billings Apr '26	PBR	* Daniel Keeping	-	20.45 - 19.05	5.24	*
+Billings Apr '26	PBR	* Keyshawn Whitehorse	-	22.15 - 22.00	5.60	*
+Everett Feb '26	PBR	Shane Scott	-	21.30 - 20.70	2.55	*
+Everett Feb '26	PBR	Cash Keeling	-	21.40 - 21.20	1.98	*
+Nampa Jan '26	PBR	Jack Strong	-	-	-	RR chute
+Spokane Jan '26	PBR	Dakota Johnson	-	21.00 - 20.60	3.31	*
+Spokane Jan '26	PBR	* Dawson Branton	-	22.00 - 20.40	2.27	*
+Portland Jan '26	PBR	Alex Koberstein	-	21.30 - 20.90	2.36	*
+Kennewick Sep '25	PBR	Dustin Martinez	-	19.50 - 21.00	4.68	*
+St. Paul Jul '25	PRCA	Juan Carrillo	-	20.00 - 22.00	3.31	*
+Previous Matchups at probability 0.247
+Rider Count	260
+Avg Rider Rating	.175
+Total Outs	378
+Qualified Rides	106
+Riding %	28.04%
+87+ points	7.14%</t>
+  </si>
+  <si>
+    <t>&lt;h2&gt;Rider&lt;/h2&gt;&lt;p&gt;&lt;strong&gt;Career:&amp;nbsp;&lt;/strong&gt;Career: 496 for 1134 - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;43.74%&lt;/em&gt;&lt;/span&gt; - Rider Rating: *.360&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Season:&amp;nbsp;&lt;/strong&gt;Rank&amp;nbsp;&lt;span style="color: #ff0000;"&gt;30&lt;/span&gt; (31 for 72 - &lt;em&gt;43.1%&lt;/em&gt;)&lt;em&gt;&lt;br /&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Points:&amp;nbsp;&lt;/strong&gt;189.00 pts &lt;span style="color: #ff0000;"&gt;&lt;em&gt;(-703.5)&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Earnings:&amp;nbsp;&lt;/strong&gt;&lt;span style="color: #008000;"&gt;&lt;em&gt;$133,872.04&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Potential&lt;/strong&gt;:&amp;nbsp;83.15 to 89.15 points&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;&lt;span style="text-decoration: underline;"&gt;&lt;strong&gt;Bull&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;ALL:&lt;/strong&gt; 31 outs 13 rides - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;58.06%&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;UTB:&lt;/strong&gt; 17 outs 10 rides - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;41.18%&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;em&gt;&lt;span style="color: #ff0000;"&gt;*No Previous Matchups&lt;/span&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t>Bull 0.00%</t>
+  </si>
+  <si>
+    <t>&lt;h2&gt;Rider&lt;/h2&gt;&lt;p&gt;&lt;strong&gt;Career:&amp;nbsp;&lt;/strong&gt;Career: 112 for 417 - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;26.86%&lt;/em&gt;&lt;/span&gt; - Rider Rating: *.202&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Season:&amp;nbsp;&lt;/strong&gt;Rank&amp;nbsp;&lt;span style="color: #ff0000;"&gt;35&lt;/span&gt; (6 for 28 - &lt;em&gt;21.4%&lt;/em&gt;)&lt;em&gt;&lt;br /&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Points:&amp;nbsp;&lt;/strong&gt;112.00 pts &lt;span style="color: #ff0000;"&gt;&lt;em&gt;(-780.5)&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Earnings:&amp;nbsp;&lt;/strong&gt;&lt;span style="color: #008000;"&gt;&lt;em&gt;$18,250.00&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Potential&lt;/strong&gt;:&amp;nbsp;81.86 to 87.86 points&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;&lt;span style="text-decoration: underline;"&gt;&lt;strong&gt;Bull&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;ALL:&lt;/strong&gt; 7 outs 1 rides - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;85.71%&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;em&gt;&lt;span style="color: #ff0000;"&gt;*No Previous Matchups&lt;/span&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t>&lt;h2&gt;Rider&lt;/h2&gt;&lt;p&gt;&lt;strong&gt;Career:&amp;nbsp;&lt;/strong&gt;Career: 94 for 332 - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;28.31%&lt;/em&gt;&lt;/span&gt; - Rider Rating: .179&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Season:&amp;nbsp;&lt;/strong&gt;Rank&amp;nbsp;&lt;span style="color: #ff0000;"&gt;33&lt;/span&gt; (16 for 53 - &lt;em&gt;30.2%&lt;/em&gt;)&lt;em&gt;&lt;br /&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Points:&amp;nbsp;&lt;/strong&gt;137.00 pts &lt;span style="color: #ff0000;"&gt;&lt;em&gt;(-755.5)&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Earnings:&amp;nbsp;&lt;/strong&gt;&lt;span style="color: #008000;"&gt;&lt;em&gt;$49,767.31&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Potential&lt;/strong&gt;:&amp;nbsp;83.07 to 89.07 points&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;&lt;span style="text-decoration: underline;"&gt;&lt;strong&gt;Bull&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;ALL:&lt;/strong&gt; 7 outs 1 rides - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;85.71%&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;em&gt;&lt;span style="color: #ff0000;"&gt;*No Previous Matchups&lt;/span&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t>Rider 42.00%</t>
+  </si>
+  <si>
+    <t>&lt;h2&gt;Rider&lt;/h2&gt;&lt;p&gt;&lt;strong&gt;Career:&amp;nbsp;&lt;/strong&gt;Career: 70 for 219 - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;31.96%&lt;/em&gt;&lt;/span&gt; - Rider Rating: *.208&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Season:&amp;nbsp;&lt;/strong&gt;Rank&amp;nbsp;&lt;span style="color: #ff0000;"&gt;42&lt;/span&gt; (9 for 34 - &lt;em&gt;26.5%&lt;/em&gt;)&lt;em&gt;&lt;br /&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Points:&amp;nbsp;&lt;/strong&gt;71.50 pts &lt;span style="color: #ff0000;"&gt;&lt;em&gt;(-821)&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Earnings:&amp;nbsp;&lt;/strong&gt;&lt;span style="color: #008000;"&gt;&lt;em&gt;$30,778.26&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Potential&lt;/strong&gt;:&amp;nbsp;83.5 to 89.5 points&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;&lt;span style="text-decoration: underline;"&gt;&lt;strong&gt;Bull&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;ALL:&lt;/strong&gt; 17 outs 9 rides - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;47.06%&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;UTB:&lt;/strong&gt; 7 outs 5 rides - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;28.57%&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;em&gt;&lt;span style="color: #ff0000;"&gt;*No Previous Matchups&lt;/span&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t>Rider 13.00%</t>
+  </si>
+  <si>
+    <t>&lt;h2&gt;Rider&lt;/h2&gt;&lt;p&gt;&lt;strong&gt;Career:&amp;nbsp;&lt;/strong&gt;Career: 62 for 178 - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;34.83%&lt;/em&gt;&lt;/span&gt; - Rider Rating: *.215&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Season:&amp;nbsp;&lt;/strong&gt;Rank&amp;nbsp;&lt;span style="color: #ff0000;"&gt;9&lt;/span&gt; (27 for 72 - &lt;em&gt;37.5%&lt;/em&gt;)&lt;em&gt;&lt;br /&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Points:&amp;nbsp;&lt;/strong&gt;405.00 pts &lt;span style="color: #ff0000;"&gt;&lt;em&gt;(-487.5)&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Earnings:&amp;nbsp;&lt;/strong&gt;&lt;span style="color: #008000;"&gt;&lt;em&gt;$143,765.82&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Potential&lt;/strong&gt;:&amp;nbsp;82.79 to 88.79 points&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;&lt;span style="text-decoration: underline;"&gt;&lt;strong&gt;Bull&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;ALL:&lt;/strong&gt; 24 outs 7 rides - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;70.83%&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;UTB:&lt;/strong&gt; 12 outs 4 rides - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;66.67%&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;em&gt;&lt;span style="color: #ff0000;"&gt;*No Previous Matchups&lt;/span&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t>&lt;h2&gt;Rider&lt;/h2&gt;&lt;p&gt;&lt;strong&gt;Career:&amp;nbsp;&lt;/strong&gt;Career: 125 for 249 - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;50.2%&lt;/em&gt;&lt;/span&gt; - Rider Rating: *.410&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Season:&amp;nbsp;&lt;/strong&gt;Rank&amp;nbsp;&lt;span style="color: #ff0000;"&gt;19&lt;/span&gt; (13 for 45 - &lt;em&gt;28.9%&lt;/em&gt;)&lt;em&gt;&lt;br /&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Points:&amp;nbsp;&lt;/strong&gt;295.50 pts &lt;span style="color: #ff0000;"&gt;&lt;em&gt;(-597)&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Earnings:&amp;nbsp;&lt;/strong&gt;&lt;span style="color: #008000;"&gt;&lt;em&gt;$98,807.28&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Potential&lt;/strong&gt;:&amp;nbsp;84.77 to 90.77 points&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;&lt;span style="text-decoration: underline;"&gt;&lt;strong&gt;Bull&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;em&gt;&lt;span style="color: #ff0000;"&gt;*No Previous Matchups&lt;/span&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t>Bull 53.00%</t>
+  </si>
+  <si>
+    <t>&lt;h2&gt;Rider&lt;/h2&gt;&lt;p&gt;&lt;strong&gt;Career:&amp;nbsp;&lt;/strong&gt;Career: 211 for 397 - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;53.15%&lt;/em&gt;&lt;/span&gt; - Rider Rating: *.339&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Season:&amp;nbsp;&lt;/strong&gt;Rank&amp;nbsp;&lt;span style="color: #ff0000;"&gt;31&lt;/span&gt; (35 for 70 - &lt;em&gt;50%&lt;/em&gt;)&lt;em&gt;&lt;br /&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Points:&amp;nbsp;&lt;/strong&gt;178.00 pts &lt;span style="color: #ff0000;"&gt;&lt;em&gt;(-714.5)&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Earnings:&amp;nbsp;&lt;/strong&gt;&lt;span style="color: #008000;"&gt;&lt;em&gt;$102,574.30&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Potential&lt;/strong&gt;:&amp;nbsp;82.98 to 88.98 points&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;&lt;span style="text-decoration: underline;"&gt;&lt;strong&gt;Bull&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;ALL:&lt;/strong&gt; 27 outs 7 rides - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;74.07%&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;UTB:&lt;/strong&gt; 13 outs 7 rides - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;46.15%&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;em&gt;&lt;span style="color: #ff0000;"&gt;*No Previous Matchups&lt;/span&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t>&lt;h2&gt;Rider&lt;/h2&gt;&lt;p&gt;&lt;strong&gt;Career:&amp;nbsp;&lt;/strong&gt;Career: 197 for 513 - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;38.4%&lt;/em&gt;&lt;/span&gt; - Rider Rating: *.270&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Season:&amp;nbsp;&lt;/strong&gt;Rank&amp;nbsp;&lt;span style="color: #ff0000;"&gt;6&lt;/span&gt; (33 for 65 - &lt;em&gt;50.8%&lt;/em&gt;)&lt;em&gt;&lt;br /&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Points:&amp;nbsp;&lt;/strong&gt;502.50 pts &lt;span style="color: #ff0000;"&gt;&lt;em&gt;(-390)&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Earnings:&amp;nbsp;&lt;/strong&gt;&lt;span style="color: #008000;"&gt;&lt;em&gt;$162,721.28&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Potential&lt;/strong&gt;:&amp;nbsp;83.67 to 89.67 points&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;&lt;span style="text-decoration: underline;"&gt;&lt;strong&gt;Bull&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;em&gt;&lt;span style="color: #ff0000;"&gt;*No Previous Matchups&lt;/span&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t>Rider 75.00%</t>
+  </si>
+  <si>
+    <t>&lt;h2&gt;Rider&lt;/h2&gt;&lt;p&gt;&lt;strong&gt;Career:&amp;nbsp;&lt;/strong&gt;Career: 25 for 78 - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;32.05%&lt;/em&gt;&lt;/span&gt; - Rider Rating: .156&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Season:&amp;nbsp;&lt;/strong&gt;Rank&amp;nbsp;&lt;span style="color: #ff0000;"&gt;60&lt;/span&gt; (1 for 11 - &lt;em&gt;9.1%&lt;/em&gt;)&lt;em&gt;&lt;br /&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Points:&amp;nbsp;&lt;/strong&gt;8.00 pts &lt;span style="color: #ff0000;"&gt;&lt;em&gt;(-884.5)&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Earnings:&amp;nbsp;&lt;/strong&gt;&lt;span style="color: #008000;"&gt;&lt;em&gt;$9,446.45&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Potential&lt;/strong&gt;:&amp;nbsp;83.32 to 89.32 points&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;&lt;span style="text-decoration: underline;"&gt;&lt;strong&gt;Bull&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;ALL:&lt;/strong&gt; 10 outs 6 rides - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;40%&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;UTB:&lt;/strong&gt; 9 outs 6 rides - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;33.33%&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;em&gt;&lt;span style="color: #ff0000;"&gt;*No Previous Matchups&lt;/span&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t>Rider 8.00%</t>
+  </si>
+  <si>
+    <t>&lt;h2&gt;Rider&lt;/h2&gt;&lt;p&gt;&lt;strong&gt;Career:&amp;nbsp;&lt;/strong&gt;Career: 183 for 462 - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;39.61%&lt;/em&gt;&lt;/span&gt; - Rider Rating: *.283&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Season:&amp;nbsp;&lt;/strong&gt;Rank&amp;nbsp;&lt;span style="color: #ff0000;"&gt;13&lt;/span&gt; (34 for 62 - &lt;em&gt;54.8%&lt;/em&gt;)&lt;em&gt;&lt;br /&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Points:&amp;nbsp;&lt;/strong&gt;396.00 pts &lt;span style="color: #ff0000;"&gt;&lt;em&gt;(-496.5)&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Earnings:&amp;nbsp;&lt;/strong&gt;&lt;span style="color: #008000;"&gt;&lt;em&gt;$123,666.07&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Potential&lt;/strong&gt;:&amp;nbsp;83.96 to 89.96 points&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;&lt;span style="text-decoration: underline;"&gt;&lt;strong&gt;Bull&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;ALL:&lt;/strong&gt; 17 outs 7 rides - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;58.82%&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;UTB:&lt;/strong&gt; 11 outs 7 rides - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;36.36%&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;em&gt;&lt;span style="color: #ff0000;"&gt;*No Previous Matchups&lt;/span&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t>&lt;h2&gt;Rider&lt;/h2&gt;&lt;p&gt;&lt;strong&gt;Career:&amp;nbsp;&lt;/strong&gt;Career: 162 for 417 - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;38.85%&lt;/em&gt;&lt;/span&gt; - Rider Rating: *.273&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Season:&amp;nbsp;&lt;/strong&gt;Rank&amp;nbsp;&lt;span style="color: #ff0000;"&gt;21&lt;/span&gt; (33 for 71 - &lt;em&gt;46.5%&lt;/em&gt;)&lt;em&gt;&lt;br /&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Points:&amp;nbsp;&lt;/strong&gt;255.00 pts &lt;span style="color: #ff0000;"&gt;&lt;em&gt;(-637.5)&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Earnings:&amp;nbsp;&lt;/strong&gt;&lt;span style="color: #008000;"&gt;&lt;em&gt;$146,643.44&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Potential&lt;/strong&gt;:&amp;nbsp;-1 to 5 points&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;&lt;span style="text-decoration: underline;"&gt;&lt;strong&gt;Bull&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;em&gt;&lt;span style="color: #ff0000;"&gt;*No Previous Matchups&lt;/span&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t>Bull 20.00%</t>
+  </si>
+  <si>
+    <t>&lt;h2&gt;Rider&lt;/h2&gt;&lt;p&gt;&lt;strong&gt;Career:&amp;nbsp;&lt;/strong&gt;Career: 268 for 553 - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;48.46%&lt;/em&gt;&lt;/span&gt; - Rider Rating: *.408&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Season:&amp;nbsp;&lt;/strong&gt;Rank&amp;nbsp;&lt;span style="color: #ff0000;"&gt;20&lt;/span&gt; (20 for 42 - &lt;em&gt;47.6%&lt;/em&gt;)&lt;em&gt;&lt;br /&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Points:&amp;nbsp;&lt;/strong&gt;292.00 pts &lt;span style="color: #ff0000;"&gt;&lt;em&gt;(-600.5)&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Earnings:&amp;nbsp;&lt;/strong&gt;&lt;span style="color: #008000;"&gt;&lt;em&gt;$230,842.06&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Potential&lt;/strong&gt;:&amp;nbsp;83.71 to 89.71 points&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;&lt;span style="text-decoration: underline;"&gt;&lt;strong&gt;Bull&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;ALL:&lt;/strong&gt; 29 outs 3 rides - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;89.66%&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;em&gt;&lt;span style="color: #ff0000;"&gt;*No Previous Matchups&lt;/span&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t>&lt;h2&gt;Rider&lt;/h2&gt;&lt;p&gt;&lt;strong&gt;Career:&amp;nbsp;&lt;/strong&gt;Career: 233 for 735 - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;31.7%&lt;/em&gt;&lt;/span&gt; - Rider Rating: *.245&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Season:&amp;nbsp;&lt;/strong&gt;Rank&amp;nbsp;&lt;span style="color: #ff0000;"&gt;25&lt;/span&gt; (19 for 64 - &lt;em&gt;29.7%&lt;/em&gt;)&lt;em&gt;&lt;br /&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Points:&amp;nbsp;&lt;/strong&gt;219.00 pts &lt;span style="color: #ff0000;"&gt;&lt;em&gt;(-673.5)&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Earnings:&amp;nbsp;&lt;/strong&gt;&lt;span style="color: #008000;"&gt;&lt;em&gt;$154,923.02&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Potential&lt;/strong&gt;:&amp;nbsp;86.19 to 92.19 points&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;&lt;span style="text-decoration: underline;"&gt;&lt;strong&gt;Bull&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;ALL:&lt;/strong&gt; 8 outs 0 rides - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;100%&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;em&gt;&lt;span style="color: #ff0000;"&gt;*No Previous Matchups&lt;/span&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t>Rider 20.00%</t>
+  </si>
+  <si>
+    <t>&lt;h2&gt;Rider&lt;/h2&gt;&lt;p&gt;&lt;strong&gt;Career:&amp;nbsp;&lt;/strong&gt;Career: 352 for 823 - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;42.77%&lt;/em&gt;&lt;/span&gt; - Rider Rating: *.341&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Season:&amp;nbsp;&lt;/strong&gt;Rank&amp;nbsp;&lt;span style="color: #ff0000;"&gt;16&lt;/span&gt; (19 for 46 - &lt;em&gt;41.3%&lt;/em&gt;)&lt;em&gt;&lt;br /&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Points:&amp;nbsp;&lt;/strong&gt;362.50 pts &lt;span style="color: #ff0000;"&gt;&lt;em&gt;(-530)&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Earnings:&amp;nbsp;&lt;/strong&gt;&lt;span style="color: #008000;"&gt;&lt;em&gt;$150,772.22&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Potential&lt;/strong&gt;:&amp;nbsp;85.25 to 91.25 points&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;&lt;span style="text-decoration: underline;"&gt;&lt;strong&gt;Bull&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;ALL:&lt;/strong&gt; 74 outs 22 rides - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;70.27%&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;UTB:&lt;/strong&gt; 32 outs 15 rides - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;53.13%&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;em&gt;&lt;span style="color: #ff0000;"&gt;*No Previous Matchups&lt;/span&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t>Bull 43.00%</t>
+  </si>
+  <si>
+    <t>&lt;h2&gt;Rider&lt;/h2&gt;&lt;p&gt;&lt;strong&gt;Career:&amp;nbsp;&lt;/strong&gt;Career: 176 for 430 - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;40.93%&lt;/em&gt;&lt;/span&gt; - Rider Rating: *.281&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Season:&amp;nbsp;&lt;/strong&gt;Rank&amp;nbsp;&lt;span style="color: #ff0000;"&gt;24&lt;/span&gt; (38 for 74 - &lt;em&gt;51.4%&lt;/em&gt;)&lt;em&gt;&lt;br /&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Points:&amp;nbsp;&lt;/strong&gt;224.00 pts &lt;span style="color: #ff0000;"&gt;&lt;em&gt;(-668.5)&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Earnings:&amp;nbsp;&lt;/strong&gt;&lt;span style="color: #008000;"&gt;&lt;em&gt;$173,189.21&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Potential&lt;/strong&gt;:&amp;nbsp;83.56 to 89.56 points&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;&lt;span style="text-decoration: underline;"&gt;&lt;strong&gt;Bull&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;ALL:&lt;/strong&gt; 15 outs 5 rides - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;66.67%&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;UTB:&lt;/strong&gt; 6 outs 4 rides - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;33.33%&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;em&gt;&lt;span style="color: #ff0000;"&gt;*No Previous Matchups&lt;/span&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t>Bull 14.00%</t>
+  </si>
+  <si>
+    <t>&lt;h2&gt;Rider&lt;/h2&gt;&lt;p&gt;&lt;strong&gt;Career:&amp;nbsp;&lt;/strong&gt;Career: 599 for 1325 - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;45.21%&lt;/em&gt;&lt;/span&gt; - Rider Rating: *.356&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Season:&amp;nbsp;&lt;/strong&gt;Rank&amp;nbsp;&lt;span style="color: #ff0000;"&gt;37&lt;/span&gt; (18 for 52 - &lt;em&gt;34.6%&lt;/em&gt;)&lt;em&gt;&lt;br /&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Points:&amp;nbsp;&lt;/strong&gt;92.50 pts &lt;span style="color: #ff0000;"&gt;&lt;em&gt;(-800)&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Earnings:&amp;nbsp;&lt;/strong&gt;&lt;span style="color: #008000;"&gt;&lt;em&gt;$83,389.62&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Potential&lt;/strong&gt;:&amp;nbsp;84.24 to 90.24 points&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;&lt;span style="text-decoration: underline;"&gt;&lt;strong&gt;Bull&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;ALL:&lt;/strong&gt; 10 outs 1 rides - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;90%&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;em&gt;&lt;span style="color: #ff0000;"&gt;*No Previous Matchups&lt;/span&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t>Rider 21.00%</t>
+  </si>
+  <si>
+    <t>&lt;h2&gt;Rider&lt;/h2&gt;&lt;p&gt;&lt;strong&gt;Career:&amp;nbsp;&lt;/strong&gt;Career: 51 for 222 - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;22.97%&lt;/em&gt;&lt;/span&gt; - Rider Rating: .119&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Season:&amp;nbsp;&lt;/strong&gt;Rank&amp;nbsp;&lt;span style="color: #ff0000;"&gt;40&lt;/span&gt; (4 for 30 - &lt;em&gt;13.3%&lt;/em&gt;)&lt;em&gt;&lt;br /&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Points:&amp;nbsp;&lt;/strong&gt;78.00 pts &lt;span style="color: #ff0000;"&gt;&lt;em&gt;(-814.5)&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Earnings:&amp;nbsp;&lt;/strong&gt;&lt;span style="color: #008000;"&gt;&lt;em&gt;$11,800.00&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Potential&lt;/strong&gt;:&amp;nbsp;84.22 to 90.22 points&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;&lt;span style="text-decoration: underline;"&gt;&lt;strong&gt;Bull&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;ALL:&lt;/strong&gt; 23 outs 4 rides - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;82.61%&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;UTB:&lt;/strong&gt; 7 outs 2 rides - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;71.43%&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;em&gt;&lt;span style="color: #ff0000;"&gt;*No Previous Matchups&lt;/span&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t>Bull 40.00%</t>
+  </si>
+  <si>
+    <t>&lt;h2&gt;Rider&lt;/h2&gt;&lt;p&gt;&lt;strong&gt;Career:&amp;nbsp;&lt;/strong&gt;Career: 154 for 517 - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;29.79%&lt;/em&gt;&lt;/span&gt; - Rider Rating: *.248&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Season:&amp;nbsp;&lt;/strong&gt;Rank&amp;nbsp;&lt;span style="color: #ff0000;"&gt;38&lt;/span&gt; (21 for 72 - &lt;em&gt;29.2%&lt;/em&gt;)&lt;em&gt;&lt;br /&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Points:&amp;nbsp;&lt;/strong&gt;86.00 pts &lt;span style="color: #ff0000;"&gt;&lt;em&gt;(-806.5)&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Earnings:&amp;nbsp;&lt;/strong&gt;&lt;span style="color: #008000;"&gt;&lt;em&gt;$86,037.98&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Potential&lt;/strong&gt;:&amp;nbsp;85.28 to 91.28 points&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;&lt;span style="text-decoration: underline;"&gt;&lt;strong&gt;Bull&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;ALL:&lt;/strong&gt; 33 outs 8 rides - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;75.76%&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;UTB:&lt;/strong&gt; 11 outs 4 rides - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;63.64%&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;em&gt;&lt;span style="color: #ff0000;"&gt;*No Previous Matchups&lt;/span&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t>&lt;h2&gt;Rider&lt;/h2&gt;&lt;p&gt;&lt;strong&gt;Career:&amp;nbsp;&lt;/strong&gt;Career: 353 for 770 - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;45.84%&lt;/em&gt;&lt;/span&gt; - Rider Rating: *.341&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Season:&amp;nbsp;&lt;/strong&gt;Rank&amp;nbsp;&lt;span style="color: #ff0000;"&gt;18&lt;/span&gt; (36 for 74 - &lt;em&gt;48.6%&lt;/em&gt;)&lt;em&gt;&lt;br /&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Points:&amp;nbsp;&lt;/strong&gt;304.00 pts &lt;span style="color: #ff0000;"&gt;&lt;em&gt;(-588.5)&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Earnings:&amp;nbsp;&lt;/strong&gt;&lt;span style="color: #008000;"&gt;&lt;em&gt;$151,952.86&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Potential&lt;/strong&gt;:&amp;nbsp;87.4 to 93.4 points&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;&lt;span style="text-decoration: underline;"&gt;&lt;strong&gt;Bull&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;em&gt;&lt;span style="color: #ff0000;"&gt;*No Previous Matchups&lt;/span&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t>Bull 13.00%</t>
+  </si>
+  <si>
+    <t>&lt;h2&gt;Rider&lt;/h2&gt;&lt;p&gt;&lt;strong&gt;Career:&amp;nbsp;&lt;/strong&gt;Career: 45 for 158 - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;28.48%&lt;/em&gt;&lt;/span&gt; - Rider Rating: .160&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Season:&amp;nbsp;&lt;/strong&gt;Rank&amp;nbsp;&lt;span style="color: #ff0000;"&gt;43&lt;/span&gt; (4 for 12 - &lt;em&gt;33.3%&lt;/em&gt;)&lt;em&gt;&lt;br /&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Points:&amp;nbsp;&lt;/strong&gt;49.50 pts &lt;span style="color: #ff0000;"&gt;&lt;em&gt;(-843)&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Earnings:&amp;nbsp;&lt;/strong&gt;&lt;span style="color: #008000;"&gt;&lt;em&gt;$4,025.00&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Potential&lt;/strong&gt;:&amp;nbsp;83.27 to 89.27 points&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;&lt;span style="text-decoration: underline;"&gt;&lt;strong&gt;Bull&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;ALL:&lt;/strong&gt; 27 outs 1 rides - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;96.3%&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;em&gt;&lt;span style="color: #ff0000;"&gt;*No Previous Matchups&lt;/span&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t>&lt;h2&gt;Rider&lt;/h2&gt;&lt;p&gt;&lt;strong&gt;Career:&amp;nbsp;&lt;/strong&gt;Career: 228 for 379 - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;60.16%&lt;/em&gt;&lt;/span&gt; - Rider Rating: *.428&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Season:&amp;nbsp;&lt;/strong&gt;Rank&amp;nbsp;&lt;span style="color: #ff0000;"&gt;1&lt;/span&gt; (54 for 82 - &lt;em&gt;65.9%&lt;/em&gt;)&lt;em&gt;&lt;br /&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Points:&amp;nbsp;&lt;/strong&gt;892.50 pts &lt;span style="color: #ff0000;"&gt;&lt;em&gt;(-0)&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Earnings:&amp;nbsp;&lt;/strong&gt;&lt;span style="color: #008000;"&gt;&lt;em&gt;$452,429.21&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Potential&lt;/strong&gt;:&amp;nbsp;86.08 to 92.08 points&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;&lt;span style="text-decoration: underline;"&gt;&lt;strong&gt;Bull&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;ALL:&lt;/strong&gt; 12 outs 1 rides - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;91.67%&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;em&gt;&lt;span style="color: #ff0000;"&gt;*No Previous Matchups&lt;/span&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t>&lt;h2&gt;Rider&lt;/h2&gt;&lt;p&gt;&lt;strong&gt;Career:&amp;nbsp;&lt;/strong&gt;Career: 242 for 475 - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;50.95%&lt;/em&gt;&lt;/span&gt; - Rider Rating: *.369&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Season:&amp;nbsp;&lt;/strong&gt;Rank&amp;nbsp;&lt;span style="color: #ff0000;"&gt;2&lt;/span&gt; (52 for 85 - &lt;em&gt;61.2%&lt;/em&gt;)&lt;em&gt;&lt;br /&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Points:&amp;nbsp;&lt;/strong&gt;717.00 pts &lt;span style="color: #ff0000;"&gt;&lt;em&gt;(-175.5)&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Earnings:&amp;nbsp;&lt;/strong&gt;&lt;span style="color: #008000;"&gt;&lt;em&gt;$412,126.95&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Potential&lt;/strong&gt;:&amp;nbsp;82.25 to 88.25 points&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;&lt;span style="text-decoration: underline;"&gt;&lt;strong&gt;Bull&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;ALL:&lt;/strong&gt; 13 outs 0 rides - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;100%&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;em&gt;&lt;span style="color: #ff0000;"&gt;*No Previous Matchups&lt;/span&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t>&lt;h2&gt;Rider&lt;/h2&gt;&lt;p&gt;&lt;strong&gt;Career:&amp;nbsp;&lt;/strong&gt;Career: 363 for 944 - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;38.45%&lt;/em&gt;&lt;/span&gt; - Rider Rating: *.293&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Season:&amp;nbsp;&lt;/strong&gt;Rank&amp;nbsp;&lt;span style="color: #ff0000;"&gt;9&lt;/span&gt; (34 for 71 - &lt;em&gt;47.9%&lt;/em&gt;)&lt;em&gt;&lt;br /&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Points:&amp;nbsp;&lt;/strong&gt;405.00 pts &lt;span style="color: #ff0000;"&gt;&lt;em&gt;(-487.5)&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Earnings:&amp;nbsp;&lt;/strong&gt;&lt;span style="color: #008000;"&gt;&lt;em&gt;$159,855.64&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Potential&lt;/strong&gt;:&amp;nbsp;83.68 to 89.68 points&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;&lt;span style="text-decoration: underline;"&gt;&lt;strong&gt;Bull&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;ALL:&lt;/strong&gt; 27 outs 12 rides - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;55.56%&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;UTB:&lt;/strong&gt; 13 outs 7 rides - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;46.15%&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;em&gt;&lt;span style="color: #ff0000;"&gt;*No Previous Matchups&lt;/span&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t>Rider 1.00%</t>
+  </si>
+  <si>
+    <t>&lt;h2&gt;Rider&lt;/h2&gt;&lt;p&gt;&lt;strong&gt;Career:&amp;nbsp;&lt;/strong&gt;Career: 140 for 260 - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;53.85%&lt;/em&gt;&lt;/span&gt; - Rider Rating: *.368&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Season:&amp;nbsp;&lt;/strong&gt;Rank&amp;nbsp;&lt;span style="color: #ff0000;"&gt;22&lt;/span&gt; (15 for 31 - &lt;em&gt;48.4%&lt;/em&gt;)&lt;em&gt;&lt;br /&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Points:&amp;nbsp;&lt;/strong&gt;247.00 pts &lt;span style="color: #ff0000;"&gt;&lt;em&gt;(-645.5)&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Earnings:&amp;nbsp;&lt;/strong&gt;&lt;span style="color: #008000;"&gt;&lt;em&gt;$73,908.24&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Potential&lt;/strong&gt;:&amp;nbsp;83.47 to 89.47 points&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;&lt;span style="text-decoration: underline;"&gt;&lt;strong&gt;Bull&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;ALL:&lt;/strong&gt; 30 outs 4 rides - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;86.67%&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;UTB:&lt;/strong&gt; 21 outs 3 rides - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;85.71%&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;em&gt;&lt;span style="color: #ff0000;"&gt;*No Previous Matchups&lt;/span&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t>Bull 60.00%</t>
+  </si>
+  <si>
+    <t>&lt;h2&gt;Rider&lt;/h2&gt;&lt;p&gt;&lt;strong&gt;Career:&amp;nbsp;&lt;/strong&gt;Career: 154 for 416 - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;37.02%&lt;/em&gt;&lt;/span&gt; - Rider Rating: *.266&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Season:&amp;nbsp;&lt;/strong&gt;Rank&amp;nbsp;&lt;span style="color: #ff0000;"&gt;23&lt;/span&gt; (35 for 80 - &lt;em&gt;43.8%&lt;/em&gt;)&lt;em&gt;&lt;br /&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Points:&amp;nbsp;&lt;/strong&gt;246.50 pts &lt;span style="color: #ff0000;"&gt;&lt;em&gt;(-646)&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Earnings:&amp;nbsp;&lt;/strong&gt;&lt;span style="color: #008000;"&gt;&lt;em&gt;$123,896.04&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Potential&lt;/strong&gt;:&amp;nbsp;85.69 to 91.69 points&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;&lt;span style="text-decoration: underline;"&gt;&lt;strong&gt;Bull&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;ALL:&lt;/strong&gt; 10 outs 3 rides - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;70%&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;em&gt;&lt;span style="color: #ff0000;"&gt;*No Previous Matchups&lt;/span&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t>Bull 73.00%</t>
+  </si>
+  <si>
+    <t>&lt;h2&gt;Rider&lt;/h2&gt;&lt;p&gt;&lt;strong&gt;Career:&amp;nbsp;&lt;/strong&gt;Career: 335 for 867 - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;38.64%&lt;/em&gt;&lt;/span&gt; - Rider Rating: *.274&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Season:&amp;nbsp;&lt;/strong&gt;Rank&amp;nbsp;&lt;span style="color: #ff0000;"&gt;9&lt;/span&gt; (35 for 69 - &lt;em&gt;50.7%&lt;/em&gt;)&lt;em&gt;&lt;br /&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Points:&amp;nbsp;&lt;/strong&gt;405.00 pts &lt;span style="color: #ff0000;"&gt;&lt;em&gt;(-487.5)&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Earnings:&amp;nbsp;&lt;/strong&gt;&lt;span style="color: #008000;"&gt;&lt;em&gt;$166,975.45&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Potential&lt;/strong&gt;:&amp;nbsp;83.75 to 89.75 points&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;&lt;span style="text-decoration: underline;"&gt;&lt;strong&gt;Bull&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;ALL:&lt;/strong&gt; 17 outs 10 rides - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;41.18%&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;UTB:&lt;/strong&gt; 11 outs 8 rides - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;27.27%&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;em&gt;&lt;span style="color: #ff0000;"&gt;*No Previous Matchups&lt;/span&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t>Bull 36.00%</t>
+  </si>
+  <si>
+    <t>&lt;h2&gt;Rider&lt;/h2&gt;&lt;p&gt;&lt;strong&gt;Career:&amp;nbsp;&lt;/strong&gt;Career: 232 for 601 - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;38.6%&lt;/em&gt;&lt;/span&gt; - Rider Rating: *.304&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Season:&amp;nbsp;&lt;/strong&gt;Rank&amp;nbsp;&lt;span style="color: #ff0000;"&gt;32&lt;/span&gt; (19 for 51 - &lt;em&gt;37.3%&lt;/em&gt;)&lt;em&gt;&lt;br /&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Points:&amp;nbsp;&lt;/strong&gt;150.00 pts &lt;span style="color: #ff0000;"&gt;&lt;em&gt;(-742.5)&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Earnings:&amp;nbsp;&lt;/strong&gt;&lt;span style="color: #008000;"&gt;&lt;em&gt;$77,559.34&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Potential&lt;/strong&gt;:&amp;nbsp;83.6 to 89.6 points&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;&lt;span style="text-decoration: underline;"&gt;&lt;strong&gt;Bull&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;ALL:&lt;/strong&gt; 13 outs 4 rides - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;69.23%&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;UTB:&lt;/strong&gt; 9 outs 3 rides - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;66.67%&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;em&gt;&lt;span style="color: #ff0000;"&gt;*No Previous Matchups&lt;/span&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t>Rider 38.00%</t>
+  </si>
+  <si>
+    <t>&lt;h2&gt;Rider&lt;/h2&gt;&lt;p&gt;&lt;strong&gt;Career:&amp;nbsp;&lt;/strong&gt;Career: 142 for 334 - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;42.51%&lt;/em&gt;&lt;/span&gt; - Rider Rating: *.316&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Season:&amp;nbsp;&lt;/strong&gt;Rank&amp;nbsp;&lt;span style="color: #ff0000;"&gt;7&lt;/span&gt; (42 for 84 - &lt;em&gt;50%&lt;/em&gt;)&lt;em&gt;&lt;br /&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Points:&amp;nbsp;&lt;/strong&gt;497.00 pts &lt;span style="color: #ff0000;"&gt;&lt;em&gt;(-395.5)&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Earnings:&amp;nbsp;&lt;/strong&gt;&lt;span style="color: #008000;"&gt;&lt;em&gt;$235,394.68&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Potential&lt;/strong&gt;:&amp;nbsp;82.61 to 88.61 points&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;&lt;span style="text-decoration: underline;"&gt;&lt;strong&gt;Bull&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;ALL:&lt;/strong&gt; 14 outs 9 rides - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;35.71%&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;UTB:&lt;/strong&gt; 11 outs 9 rides - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;18.18%&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;em&gt;&lt;span style="color: #ff0000;"&gt;*No Previous Matchups&lt;/span&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t>&lt;h2&gt;Rider&lt;/h2&gt;&lt;p&gt;&lt;strong&gt;Career:&amp;nbsp;&lt;/strong&gt;Career: 29 for 72 - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;40.28%&lt;/em&gt;&lt;/span&gt; - Rider Rating: .167&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Season:&amp;nbsp;&lt;/strong&gt;Rank&amp;nbsp;&lt;span style="color: #ff0000;"&gt;67&lt;/span&gt; (0 for 2 - &lt;em&gt;0%&lt;/em&gt;)&lt;em&gt;&lt;br /&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Points:&amp;nbsp;&lt;/strong&gt;0.00 pts &lt;span style="color: #ff0000;"&gt;&lt;em&gt;(-892.5)&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Earnings:&amp;nbsp;&lt;/strong&gt;&lt;span style="color: #008000;"&gt;&lt;em&gt;$9,000.00&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Potential&lt;/strong&gt;:&amp;nbsp;84.44 to 90.44 points&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;&lt;span style="text-decoration: underline;"&gt;&lt;strong&gt;Bull&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;ALL:&lt;/strong&gt; 36 outs 14 rides - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;61.11%&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;UTB:&lt;/strong&gt; 23 outs 7 rides - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;69.57%&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;em&gt;&lt;span style="color: #ff0000;"&gt;*No Previous Matchups&lt;/span&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t>&lt;h2&gt;Rider&lt;/h2&gt;&lt;p&gt;&lt;strong&gt;Career:&amp;nbsp;&lt;/strong&gt;Career: 33 for 82 - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;40.24%&lt;/em&gt;&lt;/span&gt; - Rider Rating: .193&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Season:&amp;nbsp;&lt;/strong&gt;Rank&amp;nbsp;&lt;span style="color: #ff0000;"&gt;67&lt;/span&gt; (4 for 27 - &lt;em&gt;14.8%&lt;/em&gt;)&lt;em&gt;&lt;br /&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Points:&amp;nbsp;&lt;/strong&gt;0.00 pts &lt;span style="color: #ff0000;"&gt;&lt;em&gt;(-892.5)&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Earnings:&amp;nbsp;&lt;/strong&gt;&lt;span style="color: #008000;"&gt;&lt;em&gt;$68,882.98&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Potential&lt;/strong&gt;:&amp;nbsp;81.2 to 87.2 points&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;&lt;span style="text-decoration: underline;"&gt;&lt;strong&gt;Bull&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;em&gt;&lt;span style="color: #ff0000;"&gt;*No Previous Matchups&lt;/span&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t>&lt;h2&gt;Rider&lt;/h2&gt;&lt;p&gt;&lt;strong&gt;Career:&amp;nbsp;&lt;/strong&gt;Career: 44 for 122 - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;36.07%&lt;/em&gt;&lt;/span&gt; - Rider Rating: *.215&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Season:&amp;nbsp;&lt;/strong&gt;Rank&amp;nbsp;&lt;span style="color: #ff0000;"&gt;67&lt;/span&gt; (1 for 4 - &lt;em&gt;25%&lt;/em&gt;)&lt;em&gt;&lt;br /&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Points:&amp;nbsp;&lt;/strong&gt;0.00 pts &lt;span style="color: #ff0000;"&gt;&lt;em&gt;(-892.5)&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Earnings:&amp;nbsp;&lt;/strong&gt;&lt;span style="color: #008000;"&gt;&lt;em&gt;$15,572.53&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Potential&lt;/strong&gt;:&amp;nbsp;-1 to 5 points&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;&lt;span style="text-decoration: underline;"&gt;&lt;strong&gt;Bull&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;em&gt;&lt;span style="color: #ff0000;"&gt;*No Previous Matchups&lt;/span&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t>&lt;h2&gt;Rider&lt;/h2&gt;&lt;p&gt;&lt;strong&gt;Career:&amp;nbsp;&lt;/strong&gt;Career: 34 for 99 - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;34.34%&lt;/em&gt;&lt;/span&gt; - Rider Rating: .160&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Season:&amp;nbsp;&lt;/strong&gt;Rank&amp;nbsp;&lt;span style="color: #ff0000;"&gt;66&lt;/span&gt; (1 for 5 - &lt;em&gt;20%&lt;/em&gt;)&lt;em&gt;&lt;br /&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Points:&amp;nbsp;&lt;/strong&gt;7.00 pts &lt;span style="color: #ff0000;"&gt;&lt;em&gt;(-885.5)&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Earnings:&amp;nbsp;&lt;/strong&gt;&lt;span style="color: #008000;"&gt;&lt;em&gt;$39,101.98&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Potential&lt;/strong&gt;:&amp;nbsp;82.53 to 88.53 points&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;&lt;span style="text-decoration: underline;"&gt;&lt;strong&gt;Bull&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;em&gt;&lt;span style="color: #ff0000;"&gt;*No Previous Matchups&lt;/span&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t>&lt;h2&gt;Rider&lt;/h2&gt;&lt;p&gt;&lt;strong&gt;Career:&amp;nbsp;&lt;/strong&gt;Career: 380 for 760 - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;50%&lt;/em&gt;&lt;/span&gt; - Rider Rating: *.369&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Season:&amp;nbsp;&lt;/strong&gt;Rank&amp;nbsp;&lt;span style="color: #ff0000;"&gt;41&lt;/span&gt; (16 for 37 - &lt;em&gt;43.2%&lt;/em&gt;)&lt;em&gt;&lt;br /&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Points:&amp;nbsp;&lt;/strong&gt;74.00 pts &lt;span style="color: #ff0000;"&gt;&lt;em&gt;(-818.5)&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Earnings:&amp;nbsp;&lt;/strong&gt;&lt;span style="color: #008000;"&gt;&lt;em&gt;$93,253.57&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Potential&lt;/strong&gt;:&amp;nbsp;81.2 to 87.2 points&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;&lt;span style="text-decoration: underline;"&gt;&lt;strong&gt;Bull&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;em&gt;&lt;span style="color: #ff0000;"&gt;*No Previous Matchups&lt;/span&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t>Bull 37.00%</t>
+  </si>
+  <si>
+    <t>&lt;h2&gt;Rider&lt;/h2&gt;&lt;p&gt;&lt;strong&gt;Career:&amp;nbsp;&lt;/strong&gt;Career: 235 for 693 - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;33.91%&lt;/em&gt;&lt;/span&gt; - Rider Rating: *.250&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Season:&amp;nbsp;&lt;/strong&gt;Rank&amp;nbsp;&lt;span style="color: #ff0000;"&gt;51&lt;/span&gt; (3 for 28 - &lt;em&gt;10.7%&lt;/em&gt;)&lt;em&gt;&lt;br /&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Points:&amp;nbsp;&lt;/strong&gt;16.00 pts &lt;span style="color: #ff0000;"&gt;&lt;em&gt;(-876.5)&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Earnings:&amp;nbsp;&lt;/strong&gt;&lt;span style="color: #008000;"&gt;&lt;em&gt;$28,189.34&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Potential&lt;/strong&gt;:&amp;nbsp;81.78 to 87.78 points&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;&lt;span style="text-decoration: underline;"&gt;&lt;strong&gt;Bull&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;ALL:&lt;/strong&gt; 12 outs 5 rides - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;58.33%&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;UTB:&lt;/strong&gt; 5 outs 2 rides - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;60%&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;em&gt;&lt;span style="color: #ff0000;"&gt;*No Previous Matchups&lt;/span&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t>&lt;h2&gt;Rider&lt;/h2&gt;&lt;p&gt;&lt;strong&gt;Career:&amp;nbsp;&lt;/strong&gt;Career: 75 for 287 - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;26.13%&lt;/em&gt;&lt;/span&gt; - Rider Rating: *.206&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Season:&amp;nbsp;&lt;/strong&gt;Rank&amp;nbsp;&lt;span style="color: #ff0000;"&gt;67&lt;/span&gt; (1 for 6 - &lt;em&gt;16.7%&lt;/em&gt;)&lt;em&gt;&lt;br /&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Points:&amp;nbsp;&lt;/strong&gt;0.00 pts &lt;span style="color: #ff0000;"&gt;&lt;em&gt;(-892.5)&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Earnings:&amp;nbsp;&lt;/strong&gt;&lt;span style="color: #008000;"&gt;&lt;em&gt;$22,645.05&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Potential&lt;/strong&gt;:&amp;nbsp;83.72 to 89.72 points&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;&lt;span style="text-decoration: underline;"&gt;&lt;strong&gt;Bull&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;ALL:&lt;/strong&gt; 5 outs 1 rides - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;80%&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;em&gt;&lt;span style="color: #ff0000;"&gt;*No Previous Matchups&lt;/span&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t>&lt;h2&gt;Rider&lt;/h2&gt;&lt;p&gt;&lt;strong&gt;Career:&amp;nbsp;&lt;/strong&gt;Career: 23 for 82 - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;28.05%&lt;/em&gt;&lt;/span&gt; - Rider Rating: .166&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Season:&amp;nbsp;&lt;/strong&gt;Rank&amp;nbsp;&lt;span style="color: #ff0000;"&gt;67&lt;/span&gt; (0 for 3 - &lt;em&gt;0%&lt;/em&gt;)&lt;em&gt;&lt;br /&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Points:&amp;nbsp;&lt;/strong&gt;0.00 pts &lt;span style="color: #ff0000;"&gt;&lt;em&gt;(-892.5)&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Earnings:&amp;nbsp;&lt;/strong&gt;&lt;span style="color: #008000;"&gt;&lt;em&gt;$17,646.45&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Potential&lt;/strong&gt;:&amp;nbsp;84.4 to 90.4 points&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;&lt;span style="text-decoration: underline;"&gt;&lt;strong&gt;Bull&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;em&gt;&lt;span style="color: #ff0000;"&gt;*No Previous Matchups&lt;/span&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t>Bull 49.00%</t>
+  </si>
+  <si>
+    <t>&lt;h2&gt;Rider&lt;/h2&gt;&lt;p&gt;&lt;strong&gt;Career:&amp;nbsp;&lt;/strong&gt;Career: 184 for 747 - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;24.63%&lt;/em&gt;&lt;/span&gt; - Rider Rating: .167&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Season:&amp;nbsp;&lt;/strong&gt;Rank&amp;nbsp;&lt;span style="color: #ff0000;"&gt;60&lt;/span&gt; (2 for 17 - &lt;em&gt;11.8%&lt;/em&gt;)&lt;em&gt;&lt;br /&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Points:&amp;nbsp;&lt;/strong&gt;8.00 pts &lt;span style="color: #ff0000;"&gt;&lt;em&gt;(-884.5)&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Earnings:&amp;nbsp;&lt;/strong&gt;&lt;span style="color: #008000;"&gt;&lt;em&gt;$55,628.97&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Potential&lt;/strong&gt;:&amp;nbsp;83.01 to 89.01 points&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;&lt;span style="text-decoration: underline;"&gt;&lt;strong&gt;Bull&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;ALL:&lt;/strong&gt; 31 outs 16 rides - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;48.39%&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;UTB:&lt;/strong&gt; 27 outs 14 rides - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;48.15%&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;em&gt;&lt;span style="color: #ff0000;"&gt;*No Previous Matchups&lt;/span&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t>&lt;h2&gt;Rider&lt;/h2&gt;&lt;p&gt;&lt;strong&gt;Career:&amp;nbsp;&lt;/strong&gt;Career: 64 for 237 - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;27%&lt;/em&gt;&lt;/span&gt; - Rider Rating: .168&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Season:&amp;nbsp;&lt;/strong&gt;Rank&amp;nbsp;&lt;span style="color: #ff0000;"&gt;36&lt;/span&gt; (6 for 24 - &lt;em&gt;25%&lt;/em&gt;)&lt;em&gt;&lt;br /&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Points:&amp;nbsp;&lt;/strong&gt;95.00 pts &lt;span style="color: #ff0000;"&gt;&lt;em&gt;(-797.5)&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Earnings:&amp;nbsp;&lt;/strong&gt;&lt;span style="color: #008000;"&gt;&lt;em&gt;$46,556.47&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Potential&lt;/strong&gt;:&amp;nbsp;84.34 to 90.34 points&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;&lt;span style="text-decoration: underline;"&gt;&lt;strong&gt;Bull&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;ALL:&lt;/strong&gt; 5 outs 2 rides - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;60%&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;em&gt;&lt;span style="color: #ff0000;"&gt;*No Previous Matchups&lt;/span&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t>&lt;h2&gt;Rider&lt;/h2&gt;&lt;p&gt;&lt;strong&gt;Career:&amp;nbsp;&lt;/strong&gt;Career: 128 for 442 - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;28.96%&lt;/em&gt;&lt;/span&gt; - Rider Rating: .190&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Season:&amp;nbsp;&lt;/strong&gt;Rank&amp;nbsp;&lt;span style="color: #ff0000;"&gt;27&lt;/span&gt; (21 for 58 - &lt;em&gt;36.2%&lt;/em&gt;)&lt;em&gt;&lt;br /&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Points:&amp;nbsp;&lt;/strong&gt;209.00 pts &lt;span style="color: #ff0000;"&gt;&lt;em&gt;(-683.5)&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Earnings:&amp;nbsp;&lt;/strong&gt;&lt;span style="color: #008000;"&gt;&lt;em&gt;$103,513.47&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Potential&lt;/strong&gt;:&amp;nbsp;85.5 to 91.5 points&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;&lt;span style="text-decoration: underline;"&gt;&lt;strong&gt;Bull&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;em&gt;&lt;span style="color: #ff0000;"&gt;*No Previous Matchups&lt;/span&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t>&lt;h2&gt;Rider&lt;/h2&gt;&lt;p&gt;&lt;strong&gt;Career:&amp;nbsp;&lt;/strong&gt;Career: 127 for 330 - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;38.48%&lt;/em&gt;&lt;/span&gt; - Rider Rating: *.269&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Season:&amp;nbsp;&lt;/strong&gt;Rank&amp;nbsp;&lt;span style="color: #ff0000;"&gt;12&lt;/span&gt; (27 for 69 - &lt;em&gt;39.1%&lt;/em&gt;)&lt;em&gt;&lt;br /&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Points:&amp;nbsp;&lt;/strong&gt;400.00 pts &lt;span style="color: #ff0000;"&gt;&lt;em&gt;(-492.5)&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Earnings:&amp;nbsp;&lt;/strong&gt;&lt;span style="color: #008000;"&gt;&lt;em&gt;$126,110.26&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Potential&lt;/strong&gt;:&amp;nbsp;82.77 to 88.77 points&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;&lt;span style="text-decoration: underline;"&gt;&lt;strong&gt;Bull&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;ALL:&lt;/strong&gt; 9 outs 0 rides - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;100%&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;em&gt;&lt;span style="color: #ff0000;"&gt;*No Previous Matchups&lt;/span&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1026,6 +3091,12 @@
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1048,7 +3119,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
@@ -1063,6 +3134,10 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1397,6 +3472,2195 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01ACAA71-EF8B-E143-BCEC-D101B7DB858C}">
+  <dimension ref="A1:Y53"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="31.83203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="24.1640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="27.5" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.83203125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="8.1640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I1" t="s">
+        <v>11</v>
+      </c>
+      <c r="J1" t="s">
+        <v>12</v>
+      </c>
+      <c r="K1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1" t="s">
+        <v>1</v>
+      </c>
+      <c r="M1" t="s">
+        <v>14</v>
+      </c>
+      <c r="N1" t="s">
+        <v>15</v>
+      </c>
+      <c r="O1" t="s">
+        <v>10</v>
+      </c>
+      <c r="P1" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q1" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="R1" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="S1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1">
+        <v>66.790000000000006</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="H2" s="1">
+        <v>1</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L2" t="s">
+        <v>404</v>
+      </c>
+      <c r="M2" t="s">
+        <v>29</v>
+      </c>
+      <c r="N2" t="s">
+        <v>445</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="P2" s="9"/>
+      <c r="Q2" s="10"/>
+      <c r="R2" s="11"/>
+      <c r="Y2" s="13" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="3" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1">
+        <v>41.71</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="H3" s="1">
+        <v>1</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K3" t="s">
+        <v>27</v>
+      </c>
+      <c r="L3" t="s">
+        <v>446</v>
+      </c>
+      <c r="M3" t="s">
+        <v>36</v>
+      </c>
+      <c r="N3" t="s">
+        <v>447</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="P3" s="9"/>
+      <c r="Q3" s="10"/>
+      <c r="R3" s="11"/>
+      <c r="Y3" s="13" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="4" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1">
+        <v>58.27</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="E4" s="1">
+        <v>10230319</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="H4" s="1">
+        <v>1</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K4" t="s">
+        <v>27</v>
+      </c>
+      <c r="L4" t="s">
+        <v>446</v>
+      </c>
+      <c r="M4" t="s">
+        <v>36</v>
+      </c>
+      <c r="N4" t="s">
+        <v>448</v>
+      </c>
+      <c r="O4" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P4" s="9"/>
+      <c r="Q4" s="10"/>
+      <c r="R4" s="11"/>
+      <c r="Y4" s="13" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="5" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1">
+        <v>48.73</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="E5" s="1">
+        <v>10256903</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="H5" s="1">
+        <v>1</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L5" t="s">
+        <v>449</v>
+      </c>
+      <c r="M5" t="s">
+        <v>29</v>
+      </c>
+      <c r="N5" t="s">
+        <v>450</v>
+      </c>
+      <c r="O5" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="P5" s="9"/>
+      <c r="Q5" s="10"/>
+      <c r="R5" s="11"/>
+      <c r="Y5" s="13" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="6" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1">
+        <v>68.94</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="E6" s="1">
+        <v>10215145</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="H6" s="1">
+        <v>1</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K6" t="s">
+        <v>43</v>
+      </c>
+      <c r="L6" t="s">
+        <v>451</v>
+      </c>
+      <c r="M6" t="s">
+        <v>99</v>
+      </c>
+      <c r="N6" t="s">
+        <v>452</v>
+      </c>
+      <c r="O6" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="P6" s="9"/>
+      <c r="Q6" s="10"/>
+      <c r="R6" s="11"/>
+      <c r="Y6" s="13" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="H7" s="1">
+        <v>1</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K7" t="s">
+        <v>43</v>
+      </c>
+      <c r="N7" t="s">
+        <v>453</v>
+      </c>
+      <c r="O7" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="P7" s="9"/>
+      <c r="Q7" s="10"/>
+      <c r="R7" s="11"/>
+      <c r="Y7" s="13" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1">
+        <v>71</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E8" s="1">
+        <v>10229185</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="H8" s="1">
+        <v>1</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K8" t="s">
+        <v>43</v>
+      </c>
+      <c r="L8" t="s">
+        <v>454</v>
+      </c>
+      <c r="M8" t="s">
+        <v>29</v>
+      </c>
+      <c r="N8" t="s">
+        <v>455</v>
+      </c>
+      <c r="O8" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="P8" s="9"/>
+      <c r="Q8" s="10"/>
+      <c r="R8" s="11"/>
+      <c r="Y8" s="13" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E9" s="1">
+        <v>10250898</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="H9" s="1">
+        <v>1</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K9" t="s">
+        <v>27</v>
+      </c>
+      <c r="N9" t="s">
+        <v>456</v>
+      </c>
+      <c r="O9" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="P9" s="9"/>
+      <c r="Q9" s="10"/>
+      <c r="R9" s="11"/>
+      <c r="Y9" s="13" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1">
+        <v>52.32</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="H10" s="1">
+        <v>1</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K10" t="s">
+        <v>27</v>
+      </c>
+      <c r="L10" t="s">
+        <v>457</v>
+      </c>
+      <c r="M10" t="s">
+        <v>29</v>
+      </c>
+      <c r="N10" t="s">
+        <v>458</v>
+      </c>
+      <c r="O10" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="P10" s="9"/>
+      <c r="Q10" s="10"/>
+      <c r="R10" s="11"/>
+      <c r="Y10" s="13" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1">
+        <v>59.59</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="H11" s="1">
+        <v>1</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K11" t="s">
+        <v>27</v>
+      </c>
+      <c r="L11" t="s">
+        <v>459</v>
+      </c>
+      <c r="M11" t="s">
+        <v>29</v>
+      </c>
+      <c r="N11" t="s">
+        <v>460</v>
+      </c>
+      <c r="O11" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="P11" s="9"/>
+      <c r="Q11" s="10"/>
+      <c r="R11" s="11"/>
+      <c r="Y11" s="13" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="12" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="1">
+        <v>11</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="E12" s="1">
+        <v>10268379</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="H12" s="1">
+        <v>1</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K12" t="s">
+        <v>27</v>
+      </c>
+      <c r="N12" t="s">
+        <v>461</v>
+      </c>
+      <c r="O12" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="P12" s="9"/>
+      <c r="Q12" s="10"/>
+      <c r="R12" s="11"/>
+      <c r="Y12" s="13" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="1">
+        <v>12</v>
+      </c>
+      <c r="B13" s="1">
+        <v>67.209999999999994</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="H13" s="1">
+        <v>1</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K13" t="s">
+        <v>27</v>
+      </c>
+      <c r="L13" t="s">
+        <v>462</v>
+      </c>
+      <c r="M13" t="s">
+        <v>99</v>
+      </c>
+      <c r="N13" t="s">
+        <v>463</v>
+      </c>
+      <c r="O13" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="P13" s="9"/>
+      <c r="Q13" s="10"/>
+      <c r="R13" s="11"/>
+      <c r="Y13" s="13" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="1">
+        <v>13</v>
+      </c>
+      <c r="B14" s="1">
+        <v>75.92</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>365</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="E14" s="1">
+        <v>10272036</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="H14" s="1">
+        <v>1</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K14" t="s">
+        <v>43</v>
+      </c>
+      <c r="L14" t="s">
+        <v>446</v>
+      </c>
+      <c r="M14" t="s">
+        <v>36</v>
+      </c>
+      <c r="N14" t="s">
+        <v>464</v>
+      </c>
+      <c r="O14" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="P14" s="9"/>
+      <c r="Q14" s="10"/>
+      <c r="R14" s="11"/>
+      <c r="Y14" s="13" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="1">
+        <v>14</v>
+      </c>
+      <c r="B15" s="1">
+        <v>78.86</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="H15" s="1">
+        <v>1</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K15" t="s">
+        <v>27</v>
+      </c>
+      <c r="L15" t="s">
+        <v>465</v>
+      </c>
+      <c r="M15" t="s">
+        <v>29</v>
+      </c>
+      <c r="N15" t="s">
+        <v>466</v>
+      </c>
+      <c r="O15" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="P15" s="9"/>
+      <c r="Q15" s="10"/>
+      <c r="R15" s="11"/>
+      <c r="Y15" s="13" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="1">
+        <v>15</v>
+      </c>
+      <c r="B16" s="1">
+        <v>57.72</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="H16" s="1">
+        <v>1</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K16" t="s">
+        <v>27</v>
+      </c>
+      <c r="L16" t="s">
+        <v>467</v>
+      </c>
+      <c r="M16" t="s">
+        <v>99</v>
+      </c>
+      <c r="N16" t="s">
+        <v>468</v>
+      </c>
+      <c r="O16" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="P16" s="9"/>
+      <c r="Q16" s="10"/>
+      <c r="R16" s="11"/>
+      <c r="Y16" s="13" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="17" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="1">
+        <v>16</v>
+      </c>
+      <c r="B17" s="1">
+        <v>65.19</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="E17" s="1">
+        <v>10276006</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="H17" s="1">
+        <v>1</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K17" t="s">
+        <v>27</v>
+      </c>
+      <c r="L17" t="s">
+        <v>469</v>
+      </c>
+      <c r="M17" t="s">
+        <v>99</v>
+      </c>
+      <c r="N17" t="s">
+        <v>470</v>
+      </c>
+      <c r="O17" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="P17" s="9"/>
+      <c r="Q17" s="10"/>
+      <c r="R17" s="11"/>
+      <c r="Y17" s="13" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="18" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="1">
+        <v>17</v>
+      </c>
+      <c r="B18" s="1">
+        <v>66.97</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="E18" s="1">
+        <v>10243159</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="H18" s="1">
+        <v>1</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K18" t="s">
+        <v>27</v>
+      </c>
+      <c r="L18" t="s">
+        <v>471</v>
+      </c>
+      <c r="M18" t="s">
+        <v>29</v>
+      </c>
+      <c r="N18" t="s">
+        <v>472</v>
+      </c>
+      <c r="O18" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="P18" s="9"/>
+      <c r="Q18" s="10"/>
+      <c r="R18" s="11"/>
+      <c r="Y18" s="13" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="19" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="1">
+        <v>18</v>
+      </c>
+      <c r="B19" s="1">
+        <v>75.709999999999994</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="E19" s="1">
+        <v>10205390</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="H19" s="1">
+        <v>1</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K19" t="s">
+        <v>27</v>
+      </c>
+      <c r="L19" t="s">
+        <v>473</v>
+      </c>
+      <c r="M19" t="s">
+        <v>99</v>
+      </c>
+      <c r="N19" t="s">
+        <v>474</v>
+      </c>
+      <c r="O19" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="P19" s="9"/>
+      <c r="Q19" s="10"/>
+      <c r="R19" s="11"/>
+      <c r="Y19" s="13" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="20" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="1">
+        <v>19</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>344</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E20" s="1"/>
+      <c r="F20" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="H20" s="1">
+        <v>1</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K20" t="s">
+        <v>27</v>
+      </c>
+      <c r="N20" t="s">
+        <v>475</v>
+      </c>
+      <c r="O20" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="P20" s="9"/>
+      <c r="Q20" s="10"/>
+      <c r="R20" s="11"/>
+      <c r="Y20" s="13" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="21" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="1">
+        <v>20</v>
+      </c>
+      <c r="B21" s="1">
+        <v>77.819999999999993</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="E21" s="1">
+        <v>10231548</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="H21" s="1">
+        <v>1</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K21" t="s">
+        <v>43</v>
+      </c>
+      <c r="L21" t="s">
+        <v>476</v>
+      </c>
+      <c r="M21" t="s">
+        <v>29</v>
+      </c>
+      <c r="N21" t="s">
+        <v>477</v>
+      </c>
+      <c r="O21" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="P21" s="9"/>
+      <c r="Q21" s="10"/>
+      <c r="R21" s="11"/>
+      <c r="Y21" s="13" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="22" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="1">
+        <v>21</v>
+      </c>
+      <c r="B22" s="1">
+        <v>73.45</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="E22" s="1">
+        <v>10268851</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="H22" s="1">
+        <v>1</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K22" t="s">
+        <v>27</v>
+      </c>
+      <c r="L22" t="s">
+        <v>465</v>
+      </c>
+      <c r="M22" t="s">
+        <v>29</v>
+      </c>
+      <c r="N22" t="s">
+        <v>478</v>
+      </c>
+      <c r="O22" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="P22" s="9"/>
+      <c r="Q22" s="10"/>
+      <c r="R22" s="11"/>
+      <c r="Y22" s="13" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="23" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="1">
+        <v>22</v>
+      </c>
+      <c r="B23" s="1">
+        <v>74.900000000000006</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="E23" s="1">
+        <v>10229189</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="H23" s="1">
+        <v>1</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K23" t="s">
+        <v>43</v>
+      </c>
+      <c r="L23" t="s">
+        <v>446</v>
+      </c>
+      <c r="M23" t="s">
+        <v>36</v>
+      </c>
+      <c r="N23" t="s">
+        <v>479</v>
+      </c>
+      <c r="O23" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="P23" s="9"/>
+      <c r="Q23" s="10"/>
+      <c r="R23" s="11"/>
+      <c r="Y23" s="13" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="24" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="1">
+        <v>23</v>
+      </c>
+      <c r="B24" s="1">
+        <v>61.01</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="E24" s="1">
+        <v>10262490</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="H24" s="1">
+        <v>1</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K24" t="s">
+        <v>43</v>
+      </c>
+      <c r="L24" t="s">
+        <v>74</v>
+      </c>
+      <c r="M24" t="s">
+        <v>99</v>
+      </c>
+      <c r="N24" t="s">
+        <v>480</v>
+      </c>
+      <c r="O24" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="P24" s="9"/>
+      <c r="Q24" s="10"/>
+      <c r="R24" s="11"/>
+      <c r="Y24" s="13" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="25" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="1">
+        <v>24</v>
+      </c>
+      <c r="B25" s="8">
+        <v>84.69</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="E25" s="1"/>
+      <c r="F25" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="H25" s="1">
+        <v>1</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K25" t="s">
+        <v>27</v>
+      </c>
+      <c r="L25" t="s">
+        <v>481</v>
+      </c>
+      <c r="M25" t="s">
+        <v>29</v>
+      </c>
+      <c r="N25" t="s">
+        <v>482</v>
+      </c>
+      <c r="O25" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="P25" s="9"/>
+      <c r="Q25" s="10"/>
+      <c r="R25" s="11"/>
+      <c r="Y25" s="13" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="26" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="1">
+        <v>25</v>
+      </c>
+      <c r="B26" s="1">
+        <v>42.09</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="E26" s="1">
+        <v>10270857</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="H26" s="1">
+        <v>1</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K26" t="s">
+        <v>27</v>
+      </c>
+      <c r="L26" t="s">
+        <v>483</v>
+      </c>
+      <c r="M26" t="s">
+        <v>99</v>
+      </c>
+      <c r="N26" t="s">
+        <v>484</v>
+      </c>
+      <c r="O26" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="P26" s="9"/>
+      <c r="Q26" s="10"/>
+      <c r="R26" s="11"/>
+      <c r="Y26" s="13" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="27" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="1">
+        <v>26</v>
+      </c>
+      <c r="B27" s="1">
+        <v>55.03</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="E27" s="1"/>
+      <c r="F27" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="H27" s="1">
+        <v>1</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K27" t="s">
+        <v>43</v>
+      </c>
+      <c r="L27" t="s">
+        <v>485</v>
+      </c>
+      <c r="M27" t="s">
+        <v>29</v>
+      </c>
+      <c r="N27" t="s">
+        <v>486</v>
+      </c>
+      <c r="O27" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="P27" s="9"/>
+      <c r="Q27" s="10"/>
+      <c r="R27" s="11"/>
+      <c r="Y27" s="13" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="28" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="1">
+        <v>27</v>
+      </c>
+      <c r="B28" s="1">
+        <v>68.459999999999994</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="E28" s="1">
+        <v>10229166</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="H28" s="1">
+        <v>1</v>
+      </c>
+      <c r="I28" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K28" t="s">
+        <v>43</v>
+      </c>
+      <c r="L28" t="s">
+        <v>487</v>
+      </c>
+      <c r="M28" t="s">
+        <v>29</v>
+      </c>
+      <c r="N28" t="s">
+        <v>488</v>
+      </c>
+      <c r="O28" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="P28" s="9"/>
+      <c r="Q28" s="10"/>
+      <c r="R28" s="11"/>
+      <c r="Y28" s="13" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="29" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="1">
+        <v>28</v>
+      </c>
+      <c r="B29" s="1">
+        <v>51.27</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="E29" s="1"/>
+      <c r="F29" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="H29" s="1">
+        <v>1</v>
+      </c>
+      <c r="I29" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="J29" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K29" t="s">
+        <v>43</v>
+      </c>
+      <c r="L29" t="s">
+        <v>489</v>
+      </c>
+      <c r="M29" t="s">
+        <v>99</v>
+      </c>
+      <c r="N29" t="s">
+        <v>490</v>
+      </c>
+      <c r="O29" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="P29" s="9"/>
+      <c r="Q29" s="10"/>
+      <c r="R29" s="11"/>
+      <c r="Y29" s="13" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="30" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="1">
+        <v>29</v>
+      </c>
+      <c r="B30" s="1">
+        <v>72.58</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="E30" s="1">
+        <v>10257997</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="H30" s="1">
+        <v>1</v>
+      </c>
+      <c r="I30" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="J30" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K30" t="s">
+        <v>43</v>
+      </c>
+      <c r="L30" t="s">
+        <v>133</v>
+      </c>
+      <c r="M30" t="s">
+        <v>29</v>
+      </c>
+      <c r="N30" t="s">
+        <v>491</v>
+      </c>
+      <c r="O30" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="P30" s="9"/>
+      <c r="Q30" s="10"/>
+      <c r="R30" s="11"/>
+      <c r="Y30" s="13" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="31" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="1">
+        <v>30</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="E31" s="1">
+        <v>10262368</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="H31" s="1">
+        <v>1</v>
+      </c>
+      <c r="I31" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="J31" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K31" t="s">
+        <v>27</v>
+      </c>
+      <c r="N31" t="s">
+        <v>492</v>
+      </c>
+      <c r="O31" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="P31" s="9"/>
+      <c r="Q31" s="10"/>
+      <c r="R31" s="11"/>
+      <c r="Y31" s="13" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="32" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="1">
+        <v>31</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C32" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="E32" s="1"/>
+      <c r="F32" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="H32" s="1">
+        <v>1</v>
+      </c>
+      <c r="I32" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="J32" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K32" t="s">
+        <v>27</v>
+      </c>
+      <c r="N32" t="s">
+        <v>493</v>
+      </c>
+      <c r="O32" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="P32" s="9"/>
+      <c r="Q32" s="10"/>
+      <c r="R32" s="11"/>
+      <c r="Y32" s="13" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="33" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="1">
+        <v>32</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="E33" s="1"/>
+      <c r="F33" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="H33" s="1">
+        <v>1</v>
+      </c>
+      <c r="I33" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="J33" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K33" t="s">
+        <v>43</v>
+      </c>
+      <c r="N33" t="s">
+        <v>494</v>
+      </c>
+      <c r="O33" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="P33" s="9"/>
+      <c r="Q33" s="10"/>
+      <c r="R33" s="11"/>
+      <c r="Y33" s="13" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="34" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="1">
+        <v>33</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="E34" s="1"/>
+      <c r="F34" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="H34" s="1">
+        <v>1</v>
+      </c>
+      <c r="I34" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="J34" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K34" t="s">
+        <v>27</v>
+      </c>
+      <c r="N34" t="s">
+        <v>495</v>
+      </c>
+      <c r="O34" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="P34" s="9"/>
+      <c r="Q34" s="10"/>
+      <c r="R34" s="11"/>
+      <c r="Y34" s="13" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="35" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="1">
+        <v>34</v>
+      </c>
+      <c r="B35" s="1">
+        <v>61.69</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="E35" s="1"/>
+      <c r="F35" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="H35" s="1">
+        <v>1</v>
+      </c>
+      <c r="I35" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="J35" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K35" t="s">
+        <v>43</v>
+      </c>
+      <c r="L35" t="s">
+        <v>496</v>
+      </c>
+      <c r="M35" t="s">
+        <v>29</v>
+      </c>
+      <c r="N35" t="s">
+        <v>497</v>
+      </c>
+      <c r="O35" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="P35" s="9"/>
+      <c r="Q35" s="10"/>
+      <c r="R35" s="11"/>
+      <c r="Y35" s="13" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="36" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="1">
+        <v>35</v>
+      </c>
+      <c r="B36" s="1">
+        <v>73.28</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E36" s="1"/>
+      <c r="F36" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="H36" s="1">
+        <v>1</v>
+      </c>
+      <c r="I36" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="J36" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K36" t="s">
+        <v>27</v>
+      </c>
+      <c r="L36" t="s">
+        <v>446</v>
+      </c>
+      <c r="M36" t="s">
+        <v>36</v>
+      </c>
+      <c r="N36" t="s">
+        <v>498</v>
+      </c>
+      <c r="O36" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="P36" s="9"/>
+      <c r="Q36" s="10"/>
+      <c r="R36" s="11"/>
+      <c r="Y36" s="13" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="37" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="1">
+        <v>36</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="E37" s="1"/>
+      <c r="F37" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="H37" s="1">
+        <v>1</v>
+      </c>
+      <c r="I37" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="J37" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K37" t="s">
+        <v>43</v>
+      </c>
+      <c r="N37" t="s">
+        <v>499</v>
+      </c>
+      <c r="O37" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="P37" s="9"/>
+      <c r="Q37" s="10"/>
+      <c r="R37" s="11"/>
+      <c r="Y37" s="13" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="38" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="1">
+        <v>37</v>
+      </c>
+      <c r="B38" s="1">
+        <v>69.680000000000007</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="E38" s="1">
+        <v>10243021</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="H38" s="1">
+        <v>1</v>
+      </c>
+      <c r="I38" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="J38" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K38" t="s">
+        <v>43</v>
+      </c>
+      <c r="L38" t="s">
+        <v>500</v>
+      </c>
+      <c r="M38" t="s">
+        <v>29</v>
+      </c>
+      <c r="N38" t="s">
+        <v>501</v>
+      </c>
+      <c r="O38" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="P38" s="9"/>
+      <c r="Q38" s="10"/>
+      <c r="R38" s="11"/>
+      <c r="Y38" s="13" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="39" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="1">
+        <v>38</v>
+      </c>
+      <c r="B39" s="1">
+        <v>52.22</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="E39" s="1">
+        <v>10276169</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="H39" s="1">
+        <v>1</v>
+      </c>
+      <c r="I39" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="J39" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K39" t="s">
+        <v>43</v>
+      </c>
+      <c r="L39" t="s">
+        <v>446</v>
+      </c>
+      <c r="M39" t="s">
+        <v>36</v>
+      </c>
+      <c r="N39" t="s">
+        <v>502</v>
+      </c>
+      <c r="O39" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="P39" s="9"/>
+      <c r="Q39" s="10"/>
+      <c r="R39" s="11"/>
+      <c r="Y39" s="13" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="40" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="1">
+        <v>39</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="E40" s="1">
+        <v>10262517</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="H40" s="1">
+        <v>1</v>
+      </c>
+      <c r="I40" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="J40" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K40" t="s">
+        <v>43</v>
+      </c>
+      <c r="N40" t="s">
+        <v>503</v>
+      </c>
+      <c r="O40" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="P40" s="9"/>
+      <c r="Q40" s="10"/>
+      <c r="R40" s="11"/>
+      <c r="Y40" s="13" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="41" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="1">
+        <v>40</v>
+      </c>
+      <c r="B41" s="1">
+        <v>75.91</v>
+      </c>
+      <c r="C41" s="5" t="s">
+        <v>280</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E41" s="1"/>
+      <c r="F41" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="H41" s="1">
+        <v>1</v>
+      </c>
+      <c r="I41" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="J41" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K41" t="s">
+        <v>43</v>
+      </c>
+      <c r="L41" t="s">
+        <v>446</v>
+      </c>
+      <c r="M41" t="s">
+        <v>36</v>
+      </c>
+      <c r="N41" t="s">
+        <v>504</v>
+      </c>
+      <c r="O41" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="P41" s="9"/>
+      <c r="Q41" s="10"/>
+      <c r="R41" s="11"/>
+      <c r="Y41" s="13" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="42" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="P42" s="9"/>
+      <c r="Q42" s="10"/>
+      <c r="R42" s="11"/>
+    </row>
+    <row r="43" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Q43" s="10"/>
+      <c r="R43" s="11"/>
+    </row>
+    <row r="44" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Q44" s="10"/>
+      <c r="R44" s="11"/>
+    </row>
+    <row r="45" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Q45" s="10"/>
+    </row>
+    <row r="46" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Q46" s="10"/>
+    </row>
+    <row r="47" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Q47" s="10"/>
+    </row>
+    <row r="48" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Q48" s="12"/>
+    </row>
+    <row r="49" spans="17:17" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Q49" s="12"/>
+    </row>
+    <row r="50" spans="17:17" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Q50" s="12"/>
+    </row>
+    <row r="51" spans="17:17" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Q51" s="12"/>
+    </row>
+    <row r="52" spans="17:17" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="53" spans="17:17" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L41">
+    <sortCondition ref="A2:A41"/>
+  </sortState>
+  <hyperlinks>
+    <hyperlink ref="J41" r:id="rId1" display="https://probullstats.com/loggers/matchup.php?bull=54839&amp;guy=Julio+Cesar+Marques" xr:uid="{7A80C17A-3232-6448-9343-11FC1CD3C297}"/>
+    <hyperlink ref="J40" r:id="rId2" display="https://probullstats.com/loggers/matchup.php?bull=56542&amp;guy=Callum+Miller" xr:uid="{0F2BD59E-A00B-4D4B-8A15-FC0C2FCD8520}"/>
+    <hyperlink ref="J39" r:id="rId3" display="https://probullstats.com/loggers/matchup.php?bull=54130&amp;guy=Trace+Redd" xr:uid="{F4C2835A-438B-0142-98F5-439B5289E417}"/>
+    <hyperlink ref="J38" r:id="rId4" display="https://probullstats.com/loggers/matchup.php?bull=51428&amp;guy=Grayson+Cole" xr:uid="{9F41CA48-CFB7-E246-92DC-10D6692090A4}"/>
+    <hyperlink ref="J37" r:id="rId5" display="https://probullstats.com/loggers/matchup.php?bull=56381&amp;guy=Vinicius+Rodrigues+Pereira" xr:uid="{F733F9C0-F92E-DD40-BD82-74810719B425}"/>
+    <hyperlink ref="J36" r:id="rId6" display="https://probullstats.com/loggers/matchup.php?bull=55806&amp;guy=Ednelio+Rodrigues" xr:uid="{07DD6F14-EB65-2C4E-A591-3E2C378C2A67}"/>
+    <hyperlink ref="J35" r:id="rId7" display="https://probullstats.com/loggers/matchup.php?bull=53419&amp;guy=Mason+Taylor" xr:uid="{864A1DB8-FE2B-5D44-9643-DB818F8A9234}"/>
+    <hyperlink ref="J34" r:id="rId8" display="https://probullstats.com/loggers/matchup.php?bull=56047&amp;guy=Dener+Barbosa" xr:uid="{2AB1932A-11A1-7447-80A6-E02A42B49BB9}"/>
+    <hyperlink ref="J33" r:id="rId9" display="https://probullstats.com/loggers/matchup.php?bull=55809&amp;guy=Ramon+Fiorini" xr:uid="{03F5EABD-CF18-5E42-A0EA-CD3101D51E6C}"/>
+    <hyperlink ref="J32" r:id="rId10" display="https://probullstats.com/loggers/matchup.php?bull=56578&amp;guy=Vinicius+Pinheiro+Correa" xr:uid="{AAF7E716-B51F-5744-80BC-B9D1B3EC32AD}"/>
+    <hyperlink ref="J31" r:id="rId11" display="https://probullstats.com/loggers/matchup.php?bull=56236&amp;guy=Macaulie+Leather" xr:uid="{2021287A-E488-FD4C-B27D-94448D0F15C7}"/>
+    <hyperlink ref="J30" r:id="rId12" display="https://probullstats.com/loggers/matchup.php?bull=51896&amp;guy=Eric+Novoa" xr:uid="{95300F1E-1D61-B745-8FB1-31564488E65C}"/>
+    <hyperlink ref="J29" r:id="rId13" display="https://probullstats.com/loggers/matchup.php?bull=52820&amp;guy=Paulo+Eduardo+Rossetto" xr:uid="{0CEAA190-6ED4-7446-8DB9-0E54B259D446}"/>
+    <hyperlink ref="J28" r:id="rId14" display="https://probullstats.com/loggers/matchup.php?bull=50989&amp;guy=Lucas+Divino" xr:uid="{68EFE952-E1A2-2A43-A2D3-BF22A8D7B3E9}"/>
+    <hyperlink ref="J27" r:id="rId15" display="https://probullstats.com/loggers/matchup.php?bull=54227&amp;guy=Claudio+Montanha+Jr." xr:uid="{3D5353E0-0288-DF4A-9DAE-4F807BED1D54}"/>
+    <hyperlink ref="J26" r:id="rId16" display="https://probullstats.com/loggers/matchup.php?bull=54171&amp;guy=Koltin+Hevalow" xr:uid="{9412B2D9-0C75-C745-978E-773B146B6A20}"/>
+    <hyperlink ref="J25" r:id="rId17" display="https://probullstats.com/loggers/matchup.php?bull=51690&amp;guy=Hudson+Bolton" xr:uid="{B6C892CC-6302-014B-A6F4-C3E51780D547}"/>
+    <hyperlink ref="J24" r:id="rId18" display="https://probullstats.com/loggers/matchup.php?bull=53018&amp;guy=Keyshawn+Whitehorse" xr:uid="{1B7B6F25-EA93-3547-A6A1-883AFE3B0758}"/>
+    <hyperlink ref="J23" r:id="rId19" display="https://probullstats.com/loggers/matchup.php?bull=47941&amp;guy=Brady+Fielder" xr:uid="{F830A1E9-FAD6-9B44-9BDC-71504F789CA3}"/>
+    <hyperlink ref="J22" r:id="rId20" display="https://probullstats.com/loggers/matchup.php?bull=53535&amp;guy=John+Crimber" xr:uid="{33956328-C1EF-D149-9DFA-586EB9743B84}"/>
+    <hyperlink ref="J21" r:id="rId21" display="https://probullstats.com/loggers/matchup.php?bull=49727&amp;guy=Alex+Junior+da+Silva" xr:uid="{FE35623D-353B-0942-AAFF-E0848495E061}"/>
+    <hyperlink ref="J20" r:id="rId22" display="https://probullstats.com/loggers/matchup.php?bull=56540&amp;guy=Luciano+De+Castro" xr:uid="{75E344EB-84EF-E243-BC8E-0F69A94B6B09}"/>
+    <hyperlink ref="J19" r:id="rId23" display="https://probullstats.com/loggers/matchup.php?bull=44656&amp;guy=Mauricio+Gulla+Moreira" xr:uid="{C6F7534C-CF8F-014E-A078-46EDB48E4C40}"/>
+    <hyperlink ref="J18" r:id="rId24" display="https://probullstats.com/loggers/matchup.php?bull=50380&amp;guy=Andy+Guzman" xr:uid="{021B2B21-CA7E-8D47-8345-68AEA1745A23}"/>
+    <hyperlink ref="J17" r:id="rId25" display="https://probullstats.com/loggers/matchup.php?bull=53892&amp;guy=Joao+Ricardo+Vieira" xr:uid="{56F7B948-B1A1-0C48-B431-53B30A3D80A9}"/>
+    <hyperlink ref="J16" r:id="rId26" display="https://probullstats.com/loggers/matchup.php?bull=53319&amp;guy=Thiago+Salgado" xr:uid="{0024AC40-1D64-BC45-BE9C-E6AE555C4C55}"/>
+    <hyperlink ref="J15" r:id="rId27" display="https://probullstats.com/loggers/matchup.php?bull=48315&amp;guy=Daylon+Swearingen" xr:uid="{C7028F27-5A31-EB46-928F-52A417BEA75F}"/>
+    <hyperlink ref="J14" r:id="rId28" display="https://probullstats.com/loggers/matchup.php?bull=54209&amp;guy=Andrew+Alvidrez" xr:uid="{5C697E8D-70AD-F046-AB04-46B464409C3E}"/>
+    <hyperlink ref="J13" r:id="rId29" display="https://probullstats.com/loggers/matchup.php?bull=51949&amp;guy=Jess+Lockwood" xr:uid="{A8987CAE-A15F-4F4C-8921-F7BBB52EF782}"/>
+    <hyperlink ref="J12" r:id="rId30" display="https://probullstats.com/loggers/matchup.php?bull=56577&amp;guy=Daniel+Keeping" xr:uid="{F416108D-A154-9D43-A6ED-1D1060E32985}"/>
+    <hyperlink ref="J11" r:id="rId31" display="https://probullstats.com/loggers/matchup.php?bull=53617&amp;guy=Bob+Mitchell" xr:uid="{93B7C777-B99A-8043-9473-B9BA8A4AF91D}"/>
+    <hyperlink ref="J10" r:id="rId32" display="https://probullstats.com/loggers/matchup.php?bull=55454&amp;guy=Romario+Leite" xr:uid="{1D408E4F-3CA9-514F-89EF-F1CDD9720C41}"/>
+    <hyperlink ref="J9" r:id="rId33" display="https://probullstats.com/loggers/matchup.php?bull=56214&amp;guy=Alex+Cerqueira" xr:uid="{C8A17F1D-296F-E745-9931-F763D38E0160}"/>
+    <hyperlink ref="J8" r:id="rId34" display="https://probullstats.com/loggers/matchup.php?bull=52839&amp;guy=Alan+de+Souza" xr:uid="{92AEEB17-6DB6-E840-B049-1DC988B9269E}"/>
+    <hyperlink ref="J7" r:id="rId35" display="https://probullstats.com/loggers/matchup.php?bull=56035&amp;guy=Cassio+Dias" xr:uid="{CBE38BD9-0AED-8B48-AE5C-A82D5055703F}"/>
+    <hyperlink ref="J6" r:id="rId36" display="https://probullstats.com/loggers/matchup.php?bull=45633&amp;guy=Marco+Rizzo" xr:uid="{E3412961-8175-8742-B289-193D41E6BF56}"/>
+    <hyperlink ref="J5" r:id="rId37" display="https://probullstats.com/loggers/matchup.php?bull=53773&amp;guy=Bruno+Carvalho" xr:uid="{4833B6B6-D785-CD4D-AD7C-80D2611062CB}"/>
+    <hyperlink ref="J4" r:id="rId38" display="https://probullstats.com/loggers/matchup.php?bull=52929&amp;guy=Kase+Hitt" xr:uid="{7AC8DC2D-E077-B34C-A679-937E544383EF}"/>
+    <hyperlink ref="J3" r:id="rId39" display="https://probullstats.com/loggers/matchup.php?bull=47126&amp;guy=Manoelito+de+Souza+Junior" xr:uid="{2DA167E7-8DE1-2141-B5ED-4F0001AD28D1}"/>
+    <hyperlink ref="J2" r:id="rId40" display="https://probullstats.com/loggers/matchup.php?bull=51996&amp;guy=Eduardo+Aparecido" xr:uid="{E556DB4A-323A-8448-8888-A75F07F470C8}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B688787-F410-204A-8FD8-EC4B8315D133}">
   <dimension ref="A1:T44"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -1632,7 +5896,7 @@
         <v>41.7</v>
       </c>
       <c r="Q4" s="10">
-        <f t="shared" ref="Q3:Q44" ca="1" si="0">IF(OR(P4="",R4=""),0,R4-P4)</f>
+        <f t="shared" ref="Q4:Q44" ca="1" si="0">IF(OR(P4="",R4=""),0,R4-P4)</f>
         <v>45.4</v>
       </c>
       <c r="R4" s="11">
@@ -1859,7 +6123,7 @@
         <v>0</v>
       </c>
       <c r="R8" s="11">
-        <f t="shared" ref="R8:R44" si="1">P8+Q8</f>
+        <f t="shared" ref="R8:R9" si="1">P8+Q8</f>
         <v>44.15</v>
       </c>
       <c r="T8" t="s">
@@ -2900,15 +7164,17 @@
       <c r="O26" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="P26" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q26" s="10">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="R26" s="11">
-        <v>0</v>
+      <c r="P26" s="9" t="s">
+        <v>274</v>
+      </c>
+      <c r="Q26" s="10" t="s">
+        <v>274</v>
+      </c>
+      <c r="R26" s="11" t="s">
+        <v>274</v>
+      </c>
+      <c r="S26" t="s">
+        <v>277</v>
       </c>
       <c r="T26" t="s">
         <v>19</v>
@@ -2958,15 +7224,18 @@
       <c r="O27" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="P27" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q27" s="10">
+      <c r="P27" s="9" t="s">
+        <v>279</v>
+      </c>
+      <c r="Q27" s="10" t="e">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
       <c r="R27" s="11">
-        <v>0</v>
+        <v>86.9</v>
+      </c>
+      <c r="S27" t="s">
+        <v>278</v>
       </c>
       <c r="T27" t="s">
         <v>45</v>
@@ -3017,11 +7286,11 @@
         <v>180</v>
       </c>
       <c r="P28" s="9">
-        <v>0</v>
+        <v>41.15</v>
       </c>
       <c r="Q28" s="10">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-41.15</v>
       </c>
       <c r="R28" s="11">
         <v>0</v>
@@ -3075,11 +7344,11 @@
         <v>187</v>
       </c>
       <c r="P29" s="9">
-        <v>0</v>
+        <v>42.2</v>
       </c>
       <c r="Q29" s="10">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-42.2</v>
       </c>
       <c r="R29" s="11">
         <v>0</v>
@@ -4007,5 +8276,6 @@
     <hyperlink ref="J44" r:id="rId43" display="https://probullstats.com/loggers/matchup.php?bull=54035&amp;guy=Dalton+Kasel" xr:uid="{0EDD66C9-F792-EC45-A24C-1F3BD6F40636}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
--- a/data/pbr_matchups_full.xlsx
+++ b/data/pbr_matchups_full.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cameronyoung/Desktop/rankratings:/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DDC9C8D-609E-CF47-B306-812F3E6188B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14D2B026-40B7-D743-9B27-E3C3F34D3444}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="740" windowWidth="30240" windowHeight="18900" xr2:uid="{63502F5A-9950-074D-B0A2-89EF4471630B}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1041" uniqueCount="505">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1050" uniqueCount="506">
   <si>
     <t>Bull Power</t>
   </si>
@@ -3011,12 +3011,15 @@
   <si>
     <t>&lt;h2&gt;Rider&lt;/h2&gt;&lt;p&gt;&lt;strong&gt;Career:&amp;nbsp;&lt;/strong&gt;Career: 127 for 330 - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;38.48%&lt;/em&gt;&lt;/span&gt; - Rider Rating: *.269&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Season:&amp;nbsp;&lt;/strong&gt;Rank&amp;nbsp;&lt;span style="color: #ff0000;"&gt;12&lt;/span&gt; (27 for 69 - &lt;em&gt;39.1%&lt;/em&gt;)&lt;em&gt;&lt;br /&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Points:&amp;nbsp;&lt;/strong&gt;400.00 pts &lt;span style="color: #ff0000;"&gt;&lt;em&gt;(-492.5)&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Earnings:&amp;nbsp;&lt;/strong&gt;&lt;span style="color: #008000;"&gt;&lt;em&gt;$126,110.26&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Potential&lt;/strong&gt;:&amp;nbsp;82.77 to 88.77 points&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;&lt;span style="text-decoration: underline;"&gt;&lt;strong&gt;Bull&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;ALL:&lt;/strong&gt; 9 outs 0 rides - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;100%&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;em&gt;&lt;span style="color: #ff0000;"&gt;*No Previous Matchups&lt;/span&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;</t>
   </si>
+  <si>
+    <t>rr</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -3097,6 +3100,13 @@
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Verdana"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -3119,7 +3129,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
@@ -3138,6 +3148,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -3593,12 +3604,18 @@
       <c r="N2" t="s">
         <v>445</v>
       </c>
-      <c r="O2" s="1" t="s">
+      <c r="O2" s="14" t="s">
         <v>141</v>
       </c>
-      <c r="P2" s="9"/>
-      <c r="Q2" s="10"/>
-      <c r="R2" s="11"/>
+      <c r="P2" s="9" t="s">
+        <v>505</v>
+      </c>
+      <c r="Q2" s="10" t="s">
+        <v>505</v>
+      </c>
+      <c r="R2" s="11" t="s">
+        <v>505</v>
+      </c>
       <c r="Y2" s="13" t="s">
         <v>405</v>
       </c>
@@ -3644,7 +3661,7 @@
       <c r="N3" t="s">
         <v>447</v>
       </c>
-      <c r="O3" s="1" t="s">
+      <c r="O3" s="14" t="s">
         <v>72</v>
       </c>
       <c r="P3" s="9"/>
@@ -3697,7 +3714,7 @@
       <c r="N4" t="s">
         <v>448</v>
       </c>
-      <c r="O4" s="1" t="s">
+      <c r="O4" s="14" t="s">
         <v>34</v>
       </c>
       <c r="P4" s="9"/>
@@ -3750,7 +3767,7 @@
       <c r="N5" t="s">
         <v>450</v>
       </c>
-      <c r="O5" s="1" t="s">
+      <c r="O5" s="14" t="s">
         <v>120</v>
       </c>
       <c r="P5" s="9"/>
@@ -3803,7 +3820,7 @@
       <c r="N6" t="s">
         <v>452</v>
       </c>
-      <c r="O6" s="1" t="s">
+      <c r="O6" s="14" t="s">
         <v>131</v>
       </c>
       <c r="P6" s="9"/>
@@ -3834,7 +3851,7 @@
         <v>281</v>
       </c>
       <c r="H7" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I7" s="1" t="s">
         <v>386</v>
@@ -3881,7 +3898,7 @@
         <v>281</v>
       </c>
       <c r="H8" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I8" s="1" t="s">
         <v>384</v>
@@ -3904,9 +3921,15 @@
       <c r="O8" s="1" t="s">
         <v>383</v>
       </c>
-      <c r="P8" s="9"/>
-      <c r="Q8" s="10"/>
-      <c r="R8" s="11"/>
+      <c r="P8" s="9" t="s">
+        <v>505</v>
+      </c>
+      <c r="Q8" s="10" t="s">
+        <v>505</v>
+      </c>
+      <c r="R8" s="11" t="s">
+        <v>505</v>
+      </c>
       <c r="Y8" s="13" t="s">
         <v>411</v>
       </c>
@@ -3934,7 +3957,7 @@
         <v>281</v>
       </c>
       <c r="H9" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I9" s="1" t="s">
         <v>381</v>
@@ -3979,7 +4002,7 @@
         <v>281</v>
       </c>
       <c r="H10" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I10" s="1" t="s">
         <v>380</v>
@@ -4002,9 +4025,15 @@
       <c r="O10" s="1" t="s">
         <v>379</v>
       </c>
-      <c r="P10" s="9"/>
-      <c r="Q10" s="10"/>
-      <c r="R10" s="11"/>
+      <c r="P10" s="9" t="s">
+        <v>505</v>
+      </c>
+      <c r="Q10" s="10" t="s">
+        <v>505</v>
+      </c>
+      <c r="R10" s="11" t="s">
+        <v>505</v>
+      </c>
       <c r="Y10" s="13" t="s">
         <v>413</v>
       </c>
@@ -4030,7 +4059,7 @@
         <v>281</v>
       </c>
       <c r="H11" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I11" s="1" t="s">
         <v>376</v>
@@ -4083,7 +4112,7 @@
         <v>281</v>
       </c>
       <c r="H12" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I12" s="1" t="s">
         <v>373</v>
@@ -4128,7 +4157,7 @@
         <v>281</v>
       </c>
       <c r="H13" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I13" s="1" t="s">
         <v>371</v>
@@ -4148,7 +4177,7 @@
       <c r="N13" t="s">
         <v>463</v>
       </c>
-      <c r="O13" s="1" t="s">
+      <c r="O13" s="14" t="s">
         <v>24</v>
       </c>
       <c r="P13" s="9"/>
@@ -4181,7 +4210,7 @@
         <v>281</v>
       </c>
       <c r="H14" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I14" s="1" t="s">
         <v>368</v>
@@ -4201,7 +4230,7 @@
       <c r="N14" t="s">
         <v>464</v>
       </c>
-      <c r="O14" s="1" t="s">
+      <c r="O14" s="14" t="s">
         <v>367</v>
       </c>
       <c r="P14" s="9"/>
@@ -4232,7 +4261,7 @@
         <v>281</v>
       </c>
       <c r="H15" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I15" s="1" t="s">
         <v>364</v>
@@ -4252,7 +4281,7 @@
       <c r="N15" t="s">
         <v>466</v>
       </c>
-      <c r="O15" s="1" t="s">
+      <c r="O15" s="14" t="s">
         <v>363</v>
       </c>
       <c r="P15" s="9"/>
@@ -4283,7 +4312,7 @@
         <v>281</v>
       </c>
       <c r="H16" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I16" s="1" t="s">
         <v>359</v>
@@ -4303,7 +4332,7 @@
       <c r="N16" t="s">
         <v>468</v>
       </c>
-      <c r="O16" s="1" t="s">
+      <c r="O16" s="14" t="s">
         <v>358</v>
       </c>
       <c r="P16" s="9"/>
@@ -4336,7 +4365,7 @@
         <v>281</v>
       </c>
       <c r="H17" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I17" s="1" t="s">
         <v>355</v>
@@ -4389,7 +4418,7 @@
         <v>281</v>
       </c>
       <c r="H18" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I18" s="1" t="s">
         <v>351</v>
@@ -4442,7 +4471,7 @@
         <v>281</v>
       </c>
       <c r="H19" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I19" s="1" t="s">
         <v>348</v>
@@ -4493,7 +4522,7 @@
         <v>281</v>
       </c>
       <c r="H20" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I20" s="1" t="s">
         <v>345</v>
@@ -4540,7 +4569,7 @@
         <v>281</v>
       </c>
       <c r="H21" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I21" s="1" t="s">
         <v>343</v>
@@ -4593,7 +4622,7 @@
         <v>281</v>
       </c>
       <c r="H22" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I22" s="1" t="s">
         <v>339</v>
@@ -4613,7 +4642,7 @@
       <c r="N22" t="s">
         <v>478</v>
       </c>
-      <c r="O22" s="1" t="s">
+      <c r="O22" s="14" t="s">
         <v>136</v>
       </c>
       <c r="P22" s="9"/>
@@ -4646,7 +4675,7 @@
         <v>281</v>
       </c>
       <c r="H23" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I23" s="1" t="s">
         <v>337</v>
@@ -4666,7 +4695,7 @@
       <c r="N23" t="s">
         <v>479</v>
       </c>
-      <c r="O23" s="1" t="s">
+      <c r="O23" s="14" t="s">
         <v>146</v>
       </c>
       <c r="P23" s="9"/>
@@ -4699,7 +4728,7 @@
         <v>281</v>
       </c>
       <c r="H24" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I24" s="1" t="s">
         <v>335</v>
@@ -4719,7 +4748,7 @@
       <c r="N24" t="s">
         <v>480</v>
       </c>
-      <c r="O24" s="1" t="s">
+      <c r="O24" s="14" t="s">
         <v>66</v>
       </c>
       <c r="P24" s="9"/>
@@ -4750,7 +4779,7 @@
         <v>281</v>
       </c>
       <c r="H25" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I25" s="1" t="s">
         <v>331</v>
@@ -4770,7 +4799,7 @@
       <c r="N25" t="s">
         <v>482</v>
       </c>
-      <c r="O25" s="1" t="s">
+      <c r="O25" s="14" t="s">
         <v>108</v>
       </c>
       <c r="P25" s="9"/>
@@ -4803,7 +4832,7 @@
         <v>281</v>
       </c>
       <c r="H26" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I26" s="1" t="s">
         <v>328</v>
@@ -4823,7 +4852,7 @@
       <c r="N26" t="s">
         <v>484</v>
       </c>
-      <c r="O26" s="1" t="s">
+      <c r="O26" s="14" t="s">
         <v>250</v>
       </c>
       <c r="P26" s="9"/>
@@ -4854,7 +4883,7 @@
         <v>281</v>
       </c>
       <c r="H27" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I27" s="1" t="s">
         <v>325</v>
@@ -4874,7 +4903,7 @@
       <c r="N27" t="s">
         <v>486</v>
       </c>
-      <c r="O27" s="1" t="s">
+      <c r="O27" s="14" t="s">
         <v>151</v>
       </c>
       <c r="P27" s="9"/>
@@ -4907,7 +4936,7 @@
         <v>281</v>
       </c>
       <c r="H28" s="1">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I28" s="1" t="s">
         <v>322</v>
@@ -4958,7 +4987,7 @@
         <v>281</v>
       </c>
       <c r="H29" s="1">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I29" s="1" t="s">
         <v>319</v>
@@ -5011,7 +5040,7 @@
         <v>281</v>
       </c>
       <c r="H30" s="1">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I30" s="1" t="s">
         <v>316</v>
@@ -5064,7 +5093,7 @@
         <v>281</v>
       </c>
       <c r="H31" s="1">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I31" s="1" t="s">
         <v>311</v>
@@ -5109,7 +5138,7 @@
         <v>281</v>
       </c>
       <c r="H32" s="1">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I32" s="1" t="s">
         <v>308</v>
@@ -5123,7 +5152,7 @@
       <c r="N32" t="s">
         <v>493</v>
       </c>
-      <c r="O32" s="1" t="s">
+      <c r="O32" s="14" t="s">
         <v>255</v>
       </c>
       <c r="P32" s="9"/>
@@ -5154,7 +5183,7 @@
         <v>281</v>
       </c>
       <c r="H33" s="1">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I33" s="1" t="s">
         <v>306</v>
@@ -5168,7 +5197,7 @@
       <c r="N33" t="s">
         <v>494</v>
       </c>
-      <c r="O33" s="1" t="s">
+      <c r="O33" s="14" t="s">
         <v>305</v>
       </c>
       <c r="P33" s="9"/>
@@ -5199,7 +5228,7 @@
         <v>281</v>
       </c>
       <c r="H34" s="1">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I34" s="1" t="s">
         <v>302</v>
@@ -5244,7 +5273,7 @@
         <v>281</v>
       </c>
       <c r="H35" s="1">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I35" s="1" t="s">
         <v>300</v>
@@ -5295,7 +5324,7 @@
         <v>281</v>
       </c>
       <c r="H36" s="1">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I36" s="1" t="s">
         <v>297</v>
@@ -5346,7 +5375,7 @@
         <v>281</v>
       </c>
       <c r="H37" s="1">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I37" s="1" t="s">
         <v>103</v>
@@ -5393,7 +5422,7 @@
         <v>281</v>
       </c>
       <c r="H38" s="1">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I38" s="1" t="s">
         <v>292</v>
@@ -5413,7 +5442,7 @@
       <c r="N38" t="s">
         <v>501</v>
       </c>
-      <c r="O38" s="1" t="s">
+      <c r="O38" s="14" t="s">
         <v>291</v>
       </c>
       <c r="P38" s="9"/>
@@ -5446,7 +5475,7 @@
         <v>281</v>
       </c>
       <c r="H39" s="1">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I39" s="1" t="s">
         <v>288</v>
@@ -5466,7 +5495,7 @@
       <c r="N39" t="s">
         <v>502</v>
       </c>
-      <c r="O39" s="1" t="s">
+      <c r="O39" s="14" t="s">
         <v>157</v>
       </c>
       <c r="P39" s="9"/>
@@ -5499,7 +5528,7 @@
         <v>281</v>
       </c>
       <c r="H40" s="1">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I40" s="1" t="s">
         <v>284</v>
@@ -5513,7 +5542,7 @@
       <c r="N40" t="s">
         <v>503</v>
       </c>
-      <c r="O40" s="1" t="s">
+      <c r="O40" s="14" t="s">
         <v>222</v>
       </c>
       <c r="P40" s="9"/>
@@ -5544,7 +5573,7 @@
         <v>281</v>
       </c>
       <c r="H41" s="1">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I41" s="1" t="s">
         <v>282</v>
@@ -5564,7 +5593,7 @@
       <c r="N41" t="s">
         <v>504</v>
       </c>
-      <c r="O41" s="1" t="s">
+      <c r="O41" s="14" t="s">
         <v>41</v>
       </c>
       <c r="P41" s="9"/>

--- a/data/pbr_matchups_full.xlsx
+++ b/data/pbr_matchups_full.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cameronyoung/Desktop/rankratings:/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14D2B026-40B7-D743-9B27-E3C3F34D3444}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E5D81FD-7DA2-7241-88AF-00E83B9D8C86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="740" windowWidth="30240" windowHeight="18900" xr2:uid="{63502F5A-9950-074D-B0A2-89EF4471630B}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1050" uniqueCount="506">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1053" uniqueCount="506">
   <si>
     <t>Bull Power</t>
   </si>
@@ -3664,9 +3664,15 @@
       <c r="O3" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="P3" s="9"/>
-      <c r="Q3" s="10"/>
-      <c r="R3" s="11"/>
+      <c r="P3" s="9">
+        <v>41</v>
+      </c>
+      <c r="Q3" s="10">
+        <v>0</v>
+      </c>
+      <c r="R3" s="11">
+        <v>0</v>
+      </c>
       <c r="Y3" s="13" t="s">
         <v>406</v>
       </c>
@@ -3717,9 +3723,15 @@
       <c r="O4" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="P4" s="9"/>
-      <c r="Q4" s="10"/>
-      <c r="R4" s="11"/>
+      <c r="P4" s="9">
+        <v>39</v>
+      </c>
+      <c r="Q4" s="10">
+        <v>38</v>
+      </c>
+      <c r="R4" s="11">
+        <v>77</v>
+      </c>
       <c r="Y4" s="13" t="s">
         <v>407</v>
       </c>
@@ -3770,9 +3782,15 @@
       <c r="O5" s="14" t="s">
         <v>120</v>
       </c>
-      <c r="P5" s="9"/>
-      <c r="Q5" s="10"/>
-      <c r="R5" s="11"/>
+      <c r="P5" s="9">
+        <v>45</v>
+      </c>
+      <c r="Q5" s="10">
+        <v>45</v>
+      </c>
+      <c r="R5" s="11">
+        <v>90</v>
+      </c>
       <c r="Y5" s="13" t="s">
         <v>408</v>
       </c>
@@ -3823,9 +3841,15 @@
       <c r="O6" s="14" t="s">
         <v>131</v>
       </c>
-      <c r="P6" s="9"/>
-      <c r="Q6" s="10"/>
-      <c r="R6" s="11"/>
+      <c r="P6" s="9" t="s">
+        <v>505</v>
+      </c>
+      <c r="Q6" s="10" t="s">
+        <v>505</v>
+      </c>
+      <c r="R6" s="11" t="s">
+        <v>505</v>
+      </c>
       <c r="Y6" s="13" t="s">
         <v>409</v>
       </c>

--- a/data/pbr_matchups_full.xlsx
+++ b/data/pbr_matchups_full.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cameronyoung/Desktop/rankratings:/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E5D81FD-7DA2-7241-88AF-00E83B9D8C86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{952C0ACE-CF7D-FA40-9C38-34F52E101DFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="740" windowWidth="30240" windowHeight="18900" xr2:uid="{63502F5A-9950-074D-B0A2-89EF4471630B}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1053" uniqueCount="506">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1057" uniqueCount="506">
   <si>
     <t>Bull Power</t>
   </si>
@@ -3484,7 +3484,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01ACAA71-EF8B-E143-BCEC-D101B7DB858C}">
-  <dimension ref="A1:Y53"/>
+  <dimension ref="A1:Y55"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.6640625" bestFit="1" customWidth="1"/>
@@ -3855,125 +3855,73 @@
       </c>
     </row>
     <row r="7" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="1">
-        <v>6</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>385</v>
-      </c>
+      <c r="A7" s="1"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
       <c r="D7" s="1" t="s">
-        <v>40</v>
+        <v>274</v>
       </c>
       <c r="E7" s="1"/>
-      <c r="F7" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>281</v>
-      </c>
-      <c r="H7" s="1">
-        <v>2</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>386</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="K7" t="s">
+      <c r="F7" s="1"/>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1"/>
+      <c r="I7" s="1"/>
+      <c r="J7" s="2"/>
+      <c r="O7" s="14" t="s">
+        <v>141</v>
+      </c>
+      <c r="P7" s="9">
+        <v>45</v>
+      </c>
+      <c r="Q7" s="10">
+        <v>45</v>
+      </c>
+      <c r="R7" s="11">
+        <v>45</v>
+      </c>
+      <c r="Y7" s="13"/>
+    </row>
+    <row r="8" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="1"/>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1"/>
+      <c r="J8" s="2"/>
+      <c r="O8" s="14" t="s">
+        <v>131</v>
+      </c>
+      <c r="P8" s="9">
         <v>43</v>
       </c>
-      <c r="N7" t="s">
-        <v>453</v>
-      </c>
-      <c r="O7" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="P7" s="9"/>
-      <c r="Q7" s="10"/>
-      <c r="R7" s="11"/>
-      <c r="Y7" s="13" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="8" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="1">
-        <v>7</v>
-      </c>
-      <c r="B8" s="1">
-        <v>71</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>382</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E8" s="1">
-        <v>10229185</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>281</v>
-      </c>
-      <c r="H8" s="1">
-        <v>2</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="K8" t="s">
-        <v>43</v>
-      </c>
-      <c r="L8" t="s">
-        <v>454</v>
-      </c>
-      <c r="M8" t="s">
-        <v>29</v>
-      </c>
-      <c r="N8" t="s">
-        <v>455</v>
-      </c>
-      <c r="O8" s="1" t="s">
-        <v>383</v>
-      </c>
-      <c r="P8" s="9" t="s">
-        <v>505</v>
-      </c>
-      <c r="Q8" s="10" t="s">
-        <v>505</v>
-      </c>
-      <c r="R8" s="11" t="s">
-        <v>505</v>
-      </c>
-      <c r="Y8" s="13" t="s">
-        <v>411</v>
-      </c>
+      <c r="Q8" s="10">
+        <v>0</v>
+      </c>
+      <c r="R8" s="11">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="13"/>
     </row>
     <row r="9" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C9" s="5" t="s">
-        <v>161</v>
+      <c r="C9" s="1" t="s">
+        <v>385</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="E9" s="1">
-        <v>10250898</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="E9" s="1"/>
       <c r="F9" s="1" t="s">
         <v>22</v>
       </c>
@@ -3984,43 +3932,45 @@
         <v>2</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>26</v>
       </c>
       <c r="K9" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="N9" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>90</v>
+        <v>260</v>
       </c>
       <c r="P9" s="9"/>
       <c r="Q9" s="10"/>
       <c r="R9" s="11"/>
       <c r="Y9" s="13" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
     </row>
     <row r="10" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B10" s="1">
-        <v>52.32</v>
+        <v>71</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>378</v>
-      </c>
-      <c r="E10" s="1"/>
+        <v>21</v>
+      </c>
+      <c r="E10" s="1">
+        <v>10229185</v>
+      </c>
       <c r="F10" s="1" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>281</v>
@@ -4029,25 +3979,25 @@
         <v>2</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>26</v>
       </c>
       <c r="K10" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="L10" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="M10" t="s">
         <v>29</v>
       </c>
       <c r="N10" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="O10" s="1" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="P10" s="9" t="s">
         <v>505</v>
@@ -4059,25 +4009,27 @@
         <v>505</v>
       </c>
       <c r="Y10" s="13" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
     </row>
     <row r="11" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
-        <v>10</v>
-      </c>
-      <c r="B11" s="1">
-        <v>59.59</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>374</v>
+        <v>8</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>161</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>375</v>
-      </c>
-      <c r="E11" s="1"/>
+        <v>33</v>
+      </c>
+      <c r="E11" s="1">
+        <v>10250898</v>
+      </c>
       <c r="F11" s="1" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="G11" s="1" t="s">
         <v>281</v>
@@ -4086,7 +4038,7 @@
         <v>2</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>26</v>
@@ -4094,41 +4046,33 @@
       <c r="K11" t="s">
         <v>27</v>
       </c>
-      <c r="L11" t="s">
-        <v>459</v>
-      </c>
-      <c r="M11" t="s">
-        <v>29</v>
-      </c>
       <c r="N11" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="P11" s="9"/>
       <c r="Q11" s="10"/>
       <c r="R11" s="11"/>
       <c r="Y11" s="13" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
     </row>
     <row r="12" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
-        <v>11</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>51</v>
+        <v>9</v>
+      </c>
+      <c r="B12" s="1">
+        <v>52.32</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>377</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>372</v>
-      </c>
-      <c r="E12" s="1">
-        <v>10268379</v>
-      </c>
+        <v>378</v>
+      </c>
+      <c r="E12" s="1"/>
       <c r="F12" s="1" t="s">
         <v>53</v>
       </c>
@@ -4139,7 +4083,7 @@
         <v>2</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>26</v>
@@ -4147,44 +4091,56 @@
       <c r="K12" t="s">
         <v>27</v>
       </c>
+      <c r="L12" t="s">
+        <v>457</v>
+      </c>
+      <c r="M12" t="s">
+        <v>29</v>
+      </c>
       <c r="N12" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="O12" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="P12" s="9"/>
-      <c r="Q12" s="10"/>
-      <c r="R12" s="11"/>
+        <v>379</v>
+      </c>
+      <c r="P12" s="9" t="s">
+        <v>505</v>
+      </c>
+      <c r="Q12" s="10" t="s">
+        <v>505</v>
+      </c>
+      <c r="R12" s="11" t="s">
+        <v>505</v>
+      </c>
       <c r="Y12" s="13" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="13" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B13" s="1">
-        <v>67.209999999999994</v>
+        <v>59.59</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="E13" s="1"/>
       <c r="F13" s="1" t="s">
-        <v>342</v>
+        <v>53</v>
       </c>
       <c r="G13" s="1" t="s">
         <v>281</v>
       </c>
       <c r="H13" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>26</v>
@@ -4193,93 +4149,87 @@
         <v>27</v>
       </c>
       <c r="L13" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="M13" t="s">
-        <v>99</v>
+        <v>29</v>
       </c>
       <c r="N13" t="s">
-        <v>463</v>
-      </c>
-      <c r="O13" s="14" t="s">
-        <v>24</v>
+        <v>460</v>
+      </c>
+      <c r="O13" s="1" t="s">
+        <v>60</v>
       </c>
       <c r="P13" s="9"/>
       <c r="Q13" s="10"/>
       <c r="R13" s="11"/>
       <c r="Y13" s="13" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
     </row>
     <row r="14" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
-        <v>13</v>
-      </c>
-      <c r="B14" s="1">
-        <v>75.92</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>365</v>
+        <v>11</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>51</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>366</v>
+        <v>372</v>
       </c>
       <c r="E14" s="1">
-        <v>10272036</v>
+        <v>10268379</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>287</v>
+        <v>53</v>
       </c>
       <c r="G14" s="1" t="s">
         <v>281</v>
       </c>
       <c r="H14" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>26</v>
       </c>
       <c r="K14" t="s">
-        <v>43</v>
-      </c>
-      <c r="L14" t="s">
-        <v>446</v>
-      </c>
-      <c r="M14" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="N14" t="s">
-        <v>464</v>
-      </c>
-      <c r="O14" s="14" t="s">
-        <v>367</v>
+        <v>461</v>
+      </c>
+      <c r="O14" s="1" t="s">
+        <v>163</v>
       </c>
       <c r="P14" s="9"/>
       <c r="Q14" s="10"/>
       <c r="R14" s="11"/>
       <c r="Y14" s="13" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
     </row>
     <row r="15" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B15" s="1">
-        <v>78.86</v>
+        <v>67.209999999999994</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>360</v>
+        <v>369</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>361</v>
+        <v>370</v>
       </c>
       <c r="E15" s="1"/>
       <c r="F15" s="1" t="s">
-        <v>362</v>
+        <v>342</v>
       </c>
       <c r="G15" s="1" t="s">
         <v>281</v>
@@ -4288,7 +4238,7 @@
         <v>3</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>364</v>
+        <v>371</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>26</v>
@@ -4297,40 +4247,42 @@
         <v>27</v>
       </c>
       <c r="L15" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="M15" t="s">
-        <v>29</v>
+        <v>99</v>
       </c>
       <c r="N15" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="O15" s="14" t="s">
-        <v>363</v>
+        <v>24</v>
       </c>
       <c r="P15" s="9"/>
       <c r="Q15" s="10"/>
       <c r="R15" s="11"/>
       <c r="Y15" s="13" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
     </row>
     <row r="16" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B16" s="1">
-        <v>57.72</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>356</v>
+        <v>75.92</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>365</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>357</v>
-      </c>
-      <c r="E16" s="1"/>
+        <v>366</v>
+      </c>
+      <c r="E16" s="1">
+        <v>10272036</v>
+      </c>
       <c r="F16" s="1" t="s">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="G16" s="1" t="s">
         <v>281</v>
@@ -4339,60 +4291,58 @@
         <v>3</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>359</v>
+        <v>368</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>26</v>
       </c>
       <c r="K16" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="L16" t="s">
-        <v>467</v>
+        <v>446</v>
       </c>
       <c r="M16" t="s">
-        <v>99</v>
+        <v>36</v>
       </c>
       <c r="N16" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
       <c r="O16" s="14" t="s">
-        <v>358</v>
+        <v>367</v>
       </c>
       <c r="P16" s="9"/>
       <c r="Q16" s="10"/>
       <c r="R16" s="11"/>
       <c r="Y16" s="13" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
     </row>
     <row r="17" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B17" s="1">
-        <v>65.19</v>
+        <v>78.86</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>352</v>
+        <v>360</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>353</v>
-      </c>
-      <c r="E17" s="1">
-        <v>10276006</v>
-      </c>
+        <v>361</v>
+      </c>
+      <c r="E17" s="1"/>
       <c r="F17" s="1" t="s">
-        <v>354</v>
+        <v>362</v>
       </c>
       <c r="G17" s="1" t="s">
         <v>281</v>
       </c>
       <c r="H17" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>355</v>
+        <v>364</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>26</v>
@@ -4401,51 +4351,49 @@
         <v>27</v>
       </c>
       <c r="L17" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="M17" t="s">
-        <v>99</v>
+        <v>29</v>
       </c>
       <c r="N17" t="s">
-        <v>470</v>
-      </c>
-      <c r="O17" s="1" t="s">
-        <v>187</v>
+        <v>466</v>
+      </c>
+      <c r="O17" s="14" t="s">
+        <v>363</v>
       </c>
       <c r="P17" s="9"/>
       <c r="Q17" s="10"/>
       <c r="R17" s="11"/>
       <c r="Y17" s="13" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
     </row>
     <row r="18" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B18" s="1">
-        <v>66.97</v>
+        <v>57.72</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>349</v>
+        <v>356</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>350</v>
-      </c>
-      <c r="E18" s="1">
-        <v>10243159</v>
-      </c>
+        <v>357</v>
+      </c>
+      <c r="E18" s="1"/>
       <c r="F18" s="1" t="s">
-        <v>310</v>
+        <v>294</v>
       </c>
       <c r="G18" s="1" t="s">
         <v>281</v>
       </c>
       <c r="H18" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>351</v>
+        <v>359</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>26</v>
@@ -4454,42 +4402,42 @@
         <v>27</v>
       </c>
       <c r="L18" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="M18" t="s">
-        <v>29</v>
+        <v>99</v>
       </c>
       <c r="N18" t="s">
-        <v>472</v>
-      </c>
-      <c r="O18" s="1" t="s">
-        <v>238</v>
+        <v>468</v>
+      </c>
+      <c r="O18" s="14" t="s">
+        <v>358</v>
       </c>
       <c r="P18" s="9"/>
       <c r="Q18" s="10"/>
       <c r="R18" s="11"/>
       <c r="Y18" s="13" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
     </row>
     <row r="19" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B19" s="1">
-        <v>75.709999999999994</v>
+        <v>65.19</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>347</v>
+        <v>353</v>
       </c>
       <c r="E19" s="1">
-        <v>10205390</v>
+        <v>10276006</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>310</v>
+        <v>354</v>
       </c>
       <c r="G19" s="1" t="s">
         <v>281</v>
@@ -4498,7 +4446,7 @@
         <v>4</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>348</v>
+        <v>355</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>26</v>
@@ -4507,40 +4455,42 @@
         <v>27</v>
       </c>
       <c r="L19" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="M19" t="s">
         <v>99</v>
       </c>
       <c r="N19" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="O19" s="1" t="s">
-        <v>54</v>
+        <v>187</v>
       </c>
       <c r="P19" s="9"/>
       <c r="Q19" s="10"/>
       <c r="R19" s="11"/>
       <c r="Y19" s="13" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
     </row>
     <row r="20" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="1">
-        <v>19</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>344</v>
+        <v>17</v>
+      </c>
+      <c r="B20" s="1">
+        <v>66.97</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>349</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="E20" s="1"/>
+        <v>350</v>
+      </c>
+      <c r="E20" s="1">
+        <v>10243159</v>
+      </c>
       <c r="F20" s="1" t="s">
-        <v>53</v>
+        <v>310</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>281</v>
@@ -4549,7 +4499,7 @@
         <v>4</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>26</v>
@@ -4557,37 +4507,43 @@
       <c r="K20" t="s">
         <v>27</v>
       </c>
+      <c r="L20" t="s">
+        <v>471</v>
+      </c>
+      <c r="M20" t="s">
+        <v>29</v>
+      </c>
       <c r="N20" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="O20" s="1" t="s">
-        <v>96</v>
+        <v>238</v>
       </c>
       <c r="P20" s="9"/>
       <c r="Q20" s="10"/>
       <c r="R20" s="11"/>
       <c r="Y20" s="13" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
     </row>
     <row r="21" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B21" s="1">
-        <v>77.819999999999993</v>
+        <v>75.709999999999994</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="E21" s="1">
-        <v>10231548</v>
+        <v>10205390</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>342</v>
+        <v>310</v>
       </c>
       <c r="G21" s="1" t="s">
         <v>281</v>
@@ -4596,60 +4552,58 @@
         <v>4</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>26</v>
       </c>
       <c r="K21" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="L21" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="M21" t="s">
-        <v>29</v>
+        <v>99</v>
       </c>
       <c r="N21" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="O21" s="1" t="s">
-        <v>114</v>
+        <v>54</v>
       </c>
       <c r="P21" s="9"/>
       <c r="Q21" s="10"/>
       <c r="R21" s="11"/>
       <c r="Y21" s="13" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
     </row>
     <row r="22" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="1">
-        <v>21</v>
-      </c>
-      <c r="B22" s="1">
-        <v>73.45</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>105</v>
+        <v>19</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>344</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>338</v>
-      </c>
-      <c r="E22" s="1">
-        <v>10268851</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="E22" s="1"/>
       <c r="F22" s="1" t="s">
-        <v>334</v>
+        <v>53</v>
       </c>
       <c r="G22" s="1" t="s">
         <v>281</v>
       </c>
       <c r="H22" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>26</v>
@@ -4657,52 +4611,46 @@
       <c r="K22" t="s">
         <v>27</v>
       </c>
-      <c r="L22" t="s">
-        <v>465</v>
-      </c>
-      <c r="M22" t="s">
-        <v>29</v>
-      </c>
       <c r="N22" t="s">
-        <v>478</v>
-      </c>
-      <c r="O22" s="14" t="s">
-        <v>136</v>
+        <v>475</v>
+      </c>
+      <c r="O22" s="1" t="s">
+        <v>96</v>
       </c>
       <c r="P22" s="9"/>
       <c r="Q22" s="10"/>
       <c r="R22" s="11"/>
       <c r="Y22" s="13" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
     </row>
     <row r="23" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="1">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B23" s="1">
-        <v>74.900000000000006</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>117</v>
+        <v>77.819999999999993</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>340</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="E23" s="1">
-        <v>10229189</v>
+        <v>10231548</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="G23" s="1" t="s">
         <v>281</v>
       </c>
       <c r="H23" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>26</v>
@@ -4711,39 +4659,39 @@
         <v>43</v>
       </c>
       <c r="L23" t="s">
-        <v>446</v>
+        <v>476</v>
       </c>
       <c r="M23" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="N23" t="s">
-        <v>479</v>
-      </c>
-      <c r="O23" s="14" t="s">
-        <v>146</v>
+        <v>477</v>
+      </c>
+      <c r="O23" s="1" t="s">
+        <v>114</v>
       </c>
       <c r="P23" s="9"/>
       <c r="Q23" s="10"/>
       <c r="R23" s="11"/>
       <c r="Y23" s="13" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
     </row>
     <row r="24" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="1">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B24" s="1">
-        <v>61.01</v>
+        <v>73.45</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>332</v>
+        <v>105</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="E24" s="1">
-        <v>10262490</v>
+        <v>10268851</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>334</v>
@@ -4755,49 +4703,51 @@
         <v>5</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>26</v>
       </c>
       <c r="K24" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="L24" t="s">
-        <v>74</v>
+        <v>465</v>
       </c>
       <c r="M24" t="s">
-        <v>99</v>
+        <v>29</v>
       </c>
       <c r="N24" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="O24" s="14" t="s">
-        <v>66</v>
+        <v>136</v>
       </c>
       <c r="P24" s="9"/>
       <c r="Q24" s="10"/>
       <c r="R24" s="11"/>
       <c r="Y24" s="13" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
     </row>
     <row r="25" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="1">
-        <v>24</v>
-      </c>
-      <c r="B25" s="8">
-        <v>84.69</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>329</v>
+        <v>22</v>
+      </c>
+      <c r="B25" s="1">
+        <v>74.900000000000006</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>117</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>330</v>
-      </c>
-      <c r="E25" s="1"/>
+        <v>336</v>
+      </c>
+      <c r="E25" s="1">
+        <v>10229189</v>
+      </c>
       <c r="F25" s="1" t="s">
-        <v>84</v>
+        <v>334</v>
       </c>
       <c r="G25" s="1" t="s">
         <v>281</v>
@@ -4806,51 +4756,51 @@
         <v>5</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>26</v>
       </c>
       <c r="K25" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="L25" t="s">
-        <v>481</v>
+        <v>446</v>
       </c>
       <c r="M25" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="N25" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="O25" s="14" t="s">
-        <v>108</v>
+        <v>146</v>
       </c>
       <c r="P25" s="9"/>
       <c r="Q25" s="10"/>
       <c r="R25" s="11"/>
       <c r="Y25" s="13" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
     </row>
     <row r="26" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="1">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B26" s="1">
-        <v>42.09</v>
+        <v>61.01</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="E26" s="1">
-        <v>10270857</v>
+        <v>10262490</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>287</v>
+        <v>334</v>
       </c>
       <c r="G26" s="1" t="s">
         <v>281</v>
@@ -4859,45 +4809,45 @@
         <v>5</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>26</v>
       </c>
       <c r="K26" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="L26" t="s">
-        <v>483</v>
+        <v>74</v>
       </c>
       <c r="M26" t="s">
         <v>99</v>
       </c>
       <c r="N26" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="O26" s="14" t="s">
-        <v>250</v>
+        <v>66</v>
       </c>
       <c r="P26" s="9"/>
       <c r="Q26" s="10"/>
       <c r="R26" s="11"/>
       <c r="Y26" s="13" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
     </row>
     <row r="27" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="1">
-        <v>26</v>
-      </c>
-      <c r="B27" s="1">
-        <v>55.03</v>
+        <v>24</v>
+      </c>
+      <c r="B27" s="8">
+        <v>84.69</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="E27" s="1"/>
       <c r="F27" s="1" t="s">
@@ -4910,111 +4860,111 @@
         <v>5</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>26</v>
       </c>
       <c r="K27" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="L27" t="s">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="M27" t="s">
         <v>29</v>
       </c>
       <c r="N27" t="s">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="O27" s="14" t="s">
-        <v>151</v>
+        <v>108</v>
       </c>
       <c r="P27" s="9"/>
       <c r="Q27" s="10"/>
       <c r="R27" s="11"/>
       <c r="Y27" s="13" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
     </row>
     <row r="28" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="1">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B28" s="1">
-        <v>68.459999999999994</v>
+        <v>42.09</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="E28" s="1">
-        <v>10229166</v>
+        <v>10270857</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>53</v>
+        <v>287</v>
       </c>
       <c r="G28" s="1" t="s">
         <v>281</v>
       </c>
       <c r="H28" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>26</v>
       </c>
       <c r="K28" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="L28" t="s">
-        <v>487</v>
+        <v>483</v>
       </c>
       <c r="M28" t="s">
-        <v>29</v>
+        <v>99</v>
       </c>
       <c r="N28" t="s">
-        <v>488</v>
-      </c>
-      <c r="O28" s="1" t="s">
-        <v>232</v>
+        <v>484</v>
+      </c>
+      <c r="O28" s="14" t="s">
+        <v>250</v>
       </c>
       <c r="P28" s="9"/>
       <c r="Q28" s="10"/>
       <c r="R28" s="11"/>
       <c r="Y28" s="13" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
     </row>
     <row r="29" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="1">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B29" s="1">
-        <v>51.27</v>
+        <v>55.03</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="E29" s="1"/>
       <c r="F29" s="1" t="s">
-        <v>53</v>
+        <v>84</v>
       </c>
       <c r="G29" s="1" t="s">
         <v>281</v>
       </c>
       <c r="H29" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>26</v>
@@ -5023,42 +4973,42 @@
         <v>43</v>
       </c>
       <c r="L29" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="M29" t="s">
-        <v>99</v>
+        <v>29</v>
       </c>
       <c r="N29" t="s">
-        <v>490</v>
-      </c>
-      <c r="O29" s="1" t="s">
-        <v>85</v>
+        <v>486</v>
+      </c>
+      <c r="O29" s="14" t="s">
+        <v>151</v>
       </c>
       <c r="P29" s="9"/>
       <c r="Q29" s="10"/>
       <c r="R29" s="11"/>
       <c r="Y29" s="13" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="30" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="1">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B30" s="1">
-        <v>72.58</v>
+        <v>68.459999999999994</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>312</v>
+        <v>320</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>313</v>
+        <v>321</v>
       </c>
       <c r="E30" s="1">
-        <v>10257997</v>
+        <v>10229166</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>314</v>
+        <v>53</v>
       </c>
       <c r="G30" s="1" t="s">
         <v>281</v>
@@ -5067,7 +5017,7 @@
         <v>6</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>26</v>
@@ -5076,42 +5026,40 @@
         <v>43</v>
       </c>
       <c r="L30" t="s">
-        <v>133</v>
+        <v>487</v>
       </c>
       <c r="M30" t="s">
         <v>29</v>
       </c>
       <c r="N30" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="O30" s="1" t="s">
-        <v>315</v>
+        <v>232</v>
       </c>
       <c r="P30" s="9"/>
       <c r="Q30" s="10"/>
       <c r="R30" s="11"/>
       <c r="Y30" s="13" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
     </row>
     <row r="31" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="1">
-        <v>30</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C31" s="5" t="s">
-        <v>161</v>
+        <v>28</v>
+      </c>
+      <c r="B31" s="1">
+        <v>51.27</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>317</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>309</v>
-      </c>
-      <c r="E31" s="1">
-        <v>10262368</v>
-      </c>
+        <v>318</v>
+      </c>
+      <c r="E31" s="1"/>
       <c r="F31" s="1" t="s">
-        <v>310</v>
+        <v>53</v>
       </c>
       <c r="G31" s="1" t="s">
         <v>281</v>
@@ -5120,75 +5068,89 @@
         <v>6</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>26</v>
       </c>
       <c r="K31" t="s">
-        <v>27</v>
+        <v>43</v>
+      </c>
+      <c r="L31" t="s">
+        <v>489</v>
+      </c>
+      <c r="M31" t="s">
+        <v>99</v>
       </c>
       <c r="N31" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="O31" s="1" t="s">
-        <v>193</v>
+        <v>85</v>
       </c>
       <c r="P31" s="9"/>
       <c r="Q31" s="10"/>
       <c r="R31" s="11"/>
       <c r="Y31" s="13" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
     </row>
     <row r="32" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="1">
-        <v>31</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C32" s="7" t="s">
-        <v>51</v>
+        <v>29</v>
+      </c>
+      <c r="B32" s="1">
+        <v>72.58</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>312</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>307</v>
-      </c>
-      <c r="E32" s="1"/>
+        <v>313</v>
+      </c>
+      <c r="E32" s="1">
+        <v>10257997</v>
+      </c>
       <c r="F32" s="1" t="s">
-        <v>84</v>
+        <v>314</v>
       </c>
       <c r="G32" s="1" t="s">
         <v>281</v>
       </c>
       <c r="H32" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="J32" s="2" t="s">
         <v>26</v>
       </c>
       <c r="K32" t="s">
-        <v>27</v>
+        <v>43</v>
+      </c>
+      <c r="L32" t="s">
+        <v>133</v>
+      </c>
+      <c r="M32" t="s">
+        <v>29</v>
       </c>
       <c r="N32" t="s">
-        <v>493</v>
-      </c>
-      <c r="O32" s="14" t="s">
-        <v>255</v>
+        <v>491</v>
+      </c>
+      <c r="O32" s="1" t="s">
+        <v>315</v>
       </c>
       <c r="P32" s="9"/>
       <c r="Q32" s="10"/>
       <c r="R32" s="11"/>
       <c r="Y32" s="13" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
     </row>
     <row r="33" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="1">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>31</v>
@@ -5197,52 +5159,54 @@
         <v>161</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="E33" s="1"/>
+        <v>309</v>
+      </c>
+      <c r="E33" s="1">
+        <v>10262368</v>
+      </c>
       <c r="F33" s="1" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="G33" s="1" t="s">
         <v>281</v>
       </c>
       <c r="H33" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="J33" s="2" t="s">
         <v>26</v>
       </c>
       <c r="K33" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="N33" t="s">
-        <v>494</v>
-      </c>
-      <c r="O33" s="14" t="s">
-        <v>305</v>
+        <v>492</v>
+      </c>
+      <c r="O33" s="1" t="s">
+        <v>193</v>
       </c>
       <c r="P33" s="9"/>
       <c r="Q33" s="10"/>
       <c r="R33" s="11"/>
       <c r="Y33" s="13" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
     </row>
     <row r="34" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="1">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C34" s="1" t="s">
-        <v>283</v>
+      <c r="C34" s="7" t="s">
+        <v>51</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="E34" s="1"/>
       <c r="F34" s="1" t="s">
@@ -5252,10 +5216,10 @@
         <v>281</v>
       </c>
       <c r="H34" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="J34" s="2" t="s">
         <v>26</v>
@@ -5264,43 +5228,43 @@
         <v>27</v>
       </c>
       <c r="N34" t="s">
-        <v>495</v>
-      </c>
-      <c r="O34" s="1" t="s">
-        <v>244</v>
+        <v>493</v>
+      </c>
+      <c r="O34" s="14" t="s">
+        <v>255</v>
       </c>
       <c r="P34" s="9"/>
       <c r="Q34" s="10"/>
       <c r="R34" s="11"/>
       <c r="Y34" s="13" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="35" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="1">
-        <v>34</v>
-      </c>
-      <c r="B35" s="1">
-        <v>61.69</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>298</v>
+        <v>32</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>161</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="E35" s="1"/>
       <c r="F35" s="1" t="s">
-        <v>84</v>
+        <v>304</v>
       </c>
       <c r="G35" s="1" t="s">
         <v>281</v>
       </c>
       <c r="H35" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="J35" s="2" t="s">
         <v>26</v>
@@ -5308,41 +5272,35 @@
       <c r="K35" t="s">
         <v>43</v>
       </c>
-      <c r="L35" t="s">
-        <v>496</v>
-      </c>
-      <c r="M35" t="s">
-        <v>29</v>
-      </c>
       <c r="N35" t="s">
-        <v>497</v>
-      </c>
-      <c r="O35" s="1" t="s">
-        <v>125</v>
+        <v>494</v>
+      </c>
+      <c r="O35" s="14" t="s">
+        <v>305</v>
       </c>
       <c r="P35" s="9"/>
       <c r="Q35" s="10"/>
       <c r="R35" s="11"/>
       <c r="Y35" s="13" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="36" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="1">
-        <v>35</v>
-      </c>
-      <c r="B36" s="1">
-        <v>73.28</v>
+        <v>33</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>31</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>149</v>
+        <v>283</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>47</v>
+        <v>301</v>
       </c>
       <c r="E36" s="1"/>
       <c r="F36" s="1" t="s">
-        <v>22</v>
+        <v>84</v>
       </c>
       <c r="G36" s="1" t="s">
         <v>281</v>
@@ -5351,7 +5309,7 @@
         <v>8</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="J36" s="2" t="s">
         <v>26</v>
@@ -5359,41 +5317,35 @@
       <c r="K36" t="s">
         <v>27</v>
       </c>
-      <c r="L36" t="s">
-        <v>446</v>
-      </c>
-      <c r="M36" t="s">
-        <v>36</v>
-      </c>
       <c r="N36" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="O36" s="1" t="s">
-        <v>296</v>
+        <v>244</v>
       </c>
       <c r="P36" s="9"/>
       <c r="Q36" s="10"/>
       <c r="R36" s="11"/>
       <c r="Y36" s="13" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
     </row>
     <row r="37" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="1">
-        <v>36</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
+      </c>
+      <c r="B37" s="1">
+        <v>61.69</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>39</v>
+        <v>298</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="E37" s="1"/>
       <c r="F37" s="1" t="s">
-        <v>294</v>
+        <v>84</v>
       </c>
       <c r="G37" s="1" t="s">
         <v>281</v>
@@ -5402,7 +5354,7 @@
         <v>8</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>103</v>
+        <v>300</v>
       </c>
       <c r="J37" s="2" t="s">
         <v>26</v>
@@ -5410,99 +5362,101 @@
       <c r="K37" t="s">
         <v>43</v>
       </c>
+      <c r="L37" t="s">
+        <v>496</v>
+      </c>
+      <c r="M37" t="s">
+        <v>29</v>
+      </c>
       <c r="N37" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="O37" s="1" t="s">
-        <v>295</v>
+        <v>125</v>
       </c>
       <c r="P37" s="9"/>
       <c r="Q37" s="10"/>
       <c r="R37" s="11"/>
       <c r="Y37" s="13" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
     </row>
     <row r="38" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="1">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B38" s="1">
-        <v>69.680000000000007</v>
+        <v>73.28</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>289</v>
+        <v>149</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>290</v>
-      </c>
-      <c r="E38" s="1">
-        <v>10243021</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="E38" s="1"/>
       <c r="F38" s="1" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="G38" s="1" t="s">
         <v>281</v>
       </c>
       <c r="H38" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I38" s="1" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="J38" s="2" t="s">
         <v>26</v>
       </c>
       <c r="K38" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="L38" t="s">
-        <v>500</v>
+        <v>446</v>
       </c>
       <c r="M38" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="N38" t="s">
-        <v>501</v>
-      </c>
-      <c r="O38" s="14" t="s">
-        <v>291</v>
+        <v>498</v>
+      </c>
+      <c r="O38" s="1" t="s">
+        <v>296</v>
       </c>
       <c r="P38" s="9"/>
       <c r="Q38" s="10"/>
       <c r="R38" s="11"/>
       <c r="Y38" s="13" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="39" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="1">
-        <v>38</v>
-      </c>
-      <c r="B39" s="1">
-        <v>52.22</v>
+        <v>36</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>31</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>285</v>
+        <v>39</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>286</v>
-      </c>
-      <c r="E39" s="1">
-        <v>10276169</v>
-      </c>
+        <v>293</v>
+      </c>
+      <c r="E39" s="1"/>
       <c r="F39" s="1" t="s">
-        <v>287</v>
+        <v>294</v>
       </c>
       <c r="G39" s="1" t="s">
         <v>281</v>
       </c>
       <c r="H39" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>288</v>
+        <v>103</v>
       </c>
       <c r="J39" s="2" t="s">
         <v>26</v>
@@ -5510,43 +5464,37 @@
       <c r="K39" t="s">
         <v>43</v>
       </c>
-      <c r="L39" t="s">
-        <v>446</v>
-      </c>
-      <c r="M39" t="s">
-        <v>36</v>
-      </c>
       <c r="N39" t="s">
-        <v>502</v>
-      </c>
-      <c r="O39" s="14" t="s">
-        <v>157</v>
+        <v>499</v>
+      </c>
+      <c r="O39" s="1" t="s">
+        <v>295</v>
       </c>
       <c r="P39" s="9"/>
       <c r="Q39" s="10"/>
       <c r="R39" s="11"/>
       <c r="Y39" s="13" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
     </row>
     <row r="40" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="1">
-        <v>39</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>31</v>
+        <v>37</v>
+      </c>
+      <c r="B40" s="1">
+        <v>69.680000000000007</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>173</v>
+        <v>290</v>
       </c>
       <c r="E40" s="1">
-        <v>10262517</v>
+        <v>10243021</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>84</v>
+        <v>53</v>
       </c>
       <c r="G40" s="1" t="s">
         <v>281</v>
@@ -5555,7 +5503,7 @@
         <v>9</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="J40" s="2" t="s">
         <v>26</v>
@@ -5563,35 +5511,43 @@
       <c r="K40" t="s">
         <v>43</v>
       </c>
+      <c r="L40" t="s">
+        <v>500</v>
+      </c>
+      <c r="M40" t="s">
+        <v>29</v>
+      </c>
       <c r="N40" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="O40" s="14" t="s">
-        <v>222</v>
+        <v>291</v>
       </c>
       <c r="P40" s="9"/>
       <c r="Q40" s="10"/>
       <c r="R40" s="11"/>
       <c r="Y40" s="13" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
     </row>
     <row r="41" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="1">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B41" s="1">
-        <v>75.91</v>
-      </c>
-      <c r="C41" s="5" t="s">
-        <v>280</v>
+        <v>52.22</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>285</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="E41" s="1"/>
+        <v>286</v>
+      </c>
+      <c r="E41" s="1">
+        <v>10276169</v>
+      </c>
       <c r="F41" s="1" t="s">
-        <v>59</v>
+        <v>287</v>
       </c>
       <c r="G41" s="1" t="s">
         <v>281</v>
@@ -5600,7 +5556,7 @@
         <v>9</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="J41" s="2" t="s">
         <v>26</v>
@@ -5615,45 +5571,137 @@
         <v>36</v>
       </c>
       <c r="N41" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="O41" s="14" t="s">
-        <v>41</v>
+        <v>157</v>
       </c>
       <c r="P41" s="9"/>
       <c r="Q41" s="10"/>
       <c r="R41" s="11"/>
       <c r="Y41" s="13" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
     </row>
     <row r="42" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="1">
+        <v>39</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="E42" s="1">
+        <v>10262517</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="G42" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="H42" s="1">
+        <v>9</v>
+      </c>
+      <c r="I42" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="J42" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K42" t="s">
+        <v>43</v>
+      </c>
+      <c r="N42" t="s">
+        <v>503</v>
+      </c>
+      <c r="O42" s="14" t="s">
+        <v>222</v>
+      </c>
       <c r="P42" s="9"/>
       <c r="Q42" s="10"/>
       <c r="R42" s="11"/>
+      <c r="Y42" s="13" t="s">
+        <v>443</v>
+      </c>
     </row>
     <row r="43" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="1">
+        <v>40</v>
+      </c>
+      <c r="B43" s="1">
+        <v>75.91</v>
+      </c>
+      <c r="C43" s="5" t="s">
+        <v>280</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E43" s="1"/>
+      <c r="F43" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="H43" s="1">
+        <v>9</v>
+      </c>
+      <c r="I43" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="J43" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K43" t="s">
+        <v>43</v>
+      </c>
+      <c r="L43" t="s">
+        <v>446</v>
+      </c>
+      <c r="M43" t="s">
+        <v>36</v>
+      </c>
+      <c r="N43" t="s">
+        <v>504</v>
+      </c>
+      <c r="O43" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="P43" s="9"/>
       <c r="Q43" s="10"/>
       <c r="R43" s="11"/>
+      <c r="Y43" s="13" t="s">
+        <v>444</v>
+      </c>
     </row>
     <row r="44" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="P44" s="9"/>
       <c r="Q44" s="10"/>
       <c r="R44" s="11"/>
     </row>
     <row r="45" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="Q45" s="10"/>
+      <c r="R45" s="11"/>
     </row>
     <row r="46" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="Q46" s="10"/>
+      <c r="R46" s="11"/>
     </row>
     <row r="47" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="Q47" s="10"/>
     </row>
     <row r="48" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="Q48" s="12"/>
+      <c r="Q48" s="10"/>
     </row>
     <row r="49" spans="17:17" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="Q49" s="12"/>
+      <c r="Q49" s="10"/>
     </row>
     <row r="50" spans="17:17" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="Q50" s="12"/>
@@ -5661,48 +5709,54 @@
     <row r="51" spans="17:17" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="Q51" s="12"/>
     </row>
-    <row r="52" spans="17:17" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="53" spans="17:17" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="52" spans="17:17" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Q52" s="12"/>
+    </row>
+    <row r="53" spans="17:17" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Q53" s="12"/>
+    </row>
+    <row r="54" spans="17:17" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="55" spans="17:17" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L41">
-    <sortCondition ref="A2:A41"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L43">
+    <sortCondition ref="A2:A43"/>
   </sortState>
   <hyperlinks>
-    <hyperlink ref="J41" r:id="rId1" display="https://probullstats.com/loggers/matchup.php?bull=54839&amp;guy=Julio+Cesar+Marques" xr:uid="{7A80C17A-3232-6448-9343-11FC1CD3C297}"/>
-    <hyperlink ref="J40" r:id="rId2" display="https://probullstats.com/loggers/matchup.php?bull=56542&amp;guy=Callum+Miller" xr:uid="{0F2BD59E-A00B-4D4B-8A15-FC0C2FCD8520}"/>
-    <hyperlink ref="J39" r:id="rId3" display="https://probullstats.com/loggers/matchup.php?bull=54130&amp;guy=Trace+Redd" xr:uid="{F4C2835A-438B-0142-98F5-439B5289E417}"/>
-    <hyperlink ref="J38" r:id="rId4" display="https://probullstats.com/loggers/matchup.php?bull=51428&amp;guy=Grayson+Cole" xr:uid="{9F41CA48-CFB7-E246-92DC-10D6692090A4}"/>
-    <hyperlink ref="J37" r:id="rId5" display="https://probullstats.com/loggers/matchup.php?bull=56381&amp;guy=Vinicius+Rodrigues+Pereira" xr:uid="{F733F9C0-F92E-DD40-BD82-74810719B425}"/>
-    <hyperlink ref="J36" r:id="rId6" display="https://probullstats.com/loggers/matchup.php?bull=55806&amp;guy=Ednelio+Rodrigues" xr:uid="{07DD6F14-EB65-2C4E-A591-3E2C378C2A67}"/>
-    <hyperlink ref="J35" r:id="rId7" display="https://probullstats.com/loggers/matchup.php?bull=53419&amp;guy=Mason+Taylor" xr:uid="{864A1DB8-FE2B-5D44-9643-DB818F8A9234}"/>
-    <hyperlink ref="J34" r:id="rId8" display="https://probullstats.com/loggers/matchup.php?bull=56047&amp;guy=Dener+Barbosa" xr:uid="{2AB1932A-11A1-7447-80A6-E02A42B49BB9}"/>
-    <hyperlink ref="J33" r:id="rId9" display="https://probullstats.com/loggers/matchup.php?bull=55809&amp;guy=Ramon+Fiorini" xr:uid="{03F5EABD-CF18-5E42-A0EA-CD3101D51E6C}"/>
-    <hyperlink ref="J32" r:id="rId10" display="https://probullstats.com/loggers/matchup.php?bull=56578&amp;guy=Vinicius+Pinheiro+Correa" xr:uid="{AAF7E716-B51F-5744-80BC-B9D1B3EC32AD}"/>
-    <hyperlink ref="J31" r:id="rId11" display="https://probullstats.com/loggers/matchup.php?bull=56236&amp;guy=Macaulie+Leather" xr:uid="{2021287A-E488-FD4C-B27D-94448D0F15C7}"/>
-    <hyperlink ref="J30" r:id="rId12" display="https://probullstats.com/loggers/matchup.php?bull=51896&amp;guy=Eric+Novoa" xr:uid="{95300F1E-1D61-B745-8FB1-31564488E65C}"/>
-    <hyperlink ref="J29" r:id="rId13" display="https://probullstats.com/loggers/matchup.php?bull=52820&amp;guy=Paulo+Eduardo+Rossetto" xr:uid="{0CEAA190-6ED4-7446-8DB9-0E54B259D446}"/>
-    <hyperlink ref="J28" r:id="rId14" display="https://probullstats.com/loggers/matchup.php?bull=50989&amp;guy=Lucas+Divino" xr:uid="{68EFE952-E1A2-2A43-A2D3-BF22A8D7B3E9}"/>
-    <hyperlink ref="J27" r:id="rId15" display="https://probullstats.com/loggers/matchup.php?bull=54227&amp;guy=Claudio+Montanha+Jr." xr:uid="{3D5353E0-0288-DF4A-9DAE-4F807BED1D54}"/>
-    <hyperlink ref="J26" r:id="rId16" display="https://probullstats.com/loggers/matchup.php?bull=54171&amp;guy=Koltin+Hevalow" xr:uid="{9412B2D9-0C75-C745-978E-773B146B6A20}"/>
-    <hyperlink ref="J25" r:id="rId17" display="https://probullstats.com/loggers/matchup.php?bull=51690&amp;guy=Hudson+Bolton" xr:uid="{B6C892CC-6302-014B-A6F4-C3E51780D547}"/>
-    <hyperlink ref="J24" r:id="rId18" display="https://probullstats.com/loggers/matchup.php?bull=53018&amp;guy=Keyshawn+Whitehorse" xr:uid="{1B7B6F25-EA93-3547-A6A1-883AFE3B0758}"/>
-    <hyperlink ref="J23" r:id="rId19" display="https://probullstats.com/loggers/matchup.php?bull=47941&amp;guy=Brady+Fielder" xr:uid="{F830A1E9-FAD6-9B44-9BDC-71504F789CA3}"/>
-    <hyperlink ref="J22" r:id="rId20" display="https://probullstats.com/loggers/matchup.php?bull=53535&amp;guy=John+Crimber" xr:uid="{33956328-C1EF-D149-9DFA-586EB9743B84}"/>
-    <hyperlink ref="J21" r:id="rId21" display="https://probullstats.com/loggers/matchup.php?bull=49727&amp;guy=Alex+Junior+da+Silva" xr:uid="{FE35623D-353B-0942-AAFF-E0848495E061}"/>
-    <hyperlink ref="J20" r:id="rId22" display="https://probullstats.com/loggers/matchup.php?bull=56540&amp;guy=Luciano+De+Castro" xr:uid="{75E344EB-84EF-E243-BC8E-0F69A94B6B09}"/>
-    <hyperlink ref="J19" r:id="rId23" display="https://probullstats.com/loggers/matchup.php?bull=44656&amp;guy=Mauricio+Gulla+Moreira" xr:uid="{C6F7534C-CF8F-014E-A078-46EDB48E4C40}"/>
-    <hyperlink ref="J18" r:id="rId24" display="https://probullstats.com/loggers/matchup.php?bull=50380&amp;guy=Andy+Guzman" xr:uid="{021B2B21-CA7E-8D47-8345-68AEA1745A23}"/>
-    <hyperlink ref="J17" r:id="rId25" display="https://probullstats.com/loggers/matchup.php?bull=53892&amp;guy=Joao+Ricardo+Vieira" xr:uid="{56F7B948-B1A1-0C48-B431-53B30A3D80A9}"/>
-    <hyperlink ref="J16" r:id="rId26" display="https://probullstats.com/loggers/matchup.php?bull=53319&amp;guy=Thiago+Salgado" xr:uid="{0024AC40-1D64-BC45-BE9C-E6AE555C4C55}"/>
-    <hyperlink ref="J15" r:id="rId27" display="https://probullstats.com/loggers/matchup.php?bull=48315&amp;guy=Daylon+Swearingen" xr:uid="{C7028F27-5A31-EB46-928F-52A417BEA75F}"/>
-    <hyperlink ref="J14" r:id="rId28" display="https://probullstats.com/loggers/matchup.php?bull=54209&amp;guy=Andrew+Alvidrez" xr:uid="{5C697E8D-70AD-F046-AB04-46B464409C3E}"/>
-    <hyperlink ref="J13" r:id="rId29" display="https://probullstats.com/loggers/matchup.php?bull=51949&amp;guy=Jess+Lockwood" xr:uid="{A8987CAE-A15F-4F4C-8921-F7BBB52EF782}"/>
-    <hyperlink ref="J12" r:id="rId30" display="https://probullstats.com/loggers/matchup.php?bull=56577&amp;guy=Daniel+Keeping" xr:uid="{F416108D-A154-9D43-A6ED-1D1060E32985}"/>
-    <hyperlink ref="J11" r:id="rId31" display="https://probullstats.com/loggers/matchup.php?bull=53617&amp;guy=Bob+Mitchell" xr:uid="{93B7C777-B99A-8043-9473-B9BA8A4AF91D}"/>
-    <hyperlink ref="J10" r:id="rId32" display="https://probullstats.com/loggers/matchup.php?bull=55454&amp;guy=Romario+Leite" xr:uid="{1D408E4F-3CA9-514F-89EF-F1CDD9720C41}"/>
-    <hyperlink ref="J9" r:id="rId33" display="https://probullstats.com/loggers/matchup.php?bull=56214&amp;guy=Alex+Cerqueira" xr:uid="{C8A17F1D-296F-E745-9931-F763D38E0160}"/>
-    <hyperlink ref="J8" r:id="rId34" display="https://probullstats.com/loggers/matchup.php?bull=52839&amp;guy=Alan+de+Souza" xr:uid="{92AEEB17-6DB6-E840-B049-1DC988B9269E}"/>
-    <hyperlink ref="J7" r:id="rId35" display="https://probullstats.com/loggers/matchup.php?bull=56035&amp;guy=Cassio+Dias" xr:uid="{CBE38BD9-0AED-8B48-AE5C-A82D5055703F}"/>
+    <hyperlink ref="J43" r:id="rId1" display="https://probullstats.com/loggers/matchup.php?bull=54839&amp;guy=Julio+Cesar+Marques" xr:uid="{7A80C17A-3232-6448-9343-11FC1CD3C297}"/>
+    <hyperlink ref="J42" r:id="rId2" display="https://probullstats.com/loggers/matchup.php?bull=56542&amp;guy=Callum+Miller" xr:uid="{0F2BD59E-A00B-4D4B-8A15-FC0C2FCD8520}"/>
+    <hyperlink ref="J41" r:id="rId3" display="https://probullstats.com/loggers/matchup.php?bull=54130&amp;guy=Trace+Redd" xr:uid="{F4C2835A-438B-0142-98F5-439B5289E417}"/>
+    <hyperlink ref="J40" r:id="rId4" display="https://probullstats.com/loggers/matchup.php?bull=51428&amp;guy=Grayson+Cole" xr:uid="{9F41CA48-CFB7-E246-92DC-10D6692090A4}"/>
+    <hyperlink ref="J39" r:id="rId5" display="https://probullstats.com/loggers/matchup.php?bull=56381&amp;guy=Vinicius+Rodrigues+Pereira" xr:uid="{F733F9C0-F92E-DD40-BD82-74810719B425}"/>
+    <hyperlink ref="J38" r:id="rId6" display="https://probullstats.com/loggers/matchup.php?bull=55806&amp;guy=Ednelio+Rodrigues" xr:uid="{07DD6F14-EB65-2C4E-A591-3E2C378C2A67}"/>
+    <hyperlink ref="J37" r:id="rId7" display="https://probullstats.com/loggers/matchup.php?bull=53419&amp;guy=Mason+Taylor" xr:uid="{864A1DB8-FE2B-5D44-9643-DB818F8A9234}"/>
+    <hyperlink ref="J36" r:id="rId8" display="https://probullstats.com/loggers/matchup.php?bull=56047&amp;guy=Dener+Barbosa" xr:uid="{2AB1932A-11A1-7447-80A6-E02A42B49BB9}"/>
+    <hyperlink ref="J35" r:id="rId9" display="https://probullstats.com/loggers/matchup.php?bull=55809&amp;guy=Ramon+Fiorini" xr:uid="{03F5EABD-CF18-5E42-A0EA-CD3101D51E6C}"/>
+    <hyperlink ref="J34" r:id="rId10" display="https://probullstats.com/loggers/matchup.php?bull=56578&amp;guy=Vinicius+Pinheiro+Correa" xr:uid="{AAF7E716-B51F-5744-80BC-B9D1B3EC32AD}"/>
+    <hyperlink ref="J33" r:id="rId11" display="https://probullstats.com/loggers/matchup.php?bull=56236&amp;guy=Macaulie+Leather" xr:uid="{2021287A-E488-FD4C-B27D-94448D0F15C7}"/>
+    <hyperlink ref="J32" r:id="rId12" display="https://probullstats.com/loggers/matchup.php?bull=51896&amp;guy=Eric+Novoa" xr:uid="{95300F1E-1D61-B745-8FB1-31564488E65C}"/>
+    <hyperlink ref="J31" r:id="rId13" display="https://probullstats.com/loggers/matchup.php?bull=52820&amp;guy=Paulo+Eduardo+Rossetto" xr:uid="{0CEAA190-6ED4-7446-8DB9-0E54B259D446}"/>
+    <hyperlink ref="J30" r:id="rId14" display="https://probullstats.com/loggers/matchup.php?bull=50989&amp;guy=Lucas+Divino" xr:uid="{68EFE952-E1A2-2A43-A2D3-BF22A8D7B3E9}"/>
+    <hyperlink ref="J29" r:id="rId15" display="https://probullstats.com/loggers/matchup.php?bull=54227&amp;guy=Claudio+Montanha+Jr." xr:uid="{3D5353E0-0288-DF4A-9DAE-4F807BED1D54}"/>
+    <hyperlink ref="J28" r:id="rId16" display="https://probullstats.com/loggers/matchup.php?bull=54171&amp;guy=Koltin+Hevalow" xr:uid="{9412B2D9-0C75-C745-978E-773B146B6A20}"/>
+    <hyperlink ref="J27" r:id="rId17" display="https://probullstats.com/loggers/matchup.php?bull=51690&amp;guy=Hudson+Bolton" xr:uid="{B6C892CC-6302-014B-A6F4-C3E51780D547}"/>
+    <hyperlink ref="J26" r:id="rId18" display="https://probullstats.com/loggers/matchup.php?bull=53018&amp;guy=Keyshawn+Whitehorse" xr:uid="{1B7B6F25-EA93-3547-A6A1-883AFE3B0758}"/>
+    <hyperlink ref="J25" r:id="rId19" display="https://probullstats.com/loggers/matchup.php?bull=47941&amp;guy=Brady+Fielder" xr:uid="{F830A1E9-FAD6-9B44-9BDC-71504F789CA3}"/>
+    <hyperlink ref="J24" r:id="rId20" display="https://probullstats.com/loggers/matchup.php?bull=53535&amp;guy=John+Crimber" xr:uid="{33956328-C1EF-D149-9DFA-586EB9743B84}"/>
+    <hyperlink ref="J23" r:id="rId21" display="https://probullstats.com/loggers/matchup.php?bull=49727&amp;guy=Alex+Junior+da+Silva" xr:uid="{FE35623D-353B-0942-AAFF-E0848495E061}"/>
+    <hyperlink ref="J22" r:id="rId22" display="https://probullstats.com/loggers/matchup.php?bull=56540&amp;guy=Luciano+De+Castro" xr:uid="{75E344EB-84EF-E243-BC8E-0F69A94B6B09}"/>
+    <hyperlink ref="J21" r:id="rId23" display="https://probullstats.com/loggers/matchup.php?bull=44656&amp;guy=Mauricio+Gulla+Moreira" xr:uid="{C6F7534C-CF8F-014E-A078-46EDB48E4C40}"/>
+    <hyperlink ref="J20" r:id="rId24" display="https://probullstats.com/loggers/matchup.php?bull=50380&amp;guy=Andy+Guzman" xr:uid="{021B2B21-CA7E-8D47-8345-68AEA1745A23}"/>
+    <hyperlink ref="J19" r:id="rId25" display="https://probullstats.com/loggers/matchup.php?bull=53892&amp;guy=Joao+Ricardo+Vieira" xr:uid="{56F7B948-B1A1-0C48-B431-53B30A3D80A9}"/>
+    <hyperlink ref="J18" r:id="rId26" display="https://probullstats.com/loggers/matchup.php?bull=53319&amp;guy=Thiago+Salgado" xr:uid="{0024AC40-1D64-BC45-BE9C-E6AE555C4C55}"/>
+    <hyperlink ref="J17" r:id="rId27" display="https://probullstats.com/loggers/matchup.php?bull=48315&amp;guy=Daylon+Swearingen" xr:uid="{C7028F27-5A31-EB46-928F-52A417BEA75F}"/>
+    <hyperlink ref="J16" r:id="rId28" display="https://probullstats.com/loggers/matchup.php?bull=54209&amp;guy=Andrew+Alvidrez" xr:uid="{5C697E8D-70AD-F046-AB04-46B464409C3E}"/>
+    <hyperlink ref="J15" r:id="rId29" display="https://probullstats.com/loggers/matchup.php?bull=51949&amp;guy=Jess+Lockwood" xr:uid="{A8987CAE-A15F-4F4C-8921-F7BBB52EF782}"/>
+    <hyperlink ref="J14" r:id="rId30" display="https://probullstats.com/loggers/matchup.php?bull=56577&amp;guy=Daniel+Keeping" xr:uid="{F416108D-A154-9D43-A6ED-1D1060E32985}"/>
+    <hyperlink ref="J13" r:id="rId31" display="https://probullstats.com/loggers/matchup.php?bull=53617&amp;guy=Bob+Mitchell" xr:uid="{93B7C777-B99A-8043-9473-B9BA8A4AF91D}"/>
+    <hyperlink ref="J12" r:id="rId32" display="https://probullstats.com/loggers/matchup.php?bull=55454&amp;guy=Romario+Leite" xr:uid="{1D408E4F-3CA9-514F-89EF-F1CDD9720C41}"/>
+    <hyperlink ref="J11" r:id="rId33" display="https://probullstats.com/loggers/matchup.php?bull=56214&amp;guy=Alex+Cerqueira" xr:uid="{C8A17F1D-296F-E745-9931-F763D38E0160}"/>
+    <hyperlink ref="J10" r:id="rId34" display="https://probullstats.com/loggers/matchup.php?bull=52839&amp;guy=Alan+de+Souza" xr:uid="{92AEEB17-6DB6-E840-B049-1DC988B9269E}"/>
+    <hyperlink ref="J9" r:id="rId35" display="https://probullstats.com/loggers/matchup.php?bull=56035&amp;guy=Cassio+Dias" xr:uid="{CBE38BD9-0AED-8B48-AE5C-A82D5055703F}"/>
     <hyperlink ref="J6" r:id="rId36" display="https://probullstats.com/loggers/matchup.php?bull=45633&amp;guy=Marco+Rizzo" xr:uid="{E3412961-8175-8742-B289-193D41E6BF56}"/>
     <hyperlink ref="J5" r:id="rId37" display="https://probullstats.com/loggers/matchup.php?bull=53773&amp;guy=Bruno+Carvalho" xr:uid="{4833B6B6-D785-CD4D-AD7C-80D2611062CB}"/>
     <hyperlink ref="J4" r:id="rId38" display="https://probullstats.com/loggers/matchup.php?bull=52929&amp;guy=Kase+Hitt" xr:uid="{7AC8DC2D-E077-B34C-A679-937E544383EF}"/>

--- a/data/pbr_matchups_full.xlsx
+++ b/data/pbr_matchups_full.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cameronyoung/Desktop/rankratings:/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{952C0ACE-CF7D-FA40-9C38-34F52E101DFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE1FF750-F7C3-3E48-A4F7-A2C2C175D1AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="740" windowWidth="30240" windowHeight="18900" xr2:uid="{63502F5A-9950-074D-B0A2-89EF4471630B}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1057" uniqueCount="506">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1053" uniqueCount="506">
   <si>
     <t>Bull Power</t>
   </si>
@@ -3857,54 +3857,92 @@
     <row r="7" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
+      <c r="C7" s="1" t="s">
+        <v>385</v>
+      </c>
       <c r="D7" s="1" t="s">
-        <v>274</v>
+        <v>40</v>
       </c>
       <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
-      <c r="J7" s="2"/>
-      <c r="O7" s="14" t="s">
-        <v>141</v>
-      </c>
-      <c r="P7" s="9">
-        <v>45</v>
-      </c>
-      <c r="Q7" s="10">
-        <v>45</v>
-      </c>
-      <c r="R7" s="11">
-        <v>45</v>
-      </c>
+      <c r="F7" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="H7" s="1">
+        <v>2</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K7" t="s">
+        <v>43</v>
+      </c>
+      <c r="N7" t="s">
+        <v>453</v>
+      </c>
+      <c r="O7" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="P7" s="9"/>
+      <c r="Q7" s="10"/>
+      <c r="R7" s="11"/>
       <c r="Y7" s="13"/>
     </row>
     <row r="8" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
+      <c r="C8" s="1" t="s">
+        <v>382</v>
+      </c>
       <c r="D8" s="1" t="s">
-        <v>274</v>
-      </c>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
-      <c r="J8" s="2"/>
-      <c r="O8" s="14" t="s">
-        <v>131</v>
-      </c>
-      <c r="P8" s="9">
+        <v>21</v>
+      </c>
+      <c r="E8" s="1">
+        <v>10229185</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="H8" s="1">
+        <v>2</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K8" t="s">
         <v>43</v>
       </c>
-      <c r="Q8" s="10">
-        <v>0</v>
-      </c>
-      <c r="R8" s="11">
-        <v>0</v>
+      <c r="L8" t="s">
+        <v>454</v>
+      </c>
+      <c r="M8" t="s">
+        <v>29</v>
+      </c>
+      <c r="N8" t="s">
+        <v>455</v>
+      </c>
+      <c r="O8" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="P8" s="9" t="s">
+        <v>505</v>
+      </c>
+      <c r="Q8" s="10" t="s">
+        <v>505</v>
+      </c>
+      <c r="R8" s="11" t="s">
+        <v>505</v>
       </c>
       <c r="Y8" s="13"/>
     </row>
@@ -3915,13 +3953,15 @@
       <c r="B9" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C9" s="1" t="s">
-        <v>385</v>
+      <c r="C9" s="5" t="s">
+        <v>161</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="E9" s="1"/>
+        <v>33</v>
+      </c>
+      <c r="E9" s="1">
+        <v>10250898</v>
+      </c>
       <c r="F9" s="1" t="s">
         <v>22</v>
       </c>
@@ -3932,19 +3972,19 @@
         <v>2</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>386</v>
+        <v>381</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>26</v>
       </c>
       <c r="K9" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="N9" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>260</v>
+        <v>90</v>
       </c>
       <c r="P9" s="9"/>
       <c r="Q9" s="10"/>
@@ -3961,16 +4001,14 @@
         <v>71</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E10" s="1">
-        <v>10229185</v>
-      </c>
+        <v>378</v>
+      </c>
+      <c r="E10" s="1"/>
       <c r="F10" s="1" t="s">
-        <v>22</v>
+        <v>53</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>281</v>
@@ -3979,25 +4017,25 @@
         <v>2</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>26</v>
       </c>
       <c r="K10" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="L10" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="M10" t="s">
         <v>29</v>
       </c>
       <c r="N10" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="O10" s="1" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="P10" s="9" t="s">
         <v>505</v>
@@ -4019,17 +4057,15 @@
       <c r="B11" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C11" s="5" t="s">
-        <v>161</v>
+      <c r="C11" s="1" t="s">
+        <v>374</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="E11" s="1">
-        <v>10250898</v>
-      </c>
+        <v>375</v>
+      </c>
+      <c r="E11" s="1"/>
       <c r="F11" s="1" t="s">
-        <v>22</v>
+        <v>53</v>
       </c>
       <c r="G11" s="1" t="s">
         <v>281</v>
@@ -4038,7 +4074,7 @@
         <v>2</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>26</v>
@@ -4046,11 +4082,17 @@
       <c r="K11" t="s">
         <v>27</v>
       </c>
+      <c r="L11" t="s">
+        <v>459</v>
+      </c>
+      <c r="M11" t="s">
+        <v>29</v>
+      </c>
       <c r="N11" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="P11" s="9"/>
       <c r="Q11" s="10"/>
@@ -4066,13 +4108,15 @@
       <c r="B12" s="1">
         <v>52.32</v>
       </c>
-      <c r="C12" s="1" t="s">
-        <v>377</v>
+      <c r="C12" s="7" t="s">
+        <v>51</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>378</v>
-      </c>
-      <c r="E12" s="1"/>
+        <v>372</v>
+      </c>
+      <c r="E12" s="1">
+        <v>10268379</v>
+      </c>
       <c r="F12" s="1" t="s">
         <v>53</v>
       </c>
@@ -4083,7 +4127,7 @@
         <v>2</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>380</v>
+        <v>373</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>26</v>
@@ -4091,27 +4135,15 @@
       <c r="K12" t="s">
         <v>27</v>
       </c>
-      <c r="L12" t="s">
-        <v>457</v>
-      </c>
-      <c r="M12" t="s">
-        <v>29</v>
-      </c>
       <c r="N12" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="O12" s="1" t="s">
-        <v>379</v>
-      </c>
-      <c r="P12" s="9" t="s">
-        <v>505</v>
-      </c>
-      <c r="Q12" s="10" t="s">
-        <v>505</v>
-      </c>
-      <c r="R12" s="11" t="s">
-        <v>505</v>
-      </c>
+        <v>163</v>
+      </c>
+      <c r="P12" s="9"/>
+      <c r="Q12" s="10"/>
+      <c r="R12" s="11"/>
       <c r="Y12" s="13" t="s">
         <v>413</v>
       </c>
@@ -4124,23 +4156,23 @@
         <v>59.59</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="E13" s="1"/>
       <c r="F13" s="1" t="s">
-        <v>53</v>
+        <v>342</v>
       </c>
       <c r="G13" s="1" t="s">
         <v>281</v>
       </c>
       <c r="H13" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>26</v>
@@ -4149,16 +4181,16 @@
         <v>27</v>
       </c>
       <c r="L13" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="M13" t="s">
-        <v>29</v>
+        <v>99</v>
       </c>
       <c r="N13" t="s">
-        <v>460</v>
-      </c>
-      <c r="O13" s="1" t="s">
-        <v>60</v>
+        <v>463</v>
+      </c>
+      <c r="O13" s="14" t="s">
+        <v>24</v>
       </c>
       <c r="P13" s="9"/>
       <c r="Q13" s="10"/>
@@ -4174,38 +4206,44 @@
       <c r="B14" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C14" s="7" t="s">
-        <v>51</v>
+      <c r="C14" s="5" t="s">
+        <v>365</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>372</v>
+        <v>366</v>
       </c>
       <c r="E14" s="1">
-        <v>10268379</v>
+        <v>10272036</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>53</v>
+        <v>287</v>
       </c>
       <c r="G14" s="1" t="s">
         <v>281</v>
       </c>
       <c r="H14" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>26</v>
       </c>
       <c r="K14" t="s">
-        <v>27</v>
+        <v>43</v>
+      </c>
+      <c r="L14" t="s">
+        <v>446</v>
+      </c>
+      <c r="M14" t="s">
+        <v>36</v>
       </c>
       <c r="N14" t="s">
-        <v>461</v>
-      </c>
-      <c r="O14" s="1" t="s">
-        <v>163</v>
+        <v>464</v>
+      </c>
+      <c r="O14" s="14" t="s">
+        <v>367</v>
       </c>
       <c r="P14" s="9"/>
       <c r="Q14" s="10"/>
@@ -4222,14 +4260,14 @@
         <v>67.209999999999994</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>369</v>
+        <v>360</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>370</v>
+        <v>361</v>
       </c>
       <c r="E15" s="1"/>
       <c r="F15" s="1" t="s">
-        <v>342</v>
+        <v>362</v>
       </c>
       <c r="G15" s="1" t="s">
         <v>281</v>
@@ -4238,7 +4276,7 @@
         <v>3</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>26</v>
@@ -4247,16 +4285,16 @@
         <v>27</v>
       </c>
       <c r="L15" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="M15" t="s">
-        <v>99</v>
+        <v>29</v>
       </c>
       <c r="N15" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="O15" s="14" t="s">
-        <v>24</v>
+        <v>363</v>
       </c>
       <c r="P15" s="9"/>
       <c r="Q15" s="10"/>
@@ -4272,17 +4310,15 @@
       <c r="B16" s="1">
         <v>75.92</v>
       </c>
-      <c r="C16" s="5" t="s">
-        <v>365</v>
+      <c r="C16" s="1" t="s">
+        <v>356</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>366</v>
-      </c>
-      <c r="E16" s="1">
-        <v>10272036</v>
-      </c>
+        <v>357</v>
+      </c>
+      <c r="E16" s="1"/>
       <c r="F16" s="1" t="s">
-        <v>287</v>
+        <v>294</v>
       </c>
       <c r="G16" s="1" t="s">
         <v>281</v>
@@ -4291,25 +4327,25 @@
         <v>3</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>368</v>
+        <v>359</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>26</v>
       </c>
       <c r="K16" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="L16" t="s">
-        <v>446</v>
+        <v>467</v>
       </c>
       <c r="M16" t="s">
-        <v>36</v>
+        <v>99</v>
       </c>
       <c r="N16" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="O16" s="14" t="s">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="P16" s="9"/>
       <c r="Q16" s="10"/>
@@ -4326,23 +4362,25 @@
         <v>78.86</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>360</v>
+        <v>352</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>361</v>
-      </c>
-      <c r="E17" s="1"/>
+        <v>353</v>
+      </c>
+      <c r="E17" s="1">
+        <v>10276006</v>
+      </c>
       <c r="F17" s="1" t="s">
-        <v>362</v>
+        <v>354</v>
       </c>
       <c r="G17" s="1" t="s">
         <v>281</v>
       </c>
       <c r="H17" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>26</v>
@@ -4351,16 +4389,16 @@
         <v>27</v>
       </c>
       <c r="L17" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="M17" t="s">
-        <v>29</v>
+        <v>99</v>
       </c>
       <c r="N17" t="s">
-        <v>466</v>
-      </c>
-      <c r="O17" s="14" t="s">
-        <v>363</v>
+        <v>470</v>
+      </c>
+      <c r="O17" s="1" t="s">
+        <v>187</v>
       </c>
       <c r="P17" s="9"/>
       <c r="Q17" s="10"/>
@@ -4377,23 +4415,25 @@
         <v>57.72</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>356</v>
+        <v>349</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>357</v>
-      </c>
-      <c r="E18" s="1"/>
+        <v>350</v>
+      </c>
+      <c r="E18" s="1">
+        <v>10243159</v>
+      </c>
       <c r="F18" s="1" t="s">
-        <v>294</v>
+        <v>310</v>
       </c>
       <c r="G18" s="1" t="s">
         <v>281</v>
       </c>
       <c r="H18" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>359</v>
+        <v>351</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>26</v>
@@ -4402,16 +4442,16 @@
         <v>27</v>
       </c>
       <c r="L18" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="M18" t="s">
-        <v>99</v>
+        <v>29</v>
       </c>
       <c r="N18" t="s">
-        <v>468</v>
-      </c>
-      <c r="O18" s="14" t="s">
-        <v>358</v>
+        <v>472</v>
+      </c>
+      <c r="O18" s="1" t="s">
+        <v>238</v>
       </c>
       <c r="P18" s="9"/>
       <c r="Q18" s="10"/>
@@ -4428,16 +4468,16 @@
         <v>65.19</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="E19" s="1">
-        <v>10276006</v>
+        <v>10205390</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="G19" s="1" t="s">
         <v>281</v>
@@ -4446,7 +4486,7 @@
         <v>4</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>355</v>
+        <v>348</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>26</v>
@@ -4455,16 +4495,16 @@
         <v>27</v>
       </c>
       <c r="L19" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="M19" t="s">
         <v>99</v>
       </c>
       <c r="N19" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="O19" s="1" t="s">
-        <v>187</v>
+        <v>54</v>
       </c>
       <c r="P19" s="9"/>
       <c r="Q19" s="10"/>
@@ -4480,17 +4520,15 @@
       <c r="B20" s="1">
         <v>66.97</v>
       </c>
-      <c r="C20" s="1" t="s">
-        <v>349</v>
+      <c r="C20" s="5" t="s">
+        <v>344</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>350</v>
-      </c>
-      <c r="E20" s="1">
-        <v>10243159</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="E20" s="1"/>
       <c r="F20" s="1" t="s">
-        <v>310</v>
+        <v>53</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>281</v>
@@ -4499,7 +4537,7 @@
         <v>4</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>26</v>
@@ -4507,17 +4545,11 @@
       <c r="K20" t="s">
         <v>27</v>
       </c>
-      <c r="L20" t="s">
-        <v>471</v>
-      </c>
-      <c r="M20" t="s">
-        <v>29</v>
-      </c>
       <c r="N20" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="O20" s="1" t="s">
-        <v>238</v>
+        <v>96</v>
       </c>
       <c r="P20" s="9"/>
       <c r="Q20" s="10"/>
@@ -4534,16 +4566,16 @@
         <v>75.709999999999994</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="E21" s="1">
-        <v>10205390</v>
+        <v>10231548</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>310</v>
+        <v>342</v>
       </c>
       <c r="G21" s="1" t="s">
         <v>281</v>
@@ -4552,25 +4584,25 @@
         <v>4</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>26</v>
       </c>
       <c r="K21" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="L21" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="M21" t="s">
-        <v>99</v>
+        <v>29</v>
       </c>
       <c r="N21" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="O21" s="1" t="s">
-        <v>54</v>
+        <v>114</v>
       </c>
       <c r="P21" s="9"/>
       <c r="Q21" s="10"/>
@@ -4586,24 +4618,26 @@
       <c r="B22" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C22" s="5" t="s">
-        <v>344</v>
+      <c r="C22" s="1" t="s">
+        <v>105</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="E22" s="1"/>
+        <v>338</v>
+      </c>
+      <c r="E22" s="1">
+        <v>10268851</v>
+      </c>
       <c r="F22" s="1" t="s">
-        <v>53</v>
+        <v>334</v>
       </c>
       <c r="G22" s="1" t="s">
         <v>281</v>
       </c>
       <c r="H22" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>26</v>
@@ -4611,11 +4645,17 @@
       <c r="K22" t="s">
         <v>27</v>
       </c>
+      <c r="L22" t="s">
+        <v>465</v>
+      </c>
+      <c r="M22" t="s">
+        <v>29</v>
+      </c>
       <c r="N22" t="s">
-        <v>475</v>
-      </c>
-      <c r="O22" s="1" t="s">
-        <v>96</v>
+        <v>478</v>
+      </c>
+      <c r="O22" s="14" t="s">
+        <v>136</v>
       </c>
       <c r="P22" s="9"/>
       <c r="Q22" s="10"/>
@@ -4631,26 +4671,26 @@
       <c r="B23" s="1">
         <v>77.819999999999993</v>
       </c>
-      <c r="C23" s="1" t="s">
-        <v>340</v>
+      <c r="C23" s="5" t="s">
+        <v>117</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="E23" s="1">
-        <v>10231548</v>
+        <v>10229189</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>342</v>
+        <v>334</v>
       </c>
       <c r="G23" s="1" t="s">
         <v>281</v>
       </c>
       <c r="H23" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>343</v>
+        <v>337</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>26</v>
@@ -4659,16 +4699,16 @@
         <v>43</v>
       </c>
       <c r="L23" t="s">
-        <v>476</v>
+        <v>446</v>
       </c>
       <c r="M23" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="N23" t="s">
-        <v>477</v>
-      </c>
-      <c r="O23" s="1" t="s">
-        <v>114</v>
+        <v>479</v>
+      </c>
+      <c r="O23" s="14" t="s">
+        <v>146</v>
       </c>
       <c r="P23" s="9"/>
       <c r="Q23" s="10"/>
@@ -4685,13 +4725,13 @@
         <v>73.45</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>105</v>
+        <v>332</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="E24" s="1">
-        <v>10268851</v>
+        <v>10262490</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>334</v>
@@ -4703,25 +4743,25 @@
         <v>5</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>26</v>
       </c>
       <c r="K24" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="L24" t="s">
-        <v>465</v>
+        <v>74</v>
       </c>
       <c r="M24" t="s">
-        <v>29</v>
+        <v>99</v>
       </c>
       <c r="N24" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="O24" s="14" t="s">
-        <v>136</v>
+        <v>66</v>
       </c>
       <c r="P24" s="9"/>
       <c r="Q24" s="10"/>
@@ -4737,17 +4777,15 @@
       <c r="B25" s="1">
         <v>74.900000000000006</v>
       </c>
-      <c r="C25" s="5" t="s">
-        <v>117</v>
+      <c r="C25" s="1" t="s">
+        <v>329</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>336</v>
-      </c>
-      <c r="E25" s="1">
-        <v>10229189</v>
-      </c>
+        <v>330</v>
+      </c>
+      <c r="E25" s="1"/>
       <c r="F25" s="1" t="s">
-        <v>334</v>
+        <v>84</v>
       </c>
       <c r="G25" s="1" t="s">
         <v>281</v>
@@ -4756,25 +4794,25 @@
         <v>5</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>26</v>
       </c>
       <c r="K25" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="L25" t="s">
-        <v>446</v>
+        <v>481</v>
       </c>
       <c r="M25" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="N25" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="O25" s="14" t="s">
-        <v>146</v>
+        <v>108</v>
       </c>
       <c r="P25" s="9"/>
       <c r="Q25" s="10"/>
@@ -4791,16 +4829,16 @@
         <v>61.01</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="E26" s="1">
-        <v>10262490</v>
+        <v>10270857</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>334</v>
+        <v>287</v>
       </c>
       <c r="G26" s="1" t="s">
         <v>281</v>
@@ -4809,25 +4847,25 @@
         <v>5</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>335</v>
+        <v>328</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>26</v>
       </c>
       <c r="K26" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="L26" t="s">
-        <v>74</v>
+        <v>483</v>
       </c>
       <c r="M26" t="s">
         <v>99</v>
       </c>
       <c r="N26" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="O26" s="14" t="s">
-        <v>66</v>
+        <v>250</v>
       </c>
       <c r="P26" s="9"/>
       <c r="Q26" s="10"/>
@@ -4844,10 +4882,10 @@
         <v>84.69</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="E27" s="1"/>
       <c r="F27" s="1" t="s">
@@ -4860,25 +4898,25 @@
         <v>5</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>26</v>
       </c>
       <c r="K27" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="L27" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="M27" t="s">
         <v>29</v>
       </c>
       <c r="N27" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="O27" s="14" t="s">
-        <v>108</v>
+        <v>151</v>
       </c>
       <c r="P27" s="9"/>
       <c r="Q27" s="10"/>
@@ -4895,43 +4933,43 @@
         <v>42.09</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="E28" s="1">
-        <v>10270857</v>
+        <v>10229166</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>287</v>
+        <v>53</v>
       </c>
       <c r="G28" s="1" t="s">
         <v>281</v>
       </c>
       <c r="H28" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>26</v>
       </c>
       <c r="K28" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="L28" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="M28" t="s">
-        <v>99</v>
+        <v>29</v>
       </c>
       <c r="N28" t="s">
-        <v>484</v>
-      </c>
-      <c r="O28" s="14" t="s">
-        <v>250</v>
+        <v>488</v>
+      </c>
+      <c r="O28" s="1" t="s">
+        <v>232</v>
       </c>
       <c r="P28" s="9"/>
       <c r="Q28" s="10"/>
@@ -4948,23 +4986,23 @@
         <v>55.03</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="E29" s="1"/>
       <c r="F29" s="1" t="s">
-        <v>84</v>
+        <v>53</v>
       </c>
       <c r="G29" s="1" t="s">
         <v>281</v>
       </c>
       <c r="H29" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>26</v>
@@ -4973,16 +5011,16 @@
         <v>43</v>
       </c>
       <c r="L29" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="M29" t="s">
-        <v>29</v>
+        <v>99</v>
       </c>
       <c r="N29" t="s">
-        <v>486</v>
-      </c>
-      <c r="O29" s="14" t="s">
-        <v>151</v>
+        <v>490</v>
+      </c>
+      <c r="O29" s="1" t="s">
+        <v>85</v>
       </c>
       <c r="P29" s="9"/>
       <c r="Q29" s="10"/>
@@ -4999,16 +5037,16 @@
         <v>68.459999999999994</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>320</v>
+        <v>312</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>321</v>
+        <v>313</v>
       </c>
       <c r="E30" s="1">
-        <v>10229166</v>
+        <v>10257997</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>53</v>
+        <v>314</v>
       </c>
       <c r="G30" s="1" t="s">
         <v>281</v>
@@ -5017,7 +5055,7 @@
         <v>6</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>26</v>
@@ -5026,16 +5064,16 @@
         <v>43</v>
       </c>
       <c r="L30" t="s">
-        <v>487</v>
+        <v>133</v>
       </c>
       <c r="M30" t="s">
         <v>29</v>
       </c>
       <c r="N30" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="O30" s="1" t="s">
-        <v>232</v>
+        <v>315</v>
       </c>
       <c r="P30" s="9"/>
       <c r="Q30" s="10"/>
@@ -5051,15 +5089,17 @@
       <c r="B31" s="1">
         <v>51.27</v>
       </c>
-      <c r="C31" s="1" t="s">
-        <v>317</v>
+      <c r="C31" s="5" t="s">
+        <v>161</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>318</v>
-      </c>
-      <c r="E31" s="1"/>
+        <v>309</v>
+      </c>
+      <c r="E31" s="1">
+        <v>10262368</v>
+      </c>
       <c r="F31" s="1" t="s">
-        <v>53</v>
+        <v>310</v>
       </c>
       <c r="G31" s="1" t="s">
         <v>281</v>
@@ -5068,25 +5108,19 @@
         <v>6</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>319</v>
+        <v>311</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>26</v>
       </c>
       <c r="K31" t="s">
-        <v>43</v>
-      </c>
-      <c r="L31" t="s">
-        <v>489</v>
-      </c>
-      <c r="M31" t="s">
-        <v>99</v>
+        <v>27</v>
       </c>
       <c r="N31" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="O31" s="1" t="s">
-        <v>85</v>
+        <v>193</v>
       </c>
       <c r="P31" s="9"/>
       <c r="Q31" s="10"/>
@@ -5102,44 +5136,36 @@
       <c r="B32" s="1">
         <v>72.58</v>
       </c>
-      <c r="C32" s="1" t="s">
-        <v>312</v>
+      <c r="C32" s="7" t="s">
+        <v>51</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="E32" s="1">
-        <v>10257997</v>
-      </c>
+        <v>307</v>
+      </c>
+      <c r="E32" s="1"/>
       <c r="F32" s="1" t="s">
-        <v>314</v>
+        <v>84</v>
       </c>
       <c r="G32" s="1" t="s">
         <v>281</v>
       </c>
       <c r="H32" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>316</v>
+        <v>308</v>
       </c>
       <c r="J32" s="2" t="s">
         <v>26</v>
       </c>
       <c r="K32" t="s">
-        <v>43</v>
-      </c>
-      <c r="L32" t="s">
-        <v>133</v>
-      </c>
-      <c r="M32" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="N32" t="s">
-        <v>491</v>
-      </c>
-      <c r="O32" s="1" t="s">
-        <v>315</v>
+        <v>493</v>
+      </c>
+      <c r="O32" s="14" t="s">
+        <v>255</v>
       </c>
       <c r="P32" s="9"/>
       <c r="Q32" s="10"/>
@@ -5159,34 +5185,32 @@
         <v>161</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>309</v>
-      </c>
-      <c r="E33" s="1">
-        <v>10262368</v>
-      </c>
+        <v>303</v>
+      </c>
+      <c r="E33" s="1"/>
       <c r="F33" s="1" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="G33" s="1" t="s">
         <v>281</v>
       </c>
       <c r="H33" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="J33" s="2" t="s">
         <v>26</v>
       </c>
       <c r="K33" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="N33" t="s">
-        <v>492</v>
-      </c>
-      <c r="O33" s="1" t="s">
-        <v>193</v>
+        <v>494</v>
+      </c>
+      <c r="O33" s="14" t="s">
+        <v>305</v>
       </c>
       <c r="P33" s="9"/>
       <c r="Q33" s="10"/>
@@ -5202,11 +5226,11 @@
       <c r="B34" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C34" s="7" t="s">
-        <v>51</v>
+      <c r="C34" s="1" t="s">
+        <v>283</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="E34" s="1"/>
       <c r="F34" s="1" t="s">
@@ -5216,10 +5240,10 @@
         <v>281</v>
       </c>
       <c r="H34" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="J34" s="2" t="s">
         <v>26</v>
@@ -5228,10 +5252,10 @@
         <v>27</v>
       </c>
       <c r="N34" t="s">
-        <v>493</v>
-      </c>
-      <c r="O34" s="14" t="s">
-        <v>255</v>
+        <v>495</v>
+      </c>
+      <c r="O34" s="1" t="s">
+        <v>244</v>
       </c>
       <c r="P34" s="9"/>
       <c r="Q34" s="10"/>
@@ -5247,24 +5271,24 @@
       <c r="B35" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C35" s="5" t="s">
-        <v>161</v>
+      <c r="C35" s="1" t="s">
+        <v>298</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="E35" s="1"/>
       <c r="F35" s="1" t="s">
-        <v>304</v>
+        <v>84</v>
       </c>
       <c r="G35" s="1" t="s">
         <v>281</v>
       </c>
       <c r="H35" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="J35" s="2" t="s">
         <v>26</v>
@@ -5272,11 +5296,17 @@
       <c r="K35" t="s">
         <v>43</v>
       </c>
+      <c r="L35" t="s">
+        <v>496</v>
+      </c>
+      <c r="M35" t="s">
+        <v>29</v>
+      </c>
       <c r="N35" t="s">
-        <v>494</v>
-      </c>
-      <c r="O35" s="14" t="s">
-        <v>305</v>
+        <v>497</v>
+      </c>
+      <c r="O35" s="1" t="s">
+        <v>125</v>
       </c>
       <c r="P35" s="9"/>
       <c r="Q35" s="10"/>
@@ -5293,14 +5323,14 @@
         <v>31</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>283</v>
+        <v>149</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>301</v>
+        <v>47</v>
       </c>
       <c r="E36" s="1"/>
       <c r="F36" s="1" t="s">
-        <v>84</v>
+        <v>22</v>
       </c>
       <c r="G36" s="1" t="s">
         <v>281</v>
@@ -5309,7 +5339,7 @@
         <v>8</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="J36" s="2" t="s">
         <v>26</v>
@@ -5317,11 +5347,17 @@
       <c r="K36" t="s">
         <v>27</v>
       </c>
+      <c r="L36" t="s">
+        <v>446</v>
+      </c>
+      <c r="M36" t="s">
+        <v>36</v>
+      </c>
       <c r="N36" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="O36" s="1" t="s">
-        <v>244</v>
+        <v>296</v>
       </c>
       <c r="P36" s="9"/>
       <c r="Q36" s="10"/>
@@ -5338,14 +5374,14 @@
         <v>61.69</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>298</v>
+        <v>39</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="E37" s="1"/>
       <c r="F37" s="1" t="s">
-        <v>84</v>
+        <v>294</v>
       </c>
       <c r="G37" s="1" t="s">
         <v>281</v>
@@ -5354,7 +5390,7 @@
         <v>8</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>300</v>
+        <v>103</v>
       </c>
       <c r="J37" s="2" t="s">
         <v>26</v>
@@ -5362,17 +5398,11 @@
       <c r="K37" t="s">
         <v>43</v>
       </c>
-      <c r="L37" t="s">
-        <v>496</v>
-      </c>
-      <c r="M37" t="s">
-        <v>29</v>
-      </c>
       <c r="N37" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="O37" s="1" t="s">
-        <v>125</v>
+        <v>295</v>
       </c>
       <c r="P37" s="9"/>
       <c r="Q37" s="10"/>
@@ -5389,41 +5419,43 @@
         <v>73.28</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>149</v>
+        <v>289</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E38" s="1"/>
+        <v>290</v>
+      </c>
+      <c r="E38" s="1">
+        <v>10243021</v>
+      </c>
       <c r="F38" s="1" t="s">
-        <v>22</v>
+        <v>53</v>
       </c>
       <c r="G38" s="1" t="s">
         <v>281</v>
       </c>
       <c r="H38" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I38" s="1" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="J38" s="2" t="s">
         <v>26</v>
       </c>
       <c r="K38" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="L38" t="s">
-        <v>446</v>
+        <v>500</v>
       </c>
       <c r="M38" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="N38" t="s">
-        <v>498</v>
-      </c>
-      <c r="O38" s="1" t="s">
-        <v>296</v>
+        <v>501</v>
+      </c>
+      <c r="O38" s="14" t="s">
+        <v>291</v>
       </c>
       <c r="P38" s="9"/>
       <c r="Q38" s="10"/>
@@ -5440,23 +5472,25 @@
         <v>31</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>39</v>
+        <v>285</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>293</v>
-      </c>
-      <c r="E39" s="1"/>
+        <v>286</v>
+      </c>
+      <c r="E39" s="1">
+        <v>10276169</v>
+      </c>
       <c r="F39" s="1" t="s">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="G39" s="1" t="s">
         <v>281</v>
       </c>
       <c r="H39" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>103</v>
+        <v>288</v>
       </c>
       <c r="J39" s="2" t="s">
         <v>26</v>
@@ -5464,11 +5498,17 @@
       <c r="K39" t="s">
         <v>43</v>
       </c>
+      <c r="L39" t="s">
+        <v>446</v>
+      </c>
+      <c r="M39" t="s">
+        <v>36</v>
+      </c>
       <c r="N39" t="s">
-        <v>499</v>
-      </c>
-      <c r="O39" s="1" t="s">
-        <v>295</v>
+        <v>502</v>
+      </c>
+      <c r="O39" s="14" t="s">
+        <v>157</v>
       </c>
       <c r="P39" s="9"/>
       <c r="Q39" s="10"/>
@@ -5485,16 +5525,16 @@
         <v>69.680000000000007</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>290</v>
+        <v>173</v>
       </c>
       <c r="E40" s="1">
-        <v>10243021</v>
+        <v>10262517</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>53</v>
+        <v>84</v>
       </c>
       <c r="G40" s="1" t="s">
         <v>281</v>
@@ -5503,7 +5543,7 @@
         <v>9</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>292</v>
+        <v>284</v>
       </c>
       <c r="J40" s="2" t="s">
         <v>26</v>
@@ -5511,17 +5551,11 @@
       <c r="K40" t="s">
         <v>43</v>
       </c>
-      <c r="L40" t="s">
-        <v>500</v>
-      </c>
-      <c r="M40" t="s">
-        <v>29</v>
-      </c>
       <c r="N40" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="O40" s="14" t="s">
-        <v>291</v>
+        <v>222</v>
       </c>
       <c r="P40" s="9"/>
       <c r="Q40" s="10"/>
@@ -5537,17 +5571,15 @@
       <c r="B41" s="1">
         <v>52.22</v>
       </c>
-      <c r="C41" s="1" t="s">
-        <v>285</v>
+      <c r="C41" s="5" t="s">
+        <v>280</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>286</v>
-      </c>
-      <c r="E41" s="1">
-        <v>10276169</v>
-      </c>
+        <v>65</v>
+      </c>
+      <c r="E41" s="1"/>
       <c r="F41" s="1" t="s">
-        <v>287</v>
+        <v>59</v>
       </c>
       <c r="G41" s="1" t="s">
         <v>281</v>
@@ -5556,7 +5588,7 @@
         <v>9</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="J41" s="2" t="s">
         <v>26</v>
@@ -5571,10 +5603,10 @@
         <v>36</v>
       </c>
       <c r="N41" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="O41" s="14" t="s">
-        <v>157</v>
+        <v>41</v>
       </c>
       <c r="P41" s="9"/>
       <c r="Q41" s="10"/>
@@ -5590,39 +5622,6 @@
       <c r="B42" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C42" s="1" t="s">
-        <v>283</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="E42" s="1">
-        <v>10262517</v>
-      </c>
-      <c r="F42" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="G42" s="1" t="s">
-        <v>281</v>
-      </c>
-      <c r="H42" s="1">
-        <v>9</v>
-      </c>
-      <c r="I42" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="J42" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="K42" t="s">
-        <v>43</v>
-      </c>
-      <c r="N42" t="s">
-        <v>503</v>
-      </c>
-      <c r="O42" s="14" t="s">
-        <v>222</v>
-      </c>
       <c r="P42" s="9"/>
       <c r="Q42" s="10"/>
       <c r="R42" s="11"/>
@@ -5637,44 +5636,6 @@
       <c r="B43" s="1">
         <v>75.91</v>
       </c>
-      <c r="C43" s="5" t="s">
-        <v>280</v>
-      </c>
-      <c r="D43" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="E43" s="1"/>
-      <c r="F43" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="G43" s="1" t="s">
-        <v>281</v>
-      </c>
-      <c r="H43" s="1">
-        <v>9</v>
-      </c>
-      <c r="I43" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="J43" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="K43" t="s">
-        <v>43</v>
-      </c>
-      <c r="L43" t="s">
-        <v>446</v>
-      </c>
-      <c r="M43" t="s">
-        <v>36</v>
-      </c>
-      <c r="N43" t="s">
-        <v>504</v>
-      </c>
-      <c r="O43" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="P43" s="9"/>
       <c r="Q43" s="10"/>
       <c r="R43" s="11"/>
       <c r="Y43" s="13" t="s">
@@ -5682,26 +5643,23 @@
       </c>
     </row>
     <row r="44" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="P44" s="9"/>
       <c r="Q44" s="10"/>
       <c r="R44" s="11"/>
     </row>
     <row r="45" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="Q45" s="10"/>
-      <c r="R45" s="11"/>
     </row>
     <row r="46" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="Q46" s="10"/>
-      <c r="R46" s="11"/>
     </row>
     <row r="47" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="Q47" s="10"/>
     </row>
     <row r="48" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="Q48" s="10"/>
+      <c r="Q48" s="12"/>
     </row>
     <row r="49" spans="17:17" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="Q49" s="10"/>
+      <c r="Q49" s="12"/>
     </row>
     <row r="50" spans="17:17" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="Q50" s="12"/>
@@ -5709,12 +5667,8 @@
     <row r="51" spans="17:17" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="Q51" s="12"/>
     </row>
-    <row r="52" spans="17:17" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="Q52" s="12"/>
-    </row>
-    <row r="53" spans="17:17" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="Q53" s="12"/>
-    </row>
+    <row r="52" spans="17:17" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="53" spans="17:17" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="54" spans="17:17" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="55" spans="17:17" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
@@ -5722,41 +5676,41 @@
     <sortCondition ref="A2:A43"/>
   </sortState>
   <hyperlinks>
-    <hyperlink ref="J43" r:id="rId1" display="https://probullstats.com/loggers/matchup.php?bull=54839&amp;guy=Julio+Cesar+Marques" xr:uid="{7A80C17A-3232-6448-9343-11FC1CD3C297}"/>
-    <hyperlink ref="J42" r:id="rId2" display="https://probullstats.com/loggers/matchup.php?bull=56542&amp;guy=Callum+Miller" xr:uid="{0F2BD59E-A00B-4D4B-8A15-FC0C2FCD8520}"/>
-    <hyperlink ref="J41" r:id="rId3" display="https://probullstats.com/loggers/matchup.php?bull=54130&amp;guy=Trace+Redd" xr:uid="{F4C2835A-438B-0142-98F5-439B5289E417}"/>
-    <hyperlink ref="J40" r:id="rId4" display="https://probullstats.com/loggers/matchup.php?bull=51428&amp;guy=Grayson+Cole" xr:uid="{9F41CA48-CFB7-E246-92DC-10D6692090A4}"/>
-    <hyperlink ref="J39" r:id="rId5" display="https://probullstats.com/loggers/matchup.php?bull=56381&amp;guy=Vinicius+Rodrigues+Pereira" xr:uid="{F733F9C0-F92E-DD40-BD82-74810719B425}"/>
-    <hyperlink ref="J38" r:id="rId6" display="https://probullstats.com/loggers/matchup.php?bull=55806&amp;guy=Ednelio+Rodrigues" xr:uid="{07DD6F14-EB65-2C4E-A591-3E2C378C2A67}"/>
-    <hyperlink ref="J37" r:id="rId7" display="https://probullstats.com/loggers/matchup.php?bull=53419&amp;guy=Mason+Taylor" xr:uid="{864A1DB8-FE2B-5D44-9643-DB818F8A9234}"/>
-    <hyperlink ref="J36" r:id="rId8" display="https://probullstats.com/loggers/matchup.php?bull=56047&amp;guy=Dener+Barbosa" xr:uid="{2AB1932A-11A1-7447-80A6-E02A42B49BB9}"/>
-    <hyperlink ref="J35" r:id="rId9" display="https://probullstats.com/loggers/matchup.php?bull=55809&amp;guy=Ramon+Fiorini" xr:uid="{03F5EABD-CF18-5E42-A0EA-CD3101D51E6C}"/>
-    <hyperlink ref="J34" r:id="rId10" display="https://probullstats.com/loggers/matchup.php?bull=56578&amp;guy=Vinicius+Pinheiro+Correa" xr:uid="{AAF7E716-B51F-5744-80BC-B9D1B3EC32AD}"/>
-    <hyperlink ref="J33" r:id="rId11" display="https://probullstats.com/loggers/matchup.php?bull=56236&amp;guy=Macaulie+Leather" xr:uid="{2021287A-E488-FD4C-B27D-94448D0F15C7}"/>
-    <hyperlink ref="J32" r:id="rId12" display="https://probullstats.com/loggers/matchup.php?bull=51896&amp;guy=Eric+Novoa" xr:uid="{95300F1E-1D61-B745-8FB1-31564488E65C}"/>
-    <hyperlink ref="J31" r:id="rId13" display="https://probullstats.com/loggers/matchup.php?bull=52820&amp;guy=Paulo+Eduardo+Rossetto" xr:uid="{0CEAA190-6ED4-7446-8DB9-0E54B259D446}"/>
-    <hyperlink ref="J30" r:id="rId14" display="https://probullstats.com/loggers/matchup.php?bull=50989&amp;guy=Lucas+Divino" xr:uid="{68EFE952-E1A2-2A43-A2D3-BF22A8D7B3E9}"/>
-    <hyperlink ref="J29" r:id="rId15" display="https://probullstats.com/loggers/matchup.php?bull=54227&amp;guy=Claudio+Montanha+Jr." xr:uid="{3D5353E0-0288-DF4A-9DAE-4F807BED1D54}"/>
-    <hyperlink ref="J28" r:id="rId16" display="https://probullstats.com/loggers/matchup.php?bull=54171&amp;guy=Koltin+Hevalow" xr:uid="{9412B2D9-0C75-C745-978E-773B146B6A20}"/>
-    <hyperlink ref="J27" r:id="rId17" display="https://probullstats.com/loggers/matchup.php?bull=51690&amp;guy=Hudson+Bolton" xr:uid="{B6C892CC-6302-014B-A6F4-C3E51780D547}"/>
-    <hyperlink ref="J26" r:id="rId18" display="https://probullstats.com/loggers/matchup.php?bull=53018&amp;guy=Keyshawn+Whitehorse" xr:uid="{1B7B6F25-EA93-3547-A6A1-883AFE3B0758}"/>
-    <hyperlink ref="J25" r:id="rId19" display="https://probullstats.com/loggers/matchup.php?bull=47941&amp;guy=Brady+Fielder" xr:uid="{F830A1E9-FAD6-9B44-9BDC-71504F789CA3}"/>
-    <hyperlink ref="J24" r:id="rId20" display="https://probullstats.com/loggers/matchup.php?bull=53535&amp;guy=John+Crimber" xr:uid="{33956328-C1EF-D149-9DFA-586EB9743B84}"/>
-    <hyperlink ref="J23" r:id="rId21" display="https://probullstats.com/loggers/matchup.php?bull=49727&amp;guy=Alex+Junior+da+Silva" xr:uid="{FE35623D-353B-0942-AAFF-E0848495E061}"/>
-    <hyperlink ref="J22" r:id="rId22" display="https://probullstats.com/loggers/matchup.php?bull=56540&amp;guy=Luciano+De+Castro" xr:uid="{75E344EB-84EF-E243-BC8E-0F69A94B6B09}"/>
-    <hyperlink ref="J21" r:id="rId23" display="https://probullstats.com/loggers/matchup.php?bull=44656&amp;guy=Mauricio+Gulla+Moreira" xr:uid="{C6F7534C-CF8F-014E-A078-46EDB48E4C40}"/>
-    <hyperlink ref="J20" r:id="rId24" display="https://probullstats.com/loggers/matchup.php?bull=50380&amp;guy=Andy+Guzman" xr:uid="{021B2B21-CA7E-8D47-8345-68AEA1745A23}"/>
-    <hyperlink ref="J19" r:id="rId25" display="https://probullstats.com/loggers/matchup.php?bull=53892&amp;guy=Joao+Ricardo+Vieira" xr:uid="{56F7B948-B1A1-0C48-B431-53B30A3D80A9}"/>
-    <hyperlink ref="J18" r:id="rId26" display="https://probullstats.com/loggers/matchup.php?bull=53319&amp;guy=Thiago+Salgado" xr:uid="{0024AC40-1D64-BC45-BE9C-E6AE555C4C55}"/>
-    <hyperlink ref="J17" r:id="rId27" display="https://probullstats.com/loggers/matchup.php?bull=48315&amp;guy=Daylon+Swearingen" xr:uid="{C7028F27-5A31-EB46-928F-52A417BEA75F}"/>
-    <hyperlink ref="J16" r:id="rId28" display="https://probullstats.com/loggers/matchup.php?bull=54209&amp;guy=Andrew+Alvidrez" xr:uid="{5C697E8D-70AD-F046-AB04-46B464409C3E}"/>
-    <hyperlink ref="J15" r:id="rId29" display="https://probullstats.com/loggers/matchup.php?bull=51949&amp;guy=Jess+Lockwood" xr:uid="{A8987CAE-A15F-4F4C-8921-F7BBB52EF782}"/>
-    <hyperlink ref="J14" r:id="rId30" display="https://probullstats.com/loggers/matchup.php?bull=56577&amp;guy=Daniel+Keeping" xr:uid="{F416108D-A154-9D43-A6ED-1D1060E32985}"/>
-    <hyperlink ref="J13" r:id="rId31" display="https://probullstats.com/loggers/matchup.php?bull=53617&amp;guy=Bob+Mitchell" xr:uid="{93B7C777-B99A-8043-9473-B9BA8A4AF91D}"/>
-    <hyperlink ref="J12" r:id="rId32" display="https://probullstats.com/loggers/matchup.php?bull=55454&amp;guy=Romario+Leite" xr:uid="{1D408E4F-3CA9-514F-89EF-F1CDD9720C41}"/>
-    <hyperlink ref="J11" r:id="rId33" display="https://probullstats.com/loggers/matchup.php?bull=56214&amp;guy=Alex+Cerqueira" xr:uid="{C8A17F1D-296F-E745-9931-F763D38E0160}"/>
-    <hyperlink ref="J10" r:id="rId34" display="https://probullstats.com/loggers/matchup.php?bull=52839&amp;guy=Alan+de+Souza" xr:uid="{92AEEB17-6DB6-E840-B049-1DC988B9269E}"/>
-    <hyperlink ref="J9" r:id="rId35" display="https://probullstats.com/loggers/matchup.php?bull=56035&amp;guy=Cassio+Dias" xr:uid="{CBE38BD9-0AED-8B48-AE5C-A82D5055703F}"/>
+    <hyperlink ref="J41" r:id="rId1" display="https://probullstats.com/loggers/matchup.php?bull=54839&amp;guy=Julio+Cesar+Marques" xr:uid="{7A80C17A-3232-6448-9343-11FC1CD3C297}"/>
+    <hyperlink ref="J40" r:id="rId2" display="https://probullstats.com/loggers/matchup.php?bull=56542&amp;guy=Callum+Miller" xr:uid="{0F2BD59E-A00B-4D4B-8A15-FC0C2FCD8520}"/>
+    <hyperlink ref="J39" r:id="rId3" display="https://probullstats.com/loggers/matchup.php?bull=54130&amp;guy=Trace+Redd" xr:uid="{F4C2835A-438B-0142-98F5-439B5289E417}"/>
+    <hyperlink ref="J38" r:id="rId4" display="https://probullstats.com/loggers/matchup.php?bull=51428&amp;guy=Grayson+Cole" xr:uid="{9F41CA48-CFB7-E246-92DC-10D6692090A4}"/>
+    <hyperlink ref="J37" r:id="rId5" display="https://probullstats.com/loggers/matchup.php?bull=56381&amp;guy=Vinicius+Rodrigues+Pereira" xr:uid="{F733F9C0-F92E-DD40-BD82-74810719B425}"/>
+    <hyperlink ref="J36" r:id="rId6" display="https://probullstats.com/loggers/matchup.php?bull=55806&amp;guy=Ednelio+Rodrigues" xr:uid="{07DD6F14-EB65-2C4E-A591-3E2C378C2A67}"/>
+    <hyperlink ref="J35" r:id="rId7" display="https://probullstats.com/loggers/matchup.php?bull=53419&amp;guy=Mason+Taylor" xr:uid="{864A1DB8-FE2B-5D44-9643-DB818F8A9234}"/>
+    <hyperlink ref="J34" r:id="rId8" display="https://probullstats.com/loggers/matchup.php?bull=56047&amp;guy=Dener+Barbosa" xr:uid="{2AB1932A-11A1-7447-80A6-E02A42B49BB9}"/>
+    <hyperlink ref="J33" r:id="rId9" display="https://probullstats.com/loggers/matchup.php?bull=55809&amp;guy=Ramon+Fiorini" xr:uid="{03F5EABD-CF18-5E42-A0EA-CD3101D51E6C}"/>
+    <hyperlink ref="J32" r:id="rId10" display="https://probullstats.com/loggers/matchup.php?bull=56578&amp;guy=Vinicius+Pinheiro+Correa" xr:uid="{AAF7E716-B51F-5744-80BC-B9D1B3EC32AD}"/>
+    <hyperlink ref="J31" r:id="rId11" display="https://probullstats.com/loggers/matchup.php?bull=56236&amp;guy=Macaulie+Leather" xr:uid="{2021287A-E488-FD4C-B27D-94448D0F15C7}"/>
+    <hyperlink ref="J30" r:id="rId12" display="https://probullstats.com/loggers/matchup.php?bull=51896&amp;guy=Eric+Novoa" xr:uid="{95300F1E-1D61-B745-8FB1-31564488E65C}"/>
+    <hyperlink ref="J29" r:id="rId13" display="https://probullstats.com/loggers/matchup.php?bull=52820&amp;guy=Paulo+Eduardo+Rossetto" xr:uid="{0CEAA190-6ED4-7446-8DB9-0E54B259D446}"/>
+    <hyperlink ref="J28" r:id="rId14" display="https://probullstats.com/loggers/matchup.php?bull=50989&amp;guy=Lucas+Divino" xr:uid="{68EFE952-E1A2-2A43-A2D3-BF22A8D7B3E9}"/>
+    <hyperlink ref="J27" r:id="rId15" display="https://probullstats.com/loggers/matchup.php?bull=54227&amp;guy=Claudio+Montanha+Jr." xr:uid="{3D5353E0-0288-DF4A-9DAE-4F807BED1D54}"/>
+    <hyperlink ref="J26" r:id="rId16" display="https://probullstats.com/loggers/matchup.php?bull=54171&amp;guy=Koltin+Hevalow" xr:uid="{9412B2D9-0C75-C745-978E-773B146B6A20}"/>
+    <hyperlink ref="J25" r:id="rId17" display="https://probullstats.com/loggers/matchup.php?bull=51690&amp;guy=Hudson+Bolton" xr:uid="{B6C892CC-6302-014B-A6F4-C3E51780D547}"/>
+    <hyperlink ref="J24" r:id="rId18" display="https://probullstats.com/loggers/matchup.php?bull=53018&amp;guy=Keyshawn+Whitehorse" xr:uid="{1B7B6F25-EA93-3547-A6A1-883AFE3B0758}"/>
+    <hyperlink ref="J23" r:id="rId19" display="https://probullstats.com/loggers/matchup.php?bull=47941&amp;guy=Brady+Fielder" xr:uid="{F830A1E9-FAD6-9B44-9BDC-71504F789CA3}"/>
+    <hyperlink ref="J22" r:id="rId20" display="https://probullstats.com/loggers/matchup.php?bull=53535&amp;guy=John+Crimber" xr:uid="{33956328-C1EF-D149-9DFA-586EB9743B84}"/>
+    <hyperlink ref="J21" r:id="rId21" display="https://probullstats.com/loggers/matchup.php?bull=49727&amp;guy=Alex+Junior+da+Silva" xr:uid="{FE35623D-353B-0942-AAFF-E0848495E061}"/>
+    <hyperlink ref="J20" r:id="rId22" display="https://probullstats.com/loggers/matchup.php?bull=56540&amp;guy=Luciano+De+Castro" xr:uid="{75E344EB-84EF-E243-BC8E-0F69A94B6B09}"/>
+    <hyperlink ref="J19" r:id="rId23" display="https://probullstats.com/loggers/matchup.php?bull=44656&amp;guy=Mauricio+Gulla+Moreira" xr:uid="{C6F7534C-CF8F-014E-A078-46EDB48E4C40}"/>
+    <hyperlink ref="J18" r:id="rId24" display="https://probullstats.com/loggers/matchup.php?bull=50380&amp;guy=Andy+Guzman" xr:uid="{021B2B21-CA7E-8D47-8345-68AEA1745A23}"/>
+    <hyperlink ref="J17" r:id="rId25" display="https://probullstats.com/loggers/matchup.php?bull=53892&amp;guy=Joao+Ricardo+Vieira" xr:uid="{56F7B948-B1A1-0C48-B431-53B30A3D80A9}"/>
+    <hyperlink ref="J16" r:id="rId26" display="https://probullstats.com/loggers/matchup.php?bull=53319&amp;guy=Thiago+Salgado" xr:uid="{0024AC40-1D64-BC45-BE9C-E6AE555C4C55}"/>
+    <hyperlink ref="J15" r:id="rId27" display="https://probullstats.com/loggers/matchup.php?bull=48315&amp;guy=Daylon+Swearingen" xr:uid="{C7028F27-5A31-EB46-928F-52A417BEA75F}"/>
+    <hyperlink ref="J14" r:id="rId28" display="https://probullstats.com/loggers/matchup.php?bull=54209&amp;guy=Andrew+Alvidrez" xr:uid="{5C697E8D-70AD-F046-AB04-46B464409C3E}"/>
+    <hyperlink ref="J13" r:id="rId29" display="https://probullstats.com/loggers/matchup.php?bull=51949&amp;guy=Jess+Lockwood" xr:uid="{A8987CAE-A15F-4F4C-8921-F7BBB52EF782}"/>
+    <hyperlink ref="J12" r:id="rId30" display="https://probullstats.com/loggers/matchup.php?bull=56577&amp;guy=Daniel+Keeping" xr:uid="{F416108D-A154-9D43-A6ED-1D1060E32985}"/>
+    <hyperlink ref="J11" r:id="rId31" display="https://probullstats.com/loggers/matchup.php?bull=53617&amp;guy=Bob+Mitchell" xr:uid="{93B7C777-B99A-8043-9473-B9BA8A4AF91D}"/>
+    <hyperlink ref="J10" r:id="rId32" display="https://probullstats.com/loggers/matchup.php?bull=55454&amp;guy=Romario+Leite" xr:uid="{1D408E4F-3CA9-514F-89EF-F1CDD9720C41}"/>
+    <hyperlink ref="J9" r:id="rId33" display="https://probullstats.com/loggers/matchup.php?bull=56214&amp;guy=Alex+Cerqueira" xr:uid="{C8A17F1D-296F-E745-9931-F763D38E0160}"/>
+    <hyperlink ref="J8" r:id="rId34" display="https://probullstats.com/loggers/matchup.php?bull=52839&amp;guy=Alan+de+Souza" xr:uid="{92AEEB17-6DB6-E840-B049-1DC988B9269E}"/>
+    <hyperlink ref="J7" r:id="rId35" display="https://probullstats.com/loggers/matchup.php?bull=56035&amp;guy=Cassio+Dias" xr:uid="{CBE38BD9-0AED-8B48-AE5C-A82D5055703F}"/>
     <hyperlink ref="J6" r:id="rId36" display="https://probullstats.com/loggers/matchup.php?bull=45633&amp;guy=Marco+Rizzo" xr:uid="{E3412961-8175-8742-B289-193D41E6BF56}"/>
     <hyperlink ref="J5" r:id="rId37" display="https://probullstats.com/loggers/matchup.php?bull=53773&amp;guy=Bruno+Carvalho" xr:uid="{4833B6B6-D785-CD4D-AD7C-80D2611062CB}"/>
     <hyperlink ref="J4" r:id="rId38" display="https://probullstats.com/loggers/matchup.php?bull=52929&amp;guy=Kase+Hitt" xr:uid="{7AC8DC2D-E077-B34C-A679-937E544383EF}"/>

--- a/data/pbr_matchups_full.xlsx
+++ b/data/pbr_matchups_full.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cameronyoung/Desktop/rankratings:/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE1FF750-F7C3-3E48-A4F7-A2C2C175D1AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F587C88-071F-EF47-A363-FFE725658C9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="740" windowWidth="30240" windowHeight="18900" xr2:uid="{63502F5A-9950-074D-B0A2-89EF4471630B}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1053" uniqueCount="506">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1044" uniqueCount="506">
   <si>
     <t>Bull Power</t>
   </si>
@@ -3665,7 +3665,7 @@
         <v>72</v>
       </c>
       <c r="P3" s="9">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="Q3" s="10">
         <v>0</v>
@@ -3724,13 +3724,13 @@
         <v>34</v>
       </c>
       <c r="P4" s="9">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="Q4" s="10">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="R4" s="11">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="Y4" s="13" t="s">
         <v>407</v>
@@ -3782,15 +3782,9 @@
       <c r="O5" s="14" t="s">
         <v>120</v>
       </c>
-      <c r="P5" s="9">
-        <v>45</v>
-      </c>
-      <c r="Q5" s="10">
-        <v>45</v>
-      </c>
-      <c r="R5" s="11">
-        <v>90</v>
-      </c>
+      <c r="P5" s="9"/>
+      <c r="Q5" s="10"/>
+      <c r="R5" s="11"/>
       <c r="Y5" s="13" t="s">
         <v>408</v>
       </c>
@@ -3841,15 +3835,9 @@
       <c r="O6" s="14" t="s">
         <v>131</v>
       </c>
-      <c r="P6" s="9" t="s">
-        <v>505</v>
-      </c>
-      <c r="Q6" s="10" t="s">
-        <v>505</v>
-      </c>
-      <c r="R6" s="11" t="s">
-        <v>505</v>
-      </c>
+      <c r="P6" s="9"/>
+      <c r="Q6" s="10"/>
+      <c r="R6" s="11"/>
       <c r="Y6" s="13" t="s">
         <v>409</v>
       </c>
@@ -3935,15 +3923,9 @@
       <c r="O8" s="1" t="s">
         <v>383</v>
       </c>
-      <c r="P8" s="9" t="s">
-        <v>505</v>
-      </c>
-      <c r="Q8" s="10" t="s">
-        <v>505</v>
-      </c>
-      <c r="R8" s="11" t="s">
-        <v>505</v>
-      </c>
+      <c r="P8" s="9"/>
+      <c r="Q8" s="10"/>
+      <c r="R8" s="11"/>
       <c r="Y8" s="13"/>
     </row>
     <row r="9" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -4037,15 +4019,9 @@
       <c r="O10" s="1" t="s">
         <v>379</v>
       </c>
-      <c r="P10" s="9" t="s">
-        <v>505</v>
-      </c>
-      <c r="Q10" s="10" t="s">
-        <v>505</v>
-      </c>
-      <c r="R10" s="11" t="s">
-        <v>505</v>
-      </c>
+      <c r="P10" s="9"/>
+      <c r="Q10" s="10"/>
+      <c r="R10" s="11"/>
       <c r="Y10" s="13" t="s">
         <v>411</v>
       </c>

--- a/data/pbr_matchups_full.xlsx
+++ b/data/pbr_matchups_full.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cameronyoung/Desktop/rankratings:/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F587C88-071F-EF47-A363-FFE725658C9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{648AA65A-D326-8341-AAC6-B88443AC2040}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="740" windowWidth="30240" windowHeight="18900" xr2:uid="{63502F5A-9950-074D-B0A2-89EF4471630B}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1044" uniqueCount="506">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1041" uniqueCount="505">
   <si>
     <t>Bull Power</t>
   </si>
@@ -3010,9 +3010,6 @@
   </si>
   <si>
     <t>&lt;h2&gt;Rider&lt;/h2&gt;&lt;p&gt;&lt;strong&gt;Career:&amp;nbsp;&lt;/strong&gt;Career: 127 for 330 - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;38.48%&lt;/em&gt;&lt;/span&gt; - Rider Rating: *.269&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Season:&amp;nbsp;&lt;/strong&gt;Rank&amp;nbsp;&lt;span style="color: #ff0000;"&gt;12&lt;/span&gt; (27 for 69 - &lt;em&gt;39.1%&lt;/em&gt;)&lt;em&gt;&lt;br /&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Points:&amp;nbsp;&lt;/strong&gt;400.00 pts &lt;span style="color: #ff0000;"&gt;&lt;em&gt;(-492.5)&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Earnings:&amp;nbsp;&lt;/strong&gt;&lt;span style="color: #008000;"&gt;&lt;em&gt;$126,110.26&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Potential&lt;/strong&gt;:&amp;nbsp;82.77 to 88.77 points&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;&lt;span style="text-decoration: underline;"&gt;&lt;strong&gt;Bull&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;ALL:&lt;/strong&gt; 9 outs 0 rides - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;100%&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;em&gt;&lt;span style="color: #ff0000;"&gt;*No Previous Matchups&lt;/span&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t>rr</t>
   </si>
 </sst>
 </file>
@@ -3607,15 +3604,9 @@
       <c r="O2" s="14" t="s">
         <v>141</v>
       </c>
-      <c r="P2" s="9" t="s">
-        <v>505</v>
-      </c>
-      <c r="Q2" s="10" t="s">
-        <v>505</v>
-      </c>
-      <c r="R2" s="11" t="s">
-        <v>505</v>
-      </c>
+      <c r="P2" s="9"/>
+      <c r="Q2" s="10"/>
+      <c r="R2" s="11"/>
       <c r="Y2" s="13" t="s">
         <v>405</v>
       </c>
@@ -3664,15 +3655,9 @@
       <c r="O3" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="P3" s="9">
-        <v>43</v>
-      </c>
-      <c r="Q3" s="10">
-        <v>0</v>
-      </c>
-      <c r="R3" s="11">
-        <v>0</v>
-      </c>
+      <c r="P3" s="9"/>
+      <c r="Q3" s="10"/>
+      <c r="R3" s="11"/>
       <c r="Y3" s="13" t="s">
         <v>406</v>
       </c>
@@ -3723,15 +3708,9 @@
       <c r="O4" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="P4" s="9">
-        <v>35</v>
-      </c>
-      <c r="Q4" s="10">
-        <v>45</v>
-      </c>
-      <c r="R4" s="11">
-        <v>80</v>
-      </c>
+      <c r="P4" s="9"/>
+      <c r="Q4" s="10"/>
+      <c r="R4" s="11"/>
       <c r="Y4" s="13" t="s">
         <v>407</v>
       </c>

--- a/data/pbr_matchups_full.xlsx
+++ b/data/pbr_matchups_full.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cameronyoung/Desktop/rankratings:/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{648AA65A-D326-8341-AAC6-B88443AC2040}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62066AF2-9A07-AE48-B370-0938E637B16F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="30240" windowHeight="18900" xr2:uid="{63502F5A-9950-074D-B0A2-89EF4471630B}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17640" xr2:uid="{63502F5A-9950-074D-B0A2-89EF4471630B}"/>
   </bookViews>
   <sheets>
     <sheet name="Tacoma Day 1" sheetId="2" r:id="rId1"/>
@@ -3822,7 +3822,9 @@
       </c>
     </row>
     <row r="7" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="1"/>
+      <c r="A7" s="1">
+        <v>5</v>
+      </c>
       <c r="B7" s="1"/>
       <c r="C7" s="1" t="s">
         <v>385</v>
@@ -3861,7 +3863,9 @@
       <c r="Y7" s="13"/>
     </row>
     <row r="8" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="1"/>
+      <c r="A8" s="1">
+        <v>6</v>
+      </c>
       <c r="B8" s="1"/>
       <c r="C8" s="1" t="s">
         <v>382</v>

--- a/data/pbr_matchups_full.xlsx
+++ b/data/pbr_matchups_full.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cameronyoung/Desktop/rankratings:/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62066AF2-9A07-AE48-B370-0938E637B16F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E542172-B9BF-B841-ABEE-F33EC6506472}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17640" xr2:uid="{63502F5A-9950-074D-B0A2-89EF4471630B}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17580" xr2:uid="{63502F5A-9950-074D-B0A2-89EF4471630B}"/>
   </bookViews>
   <sheets>
     <sheet name="Tacoma Day 1" sheetId="2" r:id="rId1"/>
@@ -3604,9 +3604,15 @@
       <c r="O2" s="14" t="s">
         <v>141</v>
       </c>
-      <c r="P2" s="9"/>
-      <c r="Q2" s="10"/>
-      <c r="R2" s="11"/>
+      <c r="P2" s="9">
+        <v>36</v>
+      </c>
+      <c r="Q2" s="10">
+        <v>0</v>
+      </c>
+      <c r="R2" s="11">
+        <v>0</v>
+      </c>
       <c r="Y2" s="13" t="s">
         <v>405</v>
       </c>
@@ -3655,9 +3661,15 @@
       <c r="O3" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="P3" s="9"/>
-      <c r="Q3" s="10"/>
-      <c r="R3" s="11"/>
+      <c r="P3" s="9">
+        <v>42</v>
+      </c>
+      <c r="Q3" s="10">
+        <v>0</v>
+      </c>
+      <c r="R3" s="11">
+        <v>0</v>
+      </c>
       <c r="Y3" s="13" t="s">
         <v>406</v>
       </c>
@@ -3708,9 +3720,15 @@
       <c r="O4" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="P4" s="9"/>
-      <c r="Q4" s="10"/>
-      <c r="R4" s="11"/>
+      <c r="P4" s="9">
+        <v>44</v>
+      </c>
+      <c r="Q4" s="10">
+        <v>44</v>
+      </c>
+      <c r="R4" s="11">
+        <v>88</v>
+      </c>
       <c r="Y4" s="13" t="s">
         <v>407</v>
       </c>
@@ -3761,9 +3779,15 @@
       <c r="O5" s="14" t="s">
         <v>120</v>
       </c>
-      <c r="P5" s="9"/>
-      <c r="Q5" s="10"/>
-      <c r="R5" s="11"/>
+      <c r="P5" s="9">
+        <v>28</v>
+      </c>
+      <c r="Q5" s="10">
+        <v>32</v>
+      </c>
+      <c r="R5" s="11">
+        <v>60</v>
+      </c>
       <c r="Y5" s="13" t="s">
         <v>408</v>
       </c>

--- a/data/pbr_matchups_full.xlsx
+++ b/data/pbr_matchups_full.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cameronyoung/Desktop/rankratings:/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E542172-B9BF-B841-ABEE-F33EC6506472}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{659596AC-5E83-1B4E-B368-E8E3D51E27A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17580" xr2:uid="{63502F5A-9950-074D-B0A2-89EF4471630B}"/>
   </bookViews>
@@ -3604,15 +3604,9 @@
       <c r="O2" s="14" t="s">
         <v>141</v>
       </c>
-      <c r="P2" s="9">
-        <v>36</v>
-      </c>
-      <c r="Q2" s="10">
-        <v>0</v>
-      </c>
-      <c r="R2" s="11">
-        <v>0</v>
-      </c>
+      <c r="P2" s="9"/>
+      <c r="Q2" s="10"/>
+      <c r="R2" s="11"/>
       <c r="Y2" s="13" t="s">
         <v>405</v>
       </c>
@@ -3661,15 +3655,9 @@
       <c r="O3" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="P3" s="9">
-        <v>42</v>
-      </c>
-      <c r="Q3" s="10">
-        <v>0</v>
-      </c>
-      <c r="R3" s="11">
-        <v>0</v>
-      </c>
+      <c r="P3" s="9"/>
+      <c r="Q3" s="10"/>
+      <c r="R3" s="11"/>
       <c r="Y3" s="13" t="s">
         <v>406</v>
       </c>
@@ -3720,15 +3708,9 @@
       <c r="O4" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="P4" s="9">
-        <v>44</v>
-      </c>
-      <c r="Q4" s="10">
-        <v>44</v>
-      </c>
-      <c r="R4" s="11">
-        <v>88</v>
-      </c>
+      <c r="P4" s="9"/>
+      <c r="Q4" s="10"/>
+      <c r="R4" s="11"/>
       <c r="Y4" s="13" t="s">
         <v>407</v>
       </c>
@@ -3779,15 +3761,9 @@
       <c r="O5" s="14" t="s">
         <v>120</v>
       </c>
-      <c r="P5" s="9">
-        <v>28</v>
-      </c>
-      <c r="Q5" s="10">
-        <v>32</v>
-      </c>
-      <c r="R5" s="11">
-        <v>60</v>
-      </c>
+      <c r="P5" s="9"/>
+      <c r="Q5" s="10"/>
+      <c r="R5" s="11"/>
       <c r="Y5" s="13" t="s">
         <v>408</v>
       </c>

--- a/data/pbr_matchups_full.xlsx
+++ b/data/pbr_matchups_full.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cameronyoung/Desktop/rankratings:/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{659596AC-5E83-1B4E-B368-E8E3D51E27A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6E3A385-4733-9143-B56C-11597A28A7DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17580" xr2:uid="{63502F5A-9950-074D-B0A2-89EF4471630B}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1041" uniqueCount="505">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1052" uniqueCount="467">
   <si>
     <t>Bull Power</t>
   </si>
@@ -1332,1506 +1332,6 @@
     <t>Bull 22.00%</t>
   </si>
   <si>
-    <t>Eduardo Aparecido on 567 Body Roc (PGAO)
-Qualified Ride Probability: 42.3% (confidence 10 of 10)
-Ride Score Potential: 83.15 to 89.15 points
-Eduardo Aparecido Riding Hand: Right
-Career: 496 for 1134 - 43.74% - Rider Rating: *.360
-Short Rounds: 53 for 156 - 33.97%
-Current Streak: 5 / 15 - 33.33%
-PBR Current Season: Rank: 30 (31 for 72 - 43.1%) 189.00 pts (-703.5) - $133,872.04
-PBR Points Per Out: 3 - Points Per QR: 6
-vs. Left: 121-231 (34.38%) -- vs. Right: 238-178 (57.21%) -- vs. ?: 18-50 (26.47%) -- +22.83%/13.47% RIGHT
-567 Body Roc - PBS -
-Power Rating: 66.79
-ALL: 31 outs 13 rides - 58.06%
-UTB: 17 outs 10 rides - 41.18%
-vs. Left:  8-10 - 44.44%
-vs. Right: 6-3 - 66.67%
-vs. Top:   8-10 - 44.44%
-Riding Hand Advantage: LEFT (22.00%)
-Previous Outs for 567 Body Roc
-Event	Level	Matchup	Score	Marks	Time	Notes
-Fort Worth Mar '26	PBR	Blake Geibel	-	21.40 - 21.40	2.62	*
-Bucktown Feb '26	OPEN	Riggs Caldwell	-	21.75 - 21.75	3.03	*
-Milwaukee Jan '26	PBR	* Keyshawn Whitehorse	-	20.90 - 21.15	3.68	*
-Nashville Aug '25	PBR	* Daylon Swearingen	-	19.75 - 18.75	7.46	*
-Fort Worth Jul '25	PBR	Damiao Soares	82.50	20.50 - 20.00	8.00	*
-Oklahoma City Jul '25	PBR	Miguel de Jesus	87.00	21.25 - 21.25	8.00	*
-Rocksprings Jun '25	PBR	Chance Lopez	-	21.50 - 21.50	3.19	*
-Rocksprings Jun '25	PBR	Douglas Lino de Souza	-	21.00 - 21.50	1.97	*
-Palm Springs Mar '25	PBR	* Derek Kolbaba	88.25	21.50 - 21.50	8.00	*
-Salt Lake City Feb '25	PBR	* Koltin Hevalow	87.75	21.25 - 21.50	8.00	*
-Fort Worth Jan '25	PBR	* Ezekiel Mitchell	86.25	21.00 - 21.00	8.00	*
-Denver Jan '25	PBR	Alex Junior da Silva	78.50	20.00 - 19.50	8.00	*
-Denver Jan '25	PBR	* Cole Melancon	-	21.00 - 20.00	6.09	*
-Wichita Dec '24	PBR	* Luciano De Castro	87.00	21.00 - 21.50	8.00	*
-St. Louis Dec '24	PBR	* Cort McFadden	86.25	21.00 - 20.75	8.00	*
-Previous Matchups at probability 0.423
-Rider Count	88
-Avg Rider Rating	.267
-Total Outs	127
-Qualified Rides	65
-Riding %	51.18%
-87+ points	18.11%</t>
-  </si>
-  <si>
-    <t>Manoelito de Souza Junior on 7030 After Hours (XVJB)
-Qualified Ride Probability: 15.6% (confidence 7 of 10)
-Ride Score Potential: 81.86 to 87.86 points
-Manoelito de Souza Junior Riding Hand: Left
-Career: 112 for 417 - 26.86% - Rider Rating: *.202
-Short Rounds: 12 for 60 - 20%
-Current Streak: 1 / 15 - 6.67%
-PBR Current Season: Rank: 35 (6 for 28 - 21.4%) 112.00 pts (-780.5) - $18,250.00
-PBR Points Per Out: 4 - Points Per QR: 19
-vs. Left: 63-83 (43.15%) -- vs. Right: 9-90 (9.09%) -- vs. ?: 13-53 (19.7%) -- +34.06%/16.29% LEFT
-7030 After Hours - PBS -
-Power Rating: 41.71
-ALL: 7 outs 1 rides - 85.71%
-vs. Left:  4-0 - 100.00%
-vs. Right: 2-1 - 66.67%
-vs. Top:   0-0 - 0.00%
-Riding Hand Advantage: UNKNOWN (0.00%)
-Previous Outs for 7030 After Hours
-Event	Level	Matchup	Score	Marks	Time	Notes
-Paris Jul '23	PBR	Laramie Craigen	-	-	-	RR foul
-Fort Worth Aug '22	PBR	Davi Henrique de Lima	-	17.00 - 19.50	6.22	*
-Paris Jul '22	PBR	Levi Hershberger	-	21.50 - 21.00	4.92	*
-Casper Apr '22	PBR	Cole Skender	82.50	20.00 - 20.00	8.00	*
-Knoxville Feb '22	PBR	Colt Robinson	-	21.50 - 21.00	7.10	*
-Memphis Feb '22	PBR	Thor Hoefer II	-	22.00 - 21.50	2.37	*
-North Charleston Feb '22	PBR	Casey Roberts	-	21.50 - 21.00	4.50	*
-Jacksonville Jan '22	PBR	Quentin Vaught	-	21.00 - 21.50	4.75	*
-Previous Matchups at probability 0.156
-Rider Count	257
-Avg Rider Rating	.111
-Total Outs	346
-Qualified Rides	45
-Riding %	13.01%
-87+ points	4.34%</t>
-  </si>
-  <si>
-    <t>Kase Hitt on 937 Whacky Wizard (PPHT)
-Qualified Ride Probability: 24.9% (confidence 7 of 10)
-Ride Score Potential: 83.07 to 89.07 points
-Kase Hitt Riding Hand: Left
-Career: 94 for 332 - 28.31% - Rider Rating: .179
-Short Rounds: 6 for 23 - 26.09%
-Current Streak: 4 / 15 - 26.67%
-PBR Current Season: Rank: 33 (16 for 53 - 30.2%) 137.00 pts (-755.5) - $49,767.31
-PBR Points Per Out: 3 - Points Per QR: 9
-vs. Left: 40-59 (40.4%) -- vs. Right: 15-81 (15.63%) -- vs. ?: 17-28 (37.78%) -- +24.77%/12.09% LEFT
-937 Whacky Wizard - PBS - 10230319
-Power Rating: 58.27
-ALL: 7 outs 1 rides - 85.71%
-vs. Left:  2-0 - 100.00%
-vs. Right: 3-1 - 75.00%
-vs. Top:   1-1 - 50.00%
-Riding Hand Advantage: UNKNOWN (0.00%)
-Previous Outs for 937 Whacky Wizard
-Event	Level	Matchup	Score	Marks	Time	Notes
-Fort Worth Mar '26	PBR	Eikson Pereira	-	21.20 - 20.80	7.58	*
-Fort Worth Jul '25	PBR	Tuff Morgan	-	20.50 - 20.00	2.81	*
-Fort Worth Feb '25	PBR	Rogerio Venancio	-	19.00 - 19.50	6.69	*
-Fort Worth Sep '24	PBR	Callum Miller	-	21.50 - 21.00	4.00	*
-Anaheim Sep '24	PBR	* Dawson Branton	-	22.00 - 21.75	5.20	*
-Anaheim Sep '24	PBR	Grayson Cole	-	22.00 - 21.75	3.13	*
-Fort Lauderdale Aug '24	PBR	* Keyshawn Whitehorse	89.00	21.25 - 22.00	8.00	*
-Previous Matchups at probability 0.249
-Rider Count	264
-Avg Rider Rating	.174
-Total Outs	411
-Qualified Rides	91
-Riding %	22.14%
-87+ points	3.41%</t>
-  </si>
-  <si>
-    <t>Bruno Carvalho on 128J Love County (PGAO)
-Qualified Ride Probability: 46.7% (confidence 9 of 10)
-Ride Score Potential: 83.5 to 89.5 points
-Bruno Carvalho Riding Hand: Left
-Career: 70 for 219 - 31.96% - Rider Rating: *.208
-Short Rounds: 6 for 22 - 27.27%
-Current Streak: 4 / 15 - 26.67%
-PBR Current Season: Rank: 42 (9 for 34 - 26.5%) 71.50 pts (-821) - $30,778.26
-PBR Points Per Out: 2 - Points Per QR: 8
-vs. Left: 33-33 (50%) -- vs. Right: 3-41 (6.82%) -- vs. ?: 10-24 (29.41%) -- +43.18%/18.04% LEFT
-128J Love County - PBS - 10256903
-Power Rating: 48.73
-ALL: 17 outs 9 rides - 47.06%
-UTB: 7 outs 5 rides - 28.57%
-vs. Left:  2-6 - 25.00%
-vs. Right: 6-3 - 66.67%
-vs. Top:   1-8 - 11.11%
-Riding Hand Advantage: LEFT (42.00%)
-Previous Outs for 128J Love County
-Event	Level	Matchup	Score	Marks	Time	Notes
-Cleburne Mar '26	OPEN	* Qynn Andersen	86.60	21.05 - 21.05	8.00	*
-Fort Worth Mar '26	PBR	Tyler Villarreal	-	21.30 - 21.10	2.59	*
-Bucktown Feb '26	OPEN	* Wacey Schalla	85.00	20.50 - 20.50	8.00	*
-Milwaukee Jan '26	PBR	Alison dos Santos	85.45	20.90 - 20.85	8.00	*
-Houma Jan '26	OPEN	* Vinicius Pinheiro Correa	-	20.60 - 20.60	4.09	*
-Granbury Nov '25	OPEN	* Alex Cerqueira	87.50	21.28 - 21.28	8.00	*
-Kansas City Oct '25	PBR	Miguel de Jesus	-	21.25 - 21.00	7.76	*
-Fort Worth Sep '25	PBR	* John Crimber	86.50	20.75 - 20.75	8.00	*
-Anaheim Sep '25	PBR	* Jess Lockwood	89.00	21.50 - 21.50	8.00	*
-Anaheim Sep '25	PBR	* John Crimber	88.25	21.00 - 21.00	8.00	*
-Fort Worth Jun '25	PBR	* Guilherme Valleiras	86.50	21.00 - 21.50	8.00	*
-Decatur May '25	PBR	Leonardo Lima	-	21.00 - 21.50	1.25	*
-Grand Forks Apr '25	PBR	Zane Cook	-	21.00 - 21.00	2.22	*
-Little Rock Mar '25	PBR	* Koltin Hevalow	84.75	20.75 - 21.00	8.00	*
-Little Rock Mar '25	PBR	Trace Redd	-	21.75 - 22.00	3.72	*
-Previous Matchups at probability 0.467
-Rider Count	63
-Avg Rider Rating	.279
-Total Outs	85
-Qualified Rides	42
-Riding %	49.41%
-87+ points	20%</t>
-  </si>
-  <si>
-    <t>Marco Rizzo on 54E Carlos Danger (TFRS)
-Qualified Ride Probability: 38.5% (confidence 9 of 10)
-Ride Score Potential: 82.79 to 88.79 points
-Marco Rizzo Riding Hand: Right
-Career: 62 for 178 - 34.83% - Rider Rating: *.215
-Short Rounds: 4 for 23 - 17.39%
-Current Streak: 6 / 15 - 40.00%
-PBR Current Season: Rank: 9 (27 for 72 - 37.5%) 405.00 pts (-487.5) - $143,765.82
-PBR Points Per Out: 6 - Points Per QR: 15
-vs. Left: 9-37 (19.57%) -- vs. Right: 30-39 (43.48%) -- vs. ?: 8-15 (34.78%) -- +23.91%/8.65% RIGHT
-54E Carlos Danger - PBS - 10215145
-Power Rating: 68.94
-ALL: 24 outs 7 rides - 70.83%
-UTB: 12 outs 4 rides - 66.67%
-vs. Left:  6-2 - 75.00%
-vs. Right: 8-5 - 61.54%
-vs. Top:   8-6 - 57.14%
-Riding Hand Advantage: RIGHT (13.00%)
-Previous Outs for 54E Carlos Danger
-Event	Level	Matchup	Score	Marks	Time	Notes
-Sacramento Jan '26	PBR	Elijah Jennings	84.40	20.40 - 20.70	8.00	*
-Waco Oct '25	PRCA	Gavan Hauck	-	22.50 - 20.50	2.58	*
-Eagle Jul '25	PRCA	Colton Clymer	-	23.00 - 23.00	2.45	*
-Fort Collins Jul '25	PBR	* Sandro Batista	83.50	20.00 - 20.50	8.00	*
-Evergreen Jun '25	PRCA	Adam Cook	-	22.00 - 19.00	4.00	(nt)
-Evergreen Jun '25	PRCA	Cody Wooldridge	-	-	4.00	(nm)(nt)
-Nampa Apr '25	PBR	* Ezekiel Mitchell	-	-	-	RR foul (head rope)
-Fort Worth Mar '25	PBR	Wallace Vieira de Oliveira	-	-	-	RR foul
-Billings Apr '24	PBR	* Silvano Alves	-	19.25 - 20.00	0.09	*
-Fort Worth Mar '24	PBR	* Paulo Eduardo Rossetto	-	21.00 - 20.50	4.31	*
-Fort Worth Mar '24	PBR	* Leandro Machado	83.00	21.00 - 20.00	8.00	*
-Fort Worth Feb '24	PBR	* Cassio Dias	-	-	-	RR foul
-Fort Worth Feb '24	PBR	Bruno Jose Barros	-	-	-	DQ chute
-Fort Worth Jan '24	PBR	Leonardo Lima	-	21.00 - 20.00	2.24	*
-Fort Worth Dec '23	PBR	Cody McCandless	-	20.50 - 21.00	5.86	*
-Previous Matchups at probability 0.385
-Rider Count	133
-Avg Rider Rating	.236
-Total Outs	193
-Qualified Rides	75
-Riding %	38.86%
-87+ points	12.95%</t>
-  </si>
-  <si>
-    <t>Cassio Dias on 012 Crockett (BMJM)
-Qualified Ride Probability: 37.1% (confidence 6 of 10)
-Ride Score Potential: 84.77 to 90.77 points
-Cassio Dias Riding Hand: Right
-Career: 125 for 249 - 50.2% - Rider Rating: *.410
-Short Rounds: 18 for 32 - 56.25%
-Current Streak: 3 / 15 - 20.00%
-PBR Current Season: Rank: 19 (13 for 45 - 28.9%) 295.50 pts (-597) - $98,807.28
-PBR Points Per Out: 7 - Points Per QR: 23
-vs. Left: 23-40 (36.51%) -- vs. Right: 79-44 (64.23%) -- vs. ?: 12-16 (42.86%) -- +27.72%/14.03% RIGHT
-012 Crockett PBS
-no compiled stats
-Previous Outs for 012 Crockett
-Event	Level	Matchup	Score	Marks	Time	Notes
-Billings Apr '26	PBR	* Julio Cesar Marques	83.15	20.80 - 20.90	8.00	*
-Belton Feb '26	OPEN	Jeferson Silva	-	20.98 - 20.98	5.97	*
-Perry Feb '26	PRCA	Cooper Caldwell	91.00	23.00 - 22.00	8.00	*
-Previous Matchups at probability 0.371
-Rider Count	140
-Avg Rider Rating	.235
-Total Outs	204
-Qualified Rides	86
-Riding %	42.16%
-87+ points	8.82%</t>
-  </si>
-  <si>
-    <t>Alan de Souza on 933G Gene's Best (BMJM)
-Qualified Ride Probability: 36.8% (confidence 10 of 10)
-Ride Score Potential: 82.98 to 88.98 points
-Alan de Souza Riding Hand: Right
-Career: 211 for 397 - 53.15% - Rider Rating: *.339
-Short Rounds: 24 for 48 - 50%
-Current Streak: 4 / 15 - 26.67%
-PBR Current Season: Rank: 31 (35 for 70 - 50%) 178.00 pts (-714.5) - $102,574.30
-PBR Points Per Out: 3 - Points Per QR: 5
-vs. Left: 38-62 (38%) -- vs. Right: 109-70 (60.89%) -- vs. ?: 22-15 (59.46%) -- +22.89%/7.74% RIGHT
-933G Gene's Best - PBS - 10229185
-Power Rating: 71.00
-ALL: 27 outs 7 rides - 74.07%
-UTB: 13 outs 7 rides - 46.15%
-vs. Left:  4-6 - 40.00%
-vs. Right: 14-1 - 93.33%
-vs. Top:   9-6 - 60.00%
-Riding Hand Advantage: LEFT (53.00%)
-Previous Outs for 933G Gene's Best
-Event	Level	Matchup	Score	Marks	Time	Notes
-Billings Apr '26	PBR	* Jess Lockwood	88.45	21.90 - 21.20	8.00	*
-Perry Feb '26	PRCA	* Hayes Weight	-	12.00 - 12.00	4.00	(nmb)(nt)
-Tulsa Jan '26	PBR	Damien Krushall	-	21.00 - 20.90	1.60	*
-Bangor Jan '26	PBR	Claudio Rogerio Alves Junior	-	21.60 - 21.80	6.41	*
-Bangor Jan '26	PBR	Grayson Cole	-	21.80 - 22.00	4.21	*
-Green Bay Sep '25	PBR	* Kyler Oliver	-	21.00 - 21.00	6.12	*
-Kansas City Apr '25	PBR	Thomas Hudson	-	19.50 - 16.50	-	RR inf
-Ardmore Mar '25	PRCAX	Jacob Carige	-	21.50 - 21.00	4.40	*
-Austin Mar '25	PRCA	Maverick Potter	-	-	-	RR foul
-Little Rock Mar '25	PBR	* Austin Richardson	-	21.25 - 21.50	6.31	*
-Jacksonville Feb '25	PBR	* John Crimber	86.00	21.00 - 20.50	8.00	*
-Salt Lake City Feb '25	PBR	* Dalton Kasel	-	22.00 - 22.50	6.36	*
-Sacramento Jan '25	PBR	* Luciano De Castro	90.75	22.00 - 22.25	8.00	*
-Sacramento Jan '25	PBR	* Keyshawn Whitehorse	-	21.50 - 21.00	4.00	*
-Sacramento Jan '25	PBR	* Claudio Montanha Jr.	-	-	-	RR chute
-Previous Matchups at probability 0.368
-Rider Count	135
-Avg Rider Rating	.235
-Total Outs	204
-Qualified Rides	90
-Riding %	44.12%
-87+ points	11.76%</t>
-  </si>
-  <si>
-    <t>Alex Cerqueira on 127 Bulldog (BMJM)
-Qualified Ride Probability: 30.1% (confidence 6 of 10)
-Ride Score Potential: 83.67 to 89.67 points
-Alex Cerqueira Riding Hand: Left
-Career: 197 for 513 - 38.4% - Rider Rating: *.270
-Short Rounds: 22 for 60 - 36.67%
-Current Streak: 6 / 15 - 40.00%
-PBR Current Season: Rank: 6 (33 for 65 - 50.8%) 502.50 pts (-390) - $162,721.28
-PBR Points Per Out: 8 - Points Per QR: 15
-vs. Left: 110-93 (54.19%) -- vs. Right: 32-108 (22.86%) -- vs. ?: 14-24 (36.84%) -- +31.33%/15.79% LEFT
-127 Bulldog PBS 10250898
-no compiled stats
-Previous Outs for 127 Bulldog
-Event	Level	Matchup	Score	Marks	Time	Notes
-Billings Apr '26	PBR	Kase Hitt	-	21.50 - 21.20	3.69	*
-Little Rock Mar '26	PBR	* Sage Kimzey	-	20.80 - 20.45	5.67	*
-Belton Feb '26	OPEN	Braydan Kilcrease	-	21.53 - 21.53	3.97	*
-Previous Matchups at probability 0.301
-Rider Count	235
-Avg Rider Rating	.194
-Total Outs	340
-Qualified Rides	92
-Riding %	27.06%
-87+ points	9.12%</t>
-  </si>
-  <si>
-    <t>Romario Leite on 106 MF Darkside (BSBL)
-Qualified Ride Probability: 38.9% (confidence 8 of 10)
-Ride Score Potential: 83.32 to 89.32 points
-Romario Leite Riding Hand: Left
-Career: 25 for 78 - 32.05% - Rider Rating: .156
-Short Rounds: 1 for 8 - 12.5%
-Current Streak: 3 / 15 - 20.00%
-PBR Current Season: Rank: 60 (1 for 11 - 9.1%) 8.00 pts (-884.5) - $9,446.45
-PBR Points Per Out: 1 - Points Per QR: 8
-vs. Left: 11-8 (57.89%) -- vs. Right: 3-12 (20%) -- vs. ?: 4-14 (22.22%) -- +37.89%/25.84% LEFT
-106 MF Darkside - PBS -
-Power Rating: 52.32
-ALL: 10 outs 6 rides - 40%
-UTB: 9 outs 6 rides - 33.33%
-vs. Left:  2-6 - 25.00%
-vs. Right: 2-0 - 100.00%
-vs. Top:   2-4 - 33.33%
-Riding Hand Advantage: LEFT (75.00%)
-Previous Outs for 106 MF Darkside
-Event	Level	Matchup	Score	Marks	Time	Notes
-Bridgeport Feb '26	PBR	* Bruno Carvalho	81.70	19.90 - 20.40	8.00	*
-Jacksonville Feb '26	PBR	* Andrew Alvidrez	-	20.70 - 21.20	6.04	*
-Pittsburgh Feb '26	PBR	* Thiago Salgado	85.15	21.15 - 21.20	8.00	*
-Milwaukee Jan '26	PBR	* John Crimber	87.60	21.35 - 21.15	8.00	*
-New York Jan '26	PBR	* Afonso Quintino	85.80	20.95 - 21.10	8.00	*
-Manchester Dec '25	PBR	* Bob Mitchell	86.85	21.30 - 20.95	8.00	*
-Las Vegas Oct '25	PBR	Winy dos Santos	-	21.25 - 21.00	7.76	*
-Las Vegas Oct '25	PBR	Lauro Nunes Vieira	-	20.75 - 20.75	4.29	*
-Glendale Oct '25	PBR	* Everton Natan da Silva	87.75	21.50 - 21.50	8.00	*
-Glendale Oct '25	PBR	* Boudreaux Campbell	-	21.50 - 22.00	3.50	*
-Previous Matchups at probability 0.389
-Rider Count	119
-Avg Rider Rating	.243
-Total Outs	167
-Qualified Rides	73
-Riding %	43.71%
-87+ points	14.37%</t>
-  </si>
-  <si>
-    <t>Bob Mitchell on 012H Sunrise (BSBL)
-Qualified Ride Probability: 54.2% (confidence 9 of 10)
-Ride Score Potential: 83.96 to 89.96 points
-Bob Mitchell Riding Hand: Left
-Career: 183 for 462 - 39.61% - Rider Rating: *.283
-Short Rounds: 18 for 73 - 24.66%
-Current Streak: 10 / 15 - 66.67%
-PBR Current Season: Rank: 13 (34 for 62 - 54.8%) 396.00 pts (-496.5) - $123,666.07
-PBR Points Per Out: 6 - Points Per QR: 12
-vs. Left: 98-90 (52.13%) -- vs. Right: 32-89 (26.45%) -- vs. ?: 18-24 (42.86%) -- +25.68%/12.52% LEFT
-012H Sunrise - PBS -
-Power Rating: 59.59
-ALL: 17 outs 7 rides - 58.82%
-UTB: 11 outs 7 rides - 36.36%
-vs. Left:  2-2 - 50.00%
-vs. Right: 7-5 - 58.33%
-vs. Top:   4-6 - 40.00%
-Riding Hand Advantage: LEFT (8.00%)
-Previous Outs for 012H Sunrise
-Event	Level	Matchup	Score	Marks	Time	Notes
-Billings Apr '26	PBR	* Jose Vitor Leme	87.20	21.30 - 21.20	8.00	*
-Bridgeport Feb '26	PBR	Elijah Jennings	-	21.05 - 21.70	6.32	*
-Jacksonville Feb '26	PBR	* Joao Ricardo Vieira	82.65	19.90 - 20.30	8.00	*
-Pittsburgh Feb '26	PBR	* Cort McFadden	87.40	21.05 - 21.30	8.00	*
-Tampa Jan '26	PBR	* Sage Kimzey	88.10	21.40 - 21.50	8.00	*
-Milwaukee Jan '26	PBR	* Leandro Zampollo	-	21.85 - 21.80	4.27	*
-Milwaukee Jan '26	PBR	JaCauy Hale	-	21.35 - 21.80	1.92	*
-Manchester Dec '25	PBR	Callum Miller	86.65	21.10 - 21.05	8.00	*
-Las Vegas Oct '25	PBR	* Cooper Davis	87.25	21.25 - 21.50	8.00	*
-Las Vegas Oct '25	PBR	Alex Junior da Silva	-	21.25 - 21.25	2.73	*
-Glendale Oct '25	PBR	* Alan de Souza	84.75	21.25 - 21.00	8.00	*
-Glendale Oct '25	PBR	* Andrew Alvidrez	-	21.50 - 21.50	6.17	*
-Topeka Jul '25	PBR	Boston Leather	-	21.50 - 21.50	1.99	*
-Tallahassee Mar '25	PBR	Weslei Ferreira de Jesus	-	22.00 - 21.00	1.17	*
-Lexington Mar '25	PBR	Brody Robinson	-	21.00 - 21.00	2.54	*
-Previous Matchups at probability 0.542
-Rider Count	28
-Avg Rider Rating	.303
-Total Outs	31
-Qualified Rides	17
-Riding %	54.84%
-87+ points	16.13%</t>
-  </si>
-  <si>
-    <t>Daniel Keeping on 38K Masterpiece (BSBL)
-Qualified Ride Probability: 34.5% (confidence 5 of 10)
-Ride Score Potential: -1 to 5 points
-Daniel Keeping Riding Hand: Left
-Career: 162 for 417 - 38.85% - Rider Rating: *.273
-Short Rounds: 10 for 45 - 22.22%
-Current Streak: 6 / 15 - 40.00%
-PBR Current Season: Rank: 21 (33 for 71 - 46.5%) 255.00 pts (-637.5) - $146,643.44
-PBR Points Per Out: 4 - Points Per QR: 8
-vs. Left: 99-76 (56.57%) -- vs. Right: 18-85 (17.48%) -- vs. ?: 13-26 (33.33%) -- +39.09%/17.72% LEFT
-38K Masterpiece PBS 10268379
-no compiled stats
-no recorded outs
-Previous Matchups at probability 0.345
-Rider Count	158
-Avg Rider Rating	.230
-Total Outs	235
-Qualified Rides	89
-Riding %	37.87%
-87+ points	10.64%</t>
-  </si>
-  <si>
-    <t>Jess Lockwood on 071H Apple Juicing (WI)
-Qualified Ride Probability: 36.4% (confidence 10 of 10)
-Ride Score Potential: 83.71 to 89.71 points
-Jess Lockwood Riding Hand: Left
-Career: 268 for 553 - 48.46% - Rider Rating: *.408
-Short Rounds: 42 for 100 - 42%
-Current Streak: 8 / 15 - 53.33%
-PBR Current Season: Rank: 20 (20 for 42 - 47.6%) 292.00 pts (-600.5) - $230,842.06
-PBR Points Per Out: 7 - Points Per QR: 15
-vs. Left: 142-99 (58.92%) -- vs. Right: 44-86 (33.85%) -- vs. ?: 23-26 (46.94%) -- +25.07%/10.46% LEFT
-071H Apple Juicing - PBS -
-Power Rating: 67.21
-ALL: 29 outs 3 rides - 89.66%
-vs. Left:  9-0 - 100.00%
-vs. Right: 12-3 - 80.00%
-vs. Top:   4-2 - 66.67%
-Riding Hand Advantage: RIGHT (20.00%)
-Previous Outs for 071H Apple Juicing
-Event	Level	Matchup	Score	Marks	Time	Notes
-Oakland Apr '26	PBR	Edgardo Figueroa	-	21.60 - 21.00	1.87	*
-Fresno Mar '26	PBR	Jairo Castellanos	-	21.10 - 21.80	2.25	*
-Bakersfield Mar '26	PBR	* Braidy Randolph	-	21.50 - 21.60	6.72	*
-Sacramento Jan '26	PBR	* Clay Guiton	87.00	21.10 - 20.95	8.00	*
-Ontario Jan '26	PBR	Landen Jones	-	20.70 - 21.30	1.52	*
-Ontario Jan '26	PBR	* Vinicius Pinheiro Correa	-	22.10 - 21.60	3.21	*
-Red Bluff Dec '25	PRCA	Ray Mayo	-	21.00 - 20.50	3.22	*
-Glendale Oct '25	PBR	* Eduardo Aparecido	-	21.00 - 21.00	3.71	*
-Bremerton Aug '25	PRCAX	Gavin Mitchell	-	21.50 - 21.00	3.28	*
-Bremerton Aug '25	PRCA	Rawley Johnson	-	-	-	RR foul
-Salinas Jul '25	PRCAX	Andy Valdez	-	22.00 - 21.00	1.61	*
-Reno Jun '25	PRCA	Kase Hitt	-	20.50 - 22.50	1.68	*
-Reno Jun '25	PRCAX	Ernie Courson	84.00	22.00 - 22.00	8.00	*
-Lakeside Apr '25	PRCA	Jate Frost	-	20.00 - 20.50	4.00	(nt)
-Oakland Apr '25	PBR	Jacob David	-	21.00 - 21.50	2.53	*
-Previous Matchups at probability 0.364
-Rider Count	140
-Avg Rider Rating	.231
-Total Outs	210
-Qualified Rides	94
-Riding %	44.76%
-87+ points	11.43%</t>
-  </si>
-  <si>
-    <t>Andrew Alvidrez on 02K Smoke Screen (HWKN)
-Qualified Ride Probability: 20.9% (confidence 7 of 10)
-Ride Score Potential: 86.19 to 92.19 points
-Andrew Alvidrez Riding Hand: Right
-Career: 233 for 735 - 31.7% - Rider Rating: *.245
-Short Rounds: 29 for 99 - 29.29%
-Current Streak: 4 / 15 - 26.67%
-PBR Current Season: Rank: 25 (19 for 64 - 29.7%) 219.00 pts (-673.5) - $154,923.02
-PBR Points Per Out: 3 - Points Per QR: 12
-vs. Left: 58-175 (24.89%) -- vs. Right: 104-146 (41.6%) -- vs. ?: 24-52 (31.58%) -- +16.71%/9.9% RIGHT
-02K Smoke Screen - PBS - 10272036
-Power Rating: 75.92
-ALL: 8 outs 0 rides - 100%
-vs. Left:  2-0 - 100.00%
-vs. Right: 3-0 - 100.00%
-vs. Top:   2-0 - 100.00%
-Riding Hand Advantage: UNKNOWN (0.00%)
-Previous Outs for 02K Smoke Screen
-Event	Level	Matchup	Score	Marks	Time	Notes
-Oakland Apr '26	PBR	* Vitor Losnake	-	22.70 - 22.60	1.87	*
-Palm Desert Mar '26	PBR	Dakota Johnson	-	22.10 - 21.10	2.80	*
-Bakersfield Mar '26	PBR	* Dener Barbosa	-	22.00 - 21.80	4.94	*
-Reno Feb '26	PBR	Dakota Johnson	-	21.50 - 20.95	4.26	*
-Ontario Jan '26	PBR	Dione de Souza Ribeiro	-	21.20 - 21.40	4.57	*
-Portland Jan '26	PBR	Dakota Johnson	-	21.40 - 21.80	4.02	*
-Portland Jan '26	PBR	Levi Quillan	-	22.00 - 21.20	3.09	*
-Ardmore Mar '25	PRCAX	Ernie Courson	-	22.00 - 23.00	4.78	*
-Previous Matchups at probability 0.209
-Rider Count	250
-Avg Rider Rating	.155
-Total Outs	366
-Qualified Rides	74
-Riding %	20.22%
-87+ points	4.37%</t>
-  </si>
-  <si>
-    <t>Daylon Swearingen on 829 Ugly This (CMCY)
-Qualified Ride Probability: 48% (confidence 10 of 10)
-Ride Score Potential: 85.25 to 91.25 points
-Daylon Swearingen Riding Hand: Left
-Career: 352 for 823 - 42.77% - Rider Rating: *.341
-Short Rounds: 47 for 123 - 38.21%
-Current Streak: 7 / 15 - 46.67%
-PBR Current Season: Rank: 16 (19 for 46 - 41.3%) 362.50 pts (-530) - $150,772.22
-PBR Points Per Out: 8 - Points Per QR: 19
-vs. Left: 204-165 (55.28%) -- vs. Right: 55-143 (27.78%) -- vs. ?: 23-48 (32.39%) -- +27.5%/12.51% LEFT
-829 Ugly This - PBS -
-Power Rating: 78.86
-ALL: 74 outs 22 rides - 70.27%
-UTB: 32 outs 15 rides - 53.13%
-vs. Left:  23-16 - 58.97%
-vs. Right: 22-6 - 78.57%
-vs. Top:   27-19 - 58.70%
-Riding Hand Advantage: LEFT (20.00%)
-Previous Matchups
-Event	Level	Matchup	Score	Marks	Time	Notes
-Las Vegas Oct '24	PBR	Daylon Swearingen on 48315	89.75	21.75 - 21.25	8.00	*
-Previous Outs for 829 Ugly This
-Event	Level	Matchup	Score	Marks	Time	Notes
-New Orleans Apr '26	HONDO	* Boudreaux Campbell	-	21.80 - 21.90	4.09	*
-New Orleans Apr '26	HONDO	* Hayden Welsh	88.90	21.60 - 21.90	8.00	*
-Albuquerque Mar '26	PBR	* Bob Mitchell	86.90	21.20 - 21.15	8.00	*
-Mercedes Mar '26	PRCAX	Cody Fraser	-	20.50 - 19.50	3.96	*
-Mercedes Mar '26	PRCAX	* Wacey Schalla	-	-	-	TO
-Mercedes Mar '26	PRCAX	Hayden Ferguson	-	21.00 - 22.50	3.66	*
-Tallahassee Mar '26	PBR	* Bruno Carvalho	85.75	21.10 - 21.00	8.00	*
-Little Rock Mar '26	PBR	* Koltin Hevalow	87.55	21.30 - 21.40	8.00	*
-Jacksonville Feb '26	PBR	Andy Guzman	-	20.95 - 21.60	2.71	*
-Guthrie Feb '26	PRCAX	Wyatt Bowman	-	20.00 - 21.00	4.00	(nt)
-Guthrie Feb '26	PRCAX	Tucker Root	-	20.00 - 21.50	4.00	(nt)
-Pawhuska Jan '26	PRCA	Patterson Starcher	-	20.00 - 21.00	4.00	(nt)
-New York Jan '26	PBR	* Qynn Andersen	-	21.30 - 21.40	6.53	*
-Las Vegas (NFR) Dec '25	PRCA	* Hayes Weight	-	21.75 - 21.50	4.02	*
-Las Vegas (NFR) Dec '25	PRCA	* Luke Mackey	82.50	21.00 - 19.75	8.00	*
-Previous Matchups at probability 0.48
-Rider Count	60
-Avg Rider Rating	.279
-Total Outs	78
-Qualified Rides	44
-Riding %	56.41%
-87+ points	15.38%</t>
-  </si>
-  <si>
-    <t>Thiago Salgado on 102 Cracky Chan (CLPB)
-Qualified Ride Probability: 39% (confidence 9 of 10)
-Ride Score Potential: 83.56 to 89.56 points
-Thiago Salgado Riding Hand: Left
-Career: 176 for 430 - 40.93% - Rider Rating: *.281
-Short Rounds: 16 for 50 - 32%
-Current Streak: 4 / 15 - 26.67%
-PBR Current Season: Rank: 24 (38 for 74 - 51.4%) 224.00 pts (-668.5) - $173,189.21
-PBR Points Per Out: 3 - Points Per QR: 6
-vs. Left: 103-89 (53.65%) -- vs. Right: 20-82 (19.61%) -- vs. ?: 15-18 (45.45%) -- +34.04%/12.72% LEFT
-102 Cracky Chan - PBS -
-Power Rating: 57.72
-ALL: 15 outs 5 rides - 66.67%
-UTB: 6 outs 4 rides - 33.33%
-vs. Left:  6-1 - 85.71%
-vs. Right: 3-4 - 42.86%
-vs. Top:   3-5 - 37.50%
-Riding Hand Advantage: RIGHT (43.00%)
-Previous Outs for 102 Cracky Chan
-Event	Level	Matchup	Score	Marks	Time	Notes
-Oakland Apr '26	PBR	Justice Forsythe	-	19.60 - 20.50	1.19	*
-Salt Lake City Feb '26	PBR	* Cort McFadden	-	21.25 - 21.60	6.93	*
-Sacramento Jan '26	PBR	* Luciano De Castro	-	20.95 - 21.25	3.23	*
-Sacramento Jan '26	PBR	* Maverick Smith	85.70	21.35 - 20.80	8.00	*
-Ontario Jan '26	PBR	Kingston Herrero	-	22.30 - 22.10	2.03	*
-Anaheim Sep '25	PBR	* Claudio Montanha Jr.	86.00	21.00 - 21.00	8.00	*
-Anaheim Sep '25	PBR	* Keyshawn Whitehorse	-	-	-	RR foul
-Anaheim Sep '25	PBR	* Paulo Eduardo Rossetto	86.25	21.00 - 21.00	8.00	*
-Oakland Apr '25	PBR	* Bob Mitchell	86.00	21.00 - 21.00	8.00	*
-Palm Springs Mar '25	PBR	* Andrew Alvidrez	85.00	20.50 - 20.50	8.00	*
-Fort Worth Jan '25	PBR	* Koltin Hevalow	-	21.00 - 21.25	6.61	*
-Fort Worth Jan '25	PBR	* Austin Richardson	-	21.75 - 21.25	-	RR no nod
-Denver Jan '25	PBR	* Ednelio Rodrigues	-	21.50 - 21.00	3.58	*
-Denver Jan '25	PBR	Eric Henrique Domingos	-	21.50 - 21.00	5.36	*
-Queen Creek Nov '24	PRCAX	Rawley Johnson	-	21.50 - 21.00	4.00	(nt)
-Previous Matchups at probability 0.39
-Rider Count	117
-Avg Rider Rating	.248
-Total Outs	168
-Qualified Rides	77
-Riding %	45.83%
-87+ points	12.5%</t>
-  </si>
-  <si>
-    <t>Joao Ricardo Vieira on 891F Testified (PGAO)
-Qualified Ride Probability: 27% (confidence 8 of 10)
-Ride Score Potential: 84.24 to 90.24 points
-Joao Ricardo Vieira Riding Hand: Left
-Career: 599 for 1325 - 45.21% - Rider Rating: *.356
-Short Rounds: 86 for 200 - 43%
-Current Streak: 2 / 15 - 13.33%
-PBR Current Season: Rank: 37 (18 for 52 - 34.6%) 92.50 pts (-800) - $83,389.62
-PBR Points Per Out: 2 - Points Per QR: 5
-vs. Left: 359-237 (60.23%) -- vs. Right: 81-232 (25.88%) -- vs. ?: 46-52 (46.94%) -- +34.35%/15.02% LEFT
-891F Testified - PBS - 10276006
-Power Rating: 65.19
-ALL: 10 outs 1 rides - 90%
-vs. Left:  1-0 - 100.00%
-vs. Right: 6-1 - 85.71%
-vs. Top:   2-1 - 66.67%
-Riding Hand Advantage: RIGHT (14.00%)
-Previous Outs for 891F Testified
-Event	Level	Matchup	Score	Marks	Time	Notes
-Bucktown Feb '26	OPEN	* Wacey Schalla	89.00	21.50 - 21.50	8.00	*
-Fort Worth Jan '26	PBR	Tennessee Owens	-	20.90 - 21.30	2.23	*
-Sioux Falls Sep '25	PRCA	Rawley Johnson	-	22.25 - 22.00	6.78	*
-Albuquerque Sep '25	PRCAX	Tyce Willis	-	21.50 - 20.00	6.35	*
-Albuquerque Sep '25	PRCAX	Hudson Williams	-	20.00 - 23.00	2.06	*
-Ogden Jul '25	PRCA	Jestyn Jax Woodward	-	22.50 - 22.00	5.11	*
-Ogden Jul '25	PRCA	Tristan Mize	-	22.00 - 22.00	2.69	*
-Oklahoma City Jul '25	PBR	* Braidy Randolph	-	19.50 - 19.25	6.87	*
-Oklahoma City Jul '25	PBR	* Guilherme Valleiras	-	21.00 - 20.75	3.09	*
-Belton Feb '25	OPEN	Jack Mitchell	-	21.63 - 21.63	2.56	*
-Previous Matchups at probability 0.27
-Rider Count	235
-Avg Rider Rating	.187
-Total Outs	358
-Qualified Rides	93
-Riding %	25.98%
-87+ points	5.31%</t>
-  </si>
-  <si>
-    <t>Andy Guzman on 0498 Long Gone (THCC)
-Qualified Ride Probability: 22.3% (confidence 9 of 10)
-Ride Score Potential: 84.22 to 90.22 points
-Andy Guzman Riding Hand: Left
-Career: 51 for 222 - 22.97% - Rider Rating: .119
-Short Rounds: 5 for 22 - 22.73%
-Current Streak: 1 / 15 - 6.67%
-PBR Current Season: Rank: 40 (4 for 30 - 13.3%) 78.00 pts (-814.5) - $11,800.00
-PBR Points Per Out: 3 - Points Per QR: 20
-vs. Left: 18-49 (26.87%) -- vs. Right: 4-52 (7.14%) -- vs. ?: 13-25 (34.21%) -- +19.73%/3.9% LEFT
-0498 Long Gone - PBS - 10243159
-Power Rating: 66.97
-ALL: 23 outs 4 rides - 82.61%
-UTB: 7 outs 2 rides - 71.43%
-vs. Left:  7-3 - 70.00%
-vs. Right: 10-1 - 90.91%
-vs. Top:   5-3 - 62.50%
-Riding Hand Advantage: LEFT (21.00%)
-Previous Outs for 0498 Long Gone
-Event	Level	Matchup	Score	Marks	Time	Notes
-Reno Feb '26	PBR	Chase Hamlin	-	21.80 - 21.70	1.80	*
-Reno Feb '26	PBR	Zane Cook	-	21.35 - 21.50	2.10	*
-Lexington Feb '26	PBR	Vinicius Rodrigues Pereira	-	20.45 - 20.30	6.30	*
-Tulsa Jan '26	PBR	Zane Cook	-	22.10 - 22.30	2.00	*
-Tucson Dec '25	PBR	Ayslan Jeferson	-	21.25 - 21.05	2.51	*
-Las Vegas Oct '25	PBR	Alvaro Ariel	-	22.00 - 21.25	1.55	*
-Las Vegas Oct '25	PBR	Wyatt Rogers	-	-	-	RR chute
-Springfield Aug '25	PBR	* Cody Jesus	-	21.75 - 21.50	6.69	*
-Springfield Aug '25	PBR	* Everton Natan da Silva	87.75	21.50 - 21.25	8.00	*
-Austin Aug '25	PBR	* Koltin Hevalow	-	20.25 - 20.25	7.75	*
-Oklahoma City Jul '25	PBR	* Daylon Swearingen	87.00	21.00 - 21.00	8.00	*
-Oklahoma City Jul '25	PBR	* Dalton Kasel	-	21.75 - 21.75	6.37	*
-Tallahassee Mar '25	PBR	Wyatt Rogers	-	21.50 - 21.00	2.46	*
-Laredo Jan '25	PBR	Guthrie Long	-	22.00 - 21.50	3.98	*
-Birmingham Jan '25	PBR	Carlos Garcia	-	20.00 - 22.00	3.37	*
-Previous Matchups at probability 0.223
-Rider Count	267
-Avg Rider Rating	.160
-Total Outs	371
-Qualified Rides	83
-Riding %	22.37%
-87+ points	4.85%</t>
-  </si>
-  <si>
-    <t>Mauricio Gulla Moreira on 68E Oreo (THCC)
-Qualified Ride Probability: 21.3% (confidence 10 of 10)
-Ride Score Potential: 85.28 to 91.28 points
-Mauricio Gulla Moreira Riding Hand: Left
-Career: 154 for 517 - 29.79% - Rider Rating: *.248
-Short Rounds: 10 for 57 - 17.54%
-Current Streak: 1 / 15 - 6.67%
-PBR Current Season: Rank: 38 (21 for 72 - 29.2%) 86.00 pts (-806.5) - $86,037.98
-PBR Points Per Out: 1 - Points Per QR: 4
-vs. Left: 81-124 (39.51%) -- vs. Right: 24-126 (16%) -- vs. ?: 14-27 (34.15%) -- +23.51%/9.72% LEFT
-68E Oreo - PBS - 10205390
-Power Rating: 75.71
-ALL: 33 outs 8 rides - 75.76%
-UTB: 11 outs 4 rides - 63.64%
-vs. Left:  10-0 - 100.00%
-vs. Right: 12-8 - 60.00%
-vs. Top:   12-8 - 60.00%
-Riding Hand Advantage: RIGHT (40.00%)
-Previous Outs for 68E Oreo
-Event	Level	Matchup	Score	Marks	Time	Notes
-Ennis Oct '25	OPEN	* Lane Vaughan	87.30	21.45 - 21.45	8.00	*
-Fort Worth Jul '25	PBR	Natanael Serra Aires	-	21.50 - 21.00	5.31	*
-Fort Worth Jan '25	PBR	Mossy Waite	-	20.00 - 21.00	6.44	*
-Anaheim Sep '24	PBR	* Julio Cesar Marques	88.50	21.50 - 21.75	8.00	*
-New York Aug '24	PBR	* Leandro Machado	-	19.75 - 20.50	1.61	*
-Fort Lauderdale Aug '24	PBR	* Silvano Alves	-	21.25 - 21.25	7.16	*
-Fort Lauderdale Aug '24	PBR	* Kaique Pacheco	85.00	20.25 - 22.00	8.00	*
-Fort Worth Jun '24	PBR	Dione de Souza Ribeiro	-	23.00 - 22.50	1.51	*
-Liberty May '24	OPEN	* Lane Vaughan	-	22.05 - 22.05	4.45	*
-Corpus Christi May '24	PBR	* Paulo Eduardo Rossetto	89.00	21.50 - 21.75	8.00	*
-Wichita Apr '24	PBR	* Elizmar Jeremias	-	21.00 - 21.50	1.49	*
-Mobile Mar '24	PBR	Alvaro Ariel	-	21.00 - 21.50	1.44	*
-Youngstown Feb '24	PBR	João Paulo Fernandes	-	21.00 - 21.50	3.26	*
-Reno Jan '24	PBR	* Leonardo Castro	90.50	22.50 - 21.50	8.00	*
-Grandview Aug '23	OPEN	Fernando Da Conceicao	-	21.93 - 21.93	2.65	*
-Previous Matchups at probability 0.213
-Rider Count	271
-Avg Rider Rating	.153
-Total Outs	387
-Qualified Rides	75
-Riding %	19.38%
-87+ points	2.58%</t>
-  </si>
-  <si>
-    <t>Luciano De Castro on 497 MF Cupcake (BSBL)
-Qualified Ride Probability: 35.1% (confidence 6 of 10)
-Ride Score Potential: 87.4 to 93.4 points
-Luciano De Castro Riding Hand: Left
-Career: 353 for 770 - 45.84% - Rider Rating: *.341
-Short Rounds: 47 for 108 - 43.52%
-Current Streak: 9 / 15 - 60.00%
-PBR Current Season: Rank: 18 (36 for 74 - 48.6%) 304.00 pts (-588.5) - $151,952.86
-PBR Points Per Out: 4 - Points Per QR: 8
-vs. Left: 207-121 (63.11%) -- vs. Right: 42-136 (23.6%) -- vs. ?: 22-36 (37.93%) -- +39.51%/17.27% LEFT
-497 MF Cupcake PBS
-no compiled stats
-Previous Outs for 497 MF Cupcake
-Event	Level	Matchup	Score	Marks	Time	Notes
-Billings Apr '26	PBR	* Mauricio Gulla Moreira	-	22.05 - 22.15	1.36	*
-Previous Matchups at probability 0.351
-Rider Count	148
-Avg Rider Rating	.238
-Total Outs	245
-Qualified Rides	84
-Riding %	34.29%
-87+ points	10.2%</t>
-  </si>
-  <si>
-    <t>Alex Junior da Silva on 2719 Unhinged (WI)
-Qualified Ride Probability: 16.3% (confidence 10 of 10)
-Ride Score Potential: 83.27 to 89.27 points
-Alex Junior da Silva Riding Hand: Right
-Career: 45 for 158 - 28.48% - Rider Rating: .160
-Short Rounds: 2 for 17 - 11.76%
-Current Streak: 5 / 15 - 33.33%
-PBR Current Season: Rank: 43 (4 for 12 - 33.3%) 49.50 pts (-843) - $4,025.00
-PBR Points Per Out: 4 - Points Per QR: 12
-vs. Left: 8-47 (14.55%) -- vs. Right: 16-12 (57.14%) -- vs. ?: 8-14 (36.36%) -- +42.59%/28.66% RIGHT
-2719 Unhinged - PBS - 10231548
-Power Rating: 77.82
-ALL: 27 outs 1 rides - 96.3%
-vs. Left:  7-1 - 87.50%
-vs. Right: 16-0 - 100.00%
-vs. Top:   6-0 - 100.00%
-Riding Hand Advantage: LEFT (13.00%)
-Previous Matchups
-Event	Level	Matchup	Score	Marks	Time	Notes
-Fort Worth Feb '25	PBR	Alex Junior da Silva on 49727	-	21.00 - 21.50	1.71	*
-Previous Outs for 2719 Unhinged
-Event	Level	Matchup	Score	Marks	Time	Notes
-Fresno Mar '26	PBR	Jace Catlin	-	20.50 - 21.30	1.60	*
-Palm Desert Mar '26	PBR	Zane Cook	-	21.50 - 21.60	2.71	*
-Vernal Mar '26	PRCAX	* Dawson Branton	-	21.50 - 19.00	2.55	*
-Vernal Mar '26	PRCAX	Connor Trevathan	-	22.00 - 22.50	3.12	*
-Sacramento Jan '26	PBR	* Cort McFadden	-	20.85 - 20.95	4.06	*
-Sacramento Jan '26	PBR	* Manoelito de Souza Junior	86.50	21.40 - 20.85	8.00	*
-Portland Jan '26	PBR	* Lane Vaughan	-	20.50 - 20.70	3.61	*
-Tucson Dec '25	PBR	Weslei Ferreira de Jesus	-	21.00 - 20.25	0.91	*
-Albuquerque Sep '25	PRCA	Cade Griego	-	-	-	RR foul
-Lovington Aug '25	PRCA	* Creek Young	-	-	-	DR
-Lovington Aug '25	PRCAX	* Wacey Schalla	-	22.00 - 22.00	7.96	*
-Manhattan Jul '25	PRCA	Lane Clark	-	21.50 - 19.50	4.00	(nt)
-Manhattan Jul '25	PRCA	Kale Visnieski	-	21.00 - 20.00	4.00	(nt)
-Colorado Springs Jul '25	PRCA	* Hudson Bolton	-	22.50 - 21.50	5.04	*
-Weatherford Jun '25	PRCA	Harley Rowland	-	-	-	RR fell decl
-Previous Matchups at probability 0.163
-Rider Count	245
-Avg Rider Rating	.125
-Total Outs	311
-Qualified Rides	44
-Riding %	14.15%
-87+ points	1.29%</t>
-  </si>
-  <si>
-    <t>John Crimber on 0160 Level Up (D4CC)
-Qualified Ride Probability: 45.7% (confidence 8 of 10)
-Ride Score Potential: 86.08 to 92.08 points
-John Crimber Riding Hand: Left
-Career: 228 for 379 - 60.16% - Rider Rating: *.428
-Short Rounds: 25 for 51 - 49.02%
-Current Streak: 11 / 15 - 73.33%
-PBR Current Season: Rank: 1 (54 for 82 - 65.9%) 892.50 pts (-0) - $452,429.21
-PBR Points Per Out: 11 - Points Per QR: 17
-vs. Left: 129-53 (70.88%) -- vs. Right: 35-47 (42.68%) -- vs. ?: 22-16 (57.89%) -- +28.2%/10.72% LEFT
-0160 Level Up - PBS - 10268851
-Power Rating: 73.45
-ALL: 12 outs 1 rides - 91.67%
-vs. Left:  4-1 - 80.00%
-vs. Right: 7-0 - 100.00%
-vs. Top:   5-1 - 83.33%
-Riding Hand Advantage: LEFT (20.00%)
-Previous Outs for 0160 Level Up
-Event	Level	Matchup	Score	Marks	Time	Notes
-Billings Apr '26	PBR	* Bob Mitchell	89.50	21.90 - 22.00	8.00	*
-Little Rock Mar '26	PBR	* Joao Ricardo Vieira	-	21.50 - 22.05	2.16	*
-Grand Forks Feb '26	PBR	Tyler Villarreal	-	22.05 - 21.35	1.69	*
-Tulsa Jan '26	PBR	Hayden Harris	-	21.90 - 21.95	3.33	*
-Tucson Dec '25	PBR	Brady Turgeon	-	21.55 - 21.95	2.53	*
-Las Vegas Dec '25	PBR	Wyatt Nez	-	21.10 - 20.80	1.99	*
-Las Vegas Oct '25	PBR	* Eduardo Aparecido	-	-	-	RR foul
-Las Vegas Oct '25	PBR	* Mason Taylor	-	22.00 - 22.00	3.60	*
-Kansas City Oct '25	PBR	Eric Henrique Domingos	-	21.50 - 21.75	6.83	*
-Kansas City Oct '25	PBR	* Leonardo Castro	-	22.25 - 22.25	3.05	*
-Greensboro Sep '25	PBR	* Ezekiel Mitchell	-	-	-	RR foul
-Fort Worth Aug '25	PBR	Jhon Carlos Moreira	-	21.50 - 22.00	1.45	*
-Las Vegas Dec '24	OPEN	* Ethan Winckler	-	21.50 - 21.88	5.06	*
-Las Vegas Dec '24	OPEN	* Cole Melancon	-	21.88 - 21.88	2.85	*
-Previous Matchups at probability 0.457
-Rider Count	64
-Avg Rider Rating	.270
-Total Outs	83
-Qualified Rides	49
-Riding %	59.04%
-87+ points	26.51%</t>
-  </si>
-  <si>
-    <t>Brady Fielder on 956G Sucker Punch (D4CC)
-Qualified Ride Probability: 40.8% (confidence 8 of 10)
-Ride Score Potential: 82.25 to 88.25 points
-Brady Fielder Riding Hand: Right
-Career: 242 for 475 - 50.95% - Rider Rating: *.369
-Short Rounds: 26 for 66 - 39.39%
-Current Streak: 10 / 15 - 66.67%
-PBR Current Season: Rank: 2 (52 for 85 - 61.2%) 717.00 pts (-175.5) - $412,126.95
-PBR Points Per Out: 8 - Points Per QR: 14
-vs. Left: 51-86 (37.23%) -- vs. Right: 116-68 (63.04%) -- vs. ?: 19-15 (55.88%) -- +25.81%/12.09% RIGHT
-956G Sucker Punch - PBS - 10229189
-Power Rating: 74.90
-ALL: 13 outs 0 rides - 100%
-vs. Left:  2-0 - 100.00%
-vs. Right: 9-0 - 100.00%
-vs. Top:   2-0 - 100.00%
-Riding Hand Advantage: UNKNOWN (0.00%)
-Previous Outs for 956G Sucker Punch
-Event	Level	Matchup	Score	Marks	Time	Notes
-Billings Apr '26	PBR	Callum Miller	-	22.50 - 22.00	4.96	*
-Tulsa Jan '26	PBR	Dalton Rudman	-	21.60 - 22.00	2.89	*
-Tucson Dec '25	PBR	Grayson Cole	-	11.85 - 13.55	4.24	*
-Las Vegas Dec '25	PBR	JaCauy Hale	-	22.30 - 22.10	5.59	*
-Las Vegas Oct '25	PBR	Leandro da Silva	-	-	-	DQ chute
-Oklahoma City Sep '25	OPEN	Lucas Martins Costa	-	-	-	DQ chute
-Fort Worth Sep '25	PBR	Natanael Serra Aires	-	21.50 - 21.50	3.16	*
-Dayton Mar '24	PBR	Grayson Cole	-	-	-	RR foul
-Las Vegas Oct '23	PBR	* Bob Mitchell	-	-	-	RR chute
-Lawton Aug '23	PRCA	Dustin Pinson	-	-	-	RR foul
-Woodstown Aug '23	PBR	Jarred Walker	-	-	-	RR foul
-Little Rock Mar '23	PBR	* Kaique Pacheco	-	-	-	RR chute
-Memphis Feb '23	PBR	Justin Bates	-	22.00 - 22.00	3.62	*
-Tulsa Feb '23	PBR	Casey Coulter	-	22.50 - 22.50	2.93	*
-Indianapolis Jan '23	PBR	* Vitor Losnake	-	22.50 - 22.75	6.74	*
-Previous Matchups at probability 0.408
-Rider Count	98
-Avg Rider Rating	.266
-Total Outs	148
-Qualified Rides	67
-Riding %	45.27%
-87+ points	16.89%</t>
-  </si>
-  <si>
-    <t>Keyshawn Whitehorse on 816 Bad Bob (D4CC)
-Qualified Ride Probability: 52.1% (confidence 10 of 10)
-Ride Score Potential: 83.68 to 89.68 points
-Keyshawn Whitehorse Riding Hand: Right
-Career: 363 for 944 - 38.45% - Rider Rating: *.293
-Short Rounds: 44 for 145 - 30.34%
-Current Streak: 9 / 15 - 60.00%
-PBR Current Season: Rank: 9 (34 for 71 - 47.9%) 405.00 pts (-487.5) - $159,855.64
-PBR Points Per Out: 6 - Points Per QR: 12
-vs. Left: 84-221 (27.54%) -- vs. Right: 138-152 (47.59%) -- vs. ?: 37-56 (39.78%) -- +20.05%/9.14% RIGHT
-816 Bad Bob - PBS - 10262490
-Power Rating: 61.01
-ALL: 27 outs 12 rides - 55.56%
-UTB: 13 outs 7 rides - 46.15%
-vs. Left:  12-8 - 60.00%
-vs. Right: 3-4 - 42.86%
-vs. Top:   5-9 - 35.71%
-Riding Hand Advantage: RIGHT (17.00%)
-Previous Outs for 816 Bad Bob
-Event	Level	Matchup	Score	Marks	Time	Notes
-Billings Apr '26	PBR	Andy Guzman	-	20.80 - 21.10	4.86	*
-Tulsa Jan '26	PBR	Dione de Souza Ribeiro	-	21.15 - 21.70	3.26	*
-Tucson Dec '25	PBR	Colt Robinson	-	21.65 - 21.60	7.70	*
-Las Vegas Dec '25	PBR	Dalton Allred	-	22.00 - 21.40	6.75	*
-Las Vegas Oct '25	PBR	Alvaro Ariel	86.00	21.25 - 20.75	8.00	*
-Ennis Oct '25	OPEN	* Aaron Pass	-	21.78 - 21.78	4.85	*
-Oklahoma City Sep '25	OPEN	Natanael Serra Aires	-	21.25 - 21.50	4.20	*
-Greensboro Sep '25	PBR	* Luciano De Castro	-	18.25 - 17.75	-	RR inf
-Greensboro Sep '25	PBR	* Thiago Salgado	-	21.75 - 22.00	5.58	*
-Austin Aug '25	PBR	Natanael Serra Aires	-	21.00 - 21.00	6.41	*
-Duluth Jul '25	PBR	* Jose Vitor Leme	86.50	21.00 - 21.00	8.00	*
-Duluth Jul '25	PBR	* Ramon de Lima	-	21.00 - 21.00	7.22	*
-Oklahoma City Jul '25	PBR	* Luciano De Castro	86.75	21.00 - 21.25	8.00	*
-Oklahoma City Jul '25	PBR	Caden Bunch	-	21.50 - 21.50	6.11	*
-Grandview Jun '25	OPEN	* Thiago Salgado	87.40	21.37 - 21.37	8.00	*
-Previous Matchups at probability 0.521
-Rider Count	40
-Avg Rider Rating	.316
-Total Outs	57
-Qualified Rides	37
-Riding %	64.91%
-87+ points	21.05%</t>
-  </si>
-  <si>
-    <t>Hudson Bolton on 67 Benjamin Ranklin (TFRS)
-Qualified Ride Probability: 36.9% (confidence 10 of 10)
-Ride Score Potential: 83.47 to 89.47 points
-Hudson Bolton Riding Hand: Left
-Career: 140 for 260 - 53.85% - Rider Rating: *.368
-Short Rounds: 10 for 21 - 47.62%
-Current Streak: 8 / 15 - 53.33%
-PBR Current Season: Rank: 22 (15 for 31 - 48.4%) 247.00 pts (-645.5) - $73,908.24
-PBR Points Per Out: 8 - Points Per QR: 16
-vs. Left: 65-43 (60.19%) -- vs. Right: 28-35 (44.44%) -- vs. ?: 15-14 (51.72%) -- +15.75%/6.34% LEFT
-67 Benjamin Ranklin - PBS -
-Power Rating: 84.69
-ALL: 30 outs 4 rides - 86.67%
-UTB: 21 outs 3 rides - 85.71%
-vs. Left:  6-1 - 85.71%
-vs. Right: 19-3 - 86.36%
-vs. Top:   18-3 - 85.71%
-Riding Hand Advantage: LEFT (1.00%)
-Previous Outs for 67 Benjamin Ranklin
-Event	Level	Matchup	Score	Marks	Time	Notes
-Albuquerque Mar '26	PBR	* Sage Kimzey	-	21.85 - 21.85	7.34	*
-Salt Lake City Feb '26	PBR	* Julio Cesar Marques	-	21.35 - 21.10	7.15	*
-Sacramento Jan '26	PBR	Alison dos Santos	-	21.40 - 21.30	4.25	*
-Las Vegas Oct '25	PBR	* Eduardo Aparecido	-	21.25 - 21.25	3.72	*
-Las Vegas Oct '25	PBR	* Ethan Winckler	-	21.50 - 21.25	3.18	*
-Glendale Oct '25	PBR	Jean Carlos Teodoro	-	20.50 - 21.00	4.61	*
-Glendale Oct '25	PBR	Kase Hitt	-	21.50 - 21.50	4.75	*
-Fort Worth Sep '25	PBR	Tate Pollmeier	-	21.25 - 21.50	4.64	*
-Fort Collins Jul '25	PBR	Andy Guzman	-	20.75 - 20.75	2.83	*
-Fort Collins Jul '25	PBR	* Leonardo Castro	-	21.00 - 20.75	6.83	*
-Evergreen Jun '25	PRCA	Mason Reine	-	21.00 - 20.00	4.00	(nt)
-Fort Worth (PBRF) May '25	PBR	* Julio Cesar Marques	-	20.00 - 20.50	6.85	*
-Fort Worth (PBRF) May '25	PBR	* Kaique Pacheco	-	21.25 - 21.50	2.75	*
-Nampa Apr '25	PBR	* Julio Cesar Marques	-	21.25 - 21.25	3.70	*
-Billings Apr '25	PBR	* Austin Richardson	-	20.75 - 20.50	6.35	*
-Previous Matchups at probability 0.369
-Rider Count	133
-Avg Rider Rating	.239
-Total Outs	192
-Qualified Rides	72
-Riding %	37.5%
-87+ points	10.94%</t>
-  </si>
-  <si>
-    <t>Koltin Hevalow on -1K Johnny Dang (HWKN)
-Qualified Ride Probability: 43.1% (confidence 8 of 10)
-Ride Score Potential: 85.69 to 91.69 points
-Koltin Hevalow Riding Hand: Left
-Career: 154 for 416 - 37.02% - Rider Rating: *.266
-Short Rounds: 9 for 40 - 22.5%
-Current Streak: 2 / 15 - 13.33%
-PBR Current Season: Rank: 23 (35 for 80 - 43.8%) 246.50 pts (-646) - $123,896.04
-PBR Points Per Out: 3 - Points Per QR: 7
-vs. Left: 108-98 (52.43%) -- vs. Right: 24-81 (22.86%) -- vs. ?: 10-22 (31.25%) -- +29.57%/15.41% LEFT
--1K Johnny Dang - PBS - 10270857
-Power Rating: 42.09
-ALL: 10 outs 3 rides - 70%
-vs. Left:  1-0 - 100.00%
-vs. Right: 2-3 - 40.00%
-vs. Top:   0-1 - 0.00%
-Riding Hand Advantage: RIGHT (60.00%)
-Previous Outs for -1K Johnny Dang
-Event	Level	Matchup	Score	Marks	Time	Notes
-Oakland Apr '26	PBR	Keola Nishimoto	-	21.70 - 20.70	1.09	*
-Palm Desert Mar '26	PBR	Grayson Cole	-	22.20 - 21.40	1.95	*
-Bakersfield Mar '26	PBR	Eric Novoa	88.80	22.00 - 21.80	8.00	*
-Reno Feb '26	PBR	Jose Natanael Marcodes da Silva	-	21.65 - 21.55	1.98	*
-Salt Lake City Feb '26	PBR	Callum Miller	-	22.15 - 21.75	2.67	*
-Salt Lake City Feb '26	PBR	Cleber Henrique Marques	-	21.70 - 21.90	1.91	*
-Sacramento Jan '26	PBR	* Lucas Divino	84.30	21.15 - 21.60	8.00	*
-Ontario Jan '26	PBR	Wyatt Vineyard	-	21.40 - 21.70	2.73	*
-Portland Jan '26	PBR	* Lane Vaughan	-	-	-	RR chute
-Las Vegas Dec '25	PBR	Dalton Allred	90.20	22.50 - 21.60	8.00	*
-Ardmore Mar '25	PRCAX	James Cole	-	21.00 - 22.00	2.82	*
-Previous Matchups at probability 0.431
-Rider Count	99
-Avg Rider Rating	.258
-Total Outs	124
-Qualified Rides	52
-Riding %	41.94%
-87+ points	13.71%</t>
-  </si>
-  <si>
-    <t>Claudio Montanha Jr. on 120 Smooth Violation (TFRS)
-Qualified Ride Probability: 48.3% (confidence 9 of 10)
-Ride Score Potential: 83.75 to 89.75 points
-Claudio Montanha Jr. Riding Hand: Right
-Career: 335 for 867 - 38.64% - Rider Rating: *.274
-Short Rounds: 39 for 128 - 30.47%
-Current Streak: 9 / 15 - 60.00%
-PBR Current Season: Rank: 9 (35 for 69 - 50.7%) 405.00 pts (-487.5) - $166,975.45
-PBR Points Per Out: 6 - Points Per QR: 12
-vs. Left: 75-192 (28.09%) -- vs. Right: 139-123 (53.05%) -- vs. ?: 31-54 (36.47%) -- +24.96%/14.41% RIGHT
-120 Smooth Violation - PBS -
-Power Rating: 55.03
-ALL: 17 outs 10 rides - 41.18%
-UTB: 11 outs 8 rides - 27.27%
-vs. Left:  1-9 - 10.00%
-vs. Right: 5-1 - 83.33%
-vs. Top:   3-6 - 33.33%
-Riding Hand Advantage: LEFT (73.00%)
-Previous Outs for 120 Smooth Violation
-Event	Level	Matchup	Score	Marks	Time	Notes
-Albuquerque Mar '26	PBR	Kase Hitt	86.45	21.40 - 21.40	8.00	*
-Sacramento Jan '26	PBR	Andy Guzman	85.50	21.30 - 21.30	8.00	*
-Las Vegas Oct '25	PBR	Ramon Fiorini	-	20.50 - 20.75	4.47	*
-Glendale Oct '25	PBR	* John Crimber	86.25	21.00 - 20.75	8.00	*
-Glendale Oct '25	PBR	* Bob Mitchell	-	-	-	RR foul
-Waco Oct '25	PRCA	Kristopher Baker	-	21.50 - 21.00	3.61	*
-Fort Worth Sep '25	PBR	Natanael Serra Aires	86.50	21.25 - 21.00	8.00	*
-Fort Worth Sep '25	PBR	* Paulo Eduardo Rossetto	87.75	21.50 - 21.50	8.00	*
-Eagle Jul '25	PRCA	Mason Spain	-	20.00 - 21.50	3.16	*
-Fort Collins Jul '25	PBR	* Sandro Batista	85.50	20.50 - 21.00	8.00	*
-Fort Collins Jul '25	PBR	* Daylon Swearingen	87.50	21.25 - 21.25	8.00	*
-Evergreen Jun '25	PRCA	Cooper McClain	-	22.00 - 19.00	4.00	(nt)
-Fort Worth (PBRF) May '25	PBR	* Vinicius Pinheiro Correa	-	21.50 - 21.50	4.20	*
-Fort Worth (PBRF) May '25	PBR	Murilo Henrique de Oliveira	87.75	21.25 - 21.25	8.00	*
-Fort Worth (PBRF) May '25	PBR	* Dener Barbosa	86.75	21.00 - 21.25	8.00	*
-Previous Matchups at probability 0.483
-Rider Count	48
-Avg Rider Rating	.296
-Total Outs	67
-Qualified Rides	44
-Riding %	65.67%
-87+ points	17.91%</t>
-  </si>
-  <si>
-    <t>Lucas Divino on 61G Big Timber (BSBL)
-Qualified Ride Probability: 29.9% (confidence 8 of 10)
-Ride Score Potential: 83.6 to 89.6 points
-Lucas Divino Riding Hand: Right
-Career: 232 for 601 - 38.6% - Rider Rating: *.304
-Short Rounds: 29 for 74 - 39.19%
-Current Streak: 4 / 15 - 26.67%
-PBR Current Season: Rank: 32 (19 for 51 - 37.3%) 150.00 pts (-742.5) - $77,559.34
-PBR Points Per Out: 3 - Points Per QR: 8
-vs. Left: 42-122 (25.61%) -- vs. Right: 130-122 (51.59%) -- vs. ?: 12-30 (28.57%) -- +25.98%/12.99% RIGHT
-61G Big Timber - PBS - 10229166
-Power Rating: 68.46
-ALL: 13 outs 4 rides - 69.23%
-UTB: 9 outs 3 rides - 66.67%
-vs. Left:  2-2 - 50.00%
-vs. Right: 6-1 - 85.71%
-vs. Top:   4-1 - 80.00%
-Riding Hand Advantage: LEFT (36.00%)
-Previous Outs for 61G Big Timber
-Event	Level	Matchup	Score	Marks	Time	Notes
-Jacksonville Feb '26	PBR	* Manoelito de Souza Junior	79.25	19.65 - 20.65	8.00	*
-Pittsburgh Feb '26	PBR	* Brady Fielder	-	21.20 - 21.05	3.21	*
-Tampa Jan '26	PBR	Callum Miller	-	21.45 - 21.40	7.08	*
-New York Jan '26	PBR	* Cort McFadden	87.00	21.00 - 21.35	8.00	*
-New York Jan '26	PBR	Alvaro Ariel	-	21.35 - 21.75	2.36	*
-Manchester Dec '25	PBR	* Kaique Pacheco	-	21.40 - 20.20	2.16	*
-Glendale Oct '25	PBR	Kase Hitt	82.50	21.00 - 21.25	8.00	*
-Greensboro Sep '25	PBR	* Maverick Smith	-	21.75 - 22.00	3.17	*
-Greensboro Sep '25	PBR	* Dawson Branton	-	21.75 - 21.50	2.51	*
-Archdale Jun '25	PBR	Carlos Garcia	-	21.50 - 21.00	2.27	*
-Archdale Jun '25	PBR	Gabriel Thiago Da Silva	-	21.50 - 21.00	-	RR no nod
-Archdale Jun '24	PBR	Caleb Cantrell	85.00	20.50 - 21.00	8.00	*
-Archdale Jun '24	PBR	Alex Cantoral	-	21.50 - 21.50	3.24	*
-Lewisville Sep '23	PBR	Ben Bode	-	21.00 - 20.00	2.57	*
-Previous Matchups at probability 0.299
-Rider Count	207
-Avg Rider Rating	.201
-Total Outs	317
-Qualified Rides	94
-Riding %	29.65%
-87+ points	8.83%</t>
-  </si>
-  <si>
-    <t>Paulo Eduardo Rossetto on X26 Real Deal (BSBL)
-Qualified Ride Probability: 64.5% (confidence 8 of 10)
-Ride Score Potential: 82.61 to 88.61 points
-Paulo Eduardo Rossetto Riding Hand: Right
-Career: 142 for 334 - 42.51% - Rider Rating: *.316
-Short Rounds: 16 for 39 - 41.03%
-Current Streak: 3 / 15 - 20.00%
-PBR Current Season: Rank: 7 (42 for 84 - 50%) 497.00 pts (-395.5) - $235,394.68
-PBR Points Per Out: 6 - Points Per QR: 12
-vs. Left: 36-67 (34.95%) -- vs. Right: 70-62 (53.03%) -- vs. ?: 11-13 (45.83%) -- +18.08%/10.52% RIGHT
-X26 Real Deal - PBS -
-Power Rating: 51.27
-ALL: 14 outs 9 rides - 35.71%
-UTB: 11 outs 9 rides - 18.18%
-vs. Left:  2-2 - 50.00%
-vs. Right: 1-7 - 12.50%
-vs. Top:   2-9 - 18.18%
-Riding Hand Advantage: RIGHT (38.00%)
-Previous Matchups
-Event	Level	Matchup	Score	Marks	Time	Notes
-Glendale Oct '25	PBR	Paulo Eduardo Rossetto on 52820	86.25	21.00 - 21.00	8.00	*
-Previous Outs for X26 Real Deal
-Event	Level	Matchup	Score	Marks	Time	Notes
-Tallahassee Mar '26	PBR	* Lucas Divino	84.95	20.80 - 20.60	8.00	*
-Bridgeport Feb '26	PBR	* Andrew Alvidrez	86.40	21.00 - 20.95	8.00	*
-Jacksonville Feb '26	PBR	* Kaiden Loud	83.30	20.00 - 20.50	8.00	*
-Pittsburgh Feb '26	PBR	* Hudson Bolton	-	21.00 - 21.25	4.78	*
-Milwaukee Jan '26	PBR	* Daylon Swearingen	87.20	21.00 - 21.15	8.00	*
-New York Jan '26	PBR	* Cassio Dias	86.35	20.65 - 21.30	8.00	*
-Manchester Dec '25	PBR	* Kaiden Loud	84.70	20.35 - 20.95	8.00	*
-Las Vegas Oct '25	PBR	* Wingson Henrique da Silva	-	21.50 - 21.50	6.37	*
-Glendale Oct '25	PBR	* Paulo Eduardo Rossetto	86.25	21.00 - 21.00	8.00	*
-Glendale Oct '25	PBR	* Daniel Keeping	88.25	21.50 - 21.50	8.00	*
-Charlottesville Sep '25	PBR	Lucas Ferreira	-	21.00 - 21.00	1.25	*
-Tacoma Apr '25	PBR	* Claudio Montanha Jr.	83.50	20.00 - 20.75	8.00	*
-Memphis Feb '25	PBR	Max Castro	-	20.50 - 20.50	2.14	*
-Fort Worth Jul '24	PBR	Joao Mauro Kugel	-	21.00 - 21.00	5.24	*
-Previous Matchups at probability 0.645
-Rider Count	11
-Avg Rider Rating	.323
-Total Outs	11
-Qualified Rides	6
-Riding %	54.55%
-87+ points	18.18%</t>
-  </si>
-  <si>
-    <t>Eric Novoa on 95J Alakazoo (FFRF)
-Qualified Ride Probability: 34.3% (confidence 10 of 10)
-Ride Score Potential: 84.44 to 90.44 points
-Eric Novoa Riding Hand: Right
-Career: 29 for 72 - 40.28% - Rider Rating: .167
-Short Rounds: 3 for 13 - 23.08%
-Current Streak: 7 / 15 - 46.67%
-PBR Current Season: Rank: 67 (0 for 2 - 0%) 0.00 pts (-892.5) - $9,000.00
-PBR Points Per Out: 0 - Points Per QR: 0
-vs. Left: 6-12 (33.33%) -- vs. Right: 11-11 (50%) -- vs. ?: 7-9 (43.75%) -- +16.67%/9.72% RIGHT
-95J Alakazoo - PBS - 10257997
-Power Rating: 72.58
-ALL: 36 outs 14 rides - 61.11%
-UTB: 23 outs 7 rides - 69.57%
-vs. Left:  11-11 - 50.00%
-vs. Right: 9-3 - 75.00%
-vs. Top:   11-10 - 52.38%
-Riding Hand Advantage: LEFT (25.00%)
-Previous Outs for 95J Alakazoo
-Event	Level	Matchup	Score	Marks	Time	Notes
-Billings Apr '26	PBR	* Lucas Divino	87.75	21.35 - 21.45	8.00	*
-Grand Forks Feb '26	PBR	Tucker Mertens	-	21.10 - 21.05	2.02	*
-Tulsa Jan '26	PBR	* Dener Barbosa	-	20.95 - 21.05	5.06	*
-Granbury Nov '25	OPEN	* Thiago Salgado	86.00	20.97 - 20.97	8.00	*
-Las Vegas Oct '25	PBR	Miguel de Jesus	-	20.50 - 21.00	2.63	*
-Fort Worth Sep '25	PBR	Riquelmi Silva	86.00	21.00 - 21.00	8.00	*
-Fort Worth Sep '25	PBR	* Bob Mitchell	-	21.25 - 21.00	2.89	*
-Greensboro Sep '25	PBR	* Braidy Randolph	-	21.25 - 21.50	2.88	*
-Greensboro Sep '25	PBR	Macaulie Leather	-	20.75 - 21.00	3.98	*
-Austin Aug '25	PBR	Jeferson Silva	-	21.25 - 21.75	2.01	*
-Austin Aug '25	PBR	Dalton Krantz	-	21.50 - 21.75	3.92	*
-Duluth Jul '25	PBR	* Luciano De Castro	87.25	21.25 - 21.00	8.00	*
-Duluth Jul '25	PBR	Brody Robinson	-	21.50 - 22.00	2.99	*
-Oklahoma City Jul '25	PBR	Eric Henrique Domingos	-	22.00 - 22.25	2.45	*
-Oklahoma City Jul '25	PBR	* Sandro Batista	88.00	21.75 - 21.50	8.00	*
-Previous Matchups at probability 0.343
-Rider Count	184
-Avg Rider Rating	.223
-Total Outs	265
-Qualified Rides	104
-Riding %	39.25%
-87+ points	11.32%</t>
-  </si>
-  <si>
-    <t>Macaulie Leather on 102 Wreck It Ralph (THCC)
-Qualified Ride Probability: 23.2% (confidence 6 of 10)
-Ride Score Potential: 81.2 to 87.2 points
-Macaulie Leather Riding Hand: Left
-Career: 33 for 82 - 40.24% - Rider Rating: .193
-Short Rounds: 5 for 9 - 55.56%
-Current Streak: 4 / 15 - 26.67%
-PBR Current Season: Rank: 67 (4 for 27 - 14.8%) 0.00 pts (-892.5) - $68,882.98
-PBR Points Per Out: 0 - Points Per QR: 0
-vs. Left: 18-15 (54.55%) -- vs. Right: 4-13 (23.53%) -- vs. ?: 3-8 (27.27%) -- +31.02%/14.31% LEFT
-102 Wreck It Ralph PBS 10262368
-no compiled stats
-Previous Outs for 102 Wreck It Ralph
-Event	Level	Matchup	Score	Marks	Time	Notes
-Indianapolis Mar '26	PBR	* Bob Mitchell	-	20.70 - 20.70	5.50	*
-Reno Feb '26	PBR	Saul Zambrano	-	20.85 - 19.55	2.20	*
-Fort Worth Sep '25	PBR	Romario Leite	-	21.50 - 20.00	3.08	*
-Previous Matchups at probability 0.232
-Rider Count	262
-Avg Rider Rating	.166
-Total Outs	403
-Qualified Rides	95
-Riding %	23.57%
-87+ points	3.23%</t>
-  </si>
-  <si>
-    <t>Vinicius Pinheiro Correa on 1710 Taco Truck (TFRS)
-Qualified Ride Probability: 37.6% (confidence 5 of 10)
-Ride Score Potential: -1 to 5 points
-Vinicius Pinheiro Correa Riding Hand: Left
-Career: 44 for 122 - 36.07% - Rider Rating: *.215
-Short Rounds: 4 for 16 - 25%
-Current Streak: 8 / 15 - 53.33%
-PBR Current Season: Rank: 67 (1 for 4 - 25%) 0.00 pts (-892.5) - $15,572.53
-PBR Points Per Out: 0 - Points Per QR: 0
-vs. Left: 25-23 (52.08%) -- vs. Right: 3-29 (9.38%) -- vs. ?: 6-8 (42.86%) -- +42.7%/16.01% LEFT
-1710 Taco Truck PBS
-no compiled stats
-no recorded outs
-Previous Matchups at probability 0.376
-Rider Count	128
-Avg Rider Rating	.238
-Total Outs	176
-Qualified Rides	73
-Riding %	41.48%
-87+ points	10.8%</t>
-  </si>
-  <si>
-    <t>Dener Barbosa on C1 Me More Cowboy (TFRS)
-Qualified Ride Probability: 50.2% (confidence 6 of 10)
-Ride Score Potential: 81.2 to 87.2 points
-Dener Barbosa Riding Hand: Left
-Career: 380 for 760 - 50% - Rider Rating: *.369
-Short Rounds: 50 for 140 - 35.71%
-Current Streak: 6 / 15 - 40.00%
-PBR Current Season: Rank: 41 (16 for 37 - 43.2%) 74.00 pts (-818.5) - $93,253.57
-PBR Points Per Out: 2 - Points Per QR: 5
-vs. Left: 198-120 (62.26%) -- vs. Right: 48-133 (26.52%) -- vs. ?: 36-28 (56.25%) -- +35.74%/12.26% LEFT
-C1 Me More Cowboy PBS
-no compiled stats
-Previous Outs for C1 Me More Cowboy
-Event	Level	Matchup	Score	Marks	Time	Notes
-Salt Lake City Feb '26	PBR	* Alan de Souza	82.35	20.50 - 20.60	8.00	*
-Sacramento Jan '26	PBR	* Marco Rizzo	-	-	-	RR fell
-Previous Matchups at probability 0.502
-Rider Count	45
-Avg Rider Rating	.293
-Total Outs	54
-Qualified Rides	27
-Riding %	50%
-87+ points	9.26%</t>
-  </si>
-  <si>
-    <t>Ramon Fiorini on 230 Dance Monkey (DMDC)
-Qualified Ride Probability: 24.9% (confidence 6 of 10)
-Ride Score Potential: 82.53 to 88.53 points
-Ramon Fiorini Riding Hand: Right
-Career: 34 for 99 - 34.34% - Rider Rating: .160
-Short Rounds: 2 for 5 - 40%
-Current Streak: 7 / 15 - 46.67%
-PBR Current Season: Rank: 66 (1 for 5 - 20%) 7.00 pts (-885.5) - $39,101.98
-PBR Points Per Out: 1 - Points Per QR: 7
-vs. Left: 8-12 (40%) -- vs. Right: 14-21 (40%) -- vs. ?: 4-16 (20%) -- +0%/5.66% PUSH
-230 Dance Monkey PBS
-no compiled stats
-Previous Outs for 230 Dance Monkey
-Event	Level	Matchup	Score	Marks	Time	Notes
-Everett Feb '26	PBR	Tahj Wells	-	21.60 - 21.10	3.02	*
-Nampa Jan '26	PBR	Jace Catlin	-	18.90 - 21.20	5.08	*
-Portland Jan '26	PBR	Colt Schneiderman	-	21.60 - 20.90	1.95	*
-Previous Matchups at probability 0.249
-Rider Count	264
-Avg Rider Rating	.174
-Total Outs	411
-Qualified Rides	91
-Riding %	22.14%
-87+ points	3.41%</t>
-  </si>
-  <si>
-    <t>Mason Taylor on 22J Average Joe (TFRS)
-Qualified Ride Probability: 32% (confidence 8 of 10)
-Ride Score Potential: 81.78 to 87.78 points
-Mason Taylor Riding Hand: Right
-Career: 235 for 693 - 33.91% - Rider Rating: *.250
-Short Rounds: 22 for 99 - 22.22%
-Current Streak: 2 / 15 - 13.33%
-PBR Current Season: Rank: 51 (3 for 28 - 10.7%) 16.00 pts (-876.5) - $28,189.34
-PBR Points Per Out: 1 - Points Per QR: 5
-vs. Left: 63-164 (27.75%) -- vs. Right: 88-128 (40.74%) -- vs. ?: 16-34 (32%) -- +12.99%/6.83% RIGHT
-22J Average Joe - PBS -
-Power Rating: 61.69
-ALL: 12 outs 5 rides - 58.33%
-UTB: 5 outs 2 rides - 60%
-vs. Left:  3-4 - 42.86%
-vs. Right: 4-1 - 80.00%
-vs. Top:   4-3 - 57.14%
-Riding Hand Advantage: LEFT (37.00%)
-Previous Outs for 22J Average Joe
-Event	Level	Matchup	Score	Marks	Time	Notes
-Billings Apr '26	PBR	* Julio Cesar Marques	-	21.40 - 21.30	4.85	*
-Bucktown Feb '26	OPEN	* Daniel Keeping	84.00	20.25 - 20.25	8.00	*
-Salt Lake City Feb '26	PBR	* Hudson Bolton	-	17.80 - 16.75	-	RR inf
-Sacramento Jan '26	PBR	Wyatt Vineyard	-	-	-	RR foul
-Sacramento Jan '26	PBR	* Kade Madsen	-	21.55 - 21.60	4.75	*
-Fort Worth Nov '25	PBR	Gavin Mitchell	-	-	-	*
-Glendale Oct '25	PBR	* Hudson Bolton	87.25	21.00 - 21.25	8.00	*
-Glendale Oct '25	PBR	Riquelmi Silva	-	21.50 - 22.00	7.21	*
-Eagle Jul '25	PRCA	Dillon Tyner	84.00	22.00 - 20.00	8.00	*
-Fort Collins Jul '25	PBR	* Eduardo Aparecido	-	19.25 - 18.25	6.80	*
-Fort Collins Jul '25	PBR	* Ezekiel Mitchell	-	21.50 - 21.50	2.60	*
-Evergreen Jun '25	PRCA	Brody Nelson	-	22.00 - 21.00	4.00	(nt)
-Fort Worth Mar '25	PBR	Anthony Lyons	-	21.00 - 21.50	5.36	*
-Fort Worth Nov '24	PBR	Rogerio Venancio	84.50	21.00 - 21.00	8.00	*
-Previous Matchups at probability 0.32
-Rider Count	185
-Avg Rider Rating	.207
-Total Outs	277
-Qualified Rides	96
-Riding %	34.66%
-87+ points	7.22%</t>
-  </si>
-  <si>
-    <t>Ednelio Rodrigues on 22-9 Kay Dog (BMJM)
-Qualified Ride Probability: 17.7% (confidence 7 of 10)
-Ride Score Potential: 83.72 to 89.72 points
-Ednelio Rodrigues Riding Hand: Left
-Career: 75 for 287 - 26.13% - Rider Rating: *.206
-Short Rounds: 5 for 27 - 18.52%
-Current Streak: 0 / 15 - 0.00%
-PBR Current Season: Rank: 67 (1 for 6 - 16.7%) 0.00 pts (-892.5) - $22,645.05
-PBR Points Per Out: 0 - Points Per QR: 0
-vs. Left: 38-58 (39.58%) -- vs. Right: 11-63 (14.86%) -- vs. ?: 5-20 (20%) -- +24.72%/13.45% LEFT
-22-9 Kay Dog - PBS -
-Power Rating: 73.28
-ALL: 5 outs 1 rides - 80%
-vs. Left:  1-0 - 100.00%
-vs. Right: 2-1 - 66.67%
-vs. Top:   2-0 - 100.00%
-Riding Hand Advantage: UNKNOWN (0.00%)
-Previous Outs for 22-9 Kay Dog
-Event	Level	Matchup	Score	Marks	Time	Notes
-Billings Apr '26	PBR	* Kaiden Loud	-	21.10 - 20.90	3.07	*
-Reading Mar '26	PBR	* Dener Barbosa	-	21.60 - 21.80	1.97	*
-Reading Mar '26	PBR	Gustavo Santos Borges	-	19.70 - 21.20	3.82	*
-Perry Feb '26	PRCA	Taylor Allen	88.50	22.00 - 21.50	8.00	*
-Perry Feb '26	PRCA	Dustin Boquet	-	21.00 - 21.00	4.00	(nt)
-Previous Matchups at probability 0.177
-Rider Count	234
-Avg Rider Rating	.128
-Total Outs	320
-Qualified Rides	48
-Riding %	15%
-87+ points	1.88%</t>
-  </si>
-  <si>
-    <t>Vinicius Rodrigues Pereira on 53 Keystone (CLPB)
-Qualified Ride Probability: 24.7% (confidence 6 of 10)
-Ride Score Potential: 84.4 to 90.4 points
-Vinicius Rodrigues Pereira Riding Hand: Right
-Career: 23 for 82 - 28.05% - Rider Rating: .166
-Short Rounds: 2 for 11 - 18.18%
-Current Streak: 1 / 15 - 6.67%
-PBR Current Season: Rank: 67 (0 for 3 - 0%) 0.00 pts (-892.5) - $17,646.45
-PBR Points Per Out: 0 - Points Per QR: 0
-vs. Left: 5-17 (22.73%) -- vs. Right: 9-11 (45%) -- vs. ?: 5-13 (27.78%) -- +22.27%/16.95% RIGHT
-53 Keystone PBS
-no compiled stats
-Previous Outs for 53 Keystone
-Event	Level	Matchup	Score	Marks	Time	Notes
-Palm Desert Mar '26	PBR	Eric Novoa	-	21.20 - 21.40	3.76	*
-Palm Desert Mar '26	PBR	Grayson Cole	87.60	21.30 - 21.50	8.00	*
-Previous Matchups at probability 0.247
-Rider Count	260
-Avg Rider Rating	.175
-Total Outs	378
-Qualified Rides	106
-Riding %	28.04%
-87+ points	7.14%</t>
-  </si>
-  <si>
-    <t>Grayson Cole on 048 Rank Hank (BSBL)
-Qualified Ride Probability: 26.6% (confidence 10 of 10)
-Ride Score Potential: 83.01 to 89.01 points
-Grayson Cole Riding Hand: Right
-Career: 184 for 747 - 24.63% - Rider Rating: .167
-Short Rounds: 13 for 72 - 18.06%
-Current Streak: 3 / 15 - 20.00%
-PBR Current Season: Rank: 60 (2 for 17 - 11.8%) 8.00 pts (-884.5) - $55,628.97
-PBR Points Per Out: 0 - Points Per QR: 4
-vs. Left: 31-192 (13.9%) -- vs. Right: 80-133 (37.56%) -- vs. ?: 27-81 (25%) -- +23.66%/12.93% RIGHT
-048 Rank Hank - PBS - 10243021
-Power Rating: 69.68
-ALL: 31 outs 16 rides - 48.39%
-UTB: 27 outs 14 rides - 48.15%
-vs. Left:  5-13 - 27.78%
-vs. Right: 10-3 - 76.92%
-vs. Top:   10-13 - 43.48%
-Riding Hand Advantage: LEFT (49.00%)
-Previous Outs for 048 Rank Hank
-Event	Level	Matchup	Score	Marks	Time	Notes
-Bridgeport Feb '26	PBR	Andy Guzman	-	21.10 - 21.10	3.37	*
-Jacksonville Feb '26	PBR	* Maverick Smith	-	19.30 - 19.80	-	RR inf
-Pittsburgh Feb '26	PBR	* Bruno Carvalho	83.45	20.95 - 21.10	8.00	*
-Tampa Jan '26	PBR	* Kade Madsen	-	21.30 - 21.05	3.19	*
-Milwaukee Jan '26	PBR	* Kaiden Loud	-	21.30 - 21.10	5.66	*
-Boston Jan '26	PBR	* Everton Natan da Silva	-	21.30 - 21.20	3.77	*
-Manchester Dec '25	PBR	Cleber Henrique Marques	-	21.05 - 21.05	3.77	*
-St. Louis Dec '25	PBR	Miguel de Jesus	84.70	20.55 - 20.60	8.00	*
-St. Louis Dec '25	PBR	Dustin Herman	-	21.00 - 21.10	2.25	*
-Granbury Nov '25	OPEN	* Alex Cerqueira	88.20	21.62 - 21.62	8.00	*
-Las Vegas Oct '25	PBR	Wyatt Rogers	-	20.50 - 21.00	2.10	*
-Glendale Oct '25	PBR	* Brady Fielder	88.25	21.50 - 21.50	8.00	*
-Glendale Oct '25	PBR	* Brady Fielder	-	21.00 - 21.00	4.22	*
-Fort Worth Sep '25	PBR	Murilo Henrique de Oliveira	85.25	20.75 - 20.75	8.00	*
-Belmont Park Sep '25	PBR	* Josh Frost	86.00	21.00 - 21.00	8.00	*
-Previous Matchups at probability 0.266
-Rider Count	239
-Avg Rider Rating	.181
-Total Outs	360
-Qualified Rides	100
-Riding %	27.78%
-87+ points	6.67%</t>
-  </si>
-  <si>
-    <t>Trace Redd on 065J Uncle Doc (HWKN)
-Qualified Ride Probability: 34.3% (confidence 7 of 10)
-Ride Score Potential: 84.34 to 90.34 points
-Trace Redd Riding Hand: Right
-Career: 64 for 237 - 27% - Rider Rating: .168
-Short Rounds: 4 for 26 - 15.38%
-Current Streak: 4 / 15 - 26.67%
-PBR Current Season: Rank: 36 (6 for 24 - 25%) 95.00 pts (-797.5) - $46,556.47
-PBR Points Per Out: 4 - Points Per QR: 16
-vs. Left: 9-55 (14.06%) -- vs. Right: 29-48 (37.66%) -- vs. ?: 11-19 (36.67%) -- +23.6%/10.66% RIGHT
-065J Uncle Doc - PBS - 10276169
-Power Rating: 52.22
-ALL: 5 outs 2 rides - 60%
-vs. Left:  1-1 - 50.00%
-vs. Right: 1-1 - 50.00%
-vs. Top:   1-2 - 33.33%
-Riding Hand Advantage: UNKNOWN (0.00%)
-Previous Outs for 065J Uncle Doc
-Event	Level	Matchup	Score	Marks	Time	Notes
-Oakland Apr '26	PBR	Jairo Castellanos	-	21.40 - 22.10	3.98	*
-Salt Lake City Feb '26	PBR	* Clay Guiton	87.60	21.25 - 21.55	8.00	*
-Sacramento Jan '26	PBR	* Mauricio Gulla Moreira	86.75	21.25 - 21.05	8.00	*
-Anaheim Sep '25	PBR	* Guilherme Valleiras	-	-	-	RR foul
-Anaheim Sep '25	PBR	* Guilherme Valleiras	-	21.75 - 21.50	6.06	*
-Eugene Apr '25	PBR	Dustin Herman	-	-	-	RR chute
-Fresno Mar '25	PBR	Andy Valdez	-	21.00 - 20.50	2.03	*
-Previous Matchups at probability 0.343
-Rider Count	184
-Avg Rider Rating	.223
-Total Outs	265
-Qualified Rides	104
-Riding %	39.25%
-87+ points	11.32%</t>
-  </si>
-  <si>
-    <t>Callum Miller on 238 Frankenstomp (TFRS)
-Qualified Ride Probability: 36.1% (confidence 6 of 10)
-Ride Score Potential: 85.5 to 91.5 points
-Callum Miller Riding Hand: Right
-Career: 128 for 442 - 28.96% - Rider Rating: .190
-Short Rounds: 19 for 68 - 27.94%
-Current Streak: 2 / 15 - 13.33%
-PBR Current Season: Rank: 27 (21 for 58 - 36.2%) 209.00 pts (-683.5) - $103,513.47
-PBR Points Per Out: 4 - Points Per QR: 10
-vs. Left: 24-111 (17.78%) -- vs. Right: 65-81 (44.52%) -- vs. ?: 10-31 (24.39%) -- +26.74%/15.56% RIGHT
-238 Frankenstomp PBS 10262517
-no compiled stats
-Previous Outs for 238 Frankenstomp
-Event	Level	Matchup	Score	Marks	Time	Notes
-Billings Apr '26	PBR	* Cort McFadden	86.90	21.55 - 21.70	8.00	*
-Previous Matchups at probability 0.361
-Rider Count	142
-Avg Rider Rating	.226
-Total Outs	211
-Qualified Rides	79
-Riding %	37.44%
-87+ points	9.48%</t>
-  </si>
-  <si>
-    <t>Julio Cesar Marques on W251 Kinky Brahmer (CWTZ)
-Qualified Ride Probability: 24.7% (confidence 7 of 10)
-Ride Score Potential: 82.77 to 88.77 points
-Julio Cesar Marques Riding Hand: Right
-Career: 127 for 330 - 38.48% - Rider Rating: *.269
-Short Rounds: 13 for 35 - 37.14%
-Current Streak: 5 / 15 - 33.33%
-PBR Current Season: Rank: 12 (27 for 69 - 39.1%) 400.00 pts (-492.5) - $126,110.26
-PBR Points Per Out: 6 - Points Per QR: 15
-vs. Left: 29-65 (30.85%) -- vs. Right: 56-50 (52.83%) -- vs. ?: 14-23 (37.84%) -- +21.98%/14.35% RIGHT
-W251 Kinky Brahmer - PBS -
-Power Rating: 75.91
-ALL: 9 outs 0 rides - 100%
-vs. Left:  3-0 - 100.00%
-vs. Right: 2-0 - 100.00%
-vs. Top:   3-0 - 100.00%
-Riding Hand Advantage: UNKNOWN (0.00%)
-Previous Outs for W251 Kinky Brahmer
-Event	Level	Matchup	Score	Marks	Time	Notes
-Billings Apr '26	PBR	* Daniel Keeping	-	20.45 - 19.05	5.24	*
-Billings Apr '26	PBR	* Keyshawn Whitehorse	-	22.15 - 22.00	5.60	*
-Everett Feb '26	PBR	Shane Scott	-	21.30 - 20.70	2.55	*
-Everett Feb '26	PBR	Cash Keeling	-	21.40 - 21.20	1.98	*
-Nampa Jan '26	PBR	Jack Strong	-	-	-	RR chute
-Spokane Jan '26	PBR	Dakota Johnson	-	21.00 - 20.60	3.31	*
-Spokane Jan '26	PBR	* Dawson Branton	-	22.00 - 20.40	2.27	*
-Portland Jan '26	PBR	Alex Koberstein	-	21.30 - 20.90	2.36	*
-Kennewick Sep '25	PBR	Dustin Martinez	-	19.50 - 21.00	4.68	*
-St. Paul Jul '25	PRCA	Juan Carrillo	-	20.00 - 22.00	3.31	*
-Previous Matchups at probability 0.247
-Rider Count	260
-Avg Rider Rating	.175
-Total Outs	378
-Qualified Rides	106
-Riding %	28.04%
-87+ points	7.14%</t>
-  </si>
-  <si>
     <t>&lt;h2&gt;Rider&lt;/h2&gt;&lt;p&gt;&lt;strong&gt;Career:&amp;nbsp;&lt;/strong&gt;Career: 496 for 1134 - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;43.74%&lt;/em&gt;&lt;/span&gt; - Rider Rating: *.360&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Season:&amp;nbsp;&lt;/strong&gt;Rank&amp;nbsp;&lt;span style="color: #ff0000;"&gt;30&lt;/span&gt; (31 for 72 - &lt;em&gt;43.1%&lt;/em&gt;)&lt;em&gt;&lt;br /&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Points:&amp;nbsp;&lt;/strong&gt;189.00 pts &lt;span style="color: #ff0000;"&gt;&lt;em&gt;(-703.5)&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Earnings:&amp;nbsp;&lt;/strong&gt;&lt;span style="color: #008000;"&gt;&lt;em&gt;$133,872.04&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Potential&lt;/strong&gt;:&amp;nbsp;83.15 to 89.15 points&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;&lt;span style="text-decoration: underline;"&gt;&lt;strong&gt;Bull&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;ALL:&lt;/strong&gt; 31 outs 13 rides - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;58.06%&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;UTB:&lt;/strong&gt; 17 outs 10 rides - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;41.18%&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;em&gt;&lt;span style="color: #ff0000;"&gt;*No Previous Matchups&lt;/span&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;</t>
   </si>
   <si>
@@ -3010,13 +1510,19 @@
   </si>
   <si>
     <t>&lt;h2&gt;Rider&lt;/h2&gt;&lt;p&gt;&lt;strong&gt;Career:&amp;nbsp;&lt;/strong&gt;Career: 127 for 330 - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;38.48%&lt;/em&gt;&lt;/span&gt; - Rider Rating: *.269&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Season:&amp;nbsp;&lt;/strong&gt;Rank&amp;nbsp;&lt;span style="color: #ff0000;"&gt;12&lt;/span&gt; (27 for 69 - &lt;em&gt;39.1%&lt;/em&gt;)&lt;em&gt;&lt;br /&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Points:&amp;nbsp;&lt;/strong&gt;400.00 pts &lt;span style="color: #ff0000;"&gt;&lt;em&gt;(-492.5)&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Earnings:&amp;nbsp;&lt;/strong&gt;&lt;span style="color: #008000;"&gt;&lt;em&gt;$126,110.26&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Potential&lt;/strong&gt;:&amp;nbsp;82.77 to 88.77 points&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;&lt;span style="text-decoration: underline;"&gt;&lt;strong&gt;Bull&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;ALL:&lt;/strong&gt; 9 outs 0 rides - &lt;span style="color: #ff0000;"&gt;&lt;em&gt;100%&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;em&gt;&lt;span style="color: #ff0000;"&gt;*No Previous Matchups&lt;/span&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t>u</t>
+  </si>
+  <si>
+    <t>rr</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -3104,6 +1610,19 @@
       <name val="Verdana"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -3126,7 +1645,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
@@ -3146,12 +1665,66 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="3">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -3162,6 +1735,35 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{29AB6ECE-D30B-794C-A08A-C4FD7E2946CA}" name="Table1" displayName="Table1" ref="A1:T48" totalsRowShown="0">
+  <autoFilter ref="A1:T48" xr:uid="{29AB6ECE-D30B-794C-A08A-C4FD7E2946CA}"/>
+  <tableColumns count="20">
+    <tableColumn id="1" xr3:uid="{057266C1-D9C1-5F49-AC88-A125C8B14462}" name="Number"/>
+    <tableColumn id="2" xr3:uid="{F49259B7-315C-D044-9EB5-E22ED4D8FA09}" name="Bull Power"/>
+    <tableColumn id="3" xr3:uid="{FAF03574-DD5A-0749-A06D-920167AA280B}" name="Bull Record"/>
+    <tableColumn id="4" xr3:uid="{B6677A56-E822-424E-9F80-9E7A824FA88E}" name="Bull Name"/>
+    <tableColumn id="5" xr3:uid="{E00B91EA-C0EF-4C4A-B55A-DEEB54CDC1BE}" name="ABBI"/>
+    <tableColumn id="6" xr3:uid="{13BA6054-661C-E848-BB06-DEE83995CDF5}" name="Stock Contractor"/>
+    <tableColumn id="7" xr3:uid="{1D3B3007-F07E-AF46-A4AE-3AC4B7D60928}" name="Event"/>
+    <tableColumn id="8" xr3:uid="{7EC8A00C-6BA4-6B4C-AD85-F46BEEB531A6}" name="Section"/>
+    <tableColumn id="9" xr3:uid="{383F777F-0BBB-D74D-9D40-FC2CF4F9A864}" name="Ride Probability (confidence"/>
+    <tableColumn id="10" xr3:uid="{E164D2B9-1D63-D944-A0B5-00C5ADCFE653}" name="Link to matchup"/>
+    <tableColumn id="11" xr3:uid="{6869D794-513E-C14F-9692-0E3B8B9C73F6}" name="Riding Hand"/>
+    <tableColumn id="12" xr3:uid="{C343CCBD-AE69-B74C-A29A-6C42C25A2477}" name="Advantage"/>
+    <tableColumn id="13" xr3:uid="{97D8911E-BD82-E046-A84D-9E3708756261}" name="Bull Direction"/>
+    <tableColumn id="14" xr3:uid="{7EF2BBF5-6F4A-BB48-BA46-0EF03F730E3C}" name="Notes"/>
+    <tableColumn id="15" xr3:uid="{964A6300-0A14-1F4A-B7D5-F8A575A7A7C6}" name="Bull Rider"/>
+    <tableColumn id="16" xr3:uid="{C294426E-90D4-4B40-8CCE-7290D333711C}" name="Bull Score" dataDxfId="2"/>
+    <tableColumn id="17" xr3:uid="{12986599-041A-4A41-A7F3-890CC2B2C123}" name="Rider Score" dataDxfId="1"/>
+    <tableColumn id="18" xr3:uid="{544C1B1E-6217-FA4B-84CF-09220BB752DC}" name="Total" dataDxfId="0"/>
+    <tableColumn id="19" xr3:uid="{26278A47-273A-EE4F-9E6C-59652EA0A482}" name="Post Ride Notes"/>
+    <tableColumn id="20" xr3:uid="{5F694644-B073-D54E-9A0A-1B5118538A0E}" name="Pick"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3481,20 +2083,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01ACAA71-EF8B-E143-BCEC-D101B7DB858C}">
-  <dimension ref="A1:Y55"/>
+  <dimension ref="A1:AA57"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="7.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="3" max="3" width="12.83203125" customWidth="1"/>
     <col min="4" max="4" width="31.83203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="24.1640625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="27.5" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="11.1640625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="13.83203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.33203125" customWidth="1"/>
+    <col min="8" max="8" width="9.6640625" customWidth="1"/>
+    <col min="9" max="9" width="6" customWidth="1"/>
+    <col min="10" max="10" width="2.1640625" customWidth="1"/>
+    <col min="11" max="11" width="5.6640625" customWidth="1"/>
+    <col min="12" max="12" width="11.83203125" customWidth="1"/>
+    <col min="13" max="13" width="7" customWidth="1"/>
+    <col min="15" max="15" width="31.5" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.6640625" customWidth="1"/>
+    <col min="17" max="17" width="13.1640625" customWidth="1"/>
+    <col min="19" max="19" width="16.1640625" customWidth="1"/>
     <col min="20" max="20" width="8.1640625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3599,17 +2205,21 @@
         <v>29</v>
       </c>
       <c r="N2" t="s">
-        <v>445</v>
+        <v>405</v>
       </c>
       <c r="O2" s="14" t="s">
         <v>141</v>
       </c>
-      <c r="P2" s="9"/>
-      <c r="Q2" s="10"/>
-      <c r="R2" s="11"/>
-      <c r="Y2" s="13" t="s">
-        <v>405</v>
-      </c>
+      <c r="P2">
+        <v>41.5</v>
+      </c>
+      <c r="Q2">
+        <v>0</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="Y2" s="13"/>
     </row>
     <row r="3" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
@@ -3644,23 +2254,27 @@
         <v>27</v>
       </c>
       <c r="L3" t="s">
-        <v>446</v>
+        <v>406</v>
       </c>
       <c r="M3" t="s">
         <v>36</v>
       </c>
       <c r="N3" t="s">
-        <v>447</v>
+        <v>407</v>
       </c>
       <c r="O3" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="P3" s="9"/>
-      <c r="Q3" s="10"/>
-      <c r="R3" s="11"/>
-      <c r="Y3" s="13" t="s">
-        <v>406</v>
-      </c>
+      <c r="P3">
+        <v>43.2</v>
+      </c>
+      <c r="Q3">
+        <v>0</v>
+      </c>
+      <c r="R3">
+        <v>0</v>
+      </c>
+      <c r="Y3" s="13"/>
     </row>
     <row r="4" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
@@ -3697,23 +2311,27 @@
         <v>27</v>
       </c>
       <c r="L4" t="s">
-        <v>446</v>
+        <v>406</v>
       </c>
       <c r="M4" t="s">
         <v>36</v>
       </c>
       <c r="N4" t="s">
-        <v>448</v>
+        <v>408</v>
       </c>
       <c r="O4" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="P4" s="9"/>
-      <c r="Q4" s="10"/>
-      <c r="R4" s="11"/>
-      <c r="Y4" s="13" t="s">
-        <v>407</v>
-      </c>
+      <c r="P4">
+        <v>42.8</v>
+      </c>
+      <c r="Q4">
+        <v>0</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="13"/>
     </row>
     <row r="5" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
@@ -3750,23 +2368,27 @@
         <v>27</v>
       </c>
       <c r="L5" t="s">
-        <v>449</v>
+        <v>409</v>
       </c>
       <c r="M5" t="s">
         <v>29</v>
       </c>
       <c r="N5" t="s">
-        <v>450</v>
+        <v>410</v>
       </c>
       <c r="O5" s="14" t="s">
         <v>120</v>
       </c>
-      <c r="P5" s="9"/>
-      <c r="Q5" s="10"/>
-      <c r="R5" s="11"/>
-      <c r="Y5" s="13" t="s">
-        <v>408</v>
-      </c>
+      <c r="P5">
+        <v>42.3</v>
+      </c>
+      <c r="Q5">
+        <v>44.65</v>
+      </c>
+      <c r="R5">
+        <v>86.95</v>
+      </c>
+      <c r="Y5" s="13"/>
     </row>
     <row r="6" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
@@ -3803,23 +2425,27 @@
         <v>43</v>
       </c>
       <c r="L6" t="s">
-        <v>451</v>
+        <v>411</v>
       </c>
       <c r="M6" t="s">
         <v>99</v>
       </c>
       <c r="N6" t="s">
-        <v>452</v>
+        <v>412</v>
       </c>
       <c r="O6" s="14" t="s">
         <v>131</v>
       </c>
-      <c r="P6" s="9"/>
-      <c r="Q6" s="10"/>
-      <c r="R6" s="11"/>
-      <c r="Y6" s="13" t="s">
-        <v>409</v>
-      </c>
+      <c r="P6">
+        <v>43.75</v>
+      </c>
+      <c r="Q6">
+        <v>0</v>
+      </c>
+      <c r="R6">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="13"/>
     </row>
     <row r="7" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
@@ -3852,14 +2478,20 @@
         <v>43</v>
       </c>
       <c r="N7" t="s">
-        <v>453</v>
+        <v>413</v>
       </c>
       <c r="O7" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="P7" s="9"/>
-      <c r="Q7" s="10"/>
-      <c r="R7" s="11"/>
+      <c r="P7">
+        <v>41.9</v>
+      </c>
+      <c r="Q7">
+        <v>44.4</v>
+      </c>
+      <c r="R7">
+        <v>86.3</v>
+      </c>
       <c r="Y7" s="13"/>
     </row>
     <row r="8" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -3895,20 +2527,26 @@
         <v>43</v>
       </c>
       <c r="L8" t="s">
-        <v>454</v>
+        <v>414</v>
       </c>
       <c r="M8" t="s">
         <v>29</v>
       </c>
       <c r="N8" t="s">
-        <v>455</v>
+        <v>415</v>
       </c>
       <c r="O8" s="1" t="s">
         <v>383</v>
       </c>
-      <c r="P8" s="9"/>
-      <c r="Q8" s="10"/>
-      <c r="R8" s="11"/>
+      <c r="P8">
+        <v>33.9</v>
+      </c>
+      <c r="Q8">
+        <v>35.65</v>
+      </c>
+      <c r="R8">
+        <v>69.55</v>
+      </c>
       <c r="Y8" s="13"/>
     </row>
     <row r="9" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -3946,17 +2584,21 @@
         <v>27</v>
       </c>
       <c r="N9" t="s">
-        <v>456</v>
+        <v>416</v>
       </c>
       <c r="O9" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="P9" s="9"/>
-      <c r="Q9" s="10"/>
-      <c r="R9" s="11"/>
-      <c r="Y9" s="13" t="s">
-        <v>410</v>
-      </c>
+      <c r="P9">
+        <v>42.7</v>
+      </c>
+      <c r="Q9">
+        <v>46.15</v>
+      </c>
+      <c r="R9">
+        <v>88.85</v>
+      </c>
+      <c r="Y9" s="13"/>
     </row>
     <row r="10" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
@@ -3991,23 +2633,27 @@
         <v>27</v>
       </c>
       <c r="L10" t="s">
-        <v>457</v>
+        <v>417</v>
       </c>
       <c r="M10" t="s">
         <v>29</v>
       </c>
       <c r="N10" t="s">
-        <v>458</v>
+        <v>418</v>
       </c>
       <c r="O10" s="1" t="s">
         <v>379</v>
       </c>
-      <c r="P10" s="9"/>
-      <c r="Q10" s="10"/>
-      <c r="R10" s="11"/>
-      <c r="Y10" s="13" t="s">
-        <v>411</v>
-      </c>
+      <c r="P10">
+        <v>41.05</v>
+      </c>
+      <c r="Q10">
+        <v>41.65</v>
+      </c>
+      <c r="R10">
+        <v>82.7</v>
+      </c>
+      <c r="Y10" s="13"/>
     </row>
     <row r="11" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
@@ -4042,23 +2688,27 @@
         <v>27</v>
       </c>
       <c r="L11" t="s">
-        <v>459</v>
+        <v>419</v>
       </c>
       <c r="M11" t="s">
         <v>29</v>
       </c>
       <c r="N11" t="s">
-        <v>460</v>
+        <v>420</v>
       </c>
       <c r="O11" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="P11" s="9"/>
-      <c r="Q11" s="10"/>
-      <c r="R11" s="11"/>
-      <c r="Y11" s="13" t="s">
-        <v>412</v>
-      </c>
+      <c r="P11">
+        <v>42</v>
+      </c>
+      <c r="Q11">
+        <v>44.8</v>
+      </c>
+      <c r="R11">
+        <v>86.8</v>
+      </c>
+      <c r="Y11" s="13"/>
     </row>
     <row r="12" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
@@ -4095,17 +2745,21 @@
         <v>27</v>
       </c>
       <c r="N12" t="s">
-        <v>461</v>
+        <v>421</v>
       </c>
       <c r="O12" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="P12" s="9"/>
-      <c r="Q12" s="10"/>
-      <c r="R12" s="11"/>
-      <c r="Y12" s="13" t="s">
-        <v>413</v>
-      </c>
+      <c r="P12">
+        <v>41.65</v>
+      </c>
+      <c r="Q12">
+        <v>43.55</v>
+      </c>
+      <c r="R12">
+        <v>85.2</v>
+      </c>
+      <c r="Y12" s="13"/>
     </row>
     <row r="13" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
@@ -4140,23 +2794,27 @@
         <v>27</v>
       </c>
       <c r="L13" t="s">
-        <v>462</v>
+        <v>422</v>
       </c>
       <c r="M13" t="s">
         <v>99</v>
       </c>
       <c r="N13" t="s">
-        <v>463</v>
+        <v>423</v>
       </c>
       <c r="O13" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="P13" s="9"/>
-      <c r="Q13" s="10"/>
-      <c r="R13" s="11"/>
-      <c r="Y13" s="13" t="s">
-        <v>414</v>
-      </c>
+      <c r="P13">
+        <v>44</v>
+      </c>
+      <c r="Q13">
+        <v>0</v>
+      </c>
+      <c r="R13">
+        <v>0</v>
+      </c>
+      <c r="Y13" s="13"/>
     </row>
     <row r="14" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
@@ -4193,23 +2851,27 @@
         <v>43</v>
       </c>
       <c r="L14" t="s">
-        <v>446</v>
+        <v>406</v>
       </c>
       <c r="M14" t="s">
         <v>36</v>
       </c>
       <c r="N14" t="s">
-        <v>464</v>
+        <v>424</v>
       </c>
       <c r="O14" s="14" t="s">
         <v>367</v>
       </c>
-      <c r="P14" s="9"/>
-      <c r="Q14" s="10"/>
-      <c r="R14" s="11"/>
-      <c r="Y14" s="13" t="s">
-        <v>415</v>
-      </c>
+      <c r="P14">
+        <v>44.35</v>
+      </c>
+      <c r="Q14">
+        <v>0</v>
+      </c>
+      <c r="R14">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="13"/>
     </row>
     <row r="15" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
@@ -4244,23 +2906,27 @@
         <v>27</v>
       </c>
       <c r="L15" t="s">
-        <v>465</v>
+        <v>425</v>
       </c>
       <c r="M15" t="s">
         <v>29</v>
       </c>
       <c r="N15" t="s">
-        <v>466</v>
+        <v>426</v>
       </c>
       <c r="O15" s="14" t="s">
         <v>363</v>
       </c>
-      <c r="P15" s="9"/>
-      <c r="Q15" s="10"/>
-      <c r="R15" s="11"/>
-      <c r="Y15" s="13" t="s">
-        <v>416</v>
-      </c>
+      <c r="P15">
+        <v>42.15</v>
+      </c>
+      <c r="Q15">
+        <v>45.35</v>
+      </c>
+      <c r="R15">
+        <v>87.5</v>
+      </c>
+      <c r="Y15" s="13"/>
     </row>
     <row r="16" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
@@ -4295,95 +2961,73 @@
         <v>27</v>
       </c>
       <c r="L16" t="s">
-        <v>467</v>
+        <v>427</v>
       </c>
       <c r="M16" t="s">
         <v>99</v>
       </c>
       <c r="N16" t="s">
-        <v>468</v>
+        <v>428</v>
       </c>
       <c r="O16" s="14" t="s">
         <v>358</v>
       </c>
-      <c r="P16" s="9"/>
-      <c r="Q16" s="10"/>
-      <c r="R16" s="11"/>
-      <c r="Y16" s="13" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="17" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="1">
+      <c r="P16">
+        <v>35.9</v>
+      </c>
+      <c r="Q16">
+        <v>0</v>
+      </c>
+      <c r="R16" t="s">
+        <v>466</v>
+      </c>
+      <c r="Y16" s="13"/>
+    </row>
+    <row r="17" spans="1:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="1"/>
+      <c r="B17" s="1"/>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1"/>
+      <c r="G17" s="1"/>
+      <c r="H17" s="1"/>
+      <c r="I17" s="1"/>
+      <c r="J17" s="2"/>
+      <c r="O17" s="14" t="s">
+        <v>358</v>
+      </c>
+      <c r="P17">
+        <v>42.3</v>
+      </c>
+      <c r="Q17">
+        <v>46.3</v>
+      </c>
+      <c r="R17">
+        <v>88.6</v>
+      </c>
+      <c r="Y17" s="13"/>
+    </row>
+    <row r="18" spans="1:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="1">
         <v>14</v>
       </c>
-      <c r="B17" s="1">
+      <c r="B18" s="1">
         <v>78.86</v>
       </c>
-      <c r="C17" s="1" t="s">
+      <c r="C18" s="1" t="s">
         <v>352</v>
       </c>
-      <c r="D17" s="1" t="s">
+      <c r="D18" s="1" t="s">
         <v>353</v>
       </c>
-      <c r="E17" s="1">
+      <c r="E18" s="1">
         <v>10276006</v>
       </c>
-      <c r="F17" s="1" t="s">
+      <c r="F18" s="1" t="s">
         <v>354</v>
-      </c>
-      <c r="G17" s="1" t="s">
-        <v>281</v>
-      </c>
-      <c r="H17" s="1">
-        <v>4</v>
-      </c>
-      <c r="I17" s="1" t="s">
-        <v>355</v>
-      </c>
-      <c r="J17" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="K17" t="s">
-        <v>27</v>
-      </c>
-      <c r="L17" t="s">
-        <v>469</v>
-      </c>
-      <c r="M17" t="s">
-        <v>99</v>
-      </c>
-      <c r="N17" t="s">
-        <v>470</v>
-      </c>
-      <c r="O17" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="P17" s="9"/>
-      <c r="Q17" s="10"/>
-      <c r="R17" s="11"/>
-      <c r="Y17" s="13" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="18" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="1">
-        <v>15</v>
-      </c>
-      <c r="B18" s="1">
-        <v>57.72</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>349</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>350</v>
-      </c>
-      <c r="E18" s="1">
-        <v>10243159</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>310</v>
       </c>
       <c r="G18" s="1" t="s">
         <v>281</v>
@@ -4392,7 +3036,7 @@
         <v>4</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>26</v>
@@ -4401,39 +3045,43 @@
         <v>27</v>
       </c>
       <c r="L18" t="s">
-        <v>471</v>
+        <v>429</v>
       </c>
       <c r="M18" t="s">
-        <v>29</v>
+        <v>99</v>
       </c>
       <c r="N18" t="s">
-        <v>472</v>
+        <v>430</v>
       </c>
       <c r="O18" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="P18" s="9"/>
-      <c r="Q18" s="10"/>
-      <c r="R18" s="11"/>
-      <c r="Y18" s="13" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="19" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <v>187</v>
+      </c>
+      <c r="P18">
+        <v>42.25</v>
+      </c>
+      <c r="Q18">
+        <v>0</v>
+      </c>
+      <c r="R18">
+        <v>0</v>
+      </c>
+      <c r="Y18" s="13"/>
+    </row>
+    <row r="19" spans="1:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B19" s="1">
-        <v>65.19</v>
+        <v>57.72</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="E19" s="1">
-        <v>10205390</v>
+        <v>10243159</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>310</v>
@@ -4445,7 +3093,7 @@
         <v>4</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>26</v>
@@ -4454,87 +3102,73 @@
         <v>27</v>
       </c>
       <c r="L19" t="s">
-        <v>473</v>
+        <v>431</v>
       </c>
       <c r="M19" t="s">
-        <v>99</v>
+        <v>29</v>
       </c>
       <c r="N19" t="s">
-        <v>474</v>
+        <v>432</v>
       </c>
       <c r="O19" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="P19" s="9"/>
-      <c r="Q19" s="10"/>
-      <c r="R19" s="11"/>
-      <c r="Y19" s="13" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="20" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="1">
-        <v>17</v>
-      </c>
-      <c r="B20" s="1">
-        <v>66.97</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>344</v>
-      </c>
+        <v>238</v>
+      </c>
+      <c r="P19">
+        <v>37.85</v>
+      </c>
+      <c r="Q19">
+        <v>0</v>
+      </c>
+      <c r="R19" t="s">
+        <v>466</v>
+      </c>
+      <c r="Y19" s="13"/>
+    </row>
+    <row r="20" spans="1:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="1"/>
+      <c r="B20" s="1"/>
+      <c r="C20" s="1"/>
       <c r="D20" s="1" t="s">
-        <v>52</v>
+        <v>466</v>
       </c>
       <c r="E20" s="1"/>
-      <c r="F20" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="G20" s="1" t="s">
-        <v>281</v>
-      </c>
-      <c r="H20" s="1">
-        <v>4</v>
-      </c>
-      <c r="I20" s="1" t="s">
-        <v>345</v>
-      </c>
-      <c r="J20" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="K20" t="s">
-        <v>27</v>
-      </c>
-      <c r="N20" t="s">
-        <v>475</v>
-      </c>
+      <c r="F20" s="1"/>
+      <c r="G20" s="1"/>
+      <c r="H20" s="1"/>
+      <c r="I20" s="1"/>
+      <c r="J20" s="2"/>
       <c r="O20" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="P20" s="9"/>
-      <c r="Q20" s="10"/>
-      <c r="R20" s="11"/>
-      <c r="Y20" s="13" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="21" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <v>238</v>
+      </c>
+      <c r="P20" s="9">
+        <v>43.15</v>
+      </c>
+      <c r="Q20" s="10">
+        <v>43.65</v>
+      </c>
+      <c r="R20" s="11">
+        <v>86.8</v>
+      </c>
+      <c r="Y20" s="13"/>
+    </row>
+    <row r="21" spans="1:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B21" s="1">
-        <v>75.709999999999994</v>
+        <v>65.19</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="E21" s="1">
-        <v>10231548</v>
+        <v>10205390</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>342</v>
+        <v>310</v>
       </c>
       <c r="G21" s="1" t="s">
         <v>281</v>
@@ -4543,60 +3177,62 @@
         <v>4</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>26</v>
       </c>
       <c r="K21" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="L21" t="s">
-        <v>476</v>
+        <v>433</v>
       </c>
       <c r="M21" t="s">
-        <v>29</v>
+        <v>99</v>
       </c>
       <c r="N21" t="s">
-        <v>477</v>
+        <v>434</v>
       </c>
       <c r="O21" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="P21" s="9"/>
-      <c r="Q21" s="10"/>
-      <c r="R21" s="11"/>
-      <c r="Y21" s="13" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="22" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <v>54</v>
+      </c>
+      <c r="P21">
+        <v>43.5</v>
+      </c>
+      <c r="Q21">
+        <v>0</v>
+      </c>
+      <c r="R21">
+        <v>0</v>
+      </c>
+      <c r="Y21" s="13"/>
+    </row>
+    <row r="22" spans="1:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="1">
-        <v>19</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>105</v>
+        <v>17</v>
+      </c>
+      <c r="B22" s="1">
+        <v>66.97</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>344</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>338</v>
-      </c>
-      <c r="E22" s="1">
-        <v>10268851</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="E22" s="1"/>
       <c r="F22" s="1" t="s">
-        <v>334</v>
+        <v>53</v>
       </c>
       <c r="G22" s="1" t="s">
         <v>281</v>
       </c>
       <c r="H22" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>26</v>
@@ -4604,52 +3240,50 @@
       <c r="K22" t="s">
         <v>27</v>
       </c>
-      <c r="L22" t="s">
-        <v>465</v>
-      </c>
-      <c r="M22" t="s">
-        <v>29</v>
-      </c>
       <c r="N22" t="s">
-        <v>478</v>
-      </c>
-      <c r="O22" s="14" t="s">
-        <v>136</v>
-      </c>
-      <c r="P22" s="9"/>
-      <c r="Q22" s="10"/>
-      <c r="R22" s="11"/>
-      <c r="Y22" s="13" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="23" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <v>435</v>
+      </c>
+      <c r="O22" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="P22">
+        <v>42.05</v>
+      </c>
+      <c r="Q22">
+        <v>44.5</v>
+      </c>
+      <c r="R22">
+        <v>86.55</v>
+      </c>
+      <c r="Y22" s="13"/>
+    </row>
+    <row r="23" spans="1:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="1">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B23" s="1">
-        <v>77.819999999999993</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>117</v>
+        <v>75.709999999999994</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>340</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="E23" s="1">
-        <v>10229189</v>
+        <v>10231548</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="G23" s="1" t="s">
         <v>281</v>
       </c>
       <c r="H23" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>26</v>
@@ -4658,39 +3292,43 @@
         <v>43</v>
       </c>
       <c r="L23" t="s">
-        <v>446</v>
+        <v>436</v>
       </c>
       <c r="M23" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="N23" t="s">
-        <v>479</v>
-      </c>
-      <c r="O23" s="14" t="s">
-        <v>146</v>
-      </c>
-      <c r="P23" s="9"/>
-      <c r="Q23" s="10"/>
-      <c r="R23" s="11"/>
-      <c r="Y23" s="13" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="24" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <v>437</v>
+      </c>
+      <c r="O23" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="P23">
+        <v>38.700000000000003</v>
+      </c>
+      <c r="Q23">
+        <v>0</v>
+      </c>
+      <c r="R23">
+        <v>0</v>
+      </c>
+      <c r="Y23" s="13"/>
+    </row>
+    <row r="24" spans="1:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="1">
-        <v>21</v>
-      </c>
-      <c r="B24" s="1">
-        <v>73.45</v>
+        <v>19</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>31</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>332</v>
+        <v>105</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="E24" s="1">
-        <v>10262490</v>
+        <v>10268851</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>334</v>
@@ -4702,49 +3340,55 @@
         <v>5</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>26</v>
       </c>
       <c r="K24" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="L24" t="s">
-        <v>74</v>
+        <v>425</v>
       </c>
       <c r="M24" t="s">
-        <v>99</v>
+        <v>29</v>
       </c>
       <c r="N24" t="s">
-        <v>480</v>
+        <v>438</v>
       </c>
       <c r="O24" s="14" t="s">
-        <v>66</v>
-      </c>
-      <c r="P24" s="9"/>
-      <c r="Q24" s="10"/>
-      <c r="R24" s="11"/>
-      <c r="Y24" s="13" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="25" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <v>136</v>
+      </c>
+      <c r="P24">
+        <v>43.65</v>
+      </c>
+      <c r="Q24">
+        <v>45.35</v>
+      </c>
+      <c r="R24">
+        <v>89</v>
+      </c>
+      <c r="Y24" s="13"/>
+    </row>
+    <row r="25" spans="1:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="1">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B25" s="1">
-        <v>74.900000000000006</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>329</v>
+        <v>77.819999999999993</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>117</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>330</v>
-      </c>
-      <c r="E25" s="1"/>
+        <v>336</v>
+      </c>
+      <c r="E25" s="1">
+        <v>10229189</v>
+      </c>
       <c r="F25" s="1" t="s">
-        <v>84</v>
+        <v>334</v>
       </c>
       <c r="G25" s="1" t="s">
         <v>281</v>
@@ -4753,51 +3397,55 @@
         <v>5</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>26</v>
       </c>
       <c r="K25" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="L25" t="s">
-        <v>481</v>
+        <v>406</v>
       </c>
       <c r="M25" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="N25" t="s">
-        <v>482</v>
+        <v>439</v>
       </c>
       <c r="O25" s="14" t="s">
-        <v>108</v>
-      </c>
-      <c r="P25" s="9"/>
-      <c r="Q25" s="10"/>
-      <c r="R25" s="11"/>
-      <c r="Y25" s="13" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="26" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <v>146</v>
+      </c>
+      <c r="P25">
+        <v>44.65</v>
+      </c>
+      <c r="Q25">
+        <v>37.700000000000003</v>
+      </c>
+      <c r="R25">
+        <v>82.35</v>
+      </c>
+      <c r="Y25" s="13"/>
+    </row>
+    <row r="26" spans="1:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="1">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B26" s="1">
-        <v>61.01</v>
+        <v>73.45</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="E26" s="1">
-        <v>10270857</v>
+        <v>10262490</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>287</v>
+        <v>334</v>
       </c>
       <c r="G26" s="1" t="s">
         <v>281</v>
@@ -4806,45 +3454,49 @@
         <v>5</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>26</v>
       </c>
       <c r="K26" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="L26" t="s">
-        <v>483</v>
+        <v>74</v>
       </c>
       <c r="M26" t="s">
         <v>99</v>
       </c>
       <c r="N26" t="s">
-        <v>484</v>
+        <v>440</v>
       </c>
       <c r="O26" s="14" t="s">
-        <v>250</v>
-      </c>
-      <c r="P26" s="9"/>
-      <c r="Q26" s="10"/>
-      <c r="R26" s="11"/>
-      <c r="Y26" s="13" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="27" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <v>66</v>
+      </c>
+      <c r="P26">
+        <v>43.35</v>
+      </c>
+      <c r="Q26">
+        <v>0</v>
+      </c>
+      <c r="R26">
+        <v>0</v>
+      </c>
+      <c r="Y26" s="13"/>
+    </row>
+    <row r="27" spans="1:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="1">
-        <v>24</v>
-      </c>
-      <c r="B27" s="8">
-        <v>84.69</v>
+        <v>22</v>
+      </c>
+      <c r="B27" s="1">
+        <v>74.900000000000006</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="E27" s="1"/>
       <c r="F27" s="1" t="s">
@@ -4857,111 +3509,127 @@
         <v>5</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>26</v>
       </c>
       <c r="K27" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="L27" t="s">
-        <v>485</v>
+        <v>441</v>
       </c>
       <c r="M27" t="s">
         <v>29</v>
       </c>
       <c r="N27" t="s">
-        <v>486</v>
+        <v>442</v>
       </c>
       <c r="O27" s="14" t="s">
-        <v>151</v>
-      </c>
-      <c r="P27" s="9"/>
-      <c r="Q27" s="10"/>
-      <c r="R27" s="11"/>
-      <c r="Y27" s="13" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="28" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+      <c r="P27" s="16">
+        <v>42.3</v>
+      </c>
+      <c r="Q27" s="16">
+        <v>44.6</v>
+      </c>
+      <c r="R27" s="16">
+        <v>86.9</v>
+      </c>
+      <c r="W27" s="15"/>
+      <c r="X27" s="15"/>
+      <c r="Y27" s="15"/>
+      <c r="Z27" s="15"/>
+      <c r="AA27" s="15"/>
+    </row>
+    <row r="28" spans="1:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="1">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B28" s="1">
-        <v>42.09</v>
+        <v>61.01</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="E28" s="1">
-        <v>10229166</v>
+        <v>10270857</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>53</v>
+        <v>287</v>
       </c>
       <c r="G28" s="1" t="s">
         <v>281</v>
       </c>
       <c r="H28" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>26</v>
       </c>
       <c r="K28" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="L28" t="s">
-        <v>487</v>
+        <v>443</v>
       </c>
       <c r="M28" t="s">
-        <v>29</v>
+        <v>99</v>
       </c>
       <c r="N28" t="s">
-        <v>488</v>
-      </c>
-      <c r="O28" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="P28" s="9"/>
-      <c r="Q28" s="10"/>
-      <c r="R28" s="11"/>
-      <c r="Y28" s="13" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="29" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <v>444</v>
+      </c>
+      <c r="O28" s="14" t="s">
+        <v>250</v>
+      </c>
+      <c r="P28" s="16">
+        <v>43.6</v>
+      </c>
+      <c r="Q28" s="16">
+        <v>0</v>
+      </c>
+      <c r="R28" s="16">
+        <v>0</v>
+      </c>
+      <c r="W28" s="16"/>
+      <c r="X28" s="16"/>
+      <c r="Y28" s="16"/>
+      <c r="Z28" s="16"/>
+      <c r="AA28" s="16"/>
+    </row>
+    <row r="29" spans="1:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="1">
-        <v>26</v>
-      </c>
-      <c r="B29" s="1">
-        <v>55.03</v>
+        <v>24</v>
+      </c>
+      <c r="B29" s="8">
+        <v>84.69</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="E29" s="1"/>
       <c r="F29" s="1" t="s">
-        <v>53</v>
+        <v>84</v>
       </c>
       <c r="G29" s="1" t="s">
         <v>281</v>
       </c>
       <c r="H29" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>26</v>
@@ -4970,42 +3638,50 @@
         <v>43</v>
       </c>
       <c r="L29" t="s">
-        <v>489</v>
+        <v>445</v>
       </c>
       <c r="M29" t="s">
-        <v>99</v>
+        <v>29</v>
       </c>
       <c r="N29" t="s">
-        <v>490</v>
-      </c>
-      <c r="O29" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="P29" s="9"/>
-      <c r="Q29" s="10"/>
-      <c r="R29" s="11"/>
-      <c r="Y29" s="13" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="30" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <v>446</v>
+      </c>
+      <c r="O29" s="14" t="s">
+        <v>151</v>
+      </c>
+      <c r="P29" s="16">
+        <v>43.45</v>
+      </c>
+      <c r="Q29" s="16">
+        <v>0</v>
+      </c>
+      <c r="R29" s="16">
+        <v>0</v>
+      </c>
+      <c r="W29" s="16"/>
+      <c r="X29" s="16"/>
+      <c r="Y29" s="16"/>
+      <c r="Z29" s="16"/>
+      <c r="AA29" s="16"/>
+    </row>
+    <row r="30" spans="1:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="1">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B30" s="1">
-        <v>68.459999999999994</v>
+        <v>42.09</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>312</v>
+        <v>320</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>313</v>
+        <v>321</v>
       </c>
       <c r="E30" s="1">
-        <v>10257997</v>
+        <v>10229166</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>314</v>
+        <v>53</v>
       </c>
       <c r="G30" s="1" t="s">
         <v>281</v>
@@ -5014,7 +3690,7 @@
         <v>6</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>26</v>
@@ -5023,42 +3699,48 @@
         <v>43</v>
       </c>
       <c r="L30" t="s">
-        <v>133</v>
+        <v>447</v>
       </c>
       <c r="M30" t="s">
         <v>29</v>
       </c>
       <c r="N30" t="s">
-        <v>491</v>
+        <v>448</v>
       </c>
       <c r="O30" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="P30" s="9"/>
-      <c r="Q30" s="10"/>
-      <c r="R30" s="11"/>
-      <c r="Y30" s="13" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="31" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <v>232</v>
+      </c>
+      <c r="P30" s="16">
+        <v>42</v>
+      </c>
+      <c r="Q30" s="16">
+        <v>0</v>
+      </c>
+      <c r="R30" s="16">
+        <v>0</v>
+      </c>
+      <c r="W30" s="16"/>
+      <c r="X30" s="16"/>
+      <c r="Y30" s="16"/>
+      <c r="Z30" s="16"/>
+      <c r="AA30" s="16"/>
+    </row>
+    <row r="31" spans="1:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="1">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B31" s="1">
-        <v>51.27</v>
-      </c>
-      <c r="C31" s="5" t="s">
-        <v>161</v>
+        <v>55.03</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>317</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>309</v>
-      </c>
-      <c r="E31" s="1">
-        <v>10262368</v>
-      </c>
+        <v>318</v>
+      </c>
+      <c r="E31" s="1"/>
       <c r="F31" s="1" t="s">
-        <v>310</v>
+        <v>53</v>
       </c>
       <c r="G31" s="1" t="s">
         <v>281</v>
@@ -5067,129 +3749,169 @@
         <v>6</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>26</v>
       </c>
       <c r="K31" t="s">
+        <v>43</v>
+      </c>
+      <c r="L31" t="s">
+        <v>449</v>
+      </c>
+      <c r="M31" t="s">
+        <v>99</v>
+      </c>
+      <c r="N31" t="s">
+        <v>450</v>
+      </c>
+      <c r="O31" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="P31" s="16">
+        <v>42.35</v>
+      </c>
+      <c r="Q31" s="16">
+        <v>44.8</v>
+      </c>
+      <c r="R31" s="16">
+        <v>87.15</v>
+      </c>
+      <c r="W31" s="16"/>
+      <c r="X31" s="16"/>
+      <c r="Y31" s="16"/>
+      <c r="Z31" s="16"/>
+      <c r="AA31" s="16"/>
+    </row>
+    <row r="32" spans="1:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="1">
         <v>27</v>
       </c>
-      <c r="N31" t="s">
-        <v>492</v>
-      </c>
-      <c r="O31" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="P31" s="9"/>
-      <c r="Q31" s="10"/>
-      <c r="R31" s="11"/>
-      <c r="Y31" s="13" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="32" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="1">
-        <v>29</v>
-      </c>
       <c r="B32" s="1">
-        <v>72.58</v>
-      </c>
-      <c r="C32" s="7" t="s">
-        <v>51</v>
+        <v>68.459999999999994</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>312</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>307</v>
-      </c>
-      <c r="E32" s="1"/>
+        <v>313</v>
+      </c>
+      <c r="E32" s="1">
+        <v>10257997</v>
+      </c>
       <c r="F32" s="1" t="s">
-        <v>84</v>
+        <v>314</v>
       </c>
       <c r="G32" s="1" t="s">
         <v>281</v>
       </c>
       <c r="H32" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="J32" s="2" t="s">
         <v>26</v>
       </c>
       <c r="K32" t="s">
-        <v>27</v>
+        <v>43</v>
+      </c>
+      <c r="L32" t="s">
+        <v>133</v>
+      </c>
+      <c r="M32" t="s">
+        <v>29</v>
       </c>
       <c r="N32" t="s">
-        <v>493</v>
-      </c>
-      <c r="O32" s="14" t="s">
-        <v>255</v>
-      </c>
-      <c r="P32" s="9"/>
-      <c r="Q32" s="10"/>
-      <c r="R32" s="11"/>
-      <c r="Y32" s="13" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="33" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <v>451</v>
+      </c>
+      <c r="O32" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="P32" s="16">
+        <v>41</v>
+      </c>
+      <c r="Q32" s="16">
+        <v>0</v>
+      </c>
+      <c r="R32" s="16">
+        <v>0</v>
+      </c>
+      <c r="W32" s="16"/>
+      <c r="X32" s="16"/>
+      <c r="Y32" s="16"/>
+      <c r="Z32" s="16"/>
+      <c r="AA32" s="16"/>
+    </row>
+    <row r="33" spans="1:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="1">
-        <v>30</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
+      </c>
+      <c r="B33" s="1">
+        <v>51.27</v>
       </c>
       <c r="C33" s="5" t="s">
         <v>161</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="E33" s="1"/>
+        <v>309</v>
+      </c>
+      <c r="E33" s="1">
+        <v>10262368</v>
+      </c>
       <c r="F33" s="1" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="G33" s="1" t="s">
         <v>281</v>
       </c>
       <c r="H33" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="J33" s="2" t="s">
         <v>26</v>
       </c>
       <c r="K33" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="N33" t="s">
-        <v>494</v>
-      </c>
-      <c r="O33" s="14" t="s">
-        <v>305</v>
-      </c>
-      <c r="P33" s="9"/>
-      <c r="Q33" s="10"/>
-      <c r="R33" s="11"/>
-      <c r="Y33" s="13" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="34" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <v>452</v>
+      </c>
+      <c r="O33" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="P33" s="16">
+        <v>43.1</v>
+      </c>
+      <c r="Q33" s="16">
+        <v>0</v>
+      </c>
+      <c r="R33" s="16">
+        <v>0</v>
+      </c>
+      <c r="W33" s="16"/>
+      <c r="X33" s="16"/>
+      <c r="Y33" s="16"/>
+      <c r="Z33" s="16"/>
+      <c r="AA33" s="16"/>
+    </row>
+    <row r="34" spans="1:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="1">
-        <v>31</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>283</v>
+        <v>29</v>
+      </c>
+      <c r="B34" s="1">
+        <v>72.58</v>
+      </c>
+      <c r="C34" s="7" t="s">
+        <v>51</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="E34" s="1"/>
       <c r="F34" s="1" t="s">
@@ -5199,10 +3921,10 @@
         <v>281</v>
       </c>
       <c r="H34" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="J34" s="2" t="s">
         <v>26</v>
@@ -5211,43 +3933,51 @@
         <v>27</v>
       </c>
       <c r="N34" t="s">
-        <v>495</v>
-      </c>
-      <c r="O34" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="P34" s="9"/>
-      <c r="Q34" s="10"/>
-      <c r="R34" s="11"/>
-      <c r="Y34" s="13" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="35" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <v>453</v>
+      </c>
+      <c r="O34" s="14" t="s">
+        <v>255</v>
+      </c>
+      <c r="P34" s="9" t="s">
+        <v>465</v>
+      </c>
+      <c r="Q34" s="10" t="s">
+        <v>465</v>
+      </c>
+      <c r="R34" s="11" t="s">
+        <v>465</v>
+      </c>
+      <c r="W34" s="16"/>
+      <c r="X34" s="16"/>
+      <c r="Y34" s="16"/>
+      <c r="Z34" s="16"/>
+      <c r="AA34" s="16"/>
+    </row>
+    <row r="35" spans="1:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="1">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C35" s="1" t="s">
-        <v>298</v>
+      <c r="C35" s="5" t="s">
+        <v>161</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="E35" s="1"/>
       <c r="F35" s="1" t="s">
-        <v>84</v>
+        <v>304</v>
       </c>
       <c r="G35" s="1" t="s">
         <v>281</v>
       </c>
       <c r="H35" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="J35" s="2" t="s">
         <v>26</v>
@@ -5255,41 +3985,39 @@
       <c r="K35" t="s">
         <v>43</v>
       </c>
-      <c r="L35" t="s">
-        <v>496</v>
-      </c>
-      <c r="M35" t="s">
-        <v>29</v>
-      </c>
       <c r="N35" t="s">
-        <v>497</v>
-      </c>
-      <c r="O35" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="P35" s="9"/>
-      <c r="Q35" s="10"/>
-      <c r="R35" s="11"/>
-      <c r="Y35" s="13" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="36" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <v>454</v>
+      </c>
+      <c r="O35" s="14" t="s">
+        <v>305</v>
+      </c>
+      <c r="P35" s="9" t="s">
+        <v>465</v>
+      </c>
+      <c r="Q35" s="10" t="s">
+        <v>465</v>
+      </c>
+      <c r="R35" s="11" t="s">
+        <v>465</v>
+      </c>
+      <c r="Y35" s="13"/>
+    </row>
+    <row r="36" spans="1:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="1">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>31</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>149</v>
+        <v>283</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>47</v>
+        <v>301</v>
       </c>
       <c r="E36" s="1"/>
       <c r="F36" s="1" t="s">
-        <v>22</v>
+        <v>84</v>
       </c>
       <c r="G36" s="1" t="s">
         <v>281</v>
@@ -5298,7 +4026,7 @@
         <v>8</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="J36" s="2" t="s">
         <v>26</v>
@@ -5306,41 +4034,39 @@
       <c r="K36" t="s">
         <v>27</v>
       </c>
-      <c r="L36" t="s">
-        <v>446</v>
-      </c>
-      <c r="M36" t="s">
-        <v>36</v>
-      </c>
       <c r="N36" t="s">
-        <v>498</v>
+        <v>455</v>
       </c>
       <c r="O36" s="1" t="s">
-        <v>296</v>
-      </c>
-      <c r="P36" s="9"/>
-      <c r="Q36" s="10"/>
-      <c r="R36" s="11"/>
-      <c r="Y36" s="13" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="37" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <v>244</v>
+      </c>
+      <c r="P36" s="9" t="s">
+        <v>465</v>
+      </c>
+      <c r="Q36" s="10" t="s">
+        <v>465</v>
+      </c>
+      <c r="R36" s="11" t="s">
+        <v>465</v>
+      </c>
+      <c r="Y36" s="13"/>
+    </row>
+    <row r="37" spans="1:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="1">
-        <v>34</v>
-      </c>
-      <c r="B37" s="1">
-        <v>61.69</v>
+        <v>32</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>31</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>39</v>
+        <v>298</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="E37" s="1"/>
       <c r="F37" s="1" t="s">
-        <v>294</v>
+        <v>84</v>
       </c>
       <c r="G37" s="1" t="s">
         <v>281</v>
@@ -5349,7 +4075,7 @@
         <v>8</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>103</v>
+        <v>300</v>
       </c>
       <c r="J37" s="2" t="s">
         <v>26</v>
@@ -5357,99 +4083,109 @@
       <c r="K37" t="s">
         <v>43</v>
       </c>
+      <c r="L37" t="s">
+        <v>456</v>
+      </c>
+      <c r="M37" t="s">
+        <v>29</v>
+      </c>
       <c r="N37" t="s">
-        <v>499</v>
+        <v>457</v>
       </c>
       <c r="O37" s="1" t="s">
-        <v>295</v>
-      </c>
-      <c r="P37" s="9"/>
-      <c r="Q37" s="10"/>
-      <c r="R37" s="11"/>
-      <c r="Y37" s="13" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="38" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <v>125</v>
+      </c>
+      <c r="P37" s="9" t="s">
+        <v>465</v>
+      </c>
+      <c r="Q37" s="10" t="s">
+        <v>465</v>
+      </c>
+      <c r="R37" s="11" t="s">
+        <v>465</v>
+      </c>
+      <c r="Y37" s="13"/>
+    </row>
+    <row r="38" spans="1:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="1">
-        <v>35</v>
-      </c>
-      <c r="B38" s="1">
-        <v>73.28</v>
+        <v>33</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>31</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>289</v>
+        <v>149</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>290</v>
-      </c>
-      <c r="E38" s="1">
-        <v>10243021</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="E38" s="1"/>
       <c r="F38" s="1" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="G38" s="1" t="s">
         <v>281</v>
       </c>
       <c r="H38" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I38" s="1" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="J38" s="2" t="s">
         <v>26</v>
       </c>
       <c r="K38" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="L38" t="s">
-        <v>500</v>
+        <v>406</v>
       </c>
       <c r="M38" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="N38" t="s">
-        <v>501</v>
-      </c>
-      <c r="O38" s="14" t="s">
-        <v>291</v>
-      </c>
-      <c r="P38" s="9"/>
-      <c r="Q38" s="10"/>
-      <c r="R38" s="11"/>
-      <c r="Y38" s="13" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="39" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <v>458</v>
+      </c>
+      <c r="O38" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="P38" s="9" t="s">
+        <v>465</v>
+      </c>
+      <c r="Q38" s="10" t="s">
+        <v>465</v>
+      </c>
+      <c r="R38" s="11" t="s">
+        <v>465</v>
+      </c>
+      <c r="Y38" s="13"/>
+    </row>
+    <row r="39" spans="1:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="1">
-        <v>36</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
+      </c>
+      <c r="B39" s="1">
+        <v>61.69</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>285</v>
+        <v>39</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>286</v>
-      </c>
-      <c r="E39" s="1">
-        <v>10276169</v>
-      </c>
+        <v>293</v>
+      </c>
+      <c r="E39" s="1"/>
       <c r="F39" s="1" t="s">
-        <v>287</v>
+        <v>294</v>
       </c>
       <c r="G39" s="1" t="s">
         <v>281</v>
       </c>
       <c r="H39" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>288</v>
+        <v>103</v>
       </c>
       <c r="J39" s="2" t="s">
         <v>26</v>
@@ -5457,43 +4193,41 @@
       <c r="K39" t="s">
         <v>43</v>
       </c>
-      <c r="L39" t="s">
-        <v>446</v>
-      </c>
-      <c r="M39" t="s">
-        <v>36</v>
-      </c>
       <c r="N39" t="s">
-        <v>502</v>
-      </c>
-      <c r="O39" s="14" t="s">
-        <v>157</v>
-      </c>
-      <c r="P39" s="9"/>
-      <c r="Q39" s="10"/>
-      <c r="R39" s="11"/>
-      <c r="Y39" s="13" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="40" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <v>459</v>
+      </c>
+      <c r="O39" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="P39" s="9" t="s">
+        <v>465</v>
+      </c>
+      <c r="Q39" s="10" t="s">
+        <v>465</v>
+      </c>
+      <c r="R39" s="11" t="s">
+        <v>465</v>
+      </c>
+      <c r="Y39" s="13"/>
+    </row>
+    <row r="40" spans="1:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="1">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B40" s="1">
-        <v>69.680000000000007</v>
+        <v>73.28</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>173</v>
+        <v>290</v>
       </c>
       <c r="E40" s="1">
-        <v>10262517</v>
+        <v>10243021</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>84</v>
+        <v>53</v>
       </c>
       <c r="G40" s="1" t="s">
         <v>281</v>
@@ -5502,7 +4236,7 @@
         <v>9</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="J40" s="2" t="s">
         <v>26</v>
@@ -5510,35 +4244,47 @@
       <c r="K40" t="s">
         <v>43</v>
       </c>
+      <c r="L40" t="s">
+        <v>460</v>
+      </c>
+      <c r="M40" t="s">
+        <v>29</v>
+      </c>
       <c r="N40" t="s">
-        <v>503</v>
+        <v>461</v>
       </c>
       <c r="O40" s="14" t="s">
-        <v>222</v>
-      </c>
-      <c r="P40" s="9"/>
-      <c r="Q40" s="10"/>
-      <c r="R40" s="11"/>
-      <c r="Y40" s="13" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="41" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <v>291</v>
+      </c>
+      <c r="P40" s="9" t="s">
+        <v>465</v>
+      </c>
+      <c r="Q40" s="10" t="s">
+        <v>465</v>
+      </c>
+      <c r="R40" s="11" t="s">
+        <v>465</v>
+      </c>
+      <c r="Y40" s="13"/>
+    </row>
+    <row r="41" spans="1:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="1">
-        <v>38</v>
-      </c>
-      <c r="B41" s="1">
-        <v>52.22</v>
-      </c>
-      <c r="C41" s="5" t="s">
-        <v>280</v>
+        <v>36</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>285</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="E41" s="1"/>
+        <v>286</v>
+      </c>
+      <c r="E41" s="1">
+        <v>10276169</v>
+      </c>
       <c r="F41" s="1" t="s">
-        <v>59</v>
+        <v>287</v>
       </c>
       <c r="G41" s="1" t="s">
         <v>281</v>
@@ -5547,7 +4293,7 @@
         <v>9</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="J41" s="2" t="s">
         <v>26</v>
@@ -5556,110 +4302,254 @@
         <v>43</v>
       </c>
       <c r="L41" t="s">
-        <v>446</v>
+        <v>406</v>
       </c>
       <c r="M41" t="s">
         <v>36</v>
       </c>
       <c r="N41" t="s">
-        <v>504</v>
+        <v>462</v>
       </c>
       <c r="O41" s="14" t="s">
+        <v>157</v>
+      </c>
+      <c r="P41" s="9" t="s">
+        <v>465</v>
+      </c>
+      <c r="Q41" s="10" t="s">
+        <v>465</v>
+      </c>
+      <c r="R41" s="11" t="s">
+        <v>465</v>
+      </c>
+      <c r="Y41" s="13"/>
+    </row>
+    <row r="42" spans="1:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="1">
+        <v>37</v>
+      </c>
+      <c r="B42" s="1">
+        <v>69.680000000000007</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="E42" s="1">
+        <v>10262517</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="G42" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="H42" s="1">
+        <v>9</v>
+      </c>
+      <c r="I42" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="J42" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K42" t="s">
+        <v>43</v>
+      </c>
+      <c r="N42" t="s">
+        <v>463</v>
+      </c>
+      <c r="O42" s="14" t="s">
+        <v>222</v>
+      </c>
+      <c r="P42" s="9" t="s">
+        <v>465</v>
+      </c>
+      <c r="Q42" s="10" t="s">
+        <v>465</v>
+      </c>
+      <c r="R42" s="11" t="s">
+        <v>465</v>
+      </c>
+      <c r="Y42" s="13"/>
+    </row>
+    <row r="43" spans="1:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="1">
+        <v>38</v>
+      </c>
+      <c r="B43" s="1">
+        <v>52.22</v>
+      </c>
+      <c r="C43" s="5" t="s">
+        <v>280</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E43" s="1"/>
+      <c r="F43" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="H43" s="1">
+        <v>9</v>
+      </c>
+      <c r="I43" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="J43" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K43" t="s">
+        <v>43</v>
+      </c>
+      <c r="L43" t="s">
+        <v>406</v>
+      </c>
+      <c r="M43" t="s">
+        <v>36</v>
+      </c>
+      <c r="N43" t="s">
+        <v>464</v>
+      </c>
+      <c r="O43" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="P41" s="9"/>
-      <c r="Q41" s="10"/>
-      <c r="R41" s="11"/>
-      <c r="Y41" s="13" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="42" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="1">
+      <c r="P43" s="9" t="s">
+        <v>465</v>
+      </c>
+      <c r="Q43" s="10" t="s">
+        <v>465</v>
+      </c>
+      <c r="R43" s="11" t="s">
+        <v>465</v>
+      </c>
+      <c r="Y43" s="13"/>
+    </row>
+    <row r="44" spans="1:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="1">
         <v>39</v>
       </c>
-      <c r="B42" s="1" t="s">
+      <c r="B44" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="P42" s="9"/>
-      <c r="Q42" s="10"/>
-      <c r="R42" s="11"/>
-      <c r="Y42" s="13" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="43" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="1">
+      <c r="P44" s="9" t="s">
+        <v>465</v>
+      </c>
+      <c r="Q44" s="10" t="s">
+        <v>465</v>
+      </c>
+      <c r="R44" s="11" t="s">
+        <v>465</v>
+      </c>
+      <c r="Y44" s="13"/>
+    </row>
+    <row r="45" spans="1:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="1">
         <v>40</v>
       </c>
-      <c r="B43" s="1">
+      <c r="B45" s="1">
         <v>75.91</v>
       </c>
-      <c r="Q43" s="10"/>
-      <c r="R43" s="11"/>
-      <c r="Y43" s="13" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="44" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="Q44" s="10"/>
-      <c r="R44" s="11"/>
-    </row>
-    <row r="45" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="Q45" s="10"/>
-    </row>
-    <row r="46" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="Q46" s="10"/>
-    </row>
-    <row r="47" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="Q47" s="10"/>
-    </row>
-    <row r="48" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="Q48" s="12"/>
+      <c r="P45" s="9" t="s">
+        <v>465</v>
+      </c>
+      <c r="Q45" s="10" t="s">
+        <v>465</v>
+      </c>
+      <c r="R45" s="11" t="s">
+        <v>465</v>
+      </c>
+      <c r="Y45" s="13"/>
+    </row>
+    <row r="46" spans="1:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="P46" s="9" t="s">
+        <v>465</v>
+      </c>
+      <c r="Q46" s="10" t="s">
+        <v>465</v>
+      </c>
+      <c r="R46" s="11" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="47" spans="1:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="P47" s="9" t="s">
+        <v>465</v>
+      </c>
+      <c r="Q47" s="10" t="s">
+        <v>465</v>
+      </c>
+      <c r="R47" s="11" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="48" spans="1:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="P48" s="9" t="s">
+        <v>465</v>
+      </c>
+      <c r="Q48" s="10" t="s">
+        <v>465</v>
+      </c>
+      <c r="R48" s="11" t="s">
+        <v>465</v>
+      </c>
     </row>
     <row r="49" spans="17:17" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="Q49" s="12"/>
+      <c r="Q49" s="10"/>
     </row>
     <row r="50" spans="17:17" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="Q50" s="12"/>
+      <c r="Q50" s="10"/>
     </row>
     <row r="51" spans="17:17" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="Q51" s="12"/>
     </row>
-    <row r="52" spans="17:17" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="53" spans="17:17" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="54" spans="17:17" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="52" spans="17:17" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Q52" s="12"/>
+    </row>
+    <row r="53" spans="17:17" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Q53" s="12"/>
+    </row>
+    <row r="54" spans="17:17" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Q54" s="12"/>
+    </row>
     <row r="55" spans="17:17" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="56" spans="17:17" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="57" spans="17:17" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L43">
-    <sortCondition ref="A2:A43"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L45">
+    <sortCondition ref="A2:A45"/>
   </sortState>
   <hyperlinks>
-    <hyperlink ref="J41" r:id="rId1" display="https://probullstats.com/loggers/matchup.php?bull=54839&amp;guy=Julio+Cesar+Marques" xr:uid="{7A80C17A-3232-6448-9343-11FC1CD3C297}"/>
-    <hyperlink ref="J40" r:id="rId2" display="https://probullstats.com/loggers/matchup.php?bull=56542&amp;guy=Callum+Miller" xr:uid="{0F2BD59E-A00B-4D4B-8A15-FC0C2FCD8520}"/>
-    <hyperlink ref="J39" r:id="rId3" display="https://probullstats.com/loggers/matchup.php?bull=54130&amp;guy=Trace+Redd" xr:uid="{F4C2835A-438B-0142-98F5-439B5289E417}"/>
-    <hyperlink ref="J38" r:id="rId4" display="https://probullstats.com/loggers/matchup.php?bull=51428&amp;guy=Grayson+Cole" xr:uid="{9F41CA48-CFB7-E246-92DC-10D6692090A4}"/>
-    <hyperlink ref="J37" r:id="rId5" display="https://probullstats.com/loggers/matchup.php?bull=56381&amp;guy=Vinicius+Rodrigues+Pereira" xr:uid="{F733F9C0-F92E-DD40-BD82-74810719B425}"/>
-    <hyperlink ref="J36" r:id="rId6" display="https://probullstats.com/loggers/matchup.php?bull=55806&amp;guy=Ednelio+Rodrigues" xr:uid="{07DD6F14-EB65-2C4E-A591-3E2C378C2A67}"/>
-    <hyperlink ref="J35" r:id="rId7" display="https://probullstats.com/loggers/matchup.php?bull=53419&amp;guy=Mason+Taylor" xr:uid="{864A1DB8-FE2B-5D44-9643-DB818F8A9234}"/>
-    <hyperlink ref="J34" r:id="rId8" display="https://probullstats.com/loggers/matchup.php?bull=56047&amp;guy=Dener+Barbosa" xr:uid="{2AB1932A-11A1-7447-80A6-E02A42B49BB9}"/>
-    <hyperlink ref="J33" r:id="rId9" display="https://probullstats.com/loggers/matchup.php?bull=55809&amp;guy=Ramon+Fiorini" xr:uid="{03F5EABD-CF18-5E42-A0EA-CD3101D51E6C}"/>
-    <hyperlink ref="J32" r:id="rId10" display="https://probullstats.com/loggers/matchup.php?bull=56578&amp;guy=Vinicius+Pinheiro+Correa" xr:uid="{AAF7E716-B51F-5744-80BC-B9D1B3EC32AD}"/>
-    <hyperlink ref="J31" r:id="rId11" display="https://probullstats.com/loggers/matchup.php?bull=56236&amp;guy=Macaulie+Leather" xr:uid="{2021287A-E488-FD4C-B27D-94448D0F15C7}"/>
-    <hyperlink ref="J30" r:id="rId12" display="https://probullstats.com/loggers/matchup.php?bull=51896&amp;guy=Eric+Novoa" xr:uid="{95300F1E-1D61-B745-8FB1-31564488E65C}"/>
-    <hyperlink ref="J29" r:id="rId13" display="https://probullstats.com/loggers/matchup.php?bull=52820&amp;guy=Paulo+Eduardo+Rossetto" xr:uid="{0CEAA190-6ED4-7446-8DB9-0E54B259D446}"/>
-    <hyperlink ref="J28" r:id="rId14" display="https://probullstats.com/loggers/matchup.php?bull=50989&amp;guy=Lucas+Divino" xr:uid="{68EFE952-E1A2-2A43-A2D3-BF22A8D7B3E9}"/>
-    <hyperlink ref="J27" r:id="rId15" display="https://probullstats.com/loggers/matchup.php?bull=54227&amp;guy=Claudio+Montanha+Jr." xr:uid="{3D5353E0-0288-DF4A-9DAE-4F807BED1D54}"/>
-    <hyperlink ref="J26" r:id="rId16" display="https://probullstats.com/loggers/matchup.php?bull=54171&amp;guy=Koltin+Hevalow" xr:uid="{9412B2D9-0C75-C745-978E-773B146B6A20}"/>
-    <hyperlink ref="J25" r:id="rId17" display="https://probullstats.com/loggers/matchup.php?bull=51690&amp;guy=Hudson+Bolton" xr:uid="{B6C892CC-6302-014B-A6F4-C3E51780D547}"/>
-    <hyperlink ref="J24" r:id="rId18" display="https://probullstats.com/loggers/matchup.php?bull=53018&amp;guy=Keyshawn+Whitehorse" xr:uid="{1B7B6F25-EA93-3547-A6A1-883AFE3B0758}"/>
-    <hyperlink ref="J23" r:id="rId19" display="https://probullstats.com/loggers/matchup.php?bull=47941&amp;guy=Brady+Fielder" xr:uid="{F830A1E9-FAD6-9B44-9BDC-71504F789CA3}"/>
-    <hyperlink ref="J22" r:id="rId20" display="https://probullstats.com/loggers/matchup.php?bull=53535&amp;guy=John+Crimber" xr:uid="{33956328-C1EF-D149-9DFA-586EB9743B84}"/>
-    <hyperlink ref="J21" r:id="rId21" display="https://probullstats.com/loggers/matchup.php?bull=49727&amp;guy=Alex+Junior+da+Silva" xr:uid="{FE35623D-353B-0942-AAFF-E0848495E061}"/>
-    <hyperlink ref="J20" r:id="rId22" display="https://probullstats.com/loggers/matchup.php?bull=56540&amp;guy=Luciano+De+Castro" xr:uid="{75E344EB-84EF-E243-BC8E-0F69A94B6B09}"/>
-    <hyperlink ref="J19" r:id="rId23" display="https://probullstats.com/loggers/matchup.php?bull=44656&amp;guy=Mauricio+Gulla+Moreira" xr:uid="{C6F7534C-CF8F-014E-A078-46EDB48E4C40}"/>
-    <hyperlink ref="J18" r:id="rId24" display="https://probullstats.com/loggers/matchup.php?bull=50380&amp;guy=Andy+Guzman" xr:uid="{021B2B21-CA7E-8D47-8345-68AEA1745A23}"/>
-    <hyperlink ref="J17" r:id="rId25" display="https://probullstats.com/loggers/matchup.php?bull=53892&amp;guy=Joao+Ricardo+Vieira" xr:uid="{56F7B948-B1A1-0C48-B431-53B30A3D80A9}"/>
+    <hyperlink ref="J43" r:id="rId1" display="https://probullstats.com/loggers/matchup.php?bull=54839&amp;guy=Julio+Cesar+Marques" xr:uid="{7A80C17A-3232-6448-9343-11FC1CD3C297}"/>
+    <hyperlink ref="J42" r:id="rId2" display="https://probullstats.com/loggers/matchup.php?bull=56542&amp;guy=Callum+Miller" xr:uid="{0F2BD59E-A00B-4D4B-8A15-FC0C2FCD8520}"/>
+    <hyperlink ref="J41" r:id="rId3" display="https://probullstats.com/loggers/matchup.php?bull=54130&amp;guy=Trace+Redd" xr:uid="{F4C2835A-438B-0142-98F5-439B5289E417}"/>
+    <hyperlink ref="J40" r:id="rId4" display="https://probullstats.com/loggers/matchup.php?bull=51428&amp;guy=Grayson+Cole" xr:uid="{9F41CA48-CFB7-E246-92DC-10D6692090A4}"/>
+    <hyperlink ref="J39" r:id="rId5" display="https://probullstats.com/loggers/matchup.php?bull=56381&amp;guy=Vinicius+Rodrigues+Pereira" xr:uid="{F733F9C0-F92E-DD40-BD82-74810719B425}"/>
+    <hyperlink ref="J38" r:id="rId6" display="https://probullstats.com/loggers/matchup.php?bull=55806&amp;guy=Ednelio+Rodrigues" xr:uid="{07DD6F14-EB65-2C4E-A591-3E2C378C2A67}"/>
+    <hyperlink ref="J37" r:id="rId7" display="https://probullstats.com/loggers/matchup.php?bull=53419&amp;guy=Mason+Taylor" xr:uid="{864A1DB8-FE2B-5D44-9643-DB818F8A9234}"/>
+    <hyperlink ref="J36" r:id="rId8" display="https://probullstats.com/loggers/matchup.php?bull=56047&amp;guy=Dener+Barbosa" xr:uid="{2AB1932A-11A1-7447-80A6-E02A42B49BB9}"/>
+    <hyperlink ref="J35" r:id="rId9" display="https://probullstats.com/loggers/matchup.php?bull=55809&amp;guy=Ramon+Fiorini" xr:uid="{03F5EABD-CF18-5E42-A0EA-CD3101D51E6C}"/>
+    <hyperlink ref="J34" r:id="rId10" display="https://probullstats.com/loggers/matchup.php?bull=56578&amp;guy=Vinicius+Pinheiro+Correa" xr:uid="{AAF7E716-B51F-5744-80BC-B9D1B3EC32AD}"/>
+    <hyperlink ref="J33" r:id="rId11" display="https://probullstats.com/loggers/matchup.php?bull=56236&amp;guy=Macaulie+Leather" xr:uid="{2021287A-E488-FD4C-B27D-94448D0F15C7}"/>
+    <hyperlink ref="J32" r:id="rId12" display="https://probullstats.com/loggers/matchup.php?bull=51896&amp;guy=Eric+Novoa" xr:uid="{95300F1E-1D61-B745-8FB1-31564488E65C}"/>
+    <hyperlink ref="J31" r:id="rId13" display="https://probullstats.com/loggers/matchup.php?bull=52820&amp;guy=Paulo+Eduardo+Rossetto" xr:uid="{0CEAA190-6ED4-7446-8DB9-0E54B259D446}"/>
+    <hyperlink ref="J30" r:id="rId14" display="https://probullstats.com/loggers/matchup.php?bull=50989&amp;guy=Lucas+Divino" xr:uid="{68EFE952-E1A2-2A43-A2D3-BF22A8D7B3E9}"/>
+    <hyperlink ref="J29" r:id="rId15" display="https://probullstats.com/loggers/matchup.php?bull=54227&amp;guy=Claudio+Montanha+Jr." xr:uid="{3D5353E0-0288-DF4A-9DAE-4F807BED1D54}"/>
+    <hyperlink ref="J28" r:id="rId16" display="https://probullstats.com/loggers/matchup.php?bull=54171&amp;guy=Koltin+Hevalow" xr:uid="{9412B2D9-0C75-C745-978E-773B146B6A20}"/>
+    <hyperlink ref="J27" r:id="rId17" display="https://probullstats.com/loggers/matchup.php?bull=51690&amp;guy=Hudson+Bolton" xr:uid="{B6C892CC-6302-014B-A6F4-C3E51780D547}"/>
+    <hyperlink ref="J26" r:id="rId18" display="https://probullstats.com/loggers/matchup.php?bull=53018&amp;guy=Keyshawn+Whitehorse" xr:uid="{1B7B6F25-EA93-3547-A6A1-883AFE3B0758}"/>
+    <hyperlink ref="J25" r:id="rId19" display="https://probullstats.com/loggers/matchup.php?bull=47941&amp;guy=Brady+Fielder" xr:uid="{F830A1E9-FAD6-9B44-9BDC-71504F789CA3}"/>
+    <hyperlink ref="J24" r:id="rId20" display="https://probullstats.com/loggers/matchup.php?bull=53535&amp;guy=John+Crimber" xr:uid="{33956328-C1EF-D149-9DFA-586EB9743B84}"/>
+    <hyperlink ref="J23" r:id="rId21" display="https://probullstats.com/loggers/matchup.php?bull=49727&amp;guy=Alex+Junior+da+Silva" xr:uid="{FE35623D-353B-0942-AAFF-E0848495E061}"/>
+    <hyperlink ref="J22" r:id="rId22" display="https://probullstats.com/loggers/matchup.php?bull=56540&amp;guy=Luciano+De+Castro" xr:uid="{75E344EB-84EF-E243-BC8E-0F69A94B6B09}"/>
+    <hyperlink ref="J21" r:id="rId23" display="https://probullstats.com/loggers/matchup.php?bull=44656&amp;guy=Mauricio+Gulla+Moreira" xr:uid="{C6F7534C-CF8F-014E-A078-46EDB48E4C40}"/>
+    <hyperlink ref="J19" r:id="rId24" display="https://probullstats.com/loggers/matchup.php?bull=50380&amp;guy=Andy+Guzman" xr:uid="{021B2B21-CA7E-8D47-8345-68AEA1745A23}"/>
+    <hyperlink ref="J18" r:id="rId25" display="https://probullstats.com/loggers/matchup.php?bull=53892&amp;guy=Joao+Ricardo+Vieira" xr:uid="{56F7B948-B1A1-0C48-B431-53B30A3D80A9}"/>
     <hyperlink ref="J16" r:id="rId26" display="https://probullstats.com/loggers/matchup.php?bull=53319&amp;guy=Thiago+Salgado" xr:uid="{0024AC40-1D64-BC45-BE9C-E6AE555C4C55}"/>
     <hyperlink ref="J15" r:id="rId27" display="https://probullstats.com/loggers/matchup.php?bull=48315&amp;guy=Daylon+Swearingen" xr:uid="{C7028F27-5A31-EB46-928F-52A417BEA75F}"/>
     <hyperlink ref="J14" r:id="rId28" display="https://probullstats.com/loggers/matchup.php?bull=54209&amp;guy=Andrew+Alvidrez" xr:uid="{5C697E8D-70AD-F046-AB04-46B464409C3E}"/>
@@ -5677,6 +4567,9 @@
     <hyperlink ref="J2" r:id="rId40" display="https://probullstats.com/loggers/matchup.php?bull=51996&amp;guy=Eduardo+Aparecido" xr:uid="{E556DB4A-323A-8448-8888-A75F07F470C8}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId41"/>
+  </tableParts>
 </worksheet>
 </file>
 
